--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -1063,7 +1063,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 53.7% — a 26.9 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
+          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 53.5% — a 27.1 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1122,10 @@
         <v>0.06499352425022978</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.103933893388768</v>
+        <v>0.1035710907401094</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.6253352215635706</v>
+        <v>0.6275257292917561</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>-0.2929242982373964</v>
@@ -1163,19 +1163,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07259324631852983</v>
+        <v>0.07315951727129665</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.08535481917334327</v>
+        <v>0.08814883647169915</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.8504879633228848</v>
+        <v>0.8299544293450211</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>-0.1928735338745831</v>
+        <v>-0.1999559307284849</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.3763774368635456</v>
+        <v>0.3658782062865548</v>
       </c>
     </row>
     <row r="11">
@@ -1185,19 +1185,19 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05887012446950701</v>
+        <v>0.05891136643505969</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.06937777317283109</v>
+        <v>0.06931186561532281</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.8485444513021793</v>
+        <v>0.8499463390873745</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-0.1655628692696721</v>
+        <v>-0.1665091655061419</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3555756476629925</v>
+        <v>0.35380254447847</v>
       </c>
     </row>
     <row r="12">
@@ -1207,19 +1207,19 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.05339171285866526</v>
+        <v>0.05341435110809257</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.06192652692456322</v>
+        <v>0.06196353510197526</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.8621783831621175</v>
+        <v>0.8620287887091489</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.1474522132085342</v>
+        <v>-0.1548283411757465</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.3620950252076314</v>
+        <v>0.3449907859405511</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1279,22 +1279,22 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.6509999999999999</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>-0.057</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
       <c r="E16" s="9" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>0.135</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>0.133</v>
       </c>
     </row>
     <row r="17">
@@ -1329,22 +1329,22 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.423</v>
+        <v>0.414</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.182</v>
+        <v>0.191</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.149</v>
+        <v>0.113</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>-0.004</v>
+        <v>0.016</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.236</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19">
@@ -1354,22 +1354,22 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.484</v>
+        <v>0.487</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>0.144</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.081</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.119</v>
+        <v>0.118</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.163</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="20">
@@ -1379,19 +1379,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.537</v>
+        <v>0.535</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.079</v>
+        <v>0.12</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.18</v>
+        <v>0.154</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.126</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>Pastor-Stambaugh</t>
         </is>
       </c>
     </row>
@@ -2044,29 +2044,29 @@
         </is>
       </c>
       <c r="B13" s="24" t="n">
-        <v>0.2662432244803207</v>
+        <v>0.2662615280266115</v>
       </c>
       <c r="C13" s="24" t="n">
-        <v>0.0341347995858011</v>
+        <v>0.03413008712923776</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>0.5391575995605099</v>
+        <v>0.2697224940806349</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>2.056026830782021</v>
+        <v>2.055745923262592</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>4.765761280351057e-05</v>
+        <v>0.01290119732786036</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>0.7410349255498354</v>
+        <v>0.7443129475785015</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>Pastor-Stambaugh</t>
+          <t>BAA-Treasury</t>
         </is>
       </c>
     </row>
@@ -2077,25 +2077,25 @@
         </is>
       </c>
       <c r="B14" s="25" t="n">
-        <v>0.3781411783147733</v>
+        <v>0.3475645787692835</v>
       </c>
       <c r="C14" s="25" t="n">
-        <v>-0.02576702956354728</v>
+        <v>-0.01789473558713058</v>
       </c>
       <c r="D14" s="25" t="n">
-        <v>3.501487241418954</v>
+        <v>1.510698166693959</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>4.00553283690104</v>
+        <v>4.474796912527248</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.079613410364969</v>
+        <v>0.07225876810085358</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.4486981761189008</v>
+        <v>0.4472956521780461</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
@@ -2110,25 +2110,25 @@
         </is>
       </c>
       <c r="B15" s="24" t="n">
-        <v>-0.09523920864949073</v>
+        <v>-0.0422572163933037</v>
       </c>
       <c r="C15" s="24" t="n">
-        <v>0.2661804770866193</v>
+        <v>0.2525396594451277</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>-0.8150509820184776</v>
+        <v>0.008416326420867809</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>14.24918935918608</v>
+        <v>13.43606605605533</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>0.1379511506886197</v>
+        <v>0.0004025644516642721</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="27" t="n">
-        <v>0.08883108523880501</v>
+        <v>0.08716459731266091</v>
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="B20" s="25" t="n">
-        <v>-0.09523920864949073</v>
+        <v>-0.0422572163933037</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>0.1943926134830137</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>0.2896318221325044</v>
+        <v>0.2366498298763174</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -2367,17 +2367,17 @@
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>Private Equity</t>
         </is>
       </c>
       <c r="B28" s="25" t="n">
-        <v>0.2662432244803207</v>
+        <v>0.3475645787692835</v>
       </c>
       <c r="C28" s="25" t="n">
-        <v>0.1884016479536835</v>
+        <v>0.2923064843573329</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>-0.0778415765266372</v>
+        <v>-0.05525809441195068</v>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
@@ -2388,17 +2388,17 @@
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Private Equity</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B29" s="24" t="n">
-        <v>0.3781411783147733</v>
+        <v>0.2662615280266115</v>
       </c>
       <c r="C29" s="24" t="n">
-        <v>0.2923064843573329</v>
+        <v>0.1884016479536835</v>
       </c>
       <c r="D29" s="24" t="n">
-        <v>-0.08583469395744048</v>
+        <v>-0.07785988007292804</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="B5" s="32" t="n">
-        <v>-0.1707478688334095</v>
+        <v>-0.1830486748285078</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>0.03872490298258668</v>
+        <v>0.03683695337861703</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>-0.1712081342323609</v>
+        <v>-0.1786484994678725</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.5170788305191565</v>
+        <v>0.5145573060842727</v>
       </c>
     </row>
     <row r="6">
@@ -2578,16 +2578,16 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>-0.165562869269672</v>
+        <v>-0.1665091655061418</v>
       </c>
       <c r="C6" s="35" t="n">
-        <v>0.02027652275640524</v>
+        <v>0.01971956610018144</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>-0.1453856043342324</v>
+        <v>-0.1449286097236309</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3376660928596036</v>
+        <v>0.3378735970052109</v>
       </c>
     </row>
     <row r="7">
@@ -2597,16 +2597,16 @@
         </is>
       </c>
       <c r="B7" s="32" t="n">
-        <v>-0.1282847277566882</v>
+        <v>-0.1257176000642428</v>
       </c>
       <c r="C7" s="34" t="n">
-        <v>0.02133537724781642</v>
+        <v>0.02542692133678326</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>-0.1234846833593276</v>
+        <v>-0.130784375396225</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.3290722039952829</v>
+        <v>0.322990144323839</v>
       </c>
     </row>
     <row r="8" ht="8" customHeight="1"/>
@@ -2989,13 +2989,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C4" s="24" t="n">
-        <v>0.07607196940227982</v>
+        <v>0.07604848222125912</v>
       </c>
       <c r="D4" s="24" t="n">
-        <v>0.005851689954021525</v>
+        <v>0.005849883247789163</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.112604074825391</v>
+        <v>0.1129636311829188</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.9718498340506938</v>
@@ -3011,13 +3011,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>0.08675677475134909</v>
+        <v>0.08671094150982253</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.006673598057796084</v>
+        <v>0.006670072423832503</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.1284200531742476</v>
+        <v>0.1288018186574803</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>0.9005695345361184</v>
@@ -3033,13 +3033,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>0.09162450191385201</v>
+        <v>0.09160479264684691</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>0.007048038608757847</v>
+        <v>0.007046522511295917</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1356254130189165</v>
+        <v>0.1360712233682608</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>0.8647852106386994</v>
@@ -3055,13 +3055,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C7" s="25" t="n">
-        <v>0.08990837169539805</v>
+        <v>0.08975643374929827</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>0.006916028591953696</v>
+        <v>0.006904341057638329</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.1330851441518518</v>
+        <v>0.1333256415144526</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>0.6547256214279519</v>
@@ -3077,13 +3077,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>-0.01920475065096846</v>
+        <v>-0.01890725699586819</v>
       </c>
       <c r="D8" s="24" t="n">
-        <v>-0.001477288511612959</v>
+        <v>-0.001454404384297553</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.02842746410138056</v>
+        <v>-0.02808514178820586</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.9800395309996239</v>
@@ -3099,13 +3099,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>0.009918762478838109</v>
+        <v>0.009951105476017614</v>
       </c>
       <c r="D9" s="25" t="n">
-        <v>0.000762981729141393</v>
+        <v>0.000765469652001355</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.01468205807103628</v>
+        <v>0.0147815311498871</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>0.8261546883028914</v>
@@ -3121,13 +3121,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C10" s="24" t="n">
-        <v>0.01580566601010246</v>
+        <v>0.01592770997060341</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>0.001215820462315574</v>
+        <v>0.001225208459277185</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.02339603420354434</v>
+        <v>0.0236592750066058</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>0.6542475111182804</v>
@@ -3143,13 +3143,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>0.088058047076991</v>
+        <v>0.08804865704708366</v>
       </c>
       <c r="D11" s="25" t="n">
-        <v>0.006773695928999308</v>
+        <v>0.006772973619006435</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1303462365960271</v>
+        <v>0.1307888827009042</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>0.6432514443485702</v>
@@ -3165,13 +3165,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C12" s="24" t="n">
-        <v>0.07546337026810851</v>
+        <v>0.075133417224411</v>
       </c>
       <c r="D12" s="24" t="n">
-        <v>0.005804874636008347</v>
+        <v>0.005779493632647</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1117032076205407</v>
+        <v>0.1116043790086071</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>0.4797912934834942</v>
@@ -3187,13 +3187,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>0.03964930468724968</v>
+        <v>0.03992411329824733</v>
       </c>
       <c r="D13" s="25" t="n">
-        <v>0.003049946514403822</v>
+        <v>0.003071085638326718</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.05869012340364081</v>
+        <v>0.05930391610981455</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -3209,16 +3209,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C14" s="24" t="n">
-        <v>0.02771691210987172</v>
+        <v>0.02736526641155149</v>
       </c>
       <c r="D14" s="24" t="n">
-        <v>0.002132070162297825</v>
+        <v>0.002105020493196269</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04102742796948342</v>
+        <v>0.04064880418182309</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.7553246822404955</v>
+        <v>0.7487919560463553</v>
       </c>
     </row>
     <row r="15">
@@ -3231,16 +3231,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C15" s="25" t="n">
-        <v>0.05404604288534002</v>
+        <v>0.05235587803403794</v>
       </c>
       <c r="D15" s="25" t="n">
-        <v>0.004157387914256925</v>
+        <v>0.004027375233387534</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.08000061921487119</v>
+        <v>0.07777025817934881</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.4740803814994422</v>
+        <v>0.4284467817562574</v>
       </c>
     </row>
     <row r="16">
@@ -3253,16 +3253,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C16" s="24" t="n">
-        <v>0.03975533439858021</v>
+        <v>0.03929254921739969</v>
       </c>
       <c r="D16" s="24" t="n">
-        <v>0.003058102646044632</v>
+        <v>0.003022503785953823</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05884707185182993</v>
+        <v>0.05836578072810264</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1419427420681525</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="18">
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="24" t="n">
-        <v>0.02622494928918073</v>
+        <v>0.02593079077558953</v>
       </c>
       <c r="D30" s="24" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.7553246822404955</v>
+        <v>0.7487919560463553</v>
       </c>
     </row>
     <row r="31">
@@ -3561,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>0.04143923567869714</v>
+        <v>0.03961123437025107</v>
       </c>
       <c r="D31" s="25" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.4740803814994422</v>
+        <v>0.4284467817562574</v>
       </c>
     </row>
     <row r="32">
@@ -3583,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="24" t="n">
-        <v>0.01650794361950855</v>
+        <v>0.01678542567237088</v>
       </c>
       <c r="D32" s="24" t="n">
         <v>0</v>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1419427420681525</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="34">
@@ -3646,16 +3646,16 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>1.12998593313295e-07</v>
+        <v>1.540461288441797e-08</v>
       </c>
       <c r="C36" s="24" t="n">
-        <v>0.05692767223547345</v>
+        <v>0.05604810820385786</v>
       </c>
       <c r="D36" s="24" t="n">
-        <v>6.432746883208821e-09</v>
+        <v>8.633994097844016e-10</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1.507295533048894e-07</v>
+        <v>1.958958153830204e-08</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.9718498340506938</v>
@@ -3668,16 +3668,16 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>9.768383840153099e-08</v>
+        <v>1.286140172707754e-08</v>
       </c>
       <c r="C37" s="25" t="n">
-        <v>0.06081953129916644</v>
+        <v>0.05994390698587126</v>
       </c>
       <c r="D37" s="25" t="n">
-        <v>5.94108526708463e-09</v>
+        <v>7.7096266883586e-10</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.392091348707364e-07</v>
+        <v>1.749229370902436e-08</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0.9005695345361184</v>
@@ -3690,16 +3690,16 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>7.870694893487945e-08</v>
+        <v>1.034391777355504e-08</v>
       </c>
       <c r="C38" s="24" t="n">
-        <v>0.06487282242693367</v>
+        <v>0.06375923942128729</v>
       </c>
       <c r="D38" s="24" t="n">
-        <v>5.105941922018171e-09</v>
+        <v>6.59520329878205e-10</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>1.196403898800077e-07</v>
+        <v>1.496378979636218e-08</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.8647852106386994</v>
@@ -3712,16 +3712,16 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>0.04190992908765714</v>
+        <v>0.07113737017120696</v>
       </c>
       <c r="C39" s="25" t="n">
-        <v>0.06748194017499352</v>
+        <v>0.06717134055346032</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>0.0028281633274315</v>
+        <v>0.004778392517847712</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.0662683924545118</v>
+        <v>0.1084164626354847</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>0.6547256214279519</v>
@@ -3734,16 +3734,16 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.2886613151522574</v>
+        <v>0.2963200956729828</v>
       </c>
       <c r="C40" s="24" t="n">
-        <v>0.01905394808611297</v>
+        <v>0.02027839680564917</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>0.005500137713380209</v>
+        <v>0.006008896481544672</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1288770280729018</v>
+        <v>0.1363352421214062</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.9800395309996239</v>
@@ -3756,16 +3756,16 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>6.941451318814953e-08</v>
+        <v>9.201562116762712e-09</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>0.01501685218419754</v>
+        <v>0.01515708195138125</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>1.042387483984472e-09</v>
+        <v>1.394688310844975e-10</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>2.44248068024732e-08</v>
+        <v>3.164394146694723e-09</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0.8261546883028914</v>
@@ -3778,16 +3778,16 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>6.965110784322271e-08</v>
+        <v>8.935097992254681e-09</v>
       </c>
       <c r="C42" s="24" t="n">
-        <v>0.02620626195947527</v>
+        <v>0.02639673412319088</v>
       </c>
       <c r="D42" s="24" t="n">
-        <v>1.825295177907157e-09</v>
+        <v>2.358574060662035e-10</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>4.276958689819837e-08</v>
+        <v>5.351344737078345e-09</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>0.6542475111182804</v>
@@ -3800,16 +3800,16 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.123639275433536</v>
+        <v>0.1364634563400894</v>
       </c>
       <c r="C43" s="25" t="n">
-        <v>0.08587485838092043</v>
+        <v>0.08498129605168152</v>
       </c>
       <c r="D43" s="25" t="n">
-        <v>0.01061750526817452</v>
+        <v>0.01159684138347285</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.2487851388124181</v>
+        <v>0.2631195565966682</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0.6432514443485702</v>
@@ -3822,16 +3822,16 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>1.08473008170814e-07</v>
+        <v>2.096350137433955e-08</v>
       </c>
       <c r="C44" s="24" t="n">
-        <v>0.02216044177934485</v>
+        <v>0.02052878880749672</v>
       </c>
       <c r="D44" s="24" t="n">
-        <v>2.403809782199721e-09</v>
+        <v>4.303552923794839e-10</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>5.632510982930986e-08</v>
+        <v>9.764287530162754e-09</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>0.4797912934834942</v>
@@ -3844,16 +3844,16 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.2457889564637488</v>
+        <v>0.1960790013757596</v>
       </c>
       <c r="C45" s="25" t="n">
-        <v>0.03591803882286684</v>
+        <v>0.03660795132295001</v>
       </c>
       <c r="D45" s="25" t="n">
-        <v>0.008828257280496857</v>
+        <v>0.007178050537816457</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.2068601952648496</v>
+        <v>0.1628620597872786</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -3866,19 +3866,19 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>1.520208122408094e-08</v>
+        <v>1.618598277387212e-09</v>
       </c>
       <c r="C46" s="24" t="n">
-        <v>0.02034412809747743</v>
+        <v>0.02013819062703088</v>
       </c>
       <c r="D46" s="24" t="n">
-        <v>3.09273087770959e-10</v>
+        <v>3.259564065860747e-11</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>7.246763352468013e-09</v>
+        <v>7.395591811146038e-10</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.7553246822404955</v>
+        <v>0.7487919560463553</v>
       </c>
     </row>
     <row r="47">
@@ -3888,19 +3888,19 @@
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.2994235045579806</v>
+        <v>0.2822620050016704</v>
       </c>
       <c r="C47" s="25" t="n">
-        <v>0.04971439597402084</v>
+        <v>0.04946939446322386</v>
       </c>
       <c r="D47" s="25" t="n">
-        <v>0.01488565866952448</v>
+        <v>0.0139633304674081</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.3487948030044762</v>
+        <v>0.3168125871267996</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.4740803814994422</v>
+        <v>0.4284467817562574</v>
       </c>
     </row>
     <row r="48">
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.0005764671747288517</v>
+        <v>0.01773799210959868</v>
       </c>
       <c r="C48" s="24" t="n">
-        <v>0.03064227747705986</v>
+        <v>0.03094508737001762</v>
       </c>
       <c r="D48" s="24" t="n">
-        <v>1.766426712445823e-05</v>
+        <v>0.0005489037156002144</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.0004139020454975051</v>
+        <v>0.01245402066711213</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.1419427420681525</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="50">
@@ -3976,16 +3976,16 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.04237184338252779</v>
+        <v>0.04239826333525394</v>
       </c>
       <c r="C52" s="24" t="n">
-        <v>0.06297462881850684</v>
+        <v>0.06287655228620766</v>
       </c>
       <c r="D52" s="24" t="n">
-        <v>0.002668351109370593</v>
+        <v>0.002665856621443495</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.0769223625187077</v>
+        <v>0.07692352810812679</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>0.9718498340506938</v>
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.03835312966778117</v>
+        <v>0.03838122897303223</v>
       </c>
       <c r="C53" s="25" t="n">
-        <v>0.06957048072837803</v>
+        <v>0.06945530211249798</v>
       </c>
       <c r="D53" s="25" t="n">
-        <v>0.002668245668425353</v>
+        <v>0.002665779853770914</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.07691932290125048</v>
+        <v>0.07692131297015872</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>0.9005695345361184</v>
@@ -4020,16 +4020,16 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.03704034967567654</v>
+        <v>0.0370534553973652</v>
       </c>
       <c r="C54" s="24" t="n">
-        <v>0.07203927821088472</v>
+        <v>0.07194606436802295</v>
       </c>
       <c r="D54" s="24" t="n">
-        <v>0.002668360055314516</v>
+        <v>0.002665850287076504</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.07692262040948493</v>
+        <v>0.07692334532940817</v>
       </c>
       <c r="F54" s="9" t="n">
         <v>0.8647852106386994</v>
@@ -4042,16 +4042,16 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.03518145231877982</v>
+        <v>0.03526861812873507</v>
       </c>
       <c r="C55" s="25" t="n">
-        <v>0.07584687705952509</v>
+        <v>0.07558698122430509</v>
       </c>
       <c r="D55" s="25" t="n">
-        <v>0.002668403288798037</v>
+        <v>0.002665848376303883</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.07692386673036102</v>
+        <v>0.07692329019389554</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>0.6547256214279519</v>
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.1916974426113651</v>
+        <v>0.1901058368847075</v>
       </c>
       <c r="C56" s="24" t="n">
-        <v>0.01391997775256079</v>
+        <v>0.01402297004707323</v>
       </c>
       <c r="D56" s="24" t="n">
-        <v>0.002668424136373002</v>
+        <v>0.002665848456408042</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.07692446771750751</v>
+        <v>0.07692329250530811</v>
       </c>
       <c r="F56" s="9" t="n">
         <v>0.9800395309996239</v>
@@ -4086,16 +4086,16 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.1560290416425018</v>
+        <v>0.1561033628971746</v>
       </c>
       <c r="C57" s="25" t="n">
-        <v>0.01710234285391538</v>
+        <v>0.01707722545808813</v>
       </c>
       <c r="D57" s="25" t="n">
-        <v>0.002668462165337904</v>
+        <v>0.002665812322960801</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.07692556400420462</v>
+        <v>0.07692224987149872</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>0.8261546883028914</v>
@@ -4108,16 +4108,16 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.09902372157555807</v>
+        <v>0.09891989158807808</v>
       </c>
       <c r="C58" s="24" t="n">
-        <v>0.0269464453755959</v>
+        <v>0.02695041436455389</v>
       </c>
       <c r="D58" s="24" t="n">
-        <v>0.002668337304323993</v>
+        <v>0.002665932067195453</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.07692196455129049</v>
+        <v>0.07692570510195861</v>
       </c>
       <c r="F58" s="9" t="n">
         <v>0.6542475111182804</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.03305541874853363</v>
+        <v>0.03310675547604956</v>
       </c>
       <c r="C59" s="25" t="n">
-        <v>0.08072243923690535</v>
+        <v>0.08052175975620807</v>
       </c>
       <c r="D59" s="25" t="n">
-        <v>0.002668314031378968</v>
+        <v>0.002665814210749988</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.07692129364636055</v>
+        <v>0.07692230434382234</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>0.6432514443485702</v>
@@ -4152,16 +4152,16 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.05433105722415058</v>
+        <v>0.05454871770448565</v>
       </c>
       <c r="C60" s="24" t="n">
-        <v>0.04911204681458394</v>
+        <v>0.04887037300574651</v>
       </c>
       <c r="D60" s="24" t="n">
-        <v>0.002668309425878322</v>
+        <v>0.002665816181203382</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.07692116088047792</v>
+        <v>0.07692236120142894</v>
       </c>
       <c r="F60" s="9" t="n">
         <v>0.4797912934834942</v>
@@ -4174,16 +4174,16 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>0.07190731636107728</v>
+        <v>0.07131481415928038</v>
       </c>
       <c r="C61" s="25" t="n">
-        <v>0.03710985177866196</v>
+        <v>0.03738288332119383</v>
       </c>
       <c r="D61" s="25" t="n">
-        <v>0.002668469851960932</v>
+        <v>0.002665953376789001</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.0769257855916865</v>
+        <v>0.07692631999216126</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -4196,19 +4196,19 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.1140716492667996</v>
+        <v>0.1147079339099366</v>
       </c>
       <c r="C62" s="24" t="n">
-        <v>0.02339356683603391</v>
+        <v>0.0232394915358965</v>
       </c>
       <c r="D62" s="24" t="n">
-        <v>0.002668542751219496</v>
+        <v>0.002665754059200145</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>0.07692788710792808</v>
+        <v>0.07692056866554248</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.7553246822404955</v>
+        <v>0.7487919560463553</v>
       </c>
     </row>
     <row r="63">
@@ -4218,19 +4218,19 @@
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>0.06063975676952887</v>
+        <v>0.06079007889326719</v>
       </c>
       <c r="C63" s="25" t="n">
-        <v>0.04400585315122874</v>
+        <v>0.04385430184744837</v>
       </c>
       <c r="D63" s="25" t="n">
-        <v>0.002668504231526117</v>
+        <v>0.002665906469115539</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.07692677667466921</v>
+        <v>0.07692496646710331</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.4740803814994422</v>
+        <v>0.4284467817562574</v>
       </c>
     </row>
     <row r="64">
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.06629782075571977</v>
+        <v>0.06730104265263419</v>
       </c>
       <c r="C64" s="24" t="n">
-        <v>0.04024510211790198</v>
+        <v>0.0396094981648834</v>
       </c>
       <c r="D64" s="24" t="n">
-        <v>0.002668162566508303</v>
+        <v>0.002665760525444253</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.0769169272660708</v>
+        <v>0.07692075524958694</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.1419427420681525</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="66">
@@ -4306,16 +4306,16 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.02620344769844228</v>
+        <v>0.06129129745559889</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.06740968278435086</v>
+        <v>0.06571255610075652</v>
       </c>
       <c r="D68" s="24" t="n">
-        <v>0.001766366097208323</v>
+        <v>0.004027607822539197</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.05704715523155528</v>
+        <v>0.1299992912254229</v>
       </c>
       <c r="F68" s="9" t="n">
         <v>0.9718498340506938</v>
@@ -4328,16 +4328,16 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>0.05077551892986816</v>
+        <v>0.01980455968018955</v>
       </c>
       <c r="C69" s="25" t="n">
-        <v>0.07548635024430657</v>
+        <v>0.07247942716059193</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>0.003832858605776446</v>
+        <v>0.001435423140787894</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.1237872942703699</v>
+        <v>0.04633122169113092</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0.9005695345361184</v>
@@ -4350,16 +4350,16 @@
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.02519040831093613</v>
+        <v>0.02491094989735838</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.07783289142166173</v>
+        <v>0.07480928774820883</v>
       </c>
       <c r="D70" s="24" t="n">
-        <v>0.001960642314932417</v>
+        <v>0.001863570418952696</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.06332156548423279</v>
+        <v>0.06015055196207775</v>
       </c>
       <c r="F70" s="9" t="n">
         <v>0.8647852106386994</v>
@@ -4372,16 +4372,16 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>0.01904658044143235</v>
+        <v>0.0188233496030912</v>
       </c>
       <c r="C71" s="25" t="n">
-        <v>0.08206660721410963</v>
+        <v>0.07976725601333907</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>0.001563088235858972</v>
+        <v>0.00150148694681836</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.05048202486030171</v>
+        <v>0.0484635663329188</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>0.6547256214279519</v>
@@ -4394,16 +4394,16 @@
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>0.0698853272913602</v>
+        <v>0.06372964737267586</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.006653786894103503</v>
+        <v>0.01095281208977317</v>
       </c>
       <c r="D72" s="24" t="n">
-        <v>0.0004650020748213863</v>
+        <v>0.0006980188522204254</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.01501786384331987</v>
+        <v>0.02252998803479094</v>
       </c>
       <c r="F72" s="9" t="n">
         <v>0.9800395309996239</v>
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>0.3247963366415298</v>
+        <v>0.3209896397522077</v>
       </c>
       <c r="C73" s="25" t="n">
-        <v>0.0170965766851034</v>
+        <v>0.01766059081007425</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>0.005552905476432574</v>
+        <v>0.005668866681936884</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.1793385081387475</v>
+        <v>0.1829742822970787</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0.8261546883028914</v>
@@ -4438,16 +4438,16 @@
         </is>
       </c>
       <c r="B74" s="9" t="n">
-        <v>0.09938010970300858</v>
+        <v>0.1515664321754441</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02657502189855462</v>
+        <v>0.02868467832979765</v>
       </c>
       <c r="D74" s="24" t="n">
-        <v>0.002641028591638213</v>
+        <v>0.004347634352547708</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.08529555015592669</v>
+        <v>0.140328802912638</v>
       </c>
       <c r="F74" s="9" t="n">
         <v>0.6542475111182804</v>
@@ -4460,16 +4460,16 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>0.02251791599980841</v>
+        <v>0.0222215038737016</v>
       </c>
       <c r="C75" s="25" t="n">
-        <v>0.08127192716573621</v>
+        <v>0.0802414429506282</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>0.001830074429060595</v>
+        <v>0.001783085535358791</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.05910470100446386</v>
+        <v>0.05755273750680341</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>0.6432514443485702</v>
@@ -4482,16 +4482,16 @@
         </is>
       </c>
       <c r="B76" s="9" t="n">
-        <v>0.01799739840041237</v>
+        <v>0.01792687522994341</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.04984858965177769</v>
+        <v>0.04468307590564768</v>
       </c>
       <c r="D76" s="24" t="n">
-        <v>0.0008971449276617164</v>
+        <v>0.0008010279266506368</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.02897449517085264</v>
+        <v>0.02585481688003633</v>
       </c>
       <c r="F76" s="9" t="n">
         <v>0.4797912934834942</v>
@@ -4504,16 +4504,16 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>0.06562781917806712</v>
+        <v>0.06139883262218021</v>
       </c>
       <c r="C77" s="25" t="n">
-        <v>0.03956645689908946</v>
+        <v>0.03926948434702817</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>0.00259666027889023</v>
+        <v>0.002411100496582508</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.08386261616296979</v>
+        <v>0.07782320658801947</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -4526,19 +4526,19 @@
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>0.2219112355471898</v>
+        <v>0.1822438014945581</v>
       </c>
       <c r="C78" s="24" t="n">
-        <v>0.02564637069020121</v>
+        <v>0.02461766227162885</v>
       </c>
       <c r="D78" s="24" t="n">
-        <v>0.005691217807163784</v>
+        <v>0.004486416356290799</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>0.1838054898217247</v>
+        <v>0.1448082763163002</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.7553246822404955</v>
+        <v>0.7487919560463553</v>
       </c>
     </row>
     <row r="79">
@@ -4548,19 +4548,19 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>0.03024721272215291</v>
+        <v>0.02896140192186942</v>
       </c>
       <c r="C79" s="25" t="n">
-        <v>0.04411012875787568</v>
+        <v>0.04190259392293433</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>0.00133420844774102</v>
+        <v>0.001213557864170984</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.04309004602716724</v>
+        <v>0.03917006549654713</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.4740803814994422</v>
+        <v>0.4284467817562574</v>
       </c>
     </row>
     <row r="80">
@@ -4570,19 +4570,19 @@
         </is>
       </c>
       <c r="B80" s="9" t="n">
-        <v>0.02642068913579193</v>
+        <v>0.02613170892118141</v>
       </c>
       <c r="C80" s="24" t="n">
-        <v>0.03149297775010471</v>
+        <v>0.02847005369509953</v>
       </c>
       <c r="D80" s="24" t="n">
-        <v>0.0008320661750959287</v>
+        <v>0.000743971156130746</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.02687268982836784</v>
+        <v>0.02401319275623543</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1419427420681525</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
   </sheetData>
@@ -4748,13 +4748,13 @@
         <v>0.732</v>
       </c>
       <c r="L3" s="40" t="n">
-        <v>0.879</v>
+        <v>0.877</v>
       </c>
       <c r="M3" s="43" t="n">
-        <v>0.641</v>
+        <v>0.621</v>
       </c>
       <c r="N3" s="42" t="n">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="4">
@@ -4794,13 +4794,13 @@
         <v>0.719</v>
       </c>
       <c r="L4" s="40" t="n">
-        <v>0.884</v>
+        <v>0.882</v>
       </c>
       <c r="M4" s="43" t="n">
-        <v>0.629</v>
+        <v>0.613</v>
       </c>
       <c r="N4" s="42" t="n">
-        <v>0.202</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="5">
@@ -4840,13 +4840,13 @@
         <v>0.673</v>
       </c>
       <c r="L5" s="40" t="n">
-        <v>0.84</v>
+        <v>0.838</v>
       </c>
       <c r="M5" s="43" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="N5" s="42" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="6">
@@ -4886,13 +4886,13 @@
         <v>0.647</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>0.851</v>
+        <v>0.844</v>
       </c>
       <c r="M6" s="43" t="n">
-        <v>0.595</v>
+        <v>0.556</v>
       </c>
       <c r="N6" s="42" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="7">
@@ -4932,10 +4932,10 @@
         <v>-0.177</v>
       </c>
       <c r="L7" s="41" t="n">
-        <v>-0.348</v>
+        <v>-0.337</v>
       </c>
       <c r="M7" s="41" t="n">
-        <v>-0.391</v>
+        <v>-0.361</v>
       </c>
       <c r="N7" s="42" t="n">
         <v>-0.139</v>
@@ -4978,13 +4978,13 @@
         <v>0.38</v>
       </c>
       <c r="L8" s="42" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="M8" s="42" t="n">
-        <v>0.136</v>
+        <v>0.154</v>
       </c>
       <c r="N8" s="42" t="n">
-        <v>0.186</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="9">
@@ -5024,13 +5024,13 @@
         <v>0.375</v>
       </c>
       <c r="L9" s="42" t="n">
-        <v>0.304</v>
+        <v>0.314</v>
       </c>
       <c r="M9" s="42" t="n">
-        <v>0.054</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="N9" s="42" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="10">
@@ -5070,13 +5070,13 @@
         <v>0.581</v>
       </c>
       <c r="L10" s="43" t="n">
-        <v>0.616</v>
+        <v>0.611</v>
       </c>
       <c r="M10" s="43" t="n">
-        <v>0.447</v>
+        <v>0.417</v>
       </c>
       <c r="N10" s="42" t="n">
-        <v>0.141</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="11">
@@ -5116,13 +5116,13 @@
         <v>0.383</v>
       </c>
       <c r="L11" s="43" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="M11" s="43" t="n">
-        <v>0.422</v>
+        <v>0.483</v>
+      </c>
+      <c r="M11" s="42" t="n">
+        <v>0.399</v>
       </c>
       <c r="N11" s="42" t="n">
-        <v>0.209</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="12">
@@ -5161,14 +5161,14 @@
       <c r="K12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="43" t="n">
-        <v>0.6830000000000001</v>
+      <c r="L12" s="40" t="n">
+        <v>0.704</v>
       </c>
       <c r="M12" s="43" t="n">
-        <v>0.476</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="N12" s="42" t="n">
-        <v>0.22</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="13">
@@ -5178,43 +5178,43 @@
         </is>
       </c>
       <c r="B13" s="40" t="n">
-        <v>0.879</v>
+        <v>0.877</v>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0.884</v>
+        <v>0.882</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0.84</v>
+        <v>0.838</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>0.851</v>
+        <v>0.844</v>
       </c>
       <c r="F13" s="41" t="n">
-        <v>-0.348</v>
+        <v>-0.337</v>
       </c>
       <c r="G13" s="42" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H13" s="42" t="n">
-        <v>0.304</v>
+        <v>0.314</v>
       </c>
       <c r="I13" s="43" t="n">
-        <v>0.616</v>
+        <v>0.611</v>
       </c>
       <c r="J13" s="43" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="K13" s="43" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.483</v>
+      </c>
+      <c r="K13" s="40" t="n">
+        <v>0.704</v>
       </c>
       <c r="L13" s="39" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="43" t="n">
-        <v>0.658</v>
+        <v>0.64</v>
       </c>
       <c r="N13" s="42" t="n">
-        <v>0.204</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="14">
@@ -5224,43 +5224,43 @@
         </is>
       </c>
       <c r="B14" s="43" t="n">
-        <v>0.641</v>
+        <v>0.621</v>
       </c>
       <c r="C14" s="43" t="n">
-        <v>0.629</v>
+        <v>0.613</v>
       </c>
       <c r="D14" s="43" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="E14" s="43" t="n">
-        <v>0.595</v>
+        <v>0.556</v>
       </c>
       <c r="F14" s="41" t="n">
-        <v>-0.391</v>
+        <v>-0.361</v>
       </c>
       <c r="G14" s="42" t="n">
-        <v>0.136</v>
+        <v>0.154</v>
       </c>
       <c r="H14" s="42" t="n">
-        <v>0.054</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="I14" s="43" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="J14" s="43" t="n">
-        <v>0.422</v>
+        <v>0.417</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>0.399</v>
       </c>
       <c r="K14" s="43" t="n">
-        <v>0.476</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L14" s="43" t="n">
-        <v>0.658</v>
+        <v>0.64</v>
       </c>
       <c r="M14" s="39" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="43" t="n">
-        <v>0.46</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="15">
@@ -5270,40 +5270,40 @@
         </is>
       </c>
       <c r="B15" s="42" t="n">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0.202</v>
+        <v>0.198</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>0.169</v>
+        <v>0.178</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>-0.139</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>0.186</v>
+        <v>0.172</v>
       </c>
       <c r="H15" s="42" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.075</v>
       </c>
       <c r="I15" s="42" t="n">
-        <v>0.141</v>
+        <v>0.152</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.209</v>
+        <v>0.205</v>
       </c>
       <c r="K15" s="42" t="n">
-        <v>0.22</v>
+        <v>0.176</v>
       </c>
       <c r="L15" s="42" t="n">
-        <v>0.204</v>
+        <v>0.198</v>
       </c>
       <c r="M15" s="43" t="n">
-        <v>0.46</v>
+        <v>0.441</v>
       </c>
       <c r="N15" s="39" t="n">
         <v>1</v>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="C22" s="29" t="n">
-        <v>0.8835248952761964</v>
+        <v>0.8818708712318351</v>
       </c>
       <c r="D22" s="45" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="C23" s="28" t="n">
-        <v>0.8791414690292736</v>
+        <v>0.8772590564733882</v>
       </c>
       <c r="D23" s="44" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="C24" s="29" t="n">
-        <v>0.85071265595919</v>
+        <v>0.8442031212496387</v>
       </c>
       <c r="D24" s="45" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="C25" s="28" t="n">
-        <v>0.8396667894157622</v>
+        <v>0.8378878973040726</v>
       </c>
       <c r="D25" s="44" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         <v>0.12</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>1.12998593313295e-07</v>
+        <v>1.540461288441797e-08</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0.04237184338252779</v>
+        <v>0.04239826333525394</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.02620344769844228</v>
+        <v>0.06129129745559889</v>
       </c>
     </row>
     <row r="4">
@@ -5829,13 +5829,13 @@
         <v>0.12</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>9.768383840153099e-08</v>
+        <v>1.286140172707754e-08</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.03835312966778117</v>
+        <v>0.03838122897303223</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>0.05077551892986816</v>
+        <v>0.01980455968018955</v>
       </c>
     </row>
     <row r="5">
@@ -5851,13 +5851,13 @@
         <v>0.12</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>7.870694893487945e-08</v>
+        <v>1.034391777355504e-08</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.03704034967567654</v>
+        <v>0.0370534553973652</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.02519040831093613</v>
+        <v>0.02491094989735838</v>
       </c>
     </row>
     <row r="6">
@@ -5873,13 +5873,13 @@
         <v>0.12</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.04190992908765714</v>
+        <v>0.07113737017120696</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.03518145231877982</v>
+        <v>0.03526861812873507</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>0.01904658044143235</v>
+        <v>0.0188233496030912</v>
       </c>
     </row>
     <row r="7">
@@ -5895,13 +5895,13 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="D7" s="46" t="n">
-        <v>0.2886613151522574</v>
+        <v>0.2963200956729828</v>
       </c>
       <c r="E7" s="46" t="n">
-        <v>0.1916974426113651</v>
+        <v>0.1901058368847075</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.0698853272913602</v>
+        <v>0.06372964737267586</v>
       </c>
     </row>
     <row r="8">
@@ -5917,13 +5917,13 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>6.941451318814953e-08</v>
+        <v>9.201562116762712e-09</v>
       </c>
       <c r="E8" s="47" t="n">
-        <v>0.1560290416425018</v>
+        <v>0.1561033628971746</v>
       </c>
       <c r="F8" s="47" t="n">
-        <v>0.3247963366415298</v>
+        <v>0.3209896397522077</v>
       </c>
     </row>
     <row r="9">
@@ -5939,13 +5939,13 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>6.965110784322271e-08</v>
+        <v>8.935097992254681e-09</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>0.09902372157555807</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0.09938010970300858</v>
+        <v>0.09891989158807808</v>
+      </c>
+      <c r="F9" s="46" t="n">
+        <v>0.1515664321754441</v>
       </c>
     </row>
     <row r="10">
@@ -5961,13 +5961,13 @@
         <v>0.12</v>
       </c>
       <c r="D10" s="47" t="n">
-        <v>0.123639275433536</v>
+        <v>0.1364634563400894</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>0.03305541874853363</v>
+        <v>0.03310675547604956</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>0.02251791599980841</v>
+        <v>0.0222215038737016</v>
       </c>
     </row>
     <row r="11">
@@ -5983,13 +5983,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1.08473008170814e-07</v>
+        <v>2.096350137433955e-08</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.05433105722415058</v>
+        <v>0.05454871770448565</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.01799739840041237</v>
+        <v>0.01792687522994341</v>
       </c>
     </row>
     <row r="12">
@@ -6005,13 +6005,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="47" t="n">
-        <v>0.2457889564637488</v>
+        <v>0.1960790013757596</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>0.07190731636107728</v>
+        <v>0.07131481415928038</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>0.06562781917806712</v>
+        <v>0.06139883262218021</v>
       </c>
     </row>
     <row r="13">
@@ -6027,13 +6027,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1.520208122408094e-08</v>
+        <v>1.618598277387212e-09</v>
       </c>
       <c r="E13" s="46" t="n">
-        <v>0.1140716492667996</v>
+        <v>0.1147079339099366</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>0.2219112355471898</v>
+        <v>0.1822438014945581</v>
       </c>
     </row>
     <row r="14">
@@ -6049,13 +6049,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="47" t="n">
-        <v>0.2994235045579806</v>
+        <v>0.2822620050016704</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.06063975676952887</v>
+        <v>0.06079007889326719</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.03024721272215291</v>
+        <v>0.02896140192186942</v>
       </c>
     </row>
     <row r="15">
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.0005764671747288517</v>
+        <v>0.01773799210959868</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>0.06629782075571977</v>
+        <v>0.06730104265263419</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.02642068913579193</v>
+        <v>0.02613170892118141</v>
       </c>
     </row>
   </sheetData>

--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Risk Decomposition" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Covariance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Portfolio Weights" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cluster Analysis" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,11 +23,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="+0.000;-0.000;0.000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,8 +124,119 @@
       <color rgb="00F0F4F8"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="007A90A8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF6B6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00D0D8E4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E6DA4"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006BCB77"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B7770D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7B45"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B3FA0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B03A2E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006BCB77"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006BCB77"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF6B6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E6DA4"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002E6DA4"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00B7770D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF6B6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001E7B45"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006B3FA0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006B3FA0"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -178,8 +291,56 @@
         <bgColor rgb="008B2E1A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B03A2E"/>
+        <bgColor rgb="00B03A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00111927"/>
+        <bgColor rgb="00111927"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A1A1A"/>
+        <bgColor rgb="003A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6DA4"/>
+        <bgColor rgb="002E6DA4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A1A"/>
+        <bgColor rgb="001E3A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7770D"/>
+        <bgColor rgb="00B7770D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B3FA0"/>
+        <bgColor rgb="006B3FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A2436"/>
+        <bgColor rgb="001A2436"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -245,11 +406,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B03A2E"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E2D3D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E2D3D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E2D3D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002E6DA4"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E2D3D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E2D3D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E2D3D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00B7770D"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E2D3D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E2D3D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E2D3D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E7B45"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E2D3D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E2D3D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E2D3D"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="006B3FA0"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E2D3D"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E2D3D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001E2D3D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -386,6 +617,147 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="27" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="33" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -744,6 +1116,86 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8667750" cy="3238500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4667250" cy="4381500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5334000" cy="3714750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1063,7 +1515,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 53.5% — a 27.1 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
+          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 42.0% — a 38.6 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
         </is>
       </c>
     </row>
@@ -1207,19 +1659,19 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.05341435110809257</v>
+        <v>0.0519153225469064</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.06196353510197526</v>
+        <v>0.05672701063600807</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.8620287887091489</v>
+        <v>0.9151781834587385</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>-0.1548283411757465</v>
+        <v>-0.1388515020427566</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.3449907859405511</v>
+        <v>0.3738909682872575</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1379,22 +1831,22 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.535</v>
+        <v>0.42</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.055</v>
+        <v>0.065</v>
       </c>
       <c r="E20" s="9" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>0.154</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0.126</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1"/>
@@ -2597,16 +3049,16 @@
         </is>
       </c>
       <c r="B7" s="32" t="n">
-        <v>-0.1257176000642428</v>
+        <v>-0.1050506428004342</v>
       </c>
       <c r="C7" s="34" t="n">
-        <v>0.02542692133678326</v>
+        <v>0.02485925553436985</v>
       </c>
       <c r="D7" s="32" t="n">
-        <v>-0.130784375396225</v>
+        <v>-0.1166178609836621</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.322990144323839</v>
+        <v>0.3183738177155639</v>
       </c>
     </row>
     <row r="8" ht="8" customHeight="1"/>
@@ -4306,16 +4758,16 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.06129129745559889</v>
+        <v>0.01418954230934598</v>
       </c>
       <c r="C68" s="24" t="n">
-        <v>0.06571255610075652</v>
+        <v>0.0621455954800322</v>
       </c>
       <c r="D68" s="24" t="n">
-        <v>0.004027607822539197</v>
+        <v>0.0008818175564034173</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.1299992912254229</v>
+        <v>0.03108986518121491</v>
       </c>
       <c r="F68" s="9" t="n">
         <v>0.9718498340506938</v>
@@ -4328,16 +4780,16 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>0.01980455968018955</v>
+        <v>0.01071962159834464</v>
       </c>
       <c r="C69" s="25" t="n">
-        <v>0.07247942716059193</v>
+        <v>0.06881032714615799</v>
       </c>
       <c r="D69" s="25" t="n">
-        <v>0.001435423140787894</v>
+        <v>0.0007376206690651158</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.04633122169113092</v>
+        <v>0.0260059770749458</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0.9005695345361184</v>
@@ -4350,16 +4802,16 @@
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.02491094989735838</v>
+        <v>0.01785691413064642</v>
       </c>
       <c r="C70" s="24" t="n">
-        <v>0.07480928774820883</v>
+        <v>0.0699804705840664</v>
       </c>
       <c r="D70" s="24" t="n">
-        <v>0.001863570418952696</v>
+        <v>0.001249635254041901</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.06015055196207775</v>
+        <v>0.04405785674342171</v>
       </c>
       <c r="F70" s="9" t="n">
         <v>0.8647852106386994</v>
@@ -4372,16 +4824,16 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>0.0188233496030912</v>
+        <v>0.01018151128031412</v>
       </c>
       <c r="C71" s="25" t="n">
-        <v>0.07976725601333907</v>
+        <v>0.07713721713992763</v>
       </c>
       <c r="D71" s="25" t="n">
-        <v>0.00150148694681836</v>
+        <v>0.000785373446442213</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.0484635663329188</v>
+        <v>0.02768957636359879</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>0.6547256214279519</v>
@@ -4394,16 +4846,16 @@
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>0.06372964737267586</v>
+        <v>0.0596596557957153</v>
       </c>
       <c r="C72" s="24" t="n">
-        <v>0.01095281208977317</v>
+        <v>0.01185652218885514</v>
       </c>
       <c r="D72" s="24" t="n">
-        <v>0.0006980188522204254</v>
+        <v>0.0007073560327213588</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.02252998803479094</v>
+        <v>0.02493894970987092</v>
       </c>
       <c r="F72" s="9" t="n">
         <v>0.9800395309996239</v>
@@ -4416,16 +4868,16 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>0.3209896397522077</v>
+        <v>0.3316397889964033</v>
       </c>
       <c r="C73" s="25" t="n">
-        <v>0.01766059081007425</v>
+        <v>0.01854942338164662</v>
       </c>
       <c r="D73" s="25" t="n">
-        <v>0.005668866681936884</v>
+        <v>0.006151726856294233</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.1829742822970787</v>
+        <v>0.2168888079002478</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0.8261546883028914</v>
@@ -4438,16 +4890,16 @@
         </is>
       </c>
       <c r="B74" s="9" t="n">
-        <v>0.1515664321754441</v>
+        <v>0.1092060125556164</v>
       </c>
       <c r="C74" s="24" t="n">
-        <v>0.02868467832979765</v>
+        <v>0.02838237345122105</v>
       </c>
       <c r="D74" s="24" t="n">
-        <v>0.004347634352547708</v>
+        <v>0.003099525831472239</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.140328802912638</v>
+        <v>0.109278659203832</v>
       </c>
       <c r="F74" s="9" t="n">
         <v>0.6542475111182804</v>
@@ -4460,16 +4912,16 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>0.0222215038737016</v>
+        <v>0.009319148736044227</v>
       </c>
       <c r="C75" s="25" t="n">
-        <v>0.0802414429506282</v>
+        <v>0.07416805794013158</v>
       </c>
       <c r="D75" s="25" t="n">
-        <v>0.001783085535358791</v>
+        <v>0.0006911831634076322</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.05755273750680341</v>
+        <v>0.02436874975988587</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>0.6432514443485702</v>
@@ -4482,16 +4934,16 @@
         </is>
       </c>
       <c r="B76" s="9" t="n">
-        <v>0.01792687522994341</v>
+        <v>0.01805983719241161</v>
       </c>
       <c r="C76" s="24" t="n">
-        <v>0.04468307590564768</v>
+        <v>0.04543999203099217</v>
       </c>
       <c r="D76" s="24" t="n">
-        <v>0.0008010279266506368</v>
+        <v>0.0008206388581041995</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.02585481688003633</v>
+        <v>0.02893291392948143</v>
       </c>
       <c r="F76" s="9" t="n">
         <v>0.4797912934834942</v>
@@ -4504,16 +4956,16 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>0.06139883262218021</v>
+        <v>0.1483922296615784</v>
       </c>
       <c r="C77" s="25" t="n">
-        <v>0.03926948434702817</v>
+        <v>0.04167679313253376</v>
       </c>
       <c r="D77" s="25" t="n">
-        <v>0.002411100496582508</v>
+        <v>0.006184512258081045</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.07782320658801947</v>
+        <v>0.2180447088165566</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -4526,16 +4978,16 @@
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>0.1822438014945581</v>
+        <v>0.2280024325953268</v>
       </c>
       <c r="C78" s="24" t="n">
-        <v>0.02461766227162885</v>
+        <v>0.02412051657055184</v>
       </c>
       <c r="D78" s="24" t="n">
-        <v>0.004486416356290799</v>
+        <v>0.005499536453541708</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>0.1448082763163002</v>
+        <v>0.1938948092586715</v>
       </c>
       <c r="F78" s="9" t="n">
         <v>0.7487919560463553</v>
@@ -4548,16 +5000,16 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>0.02896140192186942</v>
+        <v>0.02821942763967997</v>
       </c>
       <c r="C79" s="25" t="n">
-        <v>0.04190259392293433</v>
+        <v>0.04155512604382863</v>
       </c>
       <c r="D79" s="25" t="n">
-        <v>0.001213557864170984</v>
+        <v>0.001172661872451603</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.03917006549654713</v>
+        <v>0.04134403908487444</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>0.4284467817562574</v>
@@ -4570,16 +5022,16 @@
         </is>
       </c>
       <c r="B80" s="9" t="n">
-        <v>0.02613170892118141</v>
+        <v>0.01455387750857305</v>
       </c>
       <c r="C80" s="24" t="n">
-        <v>0.02847005369509953</v>
+        <v>0.02624160233260154</v>
       </c>
       <c r="D80" s="24" t="n">
-        <v>0.000743971156130746</v>
+        <v>0.0003819170659773676</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.02401319275623543</v>
+        <v>0.01346508697339823</v>
       </c>
       <c r="F80" s="9" t="n">
         <v>0.1297114447333514</v>
@@ -5813,7 +6265,7 @@
         <v>0.04239826333525394</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0.06129129745559889</v>
+        <v>0.01418954230934598</v>
       </c>
     </row>
     <row r="4">
@@ -5835,7 +6287,7 @@
         <v>0.03838122897303223</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>0.01980455968018955</v>
+        <v>0.01071962159834464</v>
       </c>
     </row>
     <row r="5">
@@ -5857,7 +6309,7 @@
         <v>0.0370534553973652</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>0.02491094989735838</v>
+        <v>0.01785691413064642</v>
       </c>
     </row>
     <row r="6">
@@ -5879,7 +6331,7 @@
         <v>0.03526861812873507</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>0.0188233496030912</v>
+        <v>0.01018151128031412</v>
       </c>
     </row>
     <row r="7">
@@ -5901,7 +6353,7 @@
         <v>0.1901058368847075</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>0.06372964737267586</v>
+        <v>0.0596596557957153</v>
       </c>
     </row>
     <row r="8">
@@ -5923,7 +6375,7 @@
         <v>0.1561033628971746</v>
       </c>
       <c r="F8" s="47" t="n">
-        <v>0.3209896397522077</v>
+        <v>0.3316397889964033</v>
       </c>
     </row>
     <row r="9">
@@ -5945,7 +6397,7 @@
         <v>0.09891989158807808</v>
       </c>
       <c r="F9" s="46" t="n">
-        <v>0.1515664321754441</v>
+        <v>0.1092060125556164</v>
       </c>
     </row>
     <row r="10">
@@ -5967,7 +6419,7 @@
         <v>0.03310675547604956</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>0.0222215038737016</v>
+        <v>0.009319148736044227</v>
       </c>
     </row>
     <row r="11">
@@ -5989,7 +6441,7 @@
         <v>0.05454871770448565</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.01792687522994341</v>
+        <v>0.01805983719241161</v>
       </c>
     </row>
     <row r="12">
@@ -6010,8 +6462,8 @@
       <c r="E12" s="12" t="n">
         <v>0.07131481415928038</v>
       </c>
-      <c r="F12" s="12" t="n">
-        <v>0.06139883262218021</v>
+      <c r="F12" s="47" t="n">
+        <v>0.1483922296615784</v>
       </c>
     </row>
     <row r="13">
@@ -6033,7 +6485,7 @@
         <v>0.1147079339099366</v>
       </c>
       <c r="F13" s="46" t="n">
-        <v>0.1822438014945581</v>
+        <v>0.2280024325953268</v>
       </c>
     </row>
     <row r="14">
@@ -6055,7 +6507,7 @@
         <v>0.06079007889326719</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0.02896140192186942</v>
+        <v>0.02821942763967997</v>
       </c>
     </row>
     <row r="15">
@@ -6077,7 +6529,7 @@
         <v>0.06730104265263419</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>0.02613170892118141</v>
+        <v>0.01455387750857305</v>
       </c>
     </row>
   </sheetData>
@@ -6087,4 +6539,869 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FACTOR-LOADING CLUSTER ANALYSIS — ENHANCED HRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ward linkage on z-scored factor betas  |  5-Factor Model  |  13 Asset Classes  |  Euclidean distance in standardised beta space  |  2004 Q4 to 2024 Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>5-CLUSTER SOLUTION — ECONOMIC INTERPRETATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="B5" s="49" t="inlineStr">
+        <is>
+          <t>CLUSTER 1</t>
+        </is>
+      </c>
+      <c r="D5" s="50" t="inlineStr">
+        <is>
+          <t>CLUSTER 2</t>
+        </is>
+      </c>
+      <c r="F5" s="51" t="inlineStr">
+        <is>
+          <t>CLUSTER 3</t>
+        </is>
+      </c>
+      <c r="H5" s="52" t="inlineStr">
+        <is>
+          <t>CLUSTER 4</t>
+        </is>
+      </c>
+      <c r="J5" s="53" t="inlineStr">
+        <is>
+          <t>CLUSTER 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>Pure Rate Duration</t>
+        </is>
+      </c>
+      <c r="F6" s="56" t="inlineStr">
+        <is>
+          <t>Inflation Hedge</t>
+        </is>
+      </c>
+      <c r="H6" s="57" t="inlineStr">
+        <is>
+          <t>Domestic Equity Beta</t>
+        </is>
+      </c>
+      <c r="J6" s="58" t="inlineStr">
+        <is>
+          <t>Credit-Sensitive Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>Dominant: Equity Premium</t>
+        </is>
+      </c>
+      <c r="D7" s="59" t="inlineStr">
+        <is>
+          <t>Dominant: Term Premium</t>
+        </is>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>Dominant: Inflation</t>
+        </is>
+      </c>
+      <c r="H7" s="59" t="inlineStr">
+        <is>
+          <t>Dominant: Equity Premium</t>
+        </is>
+      </c>
+      <c r="J7" s="59" t="inlineStr">
+        <is>
+          <t>Dominant: Credit Spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>TIPS
+Investment Grade Credit
+High Yield Credit
+Hedge Funds
+Private Equity
+Private Real Estate</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="H8" s="60" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity
+US Mid Cap Equity
+US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="J8" s="60" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity
+REITs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="B9" s="61" t="inlineStr">
+        <is>
+          <t>Low equity beta complex. Credit and alternative assets sharing below-average equity exposure.</t>
+        </is>
+      </c>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>Positive term premium, negative equity beta. Sole rate hedge in universe.</t>
+        </is>
+      </c>
+      <c r="F9" s="61" t="inlineStr">
+        <is>
+          <t>Dominant inflation beta. Real commodity dynamics orthogonal to equity and credit.</t>
+        </is>
+      </c>
+      <c r="H9" s="61" t="inlineStr">
+        <is>
+          <t>High positive equity loading across all three size segments. Essentially same systematic risk.</t>
+        </is>
+      </c>
+      <c r="J9" s="61" t="inlineStr">
+        <is>
+          <t>High credit spread sensitivity, strongly negative liquidity beta. Seizes during credit stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="B10" s="62" t="inlineStr">
+        <is>
+          <t>ERP:  -0.66</t>
+        </is>
+      </c>
+      <c r="D10" s="62" t="inlineStr">
+        <is>
+          <t>ERP:  -1.01</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>ERP:  -1.03</t>
+        </is>
+      </c>
+      <c r="H10" s="63" t="inlineStr">
+        <is>
+          <t>ERP:  +1.33</t>
+        </is>
+      </c>
+      <c r="J10" s="63" t="inlineStr">
+        <is>
+          <t>ERP:  +1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>TERM:  +0.11</t>
+        </is>
+      </c>
+      <c r="D11" s="63" t="inlineStr">
+        <is>
+          <t>TERM:  +2.58</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>TERM:  -1.56</t>
+        </is>
+      </c>
+      <c r="H11" s="62" t="inlineStr">
+        <is>
+          <t>TERM:  -0.75</t>
+        </is>
+      </c>
+      <c r="J11" s="64" t="inlineStr">
+        <is>
+          <t>TERM:  +0.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>CREDIT:  -0.45</t>
+        </is>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>CREDIT:  -0.83</t>
+        </is>
+      </c>
+      <c r="F12" s="63" t="inlineStr">
+        <is>
+          <t>CREDIT:  +0.98</t>
+        </is>
+      </c>
+      <c r="H12" s="64" t="inlineStr">
+        <is>
+          <t>CREDIT:  -0.43</t>
+        </is>
+      </c>
+      <c r="J12" s="63" t="inlineStr">
+        <is>
+          <t>CREDIT:  +1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14" customHeight="1">
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>INFL:  +0.28</t>
+        </is>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>INFL:  -0.87</t>
+        </is>
+      </c>
+      <c r="F13" s="63" t="inlineStr">
+        <is>
+          <t>INFL:  +2.06</t>
+        </is>
+      </c>
+      <c r="H13" s="62" t="inlineStr">
+        <is>
+          <t>INFL:  -0.50</t>
+        </is>
+      </c>
+      <c r="J13" s="62" t="inlineStr">
+        <is>
+          <t>INFL:  -0.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>LIQ:  +0.49</t>
+        </is>
+      </c>
+      <c r="D14" s="64" t="inlineStr">
+        <is>
+          <t>LIQ:  -0.22</t>
+        </is>
+      </c>
+      <c r="F14" s="63" t="inlineStr">
+        <is>
+          <t>LIQ:  +0.86</t>
+        </is>
+      </c>
+      <c r="H14" s="64" t="inlineStr">
+        <is>
+          <t>LIQ:  -0.03</t>
+        </is>
+      </c>
+      <c r="J14" s="62" t="inlineStr">
+        <is>
+          <t>LIQ:  -1.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1"/>
+    <row r="70" ht="20" customHeight="1">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>FULL ASSET DETAIL — CLUSTER ASSIGNMENT AND STANDARDISED BETAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Cl.</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Cluster Name</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>ERP (z)</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Term (z)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Credit (z)</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Inflation (z)</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Liquidity (z)</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>R-Sq</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="B72" s="65" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="C72" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="67" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E72" s="68" t="n">
+        <v>-0.269</v>
+      </c>
+      <c r="F72" s="68" t="n">
+        <v>-0.644</v>
+      </c>
+      <c r="G72" s="68" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="H72" s="68" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="I72" s="69" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="J72" s="70" t="n">
+        <v>0.4472956521780461</v>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="B73" s="71" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="C73" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" s="72" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E73" s="73" t="n">
+        <v>-0.436</v>
+      </c>
+      <c r="F73" s="69" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="G73" s="73" t="n">
+        <v>-0.6870000000000001</v>
+      </c>
+      <c r="H73" s="73" t="n">
+        <v>-0.546</v>
+      </c>
+      <c r="I73" s="73" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="J73" s="33" t="n">
+        <v>0.6374629953920316</v>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="B74" s="65" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C74" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="67" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E74" s="68" t="n">
+        <v>-0.456</v>
+      </c>
+      <c r="F74" s="68" t="n">
+        <v>-0.499</v>
+      </c>
+      <c r="G74" s="68" t="n">
+        <v>-0.677</v>
+      </c>
+      <c r="H74" s="68" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="I74" s="68" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="J74" s="74" t="n">
+        <v>0.7443129475785015</v>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="B75" s="71" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C75" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="72" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E75" s="73" t="n">
+        <v>-0.578</v>
+      </c>
+      <c r="F75" s="73" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="G75" s="73" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H75" s="73" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I75" s="75" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="J75" s="16" t="n">
+        <v>0.8431315161474411</v>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="B76" s="65" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="C76" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="67" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E76" s="76" t="n">
+        <v>-1.027</v>
+      </c>
+      <c r="F76" s="68" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G76" s="76" t="n">
+        <v>-0.819</v>
+      </c>
+      <c r="H76" s="68" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="I76" s="68" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="J76" s="74" t="n">
+        <v>0.8015086616077469</v>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="B77" s="71" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="C77" s="66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="72" t="inlineStr">
+        <is>
+          <t>Yield-Seeking Diversifiers</t>
+        </is>
+      </c>
+      <c r="E77" s="76" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="F77" s="73" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G77" s="73" t="n">
+        <v>-0.771</v>
+      </c>
+      <c r="H77" s="75" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="I77" s="73" t="n">
+        <v>-0.104</v>
+      </c>
+      <c r="J77" s="27" t="n">
+        <v>0.08716459731266091</v>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="B78" s="77" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="C78" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="79" t="inlineStr">
+        <is>
+          <t>Pure Rate Duration</t>
+        </is>
+      </c>
+      <c r="E78" s="76" t="n">
+        <v>-1.014</v>
+      </c>
+      <c r="F78" s="75" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="G78" s="76" t="n">
+        <v>-0.834</v>
+      </c>
+      <c r="H78" s="76" t="n">
+        <v>-0.867</v>
+      </c>
+      <c r="I78" s="68" t="n">
+        <v>-0.221</v>
+      </c>
+      <c r="J78" s="74" t="n">
+        <v>0.9812439847251684</v>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="B79" s="80" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="C79" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="82" t="inlineStr">
+        <is>
+          <t>Inflation Hedge</t>
+        </is>
+      </c>
+      <c r="E79" s="76" t="n">
+        <v>-1.034</v>
+      </c>
+      <c r="F79" s="83" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="G79" s="69" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="H79" s="75" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I79" s="69" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="J79" s="33" t="n">
+        <v>0.4370483747153048</v>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="B80" s="84" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C80" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="86" t="inlineStr">
+        <is>
+          <t>Domestic Equity Beta</t>
+        </is>
+      </c>
+      <c r="E80" s="75" t="n">
+        <v>1.666</v>
+      </c>
+      <c r="F80" s="76" t="n">
+        <v>-1.037</v>
+      </c>
+      <c r="G80" s="68" t="n">
+        <v>-0.531</v>
+      </c>
+      <c r="H80" s="76" t="n">
+        <v>-0.853</v>
+      </c>
+      <c r="I80" s="68" t="n">
+        <v>-0.317</v>
+      </c>
+      <c r="J80" s="74" t="n">
+        <v>0.8712833012703342</v>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="B81" s="87" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="C81" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="88" t="inlineStr">
+        <is>
+          <t>Domestic Equity Beta</t>
+        </is>
+      </c>
+      <c r="E81" s="69" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="F81" s="73" t="n">
+        <v>-0.672</v>
+      </c>
+      <c r="G81" s="73" t="n">
+        <v>-0.304</v>
+      </c>
+      <c r="H81" s="73" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I81" s="73" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="J81" s="16" t="n">
+        <v>0.9123635173053706</v>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="B82" s="84" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="C82" s="85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="86" t="inlineStr">
+        <is>
+          <t>Domestic Equity Beta</t>
+        </is>
+      </c>
+      <c r="E82" s="69" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="F82" s="68" t="n">
+        <v>-0.529</v>
+      </c>
+      <c r="G82" s="68" t="n">
+        <v>-0.443</v>
+      </c>
+      <c r="H82" s="68" t="n">
+        <v>-0.458</v>
+      </c>
+      <c r="I82" s="68" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="J82" s="74" t="n">
+        <v>0.9906918940400172</v>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="B83" s="89" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C83" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" s="91" t="inlineStr">
+        <is>
+          <t>Credit-Sensitive Equity</t>
+        </is>
+      </c>
+      <c r="E83" s="75" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="F83" s="73" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="G83" s="75" t="n">
+        <v>2.588</v>
+      </c>
+      <c r="H83" s="83" t="n">
+        <v>-1.859</v>
+      </c>
+      <c r="I83" s="83" t="n">
+        <v>-2.023</v>
+      </c>
+      <c r="J83" s="33" t="n">
+        <v>0.6337080092805776</v>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="B84" s="92" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C84" s="90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" s="93" t="inlineStr">
+        <is>
+          <t>Credit-Sensitive Equity</t>
+        </is>
+      </c>
+      <c r="E84" s="68" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="F84" s="68" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="G84" s="75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H84" s="68" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="I84" s="83" t="n">
+        <v>-1.452</v>
+      </c>
+      <c r="J84" s="70" t="n">
+        <v>0.6355398384728477</v>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="B86" s="94" t="inlineStr">
+        <is>
+          <t>Green = positive factor tilt  |  Red = negative factor tilt  |  Bold = strong tilt (|z| &gt; 1.2)  |  R-sq: green &gt;= 0.70, amber &gt;= 0.40, red &lt; 0.40</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B4:J4"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B70:J70"/>
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -11,13 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Analytics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Look-Through Exposure" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Testing" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Decomposition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor Performance" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Weights" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cluster Analysis" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Testing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Decomposition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Net Factor Exposure" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="+0.000;-0.000;0.000"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,11 +108,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00D0D8E4"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00F0F4F8"/>
       <sz val="8"/>
@@ -132,114 +123,8 @@
       <color rgb="00F0F4F8"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00B03A2E"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="007A90A8"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FF6B6B"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002E6DA4"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006BCB77"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00B7770D"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7B45"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B3FA0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00B03A2E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="006BCB77"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006BCB77"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF6B6B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002E6DA4"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002E6DA4"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00B7770D"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FF6B6B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001E7B45"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B3FA0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="006B3FA0"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -294,56 +179,8 @@
         <bgColor rgb="008B2E1A"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B03A2E"/>
-        <bgColor rgb="00B03A2E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00111927"/>
-        <bgColor rgb="00111927"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003A1A1A"/>
-        <bgColor rgb="003A1A1A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E6DA4"/>
-        <bgColor rgb="002E6DA4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A1A"/>
-        <bgColor rgb="001E3A1A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7770D"/>
-        <bgColor rgb="00B7770D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="006B3FA0"/>
-        <bgColor rgb="006B3FA0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A2436"/>
-        <bgColor rgb="001A2436"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -409,81 +246,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="00B03A2E"/>
-      </left>
-      <right style="thin">
-        <color rgb="001E2D3D"/>
-      </right>
-      <top style="thin">
-        <color rgb="001E2D3D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001E2D3D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="002E6DA4"/>
-      </left>
-      <right style="thin">
-        <color rgb="001E2D3D"/>
-      </right>
-      <top style="thin">
-        <color rgb="001E2D3D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001E2D3D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00B7770D"/>
-      </left>
-      <right style="thin">
-        <color rgb="001E2D3D"/>
-      </right>
-      <top style="thin">
-        <color rgb="001E2D3D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001E2D3D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="001E7B45"/>
-      </left>
-      <right style="thin">
-        <color rgb="001E2D3D"/>
-      </right>
-      <top style="thin">
-        <color rgb="001E2D3D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001E2D3D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="006B3FA0"/>
-      </left>
-      <right style="thin">
-        <color rgb="001E2D3D"/>
-      </right>
-      <top style="thin">
-        <color rgb="001E2D3D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001E2D3D"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -589,202 +356,25 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="27" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="33" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,86 +483,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>15</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8667750" cy="3238500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4667250" cy="4381500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5334000" cy="3714750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1032,7 +542,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8001000" cy="2571750"/>
+    <ext cx="6667500" cy="2476500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1057,7 +567,7 @@
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="2476500"/>
+    <ext cx="7334250" cy="2952750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1065,31 +575,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>75</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7334250" cy="2952750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1139,160 +624,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6667500" cy="2857500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7334250" cy="2952750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9334500" cy="5715000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6667500" cy="2857500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6667500" cy="5524500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="10668000" cy="3810000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2129,1227 +1464,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Portfolio Weights — All Construction Methods (%)</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="6" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>60/40</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>MVO</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Risk Parity</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Enhanced HRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C3" s="54" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>1.540461442864476e-08</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.04239826333589958</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0.01418954230934599</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C4" s="55" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>1.28614030174759e-08</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>0.03838122897153512</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>0.01071962159834465</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C5" s="54" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>1.034391881227816e-08</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.03705345539751015</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.01785691413064644</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C6" s="55" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.07113737017120601</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0.03526861812925119</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.01018151128031413</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C7" s="54" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="D7" s="54" t="n">
-        <v>0.2963200956729806</v>
-      </c>
-      <c r="E7" s="54" t="n">
-        <v>0.1901058368842273</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.05965965579571525</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C8" s="55" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>9.201563042783877e-09</v>
-      </c>
-      <c r="E8" s="55" t="n">
-        <v>0.1561033628963286</v>
-      </c>
-      <c r="F8" s="55" t="n">
-        <v>0.3316397889964035</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C9" s="54" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>8.935098891791349e-09</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0989198915904857</v>
-      </c>
-      <c r="F9" s="54" t="n">
-        <v>0.1092060125556165</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C10" s="55" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D10" s="55" t="n">
-        <v>0.1364634563400886</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0.03310675547563253</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0.009319148736044234</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>2.096350346927755e-08</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0.05454871770404718</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0.01805983719241162</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="55" t="n">
-        <v>0.1960790013757557</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0.07131481416206895</v>
-      </c>
-      <c r="F12" s="55" t="n">
-        <v>0.1483922296615783</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>1.618598447722783e-09</v>
-      </c>
-      <c r="E13" s="54" t="n">
-        <v>0.1147079339070491</v>
-      </c>
-      <c r="F13" s="54" t="n">
-        <v>0.2280024325953267</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="55" t="n">
-        <v>0.2822620050016614</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>0.06079007889478735</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0.02821942763967994</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0.01773799210960737</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.06730104265117719</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0.01455387750857303</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J86"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>FACTOR-LOADING CLUSTER ANALYSIS — ENHANCED HRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Ward linkage on z-scored factor betas  |  5-Factor Model  |  13 Asset Classes  |  Euclidean distance in standardised beta space  |  2004 Q4 to 2024 Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="56" t="inlineStr">
-        <is>
-          <t>5-CLUSTER SOLUTION — ECONOMIC INTERPRETATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="57" t="inlineStr">
-        <is>
-          <t>CLUSTER 1</t>
-        </is>
-      </c>
-      <c r="D5" s="58" t="inlineStr">
-        <is>
-          <t>CLUSTER 2</t>
-        </is>
-      </c>
-      <c r="F5" s="59" t="inlineStr">
-        <is>
-          <t>CLUSTER 3</t>
-        </is>
-      </c>
-      <c r="H5" s="60" t="inlineStr">
-        <is>
-          <t>CLUSTER 4</t>
-        </is>
-      </c>
-      <c r="J5" s="61" t="inlineStr">
-        <is>
-          <t>CLUSTER 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="B6" s="62" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="D6" s="63" t="inlineStr">
-        <is>
-          <t>Pure Rate Duration</t>
-        </is>
-      </c>
-      <c r="F6" s="64" t="inlineStr">
-        <is>
-          <t>Inflation Hedge</t>
-        </is>
-      </c>
-      <c r="H6" s="65" t="inlineStr">
-        <is>
-          <t>Domestic Equity Beta</t>
-        </is>
-      </c>
-      <c r="J6" s="66" t="inlineStr">
-        <is>
-          <t>Credit-Sensitive Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="B7" s="67" t="inlineStr">
-        <is>
-          <t>Dominant: Equity Premium</t>
-        </is>
-      </c>
-      <c r="D7" s="67" t="inlineStr">
-        <is>
-          <t>Dominant: Term Premium</t>
-        </is>
-      </c>
-      <c r="F7" s="67" t="inlineStr">
-        <is>
-          <t>Dominant: Inflation</t>
-        </is>
-      </c>
-      <c r="H7" s="67" t="inlineStr">
-        <is>
-          <t>Dominant: Equity Premium</t>
-        </is>
-      </c>
-      <c r="J7" s="67" t="inlineStr">
-        <is>
-          <t>Dominant: Credit Spread</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="B8" s="68" t="inlineStr">
-        <is>
-          <t>TIPS
-Investment Grade Credit
-High Yield Credit
-Hedge Funds
-Private Equity
-Private Real Estate</t>
-        </is>
-      </c>
-      <c r="D8" s="68" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="F8" s="68" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="H8" s="68" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity
-US Mid Cap Equity
-US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="J8" s="68" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity
-REITs</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="B9" s="69" t="inlineStr">
-        <is>
-          <t>Low equity beta complex. Credit and alternative assets sharing below-average equity exposure.</t>
-        </is>
-      </c>
-      <c r="D9" s="69" t="inlineStr">
-        <is>
-          <t>Positive term premium, negative equity beta. Sole rate hedge in universe.</t>
-        </is>
-      </c>
-      <c r="F9" s="69" t="inlineStr">
-        <is>
-          <t>Dominant inflation beta. Real commodity dynamics orthogonal to equity and credit.</t>
-        </is>
-      </c>
-      <c r="H9" s="69" t="inlineStr">
-        <is>
-          <t>High positive equity loading across all three size segments. Essentially same systematic risk.</t>
-        </is>
-      </c>
-      <c r="J9" s="69" t="inlineStr">
-        <is>
-          <t>High credit spread sensitivity, strongly negative liquidity beta. Seizes during credit stress.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="70" t="inlineStr">
-        <is>
-          <t>ERP:  -0.66</t>
-        </is>
-      </c>
-      <c r="D10" s="70" t="inlineStr">
-        <is>
-          <t>ERP:  -1.01</t>
-        </is>
-      </c>
-      <c r="F10" s="70" t="inlineStr">
-        <is>
-          <t>ERP:  -1.03</t>
-        </is>
-      </c>
-      <c r="H10" s="71" t="inlineStr">
-        <is>
-          <t>ERP:  +1.33</t>
-        </is>
-      </c>
-      <c r="J10" s="71" t="inlineStr">
-        <is>
-          <t>ERP:  +1.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="72" t="inlineStr">
-        <is>
-          <t>TERM:  +0.11</t>
-        </is>
-      </c>
-      <c r="D11" s="71" t="inlineStr">
-        <is>
-          <t>TERM:  +2.58</t>
-        </is>
-      </c>
-      <c r="F11" s="70" t="inlineStr">
-        <is>
-          <t>TERM:  -1.56</t>
-        </is>
-      </c>
-      <c r="H11" s="70" t="inlineStr">
-        <is>
-          <t>TERM:  -0.75</t>
-        </is>
-      </c>
-      <c r="J11" s="72" t="inlineStr">
-        <is>
-          <t>TERM:  +0.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="B12" s="72" t="inlineStr">
-        <is>
-          <t>CREDIT:  -0.45</t>
-        </is>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>CREDIT:  -0.83</t>
-        </is>
-      </c>
-      <c r="F12" s="71" t="inlineStr">
-        <is>
-          <t>CREDIT:  +0.98</t>
-        </is>
-      </c>
-      <c r="H12" s="72" t="inlineStr">
-        <is>
-          <t>CREDIT:  -0.43</t>
-        </is>
-      </c>
-      <c r="J12" s="71" t="inlineStr">
-        <is>
-          <t>CREDIT:  +1.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>INFL:  +0.28</t>
-        </is>
-      </c>
-      <c r="D13" s="70" t="inlineStr">
-        <is>
-          <t>INFL:  -0.87</t>
-        </is>
-      </c>
-      <c r="F13" s="71" t="inlineStr">
-        <is>
-          <t>INFL:  +2.06</t>
-        </is>
-      </c>
-      <c r="H13" s="70" t="inlineStr">
-        <is>
-          <t>INFL:  -0.50</t>
-        </is>
-      </c>
-      <c r="J13" s="70" t="inlineStr">
-        <is>
-          <t>INFL:  -0.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>LIQ:  +0.49</t>
-        </is>
-      </c>
-      <c r="D14" s="72" t="inlineStr">
-        <is>
-          <t>LIQ:  -0.22</t>
-        </is>
-      </c>
-      <c r="F14" s="71" t="inlineStr">
-        <is>
-          <t>LIQ:  +0.86</t>
-        </is>
-      </c>
-      <c r="H14" s="72" t="inlineStr">
-        <is>
-          <t>LIQ:  -0.03</t>
-        </is>
-      </c>
-      <c r="J14" s="70" t="inlineStr">
-        <is>
-          <t>LIQ:  -1.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="12" customHeight="1"/>
-    <row r="70" ht="20" customHeight="1">
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>FULL ASSET DETAIL — CLUSTER ASSIGNMENT AND STANDARDISED BETAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Cl.</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Cluster Name</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>ERP (z)</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>Term (z)</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Credit (z)</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Inflation (z)</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Liquidity (z)</t>
-        </is>
-      </c>
-      <c r="I71" s="7" t="inlineStr">
-        <is>
-          <t>R-Sq</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="B72" s="73" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="C72" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="75" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E72" s="76" t="n">
-        <v>-0.269</v>
-      </c>
-      <c r="F72" s="76" t="n">
-        <v>-0.644</v>
-      </c>
-      <c r="G72" s="76" t="n">
-        <v>-0.231</v>
-      </c>
-      <c r="H72" s="76" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="I72" s="77" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="J72" s="78" t="n">
-        <v>0.447295652178046</v>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="B73" s="79" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="C73" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" s="80" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E73" s="81" t="n">
-        <v>-0.436</v>
-      </c>
-      <c r="F73" s="77" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="G73" s="81" t="n">
-        <v>-0.6870000000000001</v>
-      </c>
-      <c r="H73" s="81" t="n">
-        <v>-0.546</v>
-      </c>
-      <c r="I73" s="81" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J73" s="28" t="n">
-        <v>0.6374629953920316</v>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="B74" s="73" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C74" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" s="75" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E74" s="76" t="n">
-        <v>-0.456</v>
-      </c>
-      <c r="F74" s="76" t="n">
-        <v>-0.499</v>
-      </c>
-      <c r="G74" s="76" t="n">
-        <v>-0.677</v>
-      </c>
-      <c r="H74" s="76" t="n">
-        <v>-0.192</v>
-      </c>
-      <c r="I74" s="76" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="J74" s="82" t="n">
-        <v>0.7443129475785015</v>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="B75" s="79" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="C75" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="80" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E75" s="81" t="n">
-        <v>-0.578</v>
-      </c>
-      <c r="F75" s="81" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="G75" s="81" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H75" s="81" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="I75" s="83" t="n">
-        <v>2.197</v>
-      </c>
-      <c r="J75" s="16" t="n">
-        <v>0.8431315161474411</v>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="B76" s="73" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="C76" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="75" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E76" s="84" t="n">
-        <v>-1.027</v>
-      </c>
-      <c r="F76" s="76" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G76" s="84" t="n">
-        <v>-0.819</v>
-      </c>
-      <c r="H76" s="76" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="I76" s="76" t="n">
-        <v>-0.193</v>
-      </c>
-      <c r="J76" s="82" t="n">
-        <v>0.8015086616077466</v>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="79" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="C77" s="74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="80" t="inlineStr">
-        <is>
-          <t>Yield-Seeking Diversifiers</t>
-        </is>
-      </c>
-      <c r="E77" s="84" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="F77" s="81" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G77" s="81" t="n">
-        <v>-0.771</v>
-      </c>
-      <c r="H77" s="83" t="n">
-        <v>1.641</v>
-      </c>
-      <c r="I77" s="81" t="n">
-        <v>-0.104</v>
-      </c>
-      <c r="J77" s="38" t="n">
-        <v>0.08716459731266069</v>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="B78" s="85" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="C78" s="86" t="n">
-        <v>2</v>
-      </c>
-      <c r="D78" s="87" t="inlineStr">
-        <is>
-          <t>Pure Rate Duration</t>
-        </is>
-      </c>
-      <c r="E78" s="84" t="n">
-        <v>-1.014</v>
-      </c>
-      <c r="F78" s="83" t="n">
-        <v>2.582</v>
-      </c>
-      <c r="G78" s="84" t="n">
-        <v>-0.834</v>
-      </c>
-      <c r="H78" s="84" t="n">
-        <v>-0.867</v>
-      </c>
-      <c r="I78" s="76" t="n">
-        <v>-0.221</v>
-      </c>
-      <c r="J78" s="82" t="n">
-        <v>0.9812439847251684</v>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="B79" s="88" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="C79" s="89" t="n">
-        <v>3</v>
-      </c>
-      <c r="D79" s="90" t="inlineStr">
-        <is>
-          <t>Inflation Hedge</t>
-        </is>
-      </c>
-      <c r="E79" s="84" t="n">
-        <v>-1.034</v>
-      </c>
-      <c r="F79" s="91" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="G79" s="77" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="H79" s="83" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I79" s="77" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="J79" s="28" t="n">
-        <v>0.4370483747153048</v>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="B80" s="92" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="C80" s="93" t="n">
-        <v>4</v>
-      </c>
-      <c r="D80" s="94" t="inlineStr">
-        <is>
-          <t>Domestic Equity Beta</t>
-        </is>
-      </c>
-      <c r="E80" s="83" t="n">
-        <v>1.666</v>
-      </c>
-      <c r="F80" s="84" t="n">
-        <v>-1.037</v>
-      </c>
-      <c r="G80" s="76" t="n">
-        <v>-0.531</v>
-      </c>
-      <c r="H80" s="84" t="n">
-        <v>-0.853</v>
-      </c>
-      <c r="I80" s="76" t="n">
-        <v>-0.317</v>
-      </c>
-      <c r="J80" s="82" t="n">
-        <v>0.8712833012703342</v>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="B81" s="95" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="C81" s="93" t="n">
-        <v>4</v>
-      </c>
-      <c r="D81" s="96" t="inlineStr">
-        <is>
-          <t>Domestic Equity Beta</t>
-        </is>
-      </c>
-      <c r="E81" s="77" t="n">
-        <v>1.174</v>
-      </c>
-      <c r="F81" s="81" t="n">
-        <v>-0.672</v>
-      </c>
-      <c r="G81" s="81" t="n">
-        <v>-0.304</v>
-      </c>
-      <c r="H81" s="81" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I81" s="81" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="J81" s="16" t="n">
-        <v>0.9123635173053706</v>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="B82" s="92" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="C82" s="93" t="n">
-        <v>4</v>
-      </c>
-      <c r="D82" s="94" t="inlineStr">
-        <is>
-          <t>Domestic Equity Beta</t>
-        </is>
-      </c>
-      <c r="E82" s="77" t="n">
-        <v>1.153</v>
-      </c>
-      <c r="F82" s="76" t="n">
-        <v>-0.529</v>
-      </c>
-      <c r="G82" s="76" t="n">
-        <v>-0.443</v>
-      </c>
-      <c r="H82" s="76" t="n">
-        <v>-0.458</v>
-      </c>
-      <c r="I82" s="76" t="n">
-        <v>-0.192</v>
-      </c>
-      <c r="J82" s="82" t="n">
-        <v>0.9906918940400172</v>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="B83" s="97" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C83" s="98" t="n">
-        <v>5</v>
-      </c>
-      <c r="D83" s="99" t="inlineStr">
-        <is>
-          <t>Credit-Sensitive Equity</t>
-        </is>
-      </c>
-      <c r="E83" s="83" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="F83" s="81" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="G83" s="83" t="n">
-        <v>2.588</v>
-      </c>
-      <c r="H83" s="91" t="n">
-        <v>-1.859</v>
-      </c>
-      <c r="I83" s="91" t="n">
-        <v>-2.023</v>
-      </c>
-      <c r="J83" s="28" t="n">
-        <v>0.6337080092805774</v>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="B84" s="100" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C84" s="98" t="n">
-        <v>5</v>
-      </c>
-      <c r="D84" s="101" t="inlineStr">
-        <is>
-          <t>Credit-Sensitive Equity</t>
-        </is>
-      </c>
-      <c r="E84" s="76" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="F84" s="76" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="G84" s="83" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H84" s="76" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="I84" s="91" t="n">
-        <v>-1.452</v>
-      </c>
-      <c r="J84" s="78" t="n">
-        <v>0.6355398384728477</v>
-      </c>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="B86" s="102" t="inlineStr">
-        <is>
-          <t>Green = positive factor tilt  |  Red = negative factor tilt  |  Bold = strong tilt (|z| &gt; 1.2)  |  R-sq: green &gt;= 0.70, amber &gt;= 0.40, red &lt; 0.40</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B70:J70"/>
-    <mergeCell ref="B2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3607,7 +1721,7 @@
         <v>0.03956381298337185</v>
       </c>
       <c r="C31" s="28" t="n">
-        <v>0.3846153846153845</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
@@ -3643,7 +1757,7 @@
         <v>0.05566283756079447</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>0.6755292397488625</v>
+        <v>0.6755292397488624</v>
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
@@ -3661,7 +1775,7 @@
         <v>0.05681108284766658</v>
       </c>
       <c r="C34" s="30" t="n">
-        <v>0.4482051204330189</v>
+        <v>0.448205120433019</v>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
@@ -3729,16 +1843,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -3830,7 +1944,7 @@
       <c r="G3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="16" t="n">
+      <c r="H3" s="9" t="n">
         <v>0.9906918940400172</v>
       </c>
       <c r="I3" s="19" t="inlineStr">
@@ -3863,7 +1977,7 @@
       <c r="G4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="17" t="n">
+      <c r="H4" s="12" t="n">
         <v>0.9123635173053706</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
@@ -3896,7 +2010,7 @@
       <c r="G5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="9" t="n">
         <v>0.8712833012703342</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
@@ -3929,7 +2043,7 @@
       <c r="G6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="37" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.6355398384728477</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -3962,7 +2076,7 @@
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="9" t="n">
         <v>0.9812439847251684</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -3995,7 +2109,7 @@
       <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="12" t="n">
         <v>0.8015086616077466</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -4028,7 +2142,7 @@
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.6374629953920316</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -4061,7 +2175,7 @@
       <c r="G10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="37" t="n">
+      <c r="H10" s="12" t="n">
         <v>0.6337080092805774</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -4094,7 +2208,7 @@
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="9" t="n">
         <v>0.4370483747153048</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
@@ -4127,7 +2241,7 @@
       <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.8431315161474411</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -4160,7 +2274,7 @@
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="9" t="n">
         <v>0.7443129475785015</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
@@ -4193,7 +2307,7 @@
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="37" t="n">
+      <c r="H14" s="12" t="n">
         <v>0.447295652178046</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -4226,7 +2340,7 @@
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="38" t="n">
+      <c r="H15" s="9" t="n">
         <v>0.08716459731266069</v>
       </c>
       <c r="I15" s="19" t="inlineStr">
@@ -4235,7 +2349,6 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="8" customHeight="1"/>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
@@ -4286,7 +2399,7 @@
       <c r="C19" s="35" t="n">
         <v>0.6128143614867044</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="35" t="n">
         <v>0.5962399756475114</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -4307,7 +2420,7 @@
       <c r="C20" s="36" t="n">
         <v>0.1943926134830142</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="36" t="n">
         <v>0.2366498298763176</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -4328,7 +2441,7 @@
       <c r="C21" s="35" t="n">
         <v>0.2968736681280802</v>
       </c>
-      <c r="D21" s="41" t="n">
+      <c r="D21" s="35" t="n">
         <v>0.08296277865812401</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -4349,7 +2462,7 @@
       <c r="C22" s="36" t="n">
         <v>0.1007620091545411</v>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="36" t="n">
         <v>0.08131372477304566</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -4547,74 +2660,9 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Alpha vs. Beta Decomposition — Private Assets (Post-Unsmoothing)</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="n"/>
-      <c r="C59" s="5" t="n"/>
-      <c r="D59" s="5" t="n"/>
-      <c r="E59" s="5" t="n"/>
-      <c r="F59" s="5" t="n"/>
-      <c r="G59" s="5" t="n"/>
-      <c r="H59" s="6" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>OLS Alpha (qtly)</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Multi-Factor Beta Ret</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Equity Beta Contrib</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>True Alpha (ex-all β)</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Alpha vs Equity-Only</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>R-Squared</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="44" customHeight="1">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>Decomposition: OLS regression → Asset Return = α + Σ(β_f × Factor_f) + ε.  Multi-Factor Beta Ret = Σ(β_f × mean_ann_factor_ret) across all 5 factors.  True Alpha (ex-all β) = annualised OLS intercept — the return unexplained by any systematic factor.  Alpha vs Equity-Only strips only equity beta, retaining other factor contributions.  Low R² assets use smoothed/stale prices; beta estimates are understated → alpha overstated.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4628,1542 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Look-Through Net Factor Exposure — Portfolio Weight × Asset Beta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="6" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Portfolio / Asset</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Equity Premium</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Term Premium</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Credit Spread</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Liquidity</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Eff. Equity Weight*</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>▶ Equal Weight</t>
-        </is>
-      </c>
-      <c r="B3" s="44" t="n">
-        <v>0.4636952933150727</v>
-      </c>
-      <c r="C3" s="44" t="n">
-        <v>0.213020599450317</v>
-      </c>
-      <c r="D3" s="44" t="n">
-        <v>2.153964607978919</v>
-      </c>
-      <c r="E3" s="44" t="n">
-        <v>3.246662089897636</v>
-      </c>
-      <c r="F3" s="44" t="n">
-        <v>0.007778258572596223</v>
-      </c>
-      <c r="G3" s="44" t="n">
-        <v>0.4636952933150727</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="n">
-        <v>0.07403878775852514</v>
-      </c>
-      <c r="C4" s="35" t="n">
-        <v>0.00180427438150007</v>
-      </c>
-      <c r="D4" s="35" t="n">
-        <v>0.07093584927477356</v>
-      </c>
-      <c r="E4" s="35" t="n">
-        <v>0.03073948051943571</v>
-      </c>
-      <c r="F4" s="35" t="n">
-        <v>-0.0004503452583190418</v>
-      </c>
-      <c r="G4" s="35" t="n">
-        <v>0.07403878775852514</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="n">
-        <v>0.07471956059952081</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>-0.002147669117705375</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0.100583697793793</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>0.1592094495295858</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0.00282578027718488</v>
-      </c>
-      <c r="G5" s="35" t="n">
-        <v>0.07471956059952081</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B6" s="35" t="n">
-        <v>0.09107921505196977</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>-0.01223212339519365</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0.05207208148019239</v>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>-0.1579100089594087</v>
-      </c>
-      <c r="F6" s="35" t="n">
-        <v>-0.001135782356027629</v>
-      </c>
-      <c r="G6" s="35" t="n">
-        <v>0.09107921505196977</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B7" s="35" t="n">
-        <v>0.05793998179611365</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>0.01840006257521074</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>0.4373518115838773</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>0.4843300517660501</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>-0.007351226500741334</v>
-      </c>
-      <c r="G7" s="35" t="n">
-        <v>0.05793998179611365</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B8" s="35" t="n">
-        <v>0.001940192808216169</v>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>0.08763309682228183</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>-0.01275396379018057</v>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>-0.1642982951692203</v>
-      </c>
-      <c r="F8" s="35" t="n">
-        <v>-0.0006100396043361612</v>
-      </c>
-      <c r="G8" s="35" t="n">
-        <v>0.001940192808216169</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TIPS</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="n">
-        <v>0.001496021875499648</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0.03430682618143567</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>-0.009620129788801583</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>0.4939748476692092</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>-0.0004601440200529026</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>0.001496021875499648</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B10" s="35" t="n">
-        <v>0.02116118687990367</v>
-      </c>
-      <c r="C10" s="35" t="n">
-        <v>0.03952270308254837</v>
-      </c>
-      <c r="D10" s="35" t="n">
-        <v>0.0186916499396817</v>
-      </c>
-      <c r="E10" s="35" t="n">
-        <v>-0.0112082962152993</v>
-      </c>
-      <c r="F10" s="35" t="n">
-        <v>0.0008940472876653939</v>
-      </c>
-      <c r="G10" s="35" t="n">
-        <v>0.02116118687990367</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REITs</t>
-        </is>
-      </c>
-      <c r="B11" s="35" t="n">
-        <v>0.07962387225980534</v>
-      </c>
-      <c r="C11" s="35" t="n">
-        <v>0.03026901533646833</v>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>0.7194170473650355</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>-0.6384334180656998</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>-0.01047777702569616</v>
-      </c>
-      <c r="G11" s="35" t="n">
-        <v>0.07962387225980534</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Commodities</t>
-        </is>
-      </c>
-      <c r="B12" s="35" t="n">
-        <v>0.001274952756861006</v>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>-0.02665252496466946</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0.3756607454935698</v>
-      </c>
-      <c r="E12" s="35" t="n">
-        <v>1.233758378177399</v>
-      </c>
-      <c r="F12" s="35" t="n">
-        <v>0.005333431276415429</v>
-      </c>
-      <c r="G12" s="35" t="n">
-        <v>0.001274952756861006</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="n">
-        <v>0.01645468380538125</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0.02144193770326859</v>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>0.2640229734580977</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>0.2806069089651869</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>0.01262858142878224</v>
-      </c>
-      <c r="G13" s="35" t="n">
-        <v>0.01645468380538125</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B14" s="35" t="n">
-        <v>0.02048165600204704</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0.002625391317633685</v>
-      </c>
-      <c r="D14" s="35" t="n">
-        <v>0.0207478841600482</v>
-      </c>
-      <c r="E14" s="35" t="n">
-        <v>0.1581343017894302</v>
-      </c>
-      <c r="F14" s="35" t="n">
-        <v>0.0009923997944508265</v>
-      </c>
-      <c r="G14" s="35" t="n">
-        <v>0.02048165600204704</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Equity</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n">
-        <v>0.02673573682840642</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>-0.001376518122086951</v>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>0.1162075512841499</v>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>0.3442151471174809</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>0.00555836677698877</v>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>0.02673573682840642</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="n">
-        <v>-0.003250555107177185</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0.01942612764962522</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0.0006474097246812393</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>1.033543542773486</v>
-      </c>
-      <c r="F16" s="35" t="n">
-        <v>3.096649628191261e-05</v>
-      </c>
-      <c r="G16" s="35" t="n">
-        <v>-0.003250555107177185</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>▶ 60/40</t>
-        </is>
-      </c>
-      <c r="B17" s="44" t="n">
-        <v>0.6313817072904651</v>
-      </c>
-      <c r="C17" s="44" t="n">
-        <v>0.3361745051400978</v>
-      </c>
-      <c r="D17" s="44" t="n">
-        <v>2.146979458188246</v>
-      </c>
-      <c r="E17" s="44" t="n">
-        <v>0.3615911096991378</v>
-      </c>
-      <c r="F17" s="44" t="n">
-        <v>-0.02618469033086924</v>
-      </c>
-      <c r="G17" s="44" t="n">
-        <v>0.6313817072904651</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="n">
-        <v>0.1155005089032992</v>
-      </c>
-      <c r="C18" s="35" t="n">
-        <v>0.002814668035140108</v>
-      </c>
-      <c r="D18" s="35" t="n">
-        <v>0.1106599248686467</v>
-      </c>
-      <c r="E18" s="35" t="n">
-        <v>0.04795358961031969</v>
-      </c>
-      <c r="F18" s="35" t="n">
-        <v>-0.0007025386029777049</v>
-      </c>
-      <c r="G18" s="35" t="n">
-        <v>0.1155005089032992</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="n">
-        <v>0.1165625145352524</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>-0.003350363823620385</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>0.156910568558317</v>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>0.2483667412661538</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>0.004408217232408411</v>
-      </c>
-      <c r="G19" s="35" t="n">
-        <v>0.1165625145352524</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B20" s="35" t="n">
-        <v>0.1420835754810728</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>-0.01908211249650209</v>
-      </c>
-      <c r="D20" s="35" t="n">
-        <v>0.08123244710910009</v>
-      </c>
-      <c r="E20" s="35" t="n">
-        <v>-0.2463396139766775</v>
-      </c>
-      <c r="F20" s="35" t="n">
-        <v>-0.001771820475403101</v>
-      </c>
-      <c r="G20" s="35" t="n">
-        <v>0.1420835754810728</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="n">
-        <v>0.09038637160193727</v>
-      </c>
-      <c r="C21" s="35" t="n">
-        <v>0.02870409761732875</v>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>0.6822688260708484</v>
-      </c>
-      <c r="E21" s="35" t="n">
-        <v>0.755554880755038</v>
-      </c>
-      <c r="F21" s="35" t="n">
-        <v>-0.01146791334115648</v>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>0.09038637160193727</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B22" s="35" t="n">
-        <v>0.003363000867574693</v>
-      </c>
-      <c r="C22" s="35" t="n">
-        <v>0.1518973678252885</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>-0.02210687056964632</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>-0.2847837116266485</v>
-      </c>
-      <c r="F22" s="35" t="n">
-        <v>-0.001057401980849346</v>
-      </c>
-      <c r="G22" s="35" t="n">
-        <v>0.003363000867574693</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TIPS</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n">
-        <v>0.002593104584199389</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.05946516538115514</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>-0.01667489163392274</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>0.8562230692932956</v>
-      </c>
-      <c r="F23" s="35" t="n">
-        <v>-0.0007975829680916976</v>
-      </c>
-      <c r="G23" s="35" t="n">
-        <v>0.002593104584199389</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="n">
-        <v>0.03667939059183301</v>
-      </c>
-      <c r="C24" s="35" t="n">
-        <v>0.06850601867641715</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>0.03239885989544827</v>
-      </c>
-      <c r="E24" s="35" t="n">
-        <v>-0.01942771343985211</v>
-      </c>
-      <c r="F24" s="35" t="n">
-        <v>0.001549681965286682</v>
-      </c>
-      <c r="G24" s="35" t="n">
-        <v>0.03667939059183301</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REITs</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="n">
-        <v>0.1242132407252963</v>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>0.04721966392489058</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>1.122290593889455</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>-0.9959561321824913</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>-0.016345332160086</v>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>0.1242132407252963</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>▶ MVO</t>
-        </is>
-      </c>
-      <c r="B26" s="44" t="n">
-        <v>0.341608936545249</v>
-      </c>
-      <c r="C26" s="44" t="n">
-        <v>0.4623755448547909</v>
-      </c>
-      <c r="D26" s="44" t="n">
-        <v>2.731154020882956</v>
-      </c>
-      <c r="E26" s="44" t="n">
-        <v>0.8990702173393043</v>
-      </c>
-      <c r="F26" s="44" t="n">
-        <v>0.02485752388917012</v>
-      </c>
-      <c r="G26" s="44" t="n">
-        <v>0.341608936545249</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B27" s="35" t="n">
-        <v>0.05358207312565996</v>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0.01701611681361957</v>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>0.4044567503039676</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>0.4479015603077713</v>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>-0.006798309970343003</v>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>0.05358207312565996</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B28" s="35" t="n">
-        <v>0.007473935541210374</v>
-      </c>
-      <c r="C28" s="35" t="n">
-        <v>0.3375768192484756</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>-0.04913032501670847</v>
-      </c>
-      <c r="E28" s="35" t="n">
-        <v>-0.6329035250648625</v>
-      </c>
-      <c r="F28" s="35" t="n">
-        <v>-0.00234997092097558</v>
-      </c>
-      <c r="G28" s="35" t="n">
-        <v>0.007473935541210374</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REITs</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n">
-        <v>0.1412547346048116</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0.05369798788673304</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>1.276263778834382</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>-1.132596801339408</v>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>-0.01858783767993452</v>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>0.1412547346048116</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B30" s="35" t="n">
-        <v>0.04194343359066868</v>
-      </c>
-      <c r="C30" s="35" t="n">
-        <v>0.05465607852143489</v>
-      </c>
-      <c r="D30" s="35" t="n">
-        <v>0.673001692686979</v>
-      </c>
-      <c r="E30" s="35" t="n">
-        <v>0.7152745923574088</v>
-      </c>
-      <c r="F30" s="35" t="n">
-        <v>0.03219059525952447</v>
-      </c>
-      <c r="G30" s="35" t="n">
-        <v>0.04194343359066868</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n">
-        <v>0.09810427487097582</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>-0.005051003945798</v>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>0.4264126934833681</v>
-      </c>
-      <c r="E31" s="35" t="n">
-        <v>1.263065148505186</v>
-      </c>
-      <c r="F31" s="35" t="n">
-        <v>0.02039590476309714</v>
-      </c>
-      <c r="G31" s="35" t="n">
-        <v>0.09810427487097582</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="n">
-        <v>-0.0007495581709583868</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>0.00447954648660061</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>0.0001492887316450257</v>
-      </c>
-      <c r="E32" s="35" t="n">
-        <v>0.2383288336864727</v>
-      </c>
-      <c r="F32" s="35" t="n">
-        <v>7.140685067239771e-06</v>
-      </c>
-      <c r="G32" s="35" t="n">
-        <v>-0.0007495581709583868</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>▶ Risk Parity</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="n">
-        <v>0.2828260983026298</v>
-      </c>
-      <c r="C33" s="44" t="n">
-        <v>0.3733154718690183</v>
-      </c>
-      <c r="D33" s="44" t="n">
-        <v>1.232021384742424</v>
-      </c>
-      <c r="E33" s="44" t="n">
-        <v>3.096735624978685</v>
-      </c>
-      <c r="F33" s="44" t="n">
-        <v>0.01283247003358824</v>
-      </c>
-      <c r="G33" s="44" t="n">
-        <v>0.2828260983026298</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B34" s="35" t="n">
-        <v>0.04080850826593745</v>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>0.0009944753046417449</v>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>0.0390982386275979</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>0.01694290766833327</v>
-      </c>
-      <c r="F34" s="35" t="n">
-        <v>-0.0002482201391056979</v>
-      </c>
-      <c r="G34" s="35" t="n">
-        <v>0.04080850826593745</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B35" s="35" t="n">
-        <v>0.03728177133229513</v>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>-0.001071592342102683</v>
-      </c>
-      <c r="D35" s="35" t="n">
-        <v>0.05018683716575439</v>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>0.07943850637875226</v>
-      </c>
-      <c r="F35" s="35" t="n">
-        <v>0.001409939957944451</v>
-      </c>
-      <c r="G35" s="35" t="n">
-        <v>0.03728177133229513</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B36" s="35" t="n">
-        <v>0.04387239522338916</v>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>-0.005892151702328428</v>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>0.02508285713156369</v>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>-0.07606444915937241</v>
-      </c>
-      <c r="F36" s="35" t="n">
-        <v>-0.0005471005913145337</v>
-      </c>
-      <c r="G36" s="35" t="n">
-        <v>0.04387239522338916</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B37" s="35" t="n">
-        <v>0.02656502020097767</v>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>0.008436282146752641</v>
-      </c>
-      <c r="D37" s="35" t="n">
-        <v>0.2005223224015438</v>
-      </c>
-      <c r="E37" s="35" t="n">
-        <v>0.2220614713753446</v>
-      </c>
-      <c r="F37" s="35" t="n">
-        <v>-0.003370478803071608</v>
-      </c>
-      <c r="G37" s="35" t="n">
-        <v>0.02656502020097767</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B38" s="35" t="n">
-        <v>0.004794945707795021</v>
-      </c>
-      <c r="C38" s="35" t="n">
-        <v>0.2165743217320333</v>
-      </c>
-      <c r="D38" s="35" t="n">
-        <v>-0.03151983847900431</v>
-      </c>
-      <c r="E38" s="35" t="n">
-        <v>-0.4060428437233534</v>
-      </c>
-      <c r="F38" s="35" t="n">
-        <v>-0.001507637163693034</v>
-      </c>
-      <c r="G38" s="35" t="n">
-        <v>0.004794945707795021</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TIPS</t>
-        </is>
-      </c>
-      <c r="B39" s="35" t="n">
-        <v>0.003035942594515579</v>
-      </c>
-      <c r="C39" s="35" t="n">
-        <v>0.06962034218388494</v>
-      </c>
-      <c r="D39" s="35" t="n">
-        <v>-0.01952254994990396</v>
-      </c>
-      <c r="E39" s="35" t="n">
-        <v>1.002444753795747</v>
-      </c>
-      <c r="F39" s="35" t="n">
-        <v>-0.0009337903763096187</v>
-      </c>
-      <c r="G39" s="35" t="n">
-        <v>0.003035942594515579</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B40" s="35" t="n">
-        <v>0.02721241005711902</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0.05082455955575231</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0.02403668781384809</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>-0.01441340480490895</v>
-      </c>
-      <c r="F40" s="35" t="n">
-        <v>0.001149707790044171</v>
-      </c>
-      <c r="G40" s="35" t="n">
-        <v>0.02721241005711902</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REITs</t>
-        </is>
-      </c>
-      <c r="B41" s="35" t="n">
-        <v>0.03426914489606889</v>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0.01302741556002416</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>0.3096283355375051</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>-0.2747739677718542</v>
-      </c>
-      <c r="F41" s="35" t="n">
-        <v>-0.004509507624933</v>
-      </c>
-      <c r="G41" s="35" t="n">
-        <v>0.03426914489606889</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Commodities</t>
-        </is>
-      </c>
-      <c r="B42" s="35" t="n">
-        <v>0.0009041114942601002</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>-0.01890019378517171</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>0.2663935554594685</v>
-      </c>
-      <c r="E42" s="35" t="n">
-        <v>0.8748991873206263</v>
-      </c>
-      <c r="F42" s="35" t="n">
-        <v>0.003782113882184576</v>
-      </c>
-      <c r="G42" s="35" t="n">
-        <v>0.0009041114942601002</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B43" s="35" t="n">
-        <v>0.0152550153297928</v>
-      </c>
-      <c r="C43" s="35" t="n">
-        <v>0.01987866143358236</v>
-      </c>
-      <c r="D43" s="35" t="n">
-        <v>0.2447737407268543</v>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>0.2601485843507838</v>
-      </c>
-      <c r="F43" s="35" t="n">
-        <v>0.01170786419041409</v>
-      </c>
-      <c r="G43" s="35" t="n">
-        <v>0.0152550153297928</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B44" s="35" t="n">
-        <v>0.03054230975886645</v>
-      </c>
-      <c r="C44" s="35" t="n">
-        <v>0.003914991778662447</v>
-      </c>
-      <c r="D44" s="35" t="n">
-        <v>0.03093931002424495</v>
-      </c>
-      <c r="E44" s="35" t="n">
-        <v>0.235810367495291</v>
-      </c>
-      <c r="F44" s="35" t="n">
-        <v>0.001479869690406048</v>
-      </c>
-      <c r="G44" s="35" t="n">
-        <v>0.03054230975886645</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Equity</t>
-        </is>
-      </c>
-      <c r="B45" s="35" t="n">
-        <v>0.02112847816441827</v>
-      </c>
-      <c r="C45" s="35" t="n">
-        <v>-0.001087822388143014</v>
-      </c>
-      <c r="D45" s="35" t="n">
-        <v>0.09183546073953576</v>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>0.2720232573506824</v>
-      </c>
-      <c r="F45" s="35" t="n">
-        <v>0.004392616213691058</v>
-      </c>
-      <c r="G45" s="35" t="n">
-        <v>0.02112847816441827</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B46" s="35" t="n">
-        <v>-0.002843954722805736</v>
-      </c>
-      <c r="C46" s="35" t="n">
-        <v>0.01699618239143031</v>
-      </c>
-      <c r="D46" s="35" t="n">
-        <v>0.0005664275434162665</v>
-      </c>
-      <c r="E46" s="35" t="n">
-        <v>0.9042612547026135</v>
-      </c>
-      <c r="F46" s="35" t="n">
-        <v>2.709300733134476e-05</v>
-      </c>
-      <c r="G46" s="35" t="n">
-        <v>-0.002843954722805736</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>▶ Enhanced HRP</t>
-        </is>
-      </c>
-      <c r="B47" s="44" t="n">
-        <v>0.2024684798488106</v>
-      </c>
-      <c r="C47" s="44" t="n">
-        <v>0.3213380633688087</v>
-      </c>
-      <c r="D47" s="44" t="n">
-        <v>0.8611775407280974</v>
-      </c>
-      <c r="E47" s="44" t="n">
-        <v>3.585820188471189</v>
-      </c>
-      <c r="F47" s="44" t="n">
-        <v>0.02721739711619322</v>
-      </c>
-      <c r="G47" s="44" t="n">
-        <v>0.2024684798488106</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B48" s="35" t="n">
-        <v>0.01365749464861964</v>
-      </c>
-      <c r="C48" s="35" t="n">
-        <v>0.0003328237597615358</v>
-      </c>
-      <c r="D48" s="35" t="n">
-        <v>0.01308511404893926</v>
-      </c>
-      <c r="E48" s="35" t="n">
-        <v>0.005670329072172044</v>
-      </c>
-      <c r="F48" s="35" t="n">
-        <v>-8.307251025750806e-05</v>
-      </c>
-      <c r="G48" s="35" t="n">
-        <v>0.01365749464861964</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B49" s="35" t="n">
-        <v>0.01041255040307878</v>
-      </c>
-      <c r="C49" s="35" t="n">
-        <v>-0.0002992886033832802</v>
-      </c>
-      <c r="D49" s="35" t="n">
-        <v>0.01401684933105228</v>
-      </c>
-      <c r="E49" s="35" t="n">
-        <v>0.02218664569989282</v>
-      </c>
-      <c r="F49" s="35" t="n">
-        <v>0.0003937868387893355</v>
-      </c>
-      <c r="G49" s="35" t="n">
-        <v>0.01041255040307878</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B50" s="35" t="n">
-        <v>0.02114311838950615</v>
-      </c>
-      <c r="C50" s="35" t="n">
-        <v>-0.002839563702344775</v>
-      </c>
-      <c r="D50" s="35" t="n">
-        <v>0.01208800693874565</v>
-      </c>
-      <c r="E50" s="35" t="n">
-        <v>-0.036657211114651</v>
-      </c>
-      <c r="F50" s="35" t="n">
-        <v>-0.0002636603840349526</v>
-      </c>
-      <c r="G50" s="35" t="n">
-        <v>0.02114311838950615</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B51" s="35" t="n">
-        <v>0.00766891551709824</v>
-      </c>
-      <c r="C51" s="35" t="n">
-        <v>0.002435425780683921</v>
-      </c>
-      <c r="D51" s="35" t="n">
-        <v>0.05788773124039183</v>
-      </c>
-      <c r="E51" s="35" t="n">
-        <v>0.06410575451086512</v>
-      </c>
-      <c r="F51" s="35" t="n">
-        <v>-0.0009730057420387463</v>
-      </c>
-      <c r="G51" s="35" t="n">
-        <v>0.00766891551709824</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B52" s="35" t="n">
-        <v>0.001504766056501484</v>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>0.06796608510548896</v>
-      </c>
-      <c r="D52" s="35" t="n">
-        <v>-0.009891662166791448</v>
-      </c>
-      <c r="E52" s="35" t="n">
-        <v>-0.1274257365890406</v>
-      </c>
-      <c r="F52" s="35" t="n">
-        <v>-0.0004731317866138459</v>
-      </c>
-      <c r="G52" s="35" t="n">
-        <v>0.001504766056501484</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TIPS</t>
-        </is>
-      </c>
-      <c r="B53" s="35" t="n">
-        <v>0.006449824928621189</v>
-      </c>
-      <c r="C53" s="35" t="n">
-        <v>0.147907611747319</v>
-      </c>
-      <c r="D53" s="35" t="n">
-        <v>-0.04147543157259023</v>
-      </c>
-      <c r="E53" s="35" t="n">
-        <v>2.129682285257111</v>
-      </c>
-      <c r="F53" s="35" t="n">
-        <v>-0.001983826854337919</v>
-      </c>
-      <c r="G53" s="35" t="n">
-        <v>0.006449824928621189</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B54" s="35" t="n">
-        <v>0.03004207492128056</v>
-      </c>
-      <c r="C54" s="35" t="n">
-        <v>0.05610951851784079</v>
-      </c>
-      <c r="D54" s="35" t="n">
-        <v>0.02653612725397487</v>
-      </c>
-      <c r="E54" s="35" t="n">
-        <v>-0.01591217338379556</v>
-      </c>
-      <c r="F54" s="35" t="n">
-        <v>0.001269259411187324</v>
-      </c>
-      <c r="G54" s="35" t="n">
-        <v>0.03004207492128056</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REITs</t>
-        </is>
-      </c>
-      <c r="B55" s="35" t="n">
-        <v>0.009646347210875858</v>
-      </c>
-      <c r="C55" s="35" t="n">
-        <v>0.003667058928183979</v>
-      </c>
-      <c r="D55" s="35" t="n">
-        <v>0.08715660807932706</v>
-      </c>
-      <c r="E55" s="35" t="n">
-        <v>-0.07734552775319972</v>
-      </c>
-      <c r="F55" s="35" t="n">
-        <v>-0.001269371512832405</v>
-      </c>
-      <c r="G55" s="35" t="n">
-        <v>0.009646347210875858</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Commodities</t>
-        </is>
-      </c>
-      <c r="B56" s="35" t="n">
-        <v>0.0002993307098200394</v>
-      </c>
-      <c r="C56" s="35" t="n">
-        <v>-0.006257423401172013</v>
-      </c>
-      <c r="D56" s="35" t="n">
-        <v>0.08819683474151997</v>
-      </c>
-      <c r="E56" s="35" t="n">
-        <v>0.2896591807805491</v>
-      </c>
-      <c r="F56" s="35" t="n">
-        <v>0.001252171706876723</v>
-      </c>
-      <c r="G56" s="35" t="n">
-        <v>0.0002993307098200394</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B57" s="35" t="n">
-        <v>0.03174271383733822</v>
-      </c>
-      <c r="C57" s="35" t="n">
-        <v>0.0413636202726849</v>
-      </c>
-      <c r="D57" s="35" t="n">
-        <v>0.5093264502732484</v>
-      </c>
-      <c r="E57" s="35" t="n">
-        <v>0.5413185034372386</v>
-      </c>
-      <c r="F57" s="35" t="n">
-        <v>0.02436178362383734</v>
-      </c>
-      <c r="G57" s="35" t="n">
-        <v>0.03174271383733822</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B58" s="35" t="n">
-        <v>0.06070827609661615</v>
-      </c>
-      <c r="C58" s="35" t="n">
-        <v>0.007781742890156688</v>
-      </c>
-      <c r="D58" s="35" t="n">
-        <v>0.06149738477606144</v>
-      </c>
-      <c r="E58" s="35" t="n">
-        <v>0.4687150713017967</v>
-      </c>
-      <c r="F58" s="35" t="n">
-        <v>0.002941504374144577</v>
-      </c>
-      <c r="G58" s="35" t="n">
-        <v>0.06070827609661615</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Equity</t>
-        </is>
-      </c>
-      <c r="B59" s="35" t="n">
-        <v>0.009808073480695628</v>
-      </c>
-      <c r="C59" s="35" t="n">
-        <v>-0.0005049791960322306</v>
-      </c>
-      <c r="D59" s="35" t="n">
-        <v>0.04263103760041701</v>
-      </c>
-      <c r="E59" s="35" t="n">
-        <v>0.1262762076753259</v>
-      </c>
-      <c r="F59" s="35" t="n">
-        <v>0.002039101077754461</v>
-      </c>
-      <c r="G59" s="35" t="n">
-        <v>0.009808073480695628</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B60" s="35" t="n">
-        <v>-0.0006150063512414017</v>
-      </c>
-      <c r="C60" s="35" t="n">
-        <v>0.003675431269621139</v>
-      </c>
-      <c r="D60" s="35" t="n">
-        <v>0.0001224901838013067</v>
-      </c>
-      <c r="E60" s="35" t="n">
-        <v>0.1955468595769251</v>
-      </c>
-      <c r="F60" s="35" t="n">
-        <v>5.858873718836295e-06</v>
-      </c>
-      <c r="G60" s="35" t="n">
-        <v>-0.0006150063512414017</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>* Effective Equity Weight = Σ(w_i × equity_beta_i). Example: 10% Private Equity with beta 0.85 contributes 0.085 to net equity exposure. A value &gt;1.0 implies leveraged equity risk.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6219,13 +2732,13 @@
           <t>Equal Weight</t>
         </is>
       </c>
-      <c r="B3" s="25" t="n">
+      <c r="B3" s="9" t="n">
         <v>-0.2929242982373964</v>
       </c>
-      <c r="C3" s="28" t="n">
+      <c r="C3" s="9" t="n">
         <v>-0.04460231281462567</v>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="9" t="n">
         <v>-0.1293955141254147</v>
       </c>
       <c r="E3" s="9" t="n">
@@ -6238,13 +2751,13 @@
           <t>60/40</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="12" t="n">
         <v>-0.2495980726306681</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>-0.003713565811961916</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="12" t="n">
         <v>-0.2018217141761193</v>
       </c>
       <c r="E4" s="12" t="n">
@@ -6257,13 +2770,13 @@
           <t>MVO</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="9" t="n">
         <v>-0.1830486748285108</v>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="9" t="n">
         <v>0.03683695337861526</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="9" t="n">
         <v>-0.1786484994678722</v>
       </c>
       <c r="E5" s="9" t="n">
@@ -6276,13 +2789,13 @@
           <t>Risk Parity</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="12" t="n">
         <v>-0.1665091655056802</v>
       </c>
-      <c r="C6" s="46" t="n">
+      <c r="C6" s="12" t="n">
         <v>0.01971956610044479</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="12" t="n">
         <v>-0.1449286097239181</v>
       </c>
       <c r="E6" s="12" t="n">
@@ -6295,316 +2808,28 @@
           <t>Enhanced HRP</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="9" t="n">
         <v>-0.1050506428004342</v>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="9" t="n">
         <v>0.02485925553436985</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="9" t="n">
         <v>-0.1166178609836621</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>0.3183738177155637</v>
       </c>
     </row>
-    <row r="8" ht="8" customHeight="1"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Asset Class Returns During Stress Periods</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="6" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>GFC (2008 Q3 - 2009 Q1)</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>COVID Crash (2020 Q1)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Rate Shock (2022)</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Recovery: 2009 Q2 – 2010 Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="n">
-        <v>-0.3812732359228665</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>-0.0357768153553959</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>-0.1947637579191616</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>0.7134011046475044</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>-0.3942462832612211</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>-0.127661491827292</v>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>-0.1310887392234659</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.9057860487413132</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="n">
-        <v>-0.3807755634480606</v>
-      </c>
-      <c r="C14" s="25" t="n">
-        <v>-0.1294762048774571</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>-0.2048479489290927</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.9033585817145788</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>-0.4438706402393807</v>
-      </c>
-      <c r="C15" s="30" t="n">
-        <v>-0.1035873392367445</v>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>-0.2056366502889209</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0.981405051156344</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="n">
-        <v>0.1798260602191641</v>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>0.2186897235323857</v>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>-0.3123453879657369</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-0.04290092630759501</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>-0.01709956820941072</v>
-      </c>
-      <c r="C17" s="46" t="n">
-        <v>0.06047075906415222</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>-0.1226253616456965</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>0.1166154176097747</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>-0.03177080884729011</v>
-      </c>
-      <c r="C18" s="31" t="n">
-        <v>0.06449381536800969</v>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>-0.1792166807482016</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.2675339675917277</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>-0.5589691261954142</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>-0.1386299596597343</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>-0.2625117017118432</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>1.459708377285921</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="n">
-        <v>-0.6638633149885664</v>
-      </c>
-      <c r="C20" s="25" t="n">
-        <v>-0.3602714083128871</v>
-      </c>
-      <c r="D20" s="31" t="n">
-        <v>0.2407947857928288</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.354249327277085</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>-0.201169630180515</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>-0.03833857046804878</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>-0.1118160673185818</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>0.7115653167449534</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="n">
-        <v>-0.1004406586565151</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>0.002594273657163138</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>-0.04182026216305001</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0.350297269953364</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>-0.2866446238219689</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>-0.02211708284419223</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>-0.02277795292382379</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>0.5667955118212424</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n">
-        <v>-0.4293500957413755</v>
-      </c>
-      <c r="C24" s="28" t="n">
-        <v>-0.08653790765277503</v>
-      </c>
-      <c r="D24" s="28" t="n">
-        <v>-0.1143057216822595</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>-0.08706019617653361</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:E10"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8298,216 +4523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Factor Performance Attribution — Brinson-Style Decomposition</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="n"/>
-      <c r="C1" s="5" t="n"/>
-      <c r="D1" s="5" t="n"/>
-      <c r="E1" s="5" t="n"/>
-      <c r="F1" s="5" t="n"/>
-      <c r="G1" s="6" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Realised Ann. Return (%)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>EW Attribution</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>60/40 Attribution</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>MVO Attribution</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Risk Parity Attrib.</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Enhanced HRP Attrib.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>Equity Premium</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
-        <v>0.09941505841052375</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>0.04609829466960289</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.06276884930961779</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.03396107238020283</v>
-      </c>
-      <c r="F3" s="9" t="n">
-        <v>0.02811717308277647</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>0.02012841575045946</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Term Premium</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="n">
-        <v>0.02704717288886098</v>
-      </c>
-      <c r="C4" s="12" t="n">
-        <v>0.005761604982221529</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>0.009092569961351507</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>0.01250595130126882</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>0.01009712810972805</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.008691286155707932</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>Credit Spread</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>0.0004345621141427859</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>0.0009360314138320559</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0.0009329959323714173</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.001186856065364468</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0.0005353898176227906</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0.0003742351327510871</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>Inflation</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>2.133767447615969e-05</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>6.927621880832407e-05</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>7.715513392233549e-06</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>1.918406762879622e-05</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>6.607713670452212e-05</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>7.651306391163982e-05</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Liquidity</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n">
-        <v>0.07299776705305443</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>0.0005677955073608027</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>-0.001911423925129159</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.001814543738377376</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0.0009367416582271762</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0.001986809214478348</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Alpha (Unexplained)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8553,667 +4569,667 @@
       <c r="N1" s="6" t="n"/>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="47" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="C2" s="47" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D2" s="37" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="E2" s="37" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="G2" s="37" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
+      <c r="H2" s="37" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="J2" s="37" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="K2" s="47" t="inlineStr">
+      <c r="K2" s="37" t="inlineStr">
         <is>
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="L2" s="47" t="inlineStr">
+      <c r="L2" s="37" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="M2" s="47" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="N2" s="47" t="inlineStr">
+      <c r="N2" s="37" t="inlineStr">
         <is>
           <t>Private Real Estate</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="49" t="n">
+      <c r="B3" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="n">
+      <c r="C3" s="40" t="n">
         <v>0.957</v>
       </c>
-      <c r="D3" s="50" t="n">
+      <c r="D3" s="40" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="E3" s="50" t="n">
+      <c r="E3" s="40" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="F3" s="51" t="n">
+      <c r="F3" s="41" t="n">
         <v>-0.345</v>
       </c>
-      <c r="G3" s="52" t="n">
+      <c r="G3" s="42" t="n">
         <v>0.204</v>
       </c>
-      <c r="H3" s="52" t="n">
+      <c r="H3" s="42" t="n">
         <v>0.302</v>
       </c>
-      <c r="I3" s="50" t="n">
+      <c r="I3" s="40" t="n">
         <v>0.753</v>
       </c>
-      <c r="J3" s="53" t="n">
+      <c r="J3" s="43" t="n">
         <v>0.476</v>
       </c>
-      <c r="K3" s="50" t="n">
+      <c r="K3" s="40" t="n">
         <v>0.732</v>
       </c>
-      <c r="L3" s="50" t="n">
+      <c r="L3" s="40" t="n">
         <v>0.877</v>
       </c>
-      <c r="M3" s="53" t="n">
+      <c r="M3" s="43" t="n">
         <v>0.621</v>
       </c>
-      <c r="N3" s="52" t="n">
+      <c r="N3" s="42" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="50" t="n">
+      <c r="B4" s="40" t="n">
         <v>0.957</v>
       </c>
-      <c r="C4" s="49" t="n">
+      <c r="C4" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="50" t="n">
+      <c r="D4" s="40" t="n">
         <v>0.956</v>
       </c>
-      <c r="E4" s="50" t="n">
+      <c r="E4" s="40" t="n">
         <v>0.78</v>
       </c>
-      <c r="F4" s="51" t="n">
+      <c r="F4" s="41" t="n">
         <v>-0.401</v>
       </c>
-      <c r="G4" s="52" t="n">
+      <c r="G4" s="42" t="n">
         <v>0.171</v>
       </c>
-      <c r="H4" s="52" t="n">
+      <c r="H4" s="42" t="n">
         <v>0.245</v>
       </c>
-      <c r="I4" s="50" t="n">
+      <c r="I4" s="40" t="n">
         <v>0.735</v>
       </c>
-      <c r="J4" s="53" t="n">
+      <c r="J4" s="43" t="n">
         <v>0.511</v>
       </c>
-      <c r="K4" s="50" t="n">
+      <c r="K4" s="40" t="n">
         <v>0.719</v>
       </c>
-      <c r="L4" s="50" t="n">
+      <c r="L4" s="40" t="n">
         <v>0.882</v>
       </c>
-      <c r="M4" s="53" t="n">
+      <c r="M4" s="43" t="n">
         <v>0.613</v>
       </c>
-      <c r="N4" s="52" t="n">
+      <c r="N4" s="42" t="n">
         <v>0.198</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="50" t="n">
+      <c r="B5" s="40" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="40" t="n">
         <v>0.956</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="40" t="n">
         <v>0.736</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="41" t="n">
         <v>-0.382</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="42" t="n">
         <v>0.099</v>
       </c>
-      <c r="H5" s="52" t="n">
+      <c r="H5" s="42" t="n">
         <v>0.224</v>
       </c>
-      <c r="I5" s="50" t="n">
+      <c r="I5" s="40" t="n">
         <v>0.74</v>
       </c>
-      <c r="J5" s="53" t="n">
+      <c r="J5" s="43" t="n">
         <v>0.438</v>
       </c>
-      <c r="K5" s="53" t="n">
+      <c r="K5" s="43" t="n">
         <v>0.673</v>
       </c>
-      <c r="L5" s="50" t="n">
+      <c r="L5" s="40" t="n">
         <v>0.838</v>
       </c>
-      <c r="M5" s="53" t="n">
+      <c r="M5" s="43" t="n">
         <v>0.58</v>
       </c>
-      <c r="N5" s="52" t="n">
+      <c r="N5" s="42" t="n">
         <v>0.163</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="48" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="40" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="40" t="n">
         <v>0.78</v>
       </c>
-      <c r="D6" s="50" t="n">
+      <c r="D6" s="40" t="n">
         <v>0.736</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="41" t="n">
         <v>-0.312</v>
       </c>
-      <c r="G6" s="52" t="n">
+      <c r="G6" s="42" t="n">
         <v>0.269</v>
       </c>
-      <c r="H6" s="52" t="n">
+      <c r="H6" s="42" t="n">
         <v>0.301</v>
       </c>
-      <c r="I6" s="53" t="n">
+      <c r="I6" s="43" t="n">
         <v>0.587</v>
       </c>
-      <c r="J6" s="53" t="n">
+      <c r="J6" s="43" t="n">
         <v>0.453</v>
       </c>
-      <c r="K6" s="53" t="n">
+      <c r="K6" s="43" t="n">
         <v>0.647</v>
       </c>
-      <c r="L6" s="50" t="n">
+      <c r="L6" s="40" t="n">
         <v>0.844</v>
       </c>
-      <c r="M6" s="53" t="n">
+      <c r="M6" s="43" t="n">
         <v>0.556</v>
       </c>
-      <c r="N6" s="52" t="n">
+      <c r="N6" s="42" t="n">
         <v>0.178</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="48" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="B7" s="51" t="n">
+      <c r="B7" s="41" t="n">
         <v>-0.345</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="41" t="n">
         <v>-0.401</v>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="41" t="n">
         <v>-0.382</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="41" t="n">
         <v>-0.312</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="43" t="n">
         <v>0.525</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="43" t="n">
         <v>0.606</v>
       </c>
-      <c r="I7" s="52" t="n">
+      <c r="I7" s="42" t="n">
         <v>-0.048</v>
       </c>
-      <c r="J7" s="51" t="n">
+      <c r="J7" s="41" t="n">
         <v>-0.543</v>
       </c>
-      <c r="K7" s="52" t="n">
+      <c r="K7" s="42" t="n">
         <v>-0.177</v>
       </c>
-      <c r="L7" s="51" t="n">
+      <c r="L7" s="41" t="n">
         <v>-0.337</v>
       </c>
-      <c r="M7" s="51" t="n">
+      <c r="M7" s="41" t="n">
         <v>-0.361</v>
       </c>
-      <c r="N7" s="52" t="n">
+      <c r="N7" s="42" t="n">
         <v>-0.139</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="48" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="42" t="n">
         <v>0.204</v>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="42" t="n">
         <v>0.171</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="42" t="n">
         <v>0.099</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="42" t="n">
         <v>0.269</v>
       </c>
-      <c r="F8" s="53" t="n">
+      <c r="F8" s="43" t="n">
         <v>0.525</v>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="43" t="n">
         <v>0.608</v>
       </c>
-      <c r="I8" s="52" t="n">
+      <c r="I8" s="42" t="n">
         <v>0.252</v>
       </c>
-      <c r="J8" s="52" t="n">
+      <c r="J8" s="42" t="n">
         <v>0.064</v>
       </c>
-      <c r="K8" s="52" t="n">
+      <c r="K8" s="42" t="n">
         <v>0.38</v>
       </c>
-      <c r="L8" s="52" t="n">
+      <c r="L8" s="42" t="n">
         <v>0.225</v>
       </c>
-      <c r="M8" s="52" t="n">
+      <c r="M8" s="42" t="n">
         <v>0.154</v>
       </c>
-      <c r="N8" s="52" t="n">
+      <c r="N8" s="42" t="n">
         <v>0.172</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="42" t="n">
         <v>0.302</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="42" t="n">
         <v>0.245</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="42" t="n">
         <v>0.224</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="42" t="n">
         <v>0.301</v>
       </c>
-      <c r="F9" s="53" t="n">
+      <c r="F9" s="43" t="n">
         <v>0.606</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="43" t="n">
         <v>0.608</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="52" t="n">
+      <c r="I9" s="42" t="n">
         <v>0.38</v>
       </c>
-      <c r="J9" s="52" t="n">
+      <c r="J9" s="42" t="n">
         <v>-0.18</v>
       </c>
-      <c r="K9" s="52" t="n">
+      <c r="K9" s="42" t="n">
         <v>0.375</v>
       </c>
-      <c r="L9" s="52" t="n">
+      <c r="L9" s="42" t="n">
         <v>0.314</v>
       </c>
-      <c r="M9" s="52" t="n">
+      <c r="M9" s="42" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="N9" s="52" t="n">
+      <c r="N9" s="42" t="n">
         <v>-0.075</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="40" t="n">
         <v>0.753</v>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="40" t="n">
         <v>0.735</v>
       </c>
-      <c r="D10" s="50" t="n">
+      <c r="D10" s="40" t="n">
         <v>0.74</v>
       </c>
-      <c r="E10" s="53" t="n">
+      <c r="E10" s="43" t="n">
         <v>0.587</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="42" t="n">
         <v>-0.048</v>
       </c>
-      <c r="G10" s="52" t="n">
+      <c r="G10" s="42" t="n">
         <v>0.252</v>
       </c>
-      <c r="H10" s="52" t="n">
+      <c r="H10" s="42" t="n">
         <v>0.38</v>
       </c>
-      <c r="I10" s="49" t="n">
+      <c r="I10" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="52" t="n">
+      <c r="J10" s="42" t="n">
         <v>0.241</v>
       </c>
-      <c r="K10" s="53" t="n">
+      <c r="K10" s="43" t="n">
         <v>0.581</v>
       </c>
-      <c r="L10" s="53" t="n">
+      <c r="L10" s="43" t="n">
         <v>0.611</v>
       </c>
-      <c r="M10" s="53" t="n">
+      <c r="M10" s="43" t="n">
         <v>0.417</v>
       </c>
-      <c r="N10" s="52" t="n">
+      <c r="N10" s="42" t="n">
         <v>0.152</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="48" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B11" s="53" t="n">
+      <c r="B11" s="43" t="n">
         <v>0.476</v>
       </c>
-      <c r="C11" s="53" t="n">
+      <c r="C11" s="43" t="n">
         <v>0.511</v>
       </c>
-      <c r="D11" s="53" t="n">
+      <c r="D11" s="43" t="n">
         <v>0.438</v>
       </c>
-      <c r="E11" s="53" t="n">
+      <c r="E11" s="43" t="n">
         <v>0.453</v>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="41" t="n">
         <v>-0.543</v>
       </c>
-      <c r="G11" s="52" t="n">
+      <c r="G11" s="42" t="n">
         <v>0.064</v>
       </c>
-      <c r="H11" s="52" t="n">
+      <c r="H11" s="42" t="n">
         <v>-0.18</v>
       </c>
-      <c r="I11" s="52" t="n">
+      <c r="I11" s="42" t="n">
         <v>0.241</v>
       </c>
-      <c r="J11" s="49" t="n">
+      <c r="J11" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="52" t="n">
+      <c r="K11" s="42" t="n">
         <v>0.383</v>
       </c>
-      <c r="L11" s="53" t="n">
+      <c r="L11" s="43" t="n">
         <v>0.483</v>
       </c>
-      <c r="M11" s="52" t="n">
+      <c r="M11" s="42" t="n">
         <v>0.399</v>
       </c>
-      <c r="N11" s="52" t="n">
+      <c r="N11" s="42" t="n">
         <v>0.205</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="B12" s="50" t="n">
+      <c r="B12" s="40" t="n">
         <v>0.732</v>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="40" t="n">
         <v>0.719</v>
       </c>
-      <c r="D12" s="53" t="n">
+      <c r="D12" s="43" t="n">
         <v>0.673</v>
       </c>
-      <c r="E12" s="53" t="n">
+      <c r="E12" s="43" t="n">
         <v>0.647</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="42" t="n">
         <v>-0.177</v>
       </c>
-      <c r="G12" s="52" t="n">
+      <c r="G12" s="42" t="n">
         <v>0.38</v>
       </c>
-      <c r="H12" s="52" t="n">
+      <c r="H12" s="42" t="n">
         <v>0.375</v>
       </c>
-      <c r="I12" s="53" t="n">
+      <c r="I12" s="43" t="n">
         <v>0.581</v>
       </c>
-      <c r="J12" s="52" t="n">
+      <c r="J12" s="42" t="n">
         <v>0.383</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="K12" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="L12" s="50" t="n">
+      <c r="L12" s="40" t="n">
         <v>0.704</v>
       </c>
-      <c r="M12" s="53" t="n">
+      <c r="M12" s="43" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="N12" s="52" t="n">
+      <c r="N12" s="42" t="n">
         <v>0.176</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="40" t="n">
         <v>0.877</v>
       </c>
-      <c r="C13" s="50" t="n">
+      <c r="C13" s="40" t="n">
         <v>0.882</v>
       </c>
-      <c r="D13" s="50" t="n">
+      <c r="D13" s="40" t="n">
         <v>0.838</v>
       </c>
-      <c r="E13" s="50" t="n">
+      <c r="E13" s="40" t="n">
         <v>0.844</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="41" t="n">
         <v>-0.337</v>
       </c>
-      <c r="G13" s="52" t="n">
+      <c r="G13" s="42" t="n">
         <v>0.225</v>
       </c>
-      <c r="H13" s="52" t="n">
+      <c r="H13" s="42" t="n">
         <v>0.314</v>
       </c>
-      <c r="I13" s="53" t="n">
+      <c r="I13" s="43" t="n">
         <v>0.611</v>
       </c>
-      <c r="J13" s="53" t="n">
+      <c r="J13" s="43" t="n">
         <v>0.483</v>
       </c>
-      <c r="K13" s="50" t="n">
+      <c r="K13" s="40" t="n">
         <v>0.704</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="L13" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="53" t="n">
+      <c r="M13" s="43" t="n">
         <v>0.64</v>
       </c>
-      <c r="N13" s="52" t="n">
+      <c r="N13" s="42" t="n">
         <v>0.198</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="48" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B14" s="53" t="n">
+      <c r="B14" s="43" t="n">
         <v>0.621</v>
       </c>
-      <c r="C14" s="53" t="n">
+      <c r="C14" s="43" t="n">
         <v>0.613</v>
       </c>
-      <c r="D14" s="53" t="n">
+      <c r="D14" s="43" t="n">
         <v>0.58</v>
       </c>
-      <c r="E14" s="53" t="n">
+      <c r="E14" s="43" t="n">
         <v>0.556</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="41" t="n">
         <v>-0.361</v>
       </c>
-      <c r="G14" s="52" t="n">
+      <c r="G14" s="42" t="n">
         <v>0.154</v>
       </c>
-      <c r="H14" s="52" t="n">
+      <c r="H14" s="42" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="I14" s="53" t="n">
+      <c r="I14" s="43" t="n">
         <v>0.417</v>
       </c>
-      <c r="J14" s="52" t="n">
+      <c r="J14" s="42" t="n">
         <v>0.399</v>
       </c>
-      <c r="K14" s="53" t="n">
+      <c r="K14" s="43" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="L14" s="53" t="n">
+      <c r="L14" s="43" t="n">
         <v>0.64</v>
       </c>
-      <c r="M14" s="49" t="n">
+      <c r="M14" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="N14" s="53" t="n">
+      <c r="N14" s="43" t="n">
         <v>0.441</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="48" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>Private Real Estate</t>
         </is>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="42" t="n">
         <v>0.19</v>
       </c>
-      <c r="C15" s="52" t="n">
+      <c r="C15" s="42" t="n">
         <v>0.198</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="42" t="n">
         <v>0.163</v>
       </c>
-      <c r="E15" s="52" t="n">
+      <c r="E15" s="42" t="n">
         <v>0.178</v>
       </c>
-      <c r="F15" s="52" t="n">
+      <c r="F15" s="42" t="n">
         <v>-0.139</v>
       </c>
-      <c r="G15" s="52" t="n">
+      <c r="G15" s="42" t="n">
         <v>0.172</v>
       </c>
-      <c r="H15" s="52" t="n">
+      <c r="H15" s="42" t="n">
         <v>-0.075</v>
       </c>
-      <c r="I15" s="52" t="n">
+      <c r="I15" s="42" t="n">
         <v>0.152</v>
       </c>
-      <c r="J15" s="52" t="n">
+      <c r="J15" s="42" t="n">
         <v>0.205</v>
       </c>
-      <c r="K15" s="52" t="n">
+      <c r="K15" s="42" t="n">
         <v>0.176</v>
       </c>
-      <c r="L15" s="52" t="n">
+      <c r="L15" s="42" t="n">
         <v>0.198</v>
       </c>
-      <c r="M15" s="53" t="n">
+      <c r="M15" s="43" t="n">
         <v>0.441</v>
       </c>
-      <c r="N15" s="49" t="n">
+      <c r="N15" s="39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9267,17 +5283,17 @@
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="C19" s="39" t="n">
+      <c r="C19" s="35" t="n">
         <v>0.9566682674249671</v>
       </c>
-      <c r="D19" s="32" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E19" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9292,17 +5308,17 @@
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="C20" s="40" t="n">
+      <c r="C20" s="36" t="n">
         <v>0.9564794466324268</v>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9317,17 +5333,17 @@
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="C21" s="39" t="n">
+      <c r="C21" s="35" t="n">
         <v>0.9327840363384615</v>
       </c>
-      <c r="D21" s="32" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E21" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9342,17 +5358,17 @@
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="C22" s="40" t="n">
+      <c r="C22" s="36" t="n">
         <v>0.8818708712318348</v>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9367,17 +5383,17 @@
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="C23" s="39" t="n">
+      <c r="C23" s="35" t="n">
         <v>0.877259056473388</v>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E23" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9392,17 +5408,17 @@
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="C24" s="40" t="n">
+      <c r="C24" s="36" t="n">
         <v>0.8442031212496384</v>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9417,17 +5433,17 @@
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="C25" s="39" t="n">
+      <c r="C25" s="35" t="n">
         <v>0.8378878973040724</v>
       </c>
-      <c r="D25" s="32" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E25" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9442,17 +5458,17 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="C26" s="40" t="n">
+      <c r="C26" s="36" t="n">
         <v>0.8114105175622475</v>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9467,17 +5483,17 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="C27" s="39" t="n">
+      <c r="C27" s="35" t="n">
         <v>0.7802907386399156</v>
       </c>
-      <c r="D27" s="32" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E27" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9492,17 +5508,17 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="C28" s="40" t="n">
+      <c r="C28" s="36" t="n">
         <v>0.752725532749333</v>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9517,17 +5533,17 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="C29" s="39" t="n">
+      <c r="C29" s="35" t="n">
         <v>0.7403645624314057</v>
       </c>
-      <c r="D29" s="32" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E29" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9542,17 +5558,17 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="C30" s="40" t="n">
+      <c r="C30" s="36" t="n">
         <v>0.7359354048313768</v>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9567,17 +5583,17 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="C31" s="39" t="n">
+      <c r="C31" s="35" t="n">
         <v>0.7346778006636191</v>
       </c>
-      <c r="D31" s="32" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9592,17 +5608,17 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="C32" s="40" t="n">
+      <c r="C32" s="36" t="n">
         <v>0.7315398350882374</v>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9617,17 +5633,17 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="C33" s="39" t="n">
+      <c r="C33" s="35" t="n">
         <v>0.7186127346808739</v>
       </c>
-      <c r="D33" s="32" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E33" s="32" t="inlineStr">
-        <is>
-          <t>Low diversification benefit between these assets</t>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
@@ -9637,6 +5653,184 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Look-Through Portfolio Beta (Net Factor Exposure)</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="5" t="n"/>
+      <c r="D1" s="5" t="n"/>
+      <c r="E1" s="5" t="n"/>
+      <c r="F1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>equity_premium</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>term_premium</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>credit_spread</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>inflation</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Equal Weight</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="n">
+        <v>0.4636952933150726</v>
+      </c>
+      <c r="C3" s="35" t="n">
+        <v>0.213020599450317</v>
+      </c>
+      <c r="D3" s="35" t="n">
+        <v>2.153964607978918</v>
+      </c>
+      <c r="E3" s="35" t="n">
+        <v>3.246662089897636</v>
+      </c>
+      <c r="F3" s="35" t="n">
+        <v>0.007778258572596224</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>60/40</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n">
+        <v>0.6313817072904651</v>
+      </c>
+      <c r="C4" s="36" t="n">
+        <v>0.3361745051400978</v>
+      </c>
+      <c r="D4" s="36" t="n">
+        <v>2.146979458188246</v>
+      </c>
+      <c r="E4" s="36" t="n">
+        <v>0.3615911096991376</v>
+      </c>
+      <c r="F4" s="36" t="n">
+        <v>-0.02618469033086923</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>MVO</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n">
+        <v>0.341608936545249</v>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>0.4623755448547909</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>2.731154020882956</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>0.8990702173393044</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>0.02485752388917012</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Risk Parity</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>0.2828260983026297</v>
+      </c>
+      <c r="C6" s="36" t="n">
+        <v>0.3733154718690183</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>1.232021384742424</v>
+      </c>
+      <c r="E6" s="36" t="n">
+        <v>3.096735624978685</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>0.01283247003358824</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Enhanced HRP</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>0.2024684798488106</v>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>0.3213380633688087</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>0.8611775407280976</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>3.585820188471191</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0.02721739711619323</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Analytics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Testing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Decomposition" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Net Factor Exposure" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Backtest Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Portfolio Analytics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Factor Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Stress Testing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Risk Decomposition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Covariance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Net Factor Exposure" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +454,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -469,13 +469,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -484,7 +484,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>2</col>
@@ -499,13 +499,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -524,13 +524,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -549,13 +549,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -574,13 +574,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -589,7 +589,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -604,13 +604,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -619,7 +619,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -634,13 +634,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.06245310112278192</v>
+        <v>0.06245310112278191</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>0.1128462018830994</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.5534355616813658</v>
+        <v>0.5534355616813655</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>1.04098829241875</v>
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07315951727129649</v>
+        <v>0.07315951727129666</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.08814883647169879</v>
+        <v>0.08814883647169917</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.8299544293450227</v>
+        <v>0.8299544293450209</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1.707951735971823</v>
+        <v>1.707951735971837</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-0.1999559307284841</v>
+        <v>-0.1999559307284849</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.3658782062865555</v>
+        <v>0.3658782062865549</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05566283756079447</v>
+        <v>0.05566283756079451</v>
       </c>
     </row>
     <row r="11">
@@ -1120,25 +1120,25 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05891136643510455</v>
+        <v>0.05891136643505968</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.0693118656153645</v>
+        <v>0.06931186561532279</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.8499463390875105</v>
+        <v>0.8499463390873745</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1.563746143547528</v>
+        <v>1.563746143545916</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-0.1665091655056802</v>
+        <v>-0.1665091655061419</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.3538025444797205</v>
+        <v>0.35380254447847</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.05681108284766658</v>
+        <v>0.0568110828478045</v>
       </c>
     </row>
     <row r="12">
@@ -1151,10 +1151,10 @@
         <v>0.05191532254690638</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.05672701063600803</v>
+        <v>0.05672701063600805</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.9151781834587387</v>
+        <v>0.9151781834587384</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>1.720196379330979</v>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.06245310112278192</v>
+        <v>0.06245310112278191</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>0.1128462018830994</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>0.5534355616813658</v>
+        <v>0.5534355616813655</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>1.04098829241875</v>
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.07315951727129649</v>
+        <v>0.07315951727129666</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.08814883647169879</v>
+        <v>0.08814883647169917</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>0.8299544293450227</v>
+        <v>0.8299544293450209</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1.707951735971823</v>
+        <v>1.707951735971837</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>-0.1999559307284841</v>
+        <v>-0.1999559307284849</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3658782062865555</v>
+        <v>0.3658782062865549</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.05566283756079447</v>
+        <v>0.05566283756079451</v>
       </c>
     </row>
     <row r="6">
@@ -1630,25 +1630,25 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.05891136643510455</v>
+        <v>0.05891136643505968</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.0693118656153645</v>
+        <v>0.06931186561532279</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>0.8499463390875105</v>
+        <v>0.8499463390873745</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1.563746143547528</v>
+        <v>1.563746143545916</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>-0.1665091655056802</v>
+        <v>-0.1665091655061419</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.3538025444797205</v>
+        <v>0.35380254447847</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.05681108284766658</v>
+        <v>0.0568110828478045</v>
       </c>
     </row>
     <row r="7">
@@ -1661,10 +1661,10 @@
         <v>0.05191532254690638</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05672701063600803</v>
+        <v>0.05672701063600805</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>0.9151781834587387</v>
+        <v>0.9151781834587384</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>1.720196379330979</v>
@@ -1721,7 +1721,7 @@
         <v>0.03956381298337185</v>
       </c>
       <c r="C31" s="28" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3846153846153845</v>
       </c>
       <c r="D31" s="32" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.05566283756079447</v>
+        <v>0.05566283756079451</v>
       </c>
       <c r="C33" s="16" t="n">
-        <v>0.6755292397488624</v>
+        <v>0.6755292397488672</v>
       </c>
       <c r="D33" s="32" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.05681108284766658</v>
+        <v>0.0568110828478045</v>
       </c>
       <c r="C34" s="30" t="n">
-        <v>0.448205120433019</v>
+        <v>0.4482051204348193</v>
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>0.06544241006043219</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>0.6355342602606396</v>
+        <v>0.6355342602606397</v>
       </c>
       <c r="D35" s="32" t="inlineStr">
         <is>
@@ -1927,19 +1927,19 @@
         </is>
       </c>
       <c r="B3" s="35" t="n">
-        <v>0.9625042408608266</v>
+        <v>0.9625042408608269</v>
       </c>
       <c r="C3" s="35" t="n">
-        <v>0.0234555669595009</v>
+        <v>0.02345556695950097</v>
       </c>
       <c r="D3" s="35" t="n">
-        <v>0.9221660405720561</v>
+        <v>0.9221660405720516</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>0.3996132467526641</v>
+        <v>0.3996132467526616</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>-0.005854488358147542</v>
+        <v>-0.005854488358147634</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>0</v>
@@ -1963,16 +1963,16 @@
         <v>0.9713542877937703</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>-0.02791969853016988</v>
+        <v>-0.02791969853016975</v>
       </c>
       <c r="D4" s="36" t="n">
-        <v>1.307588071319309</v>
+        <v>1.307588071319306</v>
       </c>
       <c r="E4" s="36" t="n">
-        <v>2.069722843884615</v>
+        <v>2.069722843884614</v>
       </c>
       <c r="F4" s="36" t="n">
-        <v>0.03673514360340343</v>
+        <v>0.03673514360340332</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>0</v>
@@ -1996,16 +1996,16 @@
         <v>1.184029795675607</v>
       </c>
       <c r="C5" s="35" t="n">
-        <v>-0.1590176041375174</v>
+        <v>-0.1590176041375175</v>
       </c>
       <c r="D5" s="35" t="n">
-        <v>0.6769370592425008</v>
+        <v>0.676937059242492</v>
       </c>
       <c r="E5" s="35" t="n">
-        <v>-2.052830116472312</v>
+        <v>-2.052830116472316</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>-0.01476517062835918</v>
+        <v>-0.01476517062835937</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="B6" s="36" t="n">
-        <v>0.7532197633494773</v>
+        <v>0.7532197633494774</v>
       </c>
       <c r="C6" s="36" t="n">
         <v>0.2392008134777396</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>5.685573550590403</v>
+        <v>5.685573550590397</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>6.29629067295865</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>-0.09556594450963732</v>
+        <v>-0.09556594450963743</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>0</v>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="B7" s="35" t="n">
-        <v>0.0252225065068102</v>
+        <v>0.02522250650681003</v>
       </c>
       <c r="C7" s="35" t="n">
         <v>1.139230258689664</v>
       </c>
       <c r="D7" s="35" t="n">
-        <v>-0.1658015292723474</v>
+        <v>-0.1658015292723478</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>-2.135877837199863</v>
+        <v>-2.135877837199861</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>-0.007930514856370094</v>
+        <v>-0.007930514856369857</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
@@ -2092,25 +2092,25 @@
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>0.01944828438149542</v>
+        <v>0.0194482843814953</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>0.4459887403586636</v>
+        <v>0.4459887403586637</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>-0.1250616872544205</v>
+        <v>-0.1250616872544132</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>6.421673019699718</v>
+        <v>6.421673019699722</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>-0.005981872260687733</v>
+        <v>-0.005981872260688031</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.8015086616077466</v>
+        <v>0.8015086616077469</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
@@ -2125,19 +2125,19 @@
         </is>
       </c>
       <c r="B9" s="35" t="n">
-        <v>0.2750954294387476</v>
+        <v>0.2750954294387477</v>
       </c>
       <c r="C9" s="35" t="n">
         <v>0.5137951400731287</v>
       </c>
       <c r="D9" s="35" t="n">
-        <v>0.242991449215862</v>
+        <v>0.2429914492158691</v>
       </c>
       <c r="E9" s="35" t="n">
-        <v>-0.1457078507988908</v>
+        <v>-0.1457078507988893</v>
       </c>
       <c r="F9" s="35" t="n">
-        <v>0.01162261473965012</v>
+        <v>0.01162261473964993</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
@@ -2161,22 +2161,22 @@
         <v>1.035110339377469</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0.3934971993740882</v>
+        <v>0.3934971993740877</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>9.35242161574546</v>
+        <v>9.352421615745463</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>-8.299634434854095</v>
+        <v>-8.299634434854106</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>-0.13621110133405</v>
+        <v>-0.136211101334049</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.6337080092805774</v>
+        <v>0.6337080092805776</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2191,19 +2191,19 @@
         </is>
       </c>
       <c r="B11" s="35" t="n">
-        <v>0.01657438583919307</v>
+        <v>0.01657438583919279</v>
       </c>
       <c r="C11" s="35" t="n">
-        <v>-0.3464828245407029</v>
+        <v>-0.3464828245407032</v>
       </c>
       <c r="D11" s="35" t="n">
-        <v>4.883589691416407</v>
+        <v>4.883589691416405</v>
       </c>
       <c r="E11" s="35" t="n">
-        <v>16.03885891630619</v>
+        <v>16.0388589163062</v>
       </c>
       <c r="F11" s="35" t="n">
-        <v>0.06933460659340056</v>
+        <v>0.06933460659340032</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         <v>0.2139108894699562</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0.2787451901424916</v>
+        <v>0.2787451901424915</v>
       </c>
       <c r="D12" s="36" t="n">
         <v>3.43229865495527</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>3.647889816547429</v>
+        <v>3.647889816547432</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>0.1641715585741691</v>
+        <v>0.1641715585741692</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>0</v>
@@ -2260,16 +2260,16 @@
         <v>0.2662615280266115</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>0.03413008712923789</v>
+        <v>0.03413008712923776</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>0.2697224940806265</v>
+        <v>0.2697224940806349</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>2.055745923262592</v>
       </c>
       <c r="F13" s="35" t="n">
-        <v>0.01290119732786074</v>
+        <v>0.01290119732786036</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>0.3475645787692834</v>
+        <v>0.3475645787692835</v>
       </c>
       <c r="C14" s="36" t="n">
-        <v>-0.01789473558713036</v>
+        <v>-0.01789473558713058</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.510698166693949</v>
+        <v>1.510698166693959</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>4.47479691252725</v>
+        <v>4.474796912527248</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>0.07225876810085399</v>
+        <v>0.07225876810085358</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.447295652178046</v>
+        <v>0.4472956521780461</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
@@ -2323,25 +2323,25 @@
         </is>
       </c>
       <c r="B15" s="35" t="n">
-        <v>-0.04225721639330339</v>
+        <v>-0.0422572163933037</v>
       </c>
       <c r="C15" s="35" t="n">
-        <v>0.2525396594451279</v>
+        <v>0.2525396594451277</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>0.008416326420856109</v>
+        <v>0.008416326420867809</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>13.43606605605532</v>
+        <v>13.43606605605533</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>0.0004025644516648638</v>
+        <v>0.0004025644516642721</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.08716459731266069</v>
+        <v>0.08716459731266091</v>
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="B19" s="35" t="n">
-        <v>0.01657438583919307</v>
+        <v>0.01657438583919279</v>
       </c>
       <c r="C19" s="35" t="n">
-        <v>0.6128143614867044</v>
+        <v>0.612814361486727</v>
       </c>
       <c r="D19" s="35" t="n">
-        <v>0.5962399756475114</v>
+        <v>0.5962399756475342</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="B20" s="36" t="n">
-        <v>-0.04225721639330339</v>
+        <v>-0.0422572163933037</v>
       </c>
       <c r="C20" s="36" t="n">
-        <v>0.1943926134830142</v>
+        <v>0.1943926134830137</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0.2366498298763176</v>
+        <v>0.2366498298763174</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         <v>0.2139108894699562</v>
       </c>
       <c r="C21" s="35" t="n">
-        <v>0.2968736681280802</v>
+        <v>0.2968736681282671</v>
       </c>
       <c r="D21" s="35" t="n">
-        <v>0.08296277865812401</v>
+        <v>0.08296277865831087</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="B22" s="36" t="n">
-        <v>0.01944828438149542</v>
+        <v>0.0194482843814953</v>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0.1007620091545411</v>
+        <v>0.1007620091545305</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0.08131372477304566</v>
+        <v>0.08131372477303518</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="B23" s="35" t="n">
-        <v>0.0252225065068102</v>
+        <v>0.02522250650681003</v>
       </c>
       <c r="C23" s="35" t="n">
-        <v>0.07165021511634978</v>
+        <v>0.07165021511635317</v>
       </c>
       <c r="D23" s="35" t="n">
-        <v>0.04642770860953958</v>
+        <v>0.04642770860954314</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="B24" s="36" t="n">
-        <v>0.9625042408608266</v>
+        <v>0.9625042408608269</v>
       </c>
       <c r="C24" s="36" t="n">
-        <v>0.9793425414193194</v>
+        <v>0.9793425414193206</v>
       </c>
       <c r="D24" s="36" t="n">
-        <v>0.01683830055849278</v>
+        <v>0.01683830055849378</v>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>1.035110339377469</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>1.031110052707944</v>
+        <v>1.031110052707938</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>-0.004000286669525455</v>
+        <v>-0.004000286669531006</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
@@ -2541,13 +2541,13 @@
         </is>
       </c>
       <c r="B26" s="36" t="n">
-        <v>0.7532197633494773</v>
+        <v>0.7532197633494774</v>
       </c>
       <c r="C26" s="36" t="n">
-        <v>0.744929893975867</v>
+        <v>0.7449298939758666</v>
       </c>
       <c r="D26" s="36" t="n">
-        <v>-0.008289869373610315</v>
+        <v>-0.008289869373610759</v>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B27" s="35" t="n">
-        <v>0.2750954294387476</v>
+        <v>0.2750954294387477</v>
       </c>
       <c r="C27" s="35" t="n">
-        <v>0.2323437215866304</v>
+        <v>0.2323437215866302</v>
       </c>
       <c r="D27" s="35" t="n">
-        <v>-0.04275170785211721</v>
+        <v>-0.04275170785211746</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B28" s="36" t="n">
-        <v>0.3475645787692834</v>
+        <v>0.3475645787692835</v>
       </c>
       <c r="C28" s="36" t="n">
-        <v>0.2923064843573309</v>
+        <v>0.2923064843573329</v>
       </c>
       <c r="D28" s="36" t="n">
-        <v>-0.05525809441195256</v>
+        <v>-0.05525809441195068</v>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
@@ -2607,10 +2607,10 @@
         <v>0.2662615280266115</v>
       </c>
       <c r="C29" s="35" t="n">
-        <v>0.1884016479536867</v>
+        <v>0.1884016479536835</v>
       </c>
       <c r="D29" s="35" t="n">
-        <v>-0.07785988007292477</v>
+        <v>-0.07785988007292804</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         <v>0.9713542877937703</v>
       </c>
       <c r="C30" s="36" t="n">
-        <v>0.81507742405682</v>
+        <v>0.8150774240568861</v>
       </c>
       <c r="D30" s="36" t="n">
-        <v>-0.1562768637369503</v>
+        <v>-0.1562768637368842</v>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
         <v>1.184029795675607</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>0.9628322446122726</v>
+        <v>0.9628322446122715</v>
       </c>
       <c r="D31" s="35" t="n">
-        <v>-0.2211975510633342</v>
+        <v>-0.2211975510633357</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
@@ -2771,16 +2771,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>-0.1830486748285108</v>
+        <v>-0.1830486748285078</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.03683695337861526</v>
+        <v>0.03683695337861703</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.1786484994678722</v>
+        <v>-0.1786484994678725</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.5145573060842663</v>
+        <v>0.5145573060842727</v>
       </c>
     </row>
     <row r="6">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-0.1665091655056802</v>
+        <v>-0.1665091655061418</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.01971956610044479</v>
+        <v>0.01971956610018144</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-0.1449286097239181</v>
+        <v>-0.1449286097236309</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3378735970067459</v>
+        <v>0.3378735970052109</v>
       </c>
     </row>
     <row r="7">
@@ -2818,7 +2818,7 @@
         <v>-0.1166178609836621</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.3183738177155637</v>
+        <v>0.3183738177155639</v>
       </c>
     </row>
   </sheetData>
@@ -2922,7 +2922,7 @@
         <v>0.1129636311829188</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.9718498340506941</v>
+        <v>0.9718498340506938</v>
       </c>
     </row>
     <row r="5">
@@ -2935,16 +2935,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C5" s="36" t="n">
-        <v>0.0867109415098225</v>
+        <v>0.08671094150982253</v>
       </c>
       <c r="D5" s="36" t="n">
-        <v>0.006670072423832502</v>
+        <v>0.006670072423832504</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>0.1288018186574803</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.9005695345361189</v>
+        <v>0.9005695345361184</v>
       </c>
     </row>
     <row r="6">
@@ -2957,16 +2957,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C6" s="35" t="n">
-        <v>0.09160479264684694</v>
+        <v>0.09160479264684693</v>
       </c>
       <c r="D6" s="35" t="n">
-        <v>0.00704652251129592</v>
+        <v>0.007046522511295919</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>0.1360712233682609</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.8647852106386996</v>
+        <v>0.8647852106386994</v>
       </c>
     </row>
     <row r="7">
@@ -2988,7 +2988,7 @@
         <v>0.1333256415144526</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.6547256214279523</v>
+        <v>0.6547256214279519</v>
       </c>
     </row>
     <row r="8">
@@ -3001,16 +3001,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C8" s="35" t="n">
-        <v>-0.01890725699586818</v>
+        <v>-0.01890725699586819</v>
       </c>
       <c r="D8" s="35" t="n">
         <v>-0.001454404384297553</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.02808514178820585</v>
+        <v>-0.02808514178820586</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.9800395309996238</v>
+        <v>0.9800395309996239</v>
       </c>
     </row>
     <row r="9">
@@ -3023,13 +3023,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0.0099511054760176</v>
+        <v>0.009951105476017614</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0.000765469652001354</v>
+        <v>0.0007654696520013551</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.01478153114988708</v>
+        <v>0.0147815311498871</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>0.8261546883028913</v>
@@ -3045,16 +3045,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>0.01592770997060339</v>
+        <v>0.01592770997060341</v>
       </c>
       <c r="D10" s="35" t="n">
-        <v>0.001225208459277184</v>
+        <v>0.001225208459277186</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.02365927500660577</v>
+        <v>0.0236592750066058</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.6542475111182807</v>
+        <v>0.6542475111182804</v>
       </c>
     </row>
     <row r="11">
@@ -3067,16 +3067,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0.08804865704708363</v>
+        <v>0.08804865704708366</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.006772973619006434</v>
+        <v>0.006772973619006437</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>0.1307888827009042</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.643251444348571</v>
+        <v>0.6432514443485702</v>
       </c>
     </row>
     <row r="12">
@@ -3089,16 +3089,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C12" s="35" t="n">
-        <v>0.07513341722441097</v>
+        <v>0.075133417224411</v>
       </c>
       <c r="D12" s="35" t="n">
-        <v>0.005779493632646999</v>
+        <v>0.005779493632647001</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.111604379008607</v>
+        <v>0.1116043790086071</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.4797912934834941</v>
+        <v>0.4797912934834942</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0.03992411329824732</v>
+        <v>0.03992411329824733</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0.003071085638326718</v>
+        <v>0.003071085638326719</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.05930391610981454</v>
+        <v>0.05930391610981455</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -3133,13 +3133,13 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C14" s="35" t="n">
-        <v>0.02736526641155148</v>
+        <v>0.0273652664115515</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>0.002105020493196268</v>
+        <v>0.002105020493196269</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04064880418182309</v>
+        <v>0.04064880418182311</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>0.7487919560463553</v>
@@ -3155,16 +3155,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0.05235587803403792</v>
+        <v>0.05235587803403795</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0.004027375233387533</v>
+        <v>0.004027375233387536</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.07777025817934878</v>
+        <v>0.07777025817934882</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.4284467817562572</v>
+        <v>0.4284467817562575</v>
       </c>
     </row>
     <row r="16">
@@ -3177,16 +3177,16 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>0.03929254921739967</v>
+        <v>0.03929254921739969</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>0.003022503785953822</v>
+        <v>0.003022503785953823</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05836578072810263</v>
+        <v>0.05836578072810264</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1297114447333512</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="18">
@@ -3252,7 +3252,7 @@
         <v>0.1592867957876898</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9718498340506941</v>
+        <v>0.9718498340506938</v>
       </c>
     </row>
     <row r="21">
@@ -3274,7 +3274,7 @@
         <v>0.1785964511717921</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.9005695345361189</v>
+        <v>0.9005695345361184</v>
       </c>
     </row>
     <row r="22">
@@ -3287,16 +3287,16 @@
         <v>0.12</v>
       </c>
       <c r="C22" s="35" t="n">
-        <v>0.09111479827874774</v>
+        <v>0.09111479827874773</v>
       </c>
       <c r="D22" s="35" t="n">
         <v>0.01093377579344973</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1937819015792191</v>
+        <v>0.193781901579219</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.8647852106386996</v>
+        <v>0.8647852106386994</v>
       </c>
     </row>
     <row r="23">
@@ -3309,7 +3309,7 @@
         <v>0.12</v>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0.08745089141391918</v>
+        <v>0.08745089141391921</v>
       </c>
       <c r="D23" s="36" t="n">
         <v>0.0104941069696703</v>
@@ -3318,7 +3318,7 @@
         <v>0.1859895467379832</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.6547256214279523</v>
+        <v>0.6547256214279519</v>
       </c>
     </row>
     <row r="24">
@@ -3331,16 +3331,16 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C24" s="35" t="n">
-        <v>-0.002026303910268674</v>
+        <v>-0.002026303910268667</v>
       </c>
       <c r="D24" s="35" t="n">
-        <v>-0.0002701738547024898</v>
+        <v>-0.000270173854702489</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-0.004788355304724753</v>
+        <v>-0.004788355304724739</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.9800395309996238</v>
+        <v>0.9800395309996239</v>
       </c>
     </row>
     <row r="25">
@@ -3353,13 +3353,13 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C25" s="36" t="n">
-        <v>0.01128184223015829</v>
+        <v>0.01128184223015831</v>
       </c>
       <c r="D25" s="36" t="n">
-        <v>0.001504245630687772</v>
+        <v>0.001504245630687774</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.02666010207850971</v>
+        <v>0.02666010207850974</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0.8261546883028913</v>
@@ -3375,16 +3375,16 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C26" s="35" t="n">
-        <v>0.02366079429953972</v>
+        <v>0.02366079429953975</v>
       </c>
       <c r="D26" s="35" t="n">
-        <v>0.003154772573271963</v>
+        <v>0.003154772573271966</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.05591278254167706</v>
+        <v>0.05591278254167711</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.6542475111182807</v>
+        <v>0.6542475111182804</v>
       </c>
     </row>
     <row r="27">
@@ -3397,16 +3397,16 @@
         <v>0.12</v>
       </c>
       <c r="C27" s="36" t="n">
-        <v>0.09618294399599181</v>
+        <v>0.0961829439959918</v>
       </c>
       <c r="D27" s="36" t="n">
-        <v>0.01154195327951902</v>
+        <v>0.01154195327951901</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>0.2045607754078538</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.643251444348571</v>
+        <v>0.6432514443485702</v>
       </c>
     </row>
     <row r="28">
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="35" t="n">
-        <v>0.04363145447238433</v>
+        <v>0.04363145447238432</v>
       </c>
       <c r="D28" s="35" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.4797912934834941</v>
+        <v>0.4797912934834942</v>
       </c>
     </row>
     <row r="29">
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="36" t="n">
-        <v>0.03736801761619854</v>
+        <v>0.03736801761619855</v>
       </c>
       <c r="D29" s="36" t="n">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="35" t="n">
-        <v>0.02593079077558951</v>
+        <v>0.02593079077558953</v>
       </c>
       <c r="D30" s="35" t="n">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="36" t="n">
-        <v>0.03961123437025103</v>
+        <v>0.03961123437025107</v>
       </c>
       <c r="D31" s="36" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.4284467817562572</v>
+        <v>0.4284467817562575</v>
       </c>
     </row>
     <row r="32">
@@ -3507,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="35" t="n">
-        <v>0.01678542567237087</v>
+        <v>0.01678542567237088</v>
       </c>
       <c r="D32" s="35" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1297114447333512</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="34">
@@ -3570,19 +3570,19 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>1.540461442864476e-08</v>
+        <v>1.540461288441797e-08</v>
       </c>
       <c r="C36" s="35" t="n">
-        <v>0.05604810820385811</v>
+        <v>0.05604810820385785</v>
       </c>
       <c r="D36" s="35" t="n">
-        <v>8.633994963353952e-10</v>
+        <v>8.633994097844016e-10</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1.958958350204883e-08</v>
+        <v>1.958958153830204e-08</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.9718498340506941</v>
+        <v>0.9718498340506938</v>
       </c>
     </row>
     <row r="37">
@@ -3592,19 +3592,19 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1.28614030174759e-08</v>
+        <v>1.286140172707754e-08</v>
       </c>
       <c r="C37" s="36" t="n">
-        <v>0.05994390698587164</v>
+        <v>0.05994390698587128</v>
       </c>
       <c r="D37" s="36" t="n">
-        <v>7.709627461873842e-10</v>
+        <v>7.709626688358602e-10</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.749229546404531e-08</v>
+        <v>1.749229370902436e-08</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.9005695345361189</v>
+        <v>0.9005695345361184</v>
       </c>
     </row>
     <row r="38">
@@ -3614,19 +3614,19 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>1.034391881227816e-08</v>
+        <v>1.034391777355504e-08</v>
       </c>
       <c r="C38" s="35" t="n">
-        <v>0.06375923942128763</v>
+        <v>0.06375923942128729</v>
       </c>
       <c r="D38" s="35" t="n">
-        <v>6.595203961064042e-10</v>
+        <v>6.595203298782051e-10</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>1.496379129900713e-08</v>
+        <v>1.496378979636218e-08</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.8647852106386996</v>
+        <v>0.8647852106386994</v>
       </c>
     </row>
     <row r="39">
@@ -3636,19 +3636,19 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>0.07113737017120601</v>
+        <v>0.07113737017120696</v>
       </c>
       <c r="C39" s="36" t="n">
-        <v>0.06717134055346052</v>
+        <v>0.0671713405534603</v>
       </c>
       <c r="D39" s="36" t="n">
-        <v>0.004778392517847663</v>
+        <v>0.004778392517847712</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.1084164626354841</v>
+        <v>0.1084164626354847</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.6547256214279523</v>
+        <v>0.6547256214279519</v>
       </c>
     </row>
     <row r="40">
@@ -3658,19 +3658,19 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.2963200956729806</v>
+        <v>0.2963200956729828</v>
       </c>
       <c r="C40" s="35" t="n">
-        <v>0.02027839680564883</v>
+        <v>0.02027839680564917</v>
       </c>
       <c r="D40" s="35" t="n">
-        <v>0.006008896481544524</v>
+        <v>0.00600889648154467</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1363352421214034</v>
+        <v>0.1363352421214061</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.9800395309996238</v>
+        <v>0.9800395309996239</v>
       </c>
     </row>
     <row r="41">
@@ -3680,16 +3680,16 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>9.201563042783877e-09</v>
+        <v>9.201562116762712e-09</v>
       </c>
       <c r="C41" s="36" t="n">
-        <v>0.01515708195138129</v>
+        <v>0.01515708195138125</v>
       </c>
       <c r="D41" s="36" t="n">
-        <v>1.394688451202766e-10</v>
+        <v>1.394688310844975e-10</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.164394465151101e-09</v>
+        <v>3.164394146694722e-09</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0.8261546883028913</v>
@@ -3702,19 +3702,19 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8.935098891791349e-09</v>
+        <v>8.935097992254681e-09</v>
       </c>
       <c r="C42" s="35" t="n">
-        <v>0.02639673412319072</v>
+        <v>0.02639673412319088</v>
       </c>
       <c r="D42" s="35" t="n">
-        <v>2.358574298110323e-10</v>
+        <v>2.358574060662035e-10</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5.351345275822377e-09</v>
+        <v>5.351344737078344e-09</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.6542475111182807</v>
+        <v>0.6542475111182804</v>
       </c>
     </row>
     <row r="43">
@@ -3724,19 +3724,19 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.1364634563400886</v>
+        <v>0.1364634563400894</v>
       </c>
       <c r="C43" s="36" t="n">
-        <v>0.08498129605168174</v>
+        <v>0.08498129605168149</v>
       </c>
       <c r="D43" s="36" t="n">
-        <v>0.01159684138347282</v>
+        <v>0.01159684138347285</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.2631195565966686</v>
+        <v>0.2631195565966681</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.643251444348571</v>
+        <v>0.6432514443485702</v>
       </c>
     </row>
     <row r="44">
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>2.096350346927755e-08</v>
+        <v>2.096350137433955e-08</v>
       </c>
       <c r="C44" s="35" t="n">
-        <v>0.02052878880749777</v>
+        <v>0.02052878880749672</v>
       </c>
       <c r="D44" s="35" t="n">
-        <v>4.303553353860456e-10</v>
+        <v>4.303552923794839e-10</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>9.764288505934306e-09</v>
+        <v>9.764287530162752e-09</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.4797912934834941</v>
+        <v>0.4797912934834942</v>
       </c>
     </row>
     <row r="45">
@@ -3768,16 +3768,16 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.1960790013757557</v>
+        <v>0.1960790013757596</v>
       </c>
       <c r="C45" s="36" t="n">
-        <v>0.03660795132295</v>
+        <v>0.03660795132295001</v>
       </c>
       <c r="D45" s="36" t="n">
-        <v>0.007178050537816312</v>
+        <v>0.007178050537816456</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.162862059787276</v>
+        <v>0.1628620597872786</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>1.618598447722783e-09</v>
+        <v>1.618598277387212e-09</v>
       </c>
       <c r="C46" s="35" t="n">
-        <v>0.02013819062703096</v>
+        <v>0.02013819062703088</v>
       </c>
       <c r="D46" s="35" t="n">
-        <v>3.259564408885779e-11</v>
+        <v>3.259564065860747e-11</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>7.39559258943208e-10</v>
+        <v>7.395591811146036e-10</v>
       </c>
       <c r="F46" s="9" t="n">
         <v>0.7487919560463553</v>
@@ -3812,19 +3812,19 @@
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.2822620050016614</v>
+        <v>0.2822620050016704</v>
       </c>
       <c r="C47" s="36" t="n">
-        <v>0.04946939446322393</v>
+        <v>0.04946939446322386</v>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.01396333046740768</v>
+        <v>0.0139633304674081</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.3168125871267913</v>
+        <v>0.3168125871267995</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.4284467817562572</v>
+        <v>0.4284467817562575</v>
       </c>
     </row>
     <row r="48">
@@ -3834,19 +3834,19 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.01773799210960737</v>
+        <v>0.01773799210959868</v>
       </c>
       <c r="C48" s="35" t="n">
-        <v>0.03094508737001937</v>
+        <v>0.03094508737001761</v>
       </c>
       <c r="D48" s="35" t="n">
-        <v>0.0005489037156005142</v>
+        <v>0.0005489037156002144</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.01245402066711899</v>
+        <v>0.01245402066711213</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.1297114447333512</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="50">
@@ -3900,19 +3900,19 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.04239826333589958</v>
+        <v>0.04239826333525394</v>
       </c>
       <c r="C52" s="35" t="n">
-        <v>0.06287655228621657</v>
+        <v>0.06287655228620767</v>
       </c>
       <c r="D52" s="35" t="n">
-        <v>0.00266585662148447</v>
+        <v>0.002665856621443495</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.07692352810926284</v>
+        <v>0.0769235281081268</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.9718498340506941</v>
+        <v>0.9718498340506938</v>
       </c>
     </row>
     <row r="53">
@@ -3922,19 +3922,19 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.03838122897153512</v>
+        <v>0.03838122897303223</v>
       </c>
       <c r="C53" s="36" t="n">
-        <v>0.06945530211246037</v>
+        <v>0.06945530211249798</v>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.002665779853665489</v>
+        <v>0.002665779853770914</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.0769213129670704</v>
+        <v>0.07692131297015872</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.9005695345361189</v>
+        <v>0.9005695345361184</v>
       </c>
     </row>
     <row r="54">
@@ -3944,19 +3944,19 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.03705345539751015</v>
+        <v>0.0370534553973652</v>
       </c>
       <c r="C54" s="35" t="n">
-        <v>0.0719460643679987</v>
+        <v>0.07194606436802295</v>
       </c>
       <c r="D54" s="35" t="n">
-        <v>0.002665850287086035</v>
+        <v>0.002665850287076504</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.07692334532963691</v>
+        <v>0.07692334532940817</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.8647852106386996</v>
+        <v>0.8647852106386994</v>
       </c>
     </row>
     <row r="55">
@@ -3966,19 +3966,19 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.03526861812925119</v>
+        <v>0.03526861812873507</v>
       </c>
       <c r="C55" s="36" t="n">
-        <v>0.07558698122436444</v>
+        <v>0.07558698122430507</v>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.002665848376344989</v>
+        <v>0.002665848376303882</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0769232901950354</v>
+        <v>0.07692329019389553</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.6547256214279523</v>
+        <v>0.6547256214279519</v>
       </c>
     </row>
     <row r="56">
@@ -3988,19 +3988,19 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.1901058368842273</v>
+        <v>0.1901058368847075</v>
       </c>
       <c r="C56" s="35" t="n">
-        <v>0.01402297004717164</v>
+        <v>0.01402297004707323</v>
       </c>
       <c r="D56" s="35" t="n">
-        <v>0.002665848456420016</v>
+        <v>0.002665848456408041</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.07692329250560737</v>
+        <v>0.07692329250530809</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.9800395309996238</v>
+        <v>0.9800395309996239</v>
       </c>
     </row>
     <row r="57">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.1561033628963286</v>
+        <v>0.1561033628971746</v>
       </c>
       <c r="C57" s="36" t="n">
-        <v>0.01707722545810178</v>
+        <v>0.01707722545808812</v>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.002665812322948484</v>
+        <v>0.002665812322960799</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.07692224987109705</v>
+        <v>0.07692224987149869</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>0.8261546883028913</v>
@@ -4032,19 +4032,19 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.0989198915904857</v>
+        <v>0.09891989158807808</v>
       </c>
       <c r="C58" s="35" t="n">
-        <v>0.02695041436466309</v>
+        <v>0.02695041436455389</v>
       </c>
       <c r="D58" s="35" t="n">
-        <v>0.002665932067271142</v>
+        <v>0.002665932067195453</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.07692570510409633</v>
+        <v>0.07692570510195859</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.6542475111182807</v>
+        <v>0.6542475111182804</v>
       </c>
     </row>
     <row r="59">
@@ -4054,19 +4054,19 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.03310675547563253</v>
+        <v>0.03310675547604956</v>
       </c>
       <c r="C59" s="36" t="n">
-        <v>0.08052175975617794</v>
+        <v>0.08052175975620805</v>
       </c>
       <c r="D59" s="36" t="n">
-        <v>0.002665814210715412</v>
+        <v>0.002665814210749987</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.07692230434277839</v>
+        <v>0.07692230434382233</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.643251444348571</v>
+        <v>0.6432514443485702</v>
       </c>
     </row>
     <row r="60">
@@ -4076,19 +4076,19 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.05454871770404718</v>
+        <v>0.05454871770448565</v>
       </c>
       <c r="C60" s="35" t="n">
-        <v>0.04887037300549023</v>
+        <v>0.04887037300574652</v>
       </c>
       <c r="D60" s="35" t="n">
-        <v>0.002665816181167974</v>
+        <v>0.002665816181203382</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.07692236120036099</v>
+        <v>0.07692236120142895</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.4797912934834941</v>
+        <v>0.4797912934834942</v>
       </c>
     </row>
     <row r="61">
@@ -4098,16 +4098,16 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>0.07131481416206895</v>
+        <v>0.07131481415928038</v>
       </c>
       <c r="C61" s="36" t="n">
-        <v>0.03738288332129727</v>
+        <v>0.03738288332119384</v>
       </c>
       <c r="D61" s="36" t="n">
-        <v>0.002665953376900622</v>
+        <v>0.002665953376789001</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.07692631999533582</v>
+        <v>0.07692631999216128</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -4120,16 +4120,16 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.1147079339070491</v>
+        <v>0.1147079339099366</v>
       </c>
       <c r="C62" s="35" t="n">
-        <v>0.02323949153589772</v>
+        <v>0.0232394915358965</v>
       </c>
       <c r="D62" s="35" t="n">
-        <v>0.002665754059133183</v>
+        <v>0.002665754059200145</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>0.07692056866356399</v>
+        <v>0.07692056866554249</v>
       </c>
       <c r="F62" s="9" t="n">
         <v>0.7487919560463553</v>
@@ -4142,19 +4142,19 @@
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>0.06079007889478735</v>
+        <v>0.06079007889326719</v>
       </c>
       <c r="C63" s="36" t="n">
-        <v>0.04385430184748499</v>
+        <v>0.04385430184744837</v>
       </c>
       <c r="D63" s="36" t="n">
-        <v>0.002665906469184431</v>
+        <v>0.002665906469115539</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.07692496646904494</v>
+        <v>0.07692496646710331</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.4284467817562572</v>
+        <v>0.4284467817562575</v>
       </c>
     </row>
     <row r="64">
@@ -4164,19 +4164,19 @@
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.06730104265117719</v>
+        <v>0.06730104265263419</v>
       </c>
       <c r="C64" s="35" t="n">
-        <v>0.03960949816448898</v>
+        <v>0.0396094981648834</v>
       </c>
       <c r="D64" s="35" t="n">
-        <v>0.002665760525359998</v>
+        <v>0.002665760525444253</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.07692075524710948</v>
+        <v>0.07692075524958694</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.1297114447333512</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
     <row r="66">
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.01418954230934599</v>
+        <v>0.01418954230934598</v>
       </c>
       <c r="C68" s="35" t="n">
-        <v>0.06214559548003216</v>
+        <v>0.0621455954800322</v>
       </c>
       <c r="D68" s="35" t="n">
         <v>0.0008818175564034171</v>
@@ -4242,7 +4242,7 @@
         <v>0.03108986518121491</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.9718498340506941</v>
+        <v>0.9718498340506938</v>
       </c>
     </row>
     <row r="69">
@@ -4252,19 +4252,19 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>0.01071962159834465</v>
+        <v>0.01071962159834464</v>
       </c>
       <c r="C69" s="36" t="n">
-        <v>0.06881032714615794</v>
+        <v>0.06881032714615799</v>
       </c>
       <c r="D69" s="36" t="n">
-        <v>0.0007376206690651155</v>
+        <v>0.0007376206690651157</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>0.0260059770749458</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.9005695345361189</v>
+        <v>0.9005695345361184</v>
       </c>
     </row>
     <row r="70">
@@ -4274,19 +4274,19 @@
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.01785691413064644</v>
+        <v>0.01785691413064642</v>
       </c>
       <c r="C70" s="35" t="n">
-        <v>0.06998047058406635</v>
+        <v>0.0699804705840664</v>
       </c>
       <c r="D70" s="35" t="n">
         <v>0.001249635254041901</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.04405785674342173</v>
+        <v>0.04405785674342171</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.8647852106386996</v>
+        <v>0.8647852106386994</v>
       </c>
     </row>
     <row r="71">
@@ -4296,19 +4296,19 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>0.01018151128031413</v>
+        <v>0.01018151128031412</v>
       </c>
       <c r="C71" s="36" t="n">
-        <v>0.07713721713992756</v>
+        <v>0.07713721713992762</v>
       </c>
       <c r="D71" s="36" t="n">
-        <v>0.0007853734464422126</v>
+        <v>0.0007853734464422128</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>0.02768957636359879</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.6547256214279523</v>
+        <v>0.6547256214279519</v>
       </c>
     </row>
     <row r="72">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>0.05965965579571525</v>
+        <v>0.0596596557957153</v>
       </c>
       <c r="C72" s="35" t="n">
-        <v>0.01185652218885519</v>
+        <v>0.01185652218885514</v>
       </c>
       <c r="D72" s="35" t="n">
-        <v>0.0007073560327213609</v>
+        <v>0.0007073560327213587</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.024938949709871</v>
+        <v>0.02493894970987092</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.9800395309996238</v>
+        <v>0.9800395309996239</v>
       </c>
     </row>
     <row r="73">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>0.3316397889964035</v>
+        <v>0.3316397889964033</v>
       </c>
       <c r="C73" s="36" t="n">
         <v>0.01854942338164661</v>
       </c>
       <c r="D73" s="36" t="n">
-        <v>0.006151726856294234</v>
+        <v>0.00615172685629423</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.2168888079002479</v>
+        <v>0.2168888079002477</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0.8261546883028913</v>
@@ -4362,19 +4362,19 @@
         </is>
       </c>
       <c r="B74" s="9" t="n">
-        <v>0.1092060125556165</v>
+        <v>0.1092060125556164</v>
       </c>
       <c r="C74" s="35" t="n">
-        <v>0.02838237345122104</v>
+        <v>0.02838237345122105</v>
       </c>
       <c r="D74" s="35" t="n">
-        <v>0.00309952583147224</v>
+        <v>0.003099525831472238</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.1092786592038321</v>
+        <v>0.109278659203832</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>0.6542475111182807</v>
+        <v>0.6542475111182804</v>
       </c>
     </row>
     <row r="75">
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>0.009319148736044234</v>
+        <v>0.009319148736044227</v>
       </c>
       <c r="C75" s="36" t="n">
-        <v>0.07416805794013152</v>
+        <v>0.07416805794013157</v>
       </c>
       <c r="D75" s="36" t="n">
-        <v>0.000691183163407632</v>
+        <v>0.0006911831634076319</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.02436874975988587</v>
+        <v>0.02436874975988586</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.643251444348571</v>
+        <v>0.6432514443485702</v>
       </c>
     </row>
     <row r="76">
@@ -4406,19 +4406,19 @@
         </is>
       </c>
       <c r="B76" s="9" t="n">
-        <v>0.01805983719241162</v>
+        <v>0.01805983719241161</v>
       </c>
       <c r="C76" s="35" t="n">
-        <v>0.04543999203099211</v>
+        <v>0.04543999203099216</v>
       </c>
       <c r="D76" s="35" t="n">
-        <v>0.0008206388581041986</v>
+        <v>0.0008206388581041992</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.02893291392948142</v>
+        <v>0.02893291392948143</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.4797912934834941</v>
+        <v>0.4797912934834942</v>
       </c>
     </row>
     <row r="77">
@@ -4428,16 +4428,16 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>0.1483922296615783</v>
+        <v>0.1483922296615784</v>
       </c>
       <c r="C77" s="36" t="n">
-        <v>0.04167679313253375</v>
+        <v>0.04167679313253376</v>
       </c>
       <c r="D77" s="36" t="n">
-        <v>0.006184512258081034</v>
+        <v>0.006184512258081044</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.2180447088165564</v>
+        <v>0.2180447088165566</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0.6813173339403511</v>
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>0.2280024325953267</v>
+        <v>0.2280024325953268</v>
       </c>
       <c r="C78" s="35" t="n">
-        <v>0.02412051657055183</v>
+        <v>0.02412051657055184</v>
       </c>
       <c r="D78" s="35" t="n">
-        <v>0.005499536453541702</v>
+        <v>0.005499536453541706</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>0.1938948092586714</v>
+        <v>0.1938948092586715</v>
       </c>
       <c r="F78" s="9" t="n">
         <v>0.7487919560463553</v>
@@ -4472,19 +4472,19 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>0.02821942763967994</v>
+        <v>0.02821942763967997</v>
       </c>
       <c r="C79" s="36" t="n">
-        <v>0.0415551260438286</v>
+        <v>0.04155512604382863</v>
       </c>
       <c r="D79" s="36" t="n">
-        <v>0.0011726618724516</v>
+        <v>0.001172661872451602</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.04134403908487437</v>
+        <v>0.04134403908487444</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.4284467817562572</v>
+        <v>0.4284467817562575</v>
       </c>
     </row>
     <row r="80">
@@ -4494,19 +4494,19 @@
         </is>
       </c>
       <c r="B80" s="9" t="n">
-        <v>0.01455387750857303</v>
+        <v>0.01455387750857305</v>
       </c>
       <c r="C80" s="35" t="n">
-        <v>0.0262416023326015</v>
+        <v>0.02624160233260154</v>
       </c>
       <c r="D80" s="35" t="n">
-        <v>0.0003819170659773665</v>
+        <v>0.0003819170659773675</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0134650869733982</v>
+        <v>0.01346508697339823</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1297114447333512</v>
+        <v>0.1297114447333514</v>
       </c>
     </row>
   </sheetData>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>0.9564794466324268</v>
+        <v>0.9564794466324271</v>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="C21" s="35" t="n">
-        <v>0.9327840363384615</v>
+        <v>0.9327840363384619</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0.8818708712318348</v>
+        <v>0.8818708712318351</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>0.877259056473388</v>
+        <v>0.8772590564733882</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="C24" s="36" t="n">
-        <v>0.8442031212496384</v>
+        <v>0.8442031212496387</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="C25" s="35" t="n">
-        <v>0.8378878973040724</v>
+        <v>0.8378878973040726</v>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="C26" s="36" t="n">
-        <v>0.8114105175622475</v>
+        <v>0.8114105175622477</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="C27" s="35" t="n">
-        <v>0.7802907386399156</v>
+        <v>0.7802907386399155</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="C28" s="36" t="n">
-        <v>0.752725532749333</v>
+        <v>0.7527255327493332</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="C29" s="35" t="n">
-        <v>0.7403645624314057</v>
+        <v>0.7403645624314058</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C30" s="36" t="n">
-        <v>0.7359354048313768</v>
+        <v>0.7359354048313766</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="C32" s="36" t="n">
-        <v>0.7315398350882374</v>
+        <v>0.7315398350882377</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="C33" s="35" t="n">
-        <v>0.7186127346808739</v>
+        <v>0.7186127346808743</v>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
@@ -5730,13 +5730,13 @@
         <v>0.213020599450317</v>
       </c>
       <c r="D3" s="35" t="n">
-        <v>2.153964607978918</v>
+        <v>2.15396460797892</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>3.246662089897636</v>
+        <v>3.246662089897637</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>0.007778258572596224</v>
+        <v>0.007778258572596125</v>
       </c>
     </row>
     <row r="4">
@@ -5749,16 +5749,16 @@
         <v>0.6313817072904651</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>0.3361745051400978</v>
+        <v>0.3361745051400977</v>
       </c>
       <c r="D4" s="36" t="n">
         <v>2.146979458188246</v>
       </c>
       <c r="E4" s="36" t="n">
-        <v>0.3615911096991376</v>
+        <v>0.3615911096991364</v>
       </c>
       <c r="F4" s="36" t="n">
-        <v>-0.02618469033086923</v>
+        <v>-0.02618469033086921</v>
       </c>
     </row>
     <row r="5">
@@ -5768,19 +5768,19 @@
         </is>
       </c>
       <c r="B5" s="35" t="n">
-        <v>0.341608936545249</v>
+        <v>0.3416089365452504</v>
       </c>
       <c r="C5" s="35" t="n">
-        <v>0.4623755448547909</v>
+        <v>0.4623755448547925</v>
       </c>
       <c r="D5" s="35" t="n">
-        <v>2.731154020882956</v>
+        <v>2.731154020882983</v>
       </c>
       <c r="E5" s="35" t="n">
-        <v>0.8990702173393044</v>
+        <v>0.8990702173391955</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>0.02485752388917012</v>
+        <v>0.02485752388917111</v>
       </c>
     </row>
     <row r="6">
@@ -5790,19 +5790,19 @@
         </is>
       </c>
       <c r="B6" s="36" t="n">
-        <v>0.2828260983026297</v>
+        <v>0.2828260983022897</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>0.3733154718690183</v>
+        <v>0.3733154718682769</v>
       </c>
       <c r="D6" s="36" t="n">
-        <v>1.232021384742424</v>
+        <v>1.232021384734952</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>3.096735624978685</v>
+        <v>3.096735624995443</v>
       </c>
       <c r="F6" s="36" t="n">
-        <v>0.01283247003358824</v>
+        <v>0.0128324700331053</v>
       </c>
     </row>
     <row r="7">
@@ -5815,16 +5815,16 @@
         <v>0.2024684798488106</v>
       </c>
       <c r="C7" s="35" t="n">
-        <v>0.3213380633688087</v>
+        <v>0.3213380633688086</v>
       </c>
       <c r="D7" s="35" t="n">
-        <v>0.8611775407280976</v>
+        <v>0.8611775407281035</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>3.585820188471191</v>
+        <v>3.585820188471193</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>0.02721739711619323</v>
+        <v>0.02721739711619306</v>
       </c>
     </row>
   </sheetData>

--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,12 +71,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B7770D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00B03A2E"/>
       <sz val="10"/>
     </font>
@@ -94,11 +88,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="00B7770D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001E7B45"/>
       <sz val="10"/>
     </font>
     <font>
@@ -250,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,13 +279,13 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,7 +294,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,37 +303,31 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,25 +339,25 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -594,7 +577,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>25</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8667750" cy="2952750"/>
@@ -624,7 +607,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9334500" cy="5715000"/>
@@ -968,7 +951,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 42.0% — a 38.6 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
+          <t>Key Finding: A conventional 60/40 portfolio allocates 79.8% of total risk to Equity Premium. Enhanced HRP reduces this to 19.7% — a 60.1 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
         </is>
       </c>
     </row>
@@ -1036,25 +1019,25 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.06499352425022981</v>
+        <v>0.07378527590086548</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.1035710907401094</v>
+        <v>0.1102367794102579</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.6275257292917563</v>
+        <v>0.4865415659165658</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1.00809746126433</v>
+        <v>0.6069203385934979</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.2929242982373964</v>
+        <v>-0.1958991860781159</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.221878228065453</v>
+        <v>0.376649221357373</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03956381298337185</v>
+        <v>0.02666080197108656</v>
       </c>
     </row>
     <row r="9">
@@ -1064,22 +1047,22 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.06245310112278191</v>
+        <v>0.07998380339703903</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.1128462018830994</v>
+        <v>0.1069805129364676</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.5534355616813655</v>
+        <v>0.5592916048885708</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1.04098829241875</v>
+        <v>0.7881504656053266</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>-0.2800420148978708</v>
+        <v>-0.241238590731507</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.2230133258595432</v>
+        <v>0.3315547614272841</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -1092,25 +1075,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07315951727129666</v>
+        <v>0.06222171082584271</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.08814883647169917</v>
+        <v>0.0973601500872822</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.8299544293450209</v>
+        <v>0.432119405764338</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1.707951735971837</v>
+        <v>0.5783968614119489</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-0.1999559307284849</v>
+        <v>-0.27765624040269</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.3658782062865549</v>
+        <v>0.2240962088069816</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05566283756079451</v>
+        <v>0.05645299427673103</v>
       </c>
     </row>
     <row r="11">
@@ -1120,25 +1103,25 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05891136643505968</v>
+        <v>0.05336149921976885</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.06931186561532279</v>
+        <v>0.07659729222579761</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.8499463390873745</v>
+        <v>0.4335792771481806</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1.563746143545916</v>
+        <v>0.5934387331649268</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-0.1665091655061419</v>
+        <v>-0.2057596347263281</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.35380254447847</v>
+        <v>0.2593390063641134</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.0568110828478045</v>
+        <v>0.05369797654498694</v>
       </c>
     </row>
     <row r="12">
@@ -1148,25 +1131,25 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.05191532254690638</v>
+        <v>0.03786650154700966</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.05672701063600805</v>
+        <v>0.06181265212606881</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.9151781834587384</v>
+        <v>0.2866080052005819</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1.720196379330979</v>
+        <v>0.3782437630813464</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-0.1388515020427566</v>
+        <v>-0.1798794517404291</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.3738909682872574</v>
+        <v>0.2105104345195139</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.06544241006043219</v>
+        <v>0.07404845446758664</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1226,22 +1209,22 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>0.6509999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.043</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.131</v>
+        <v>0.124</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.133</v>
+        <v>0.064</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.006</v>
+        <v>-0.011</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="17">
@@ -1251,13 +1234,13 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.7979999999999999</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>0.009000000000000001</v>
@@ -1266,7 +1249,7 @@
         <v>-0.015</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.1</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="18">
@@ -1276,22 +1259,22 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.414</v>
+        <v>0.478</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.191</v>
+        <v>0.303</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.113</v>
+        <v>0.083</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.016</v>
+        <v>-0.016</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.25</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="19">
@@ -1301,22 +1284,22 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.487</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.144</v>
+        <v>0.194</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.118</v>
+        <v>0.062</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.011</v>
+        <v>-0.006</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.166</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="20">
@@ -1326,22 +1309,22 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.42</v>
+        <v>0.197</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.14</v>
+        <v>0.556</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.065</v>
+        <v>0.012</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.191</v>
+        <v>0.078</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.031</v>
+        <v>-0.002</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.154</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1"/>
@@ -1394,7 +1377,7 @@
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
@@ -1425,7 +1408,7 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -1442,7 +1425,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -1546,25 +1529,25 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.06499352425022981</v>
+        <v>0.07378527590086548</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>0.1035710907401094</v>
+        <v>0.1102367794102579</v>
       </c>
       <c r="D3" s="24" t="n">
-        <v>0.6275257292917563</v>
+        <v>0.4865415659165658</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1.00809746126433</v>
+        <v>0.6069203385934979</v>
       </c>
       <c r="F3" s="25" t="n">
-        <v>-0.2929242982373964</v>
+        <v>-0.1958991860781159</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.221878228065453</v>
+        <v>0.376649221357373</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.03956381298337185</v>
+        <v>0.02666080197108656</v>
       </c>
     </row>
     <row r="4">
@@ -1574,22 +1557,22 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.06245310112278191</v>
+        <v>0.07998380339703903</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>0.1128462018830994</v>
+        <v>0.1069805129364676</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>0.5534355616813655</v>
+        <v>0.5592916048885708</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>1.04098829241875</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>-0.2800420148978708</v>
+        <v>0.7881504656053266</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>-0.241238590731507</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.2230133258595432</v>
+        <v>0.3315547614272841</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -1602,25 +1585,25 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.07315951727129666</v>
+        <v>0.06222171082584271</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.08814883647169917</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>0.8299544293450209</v>
+        <v>0.0973601500872822</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>0.432119405764338</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1.707951735971837</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-0.1999559307284849</v>
+        <v>0.5783968614119489</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>-0.27765624040269</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3658782062865549</v>
+        <v>0.2240962088069816</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.05566283756079451</v>
+        <v>0.05645299427673103</v>
       </c>
     </row>
     <row r="6">
@@ -1630,25 +1613,25 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.05891136643505968</v>
+        <v>0.05336149921976885</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.06931186561532279</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>0.8499463390873745</v>
+        <v>0.07659729222579761</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.4335792771481806</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1.563746143545916</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>-0.1665091655061419</v>
+        <v>0.5934387331649268</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>-0.2057596347263281</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.35380254447847</v>
+        <v>0.2593390063641134</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.0568110828478045</v>
+        <v>0.05369797654498694</v>
       </c>
     </row>
     <row r="7">
@@ -1658,25 +1641,25 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.05191532254690638</v>
+        <v>0.03786650154700966</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05672701063600805</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0.9151781834587384</v>
+        <v>0.06181265212606881</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0.2866080052005819</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1.720196379330979</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>-0.1388515020427566</v>
+        <v>0.3782437630813464</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-0.1798794517404291</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.3738909682872574</v>
+        <v>0.2105104345195139</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.06544241006043219</v>
+        <v>0.07404845446758664</v>
       </c>
     </row>
     <row r="29">
@@ -1718,14 +1701,14 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.03956381298337185</v>
-      </c>
-      <c r="C31" s="28" t="n">
-        <v>0.3846153846153845</v>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
-        <is>
-          <t>Moderate Active</t>
+        <v>0.02666080197108656</v>
+      </c>
+      <c r="C31" s="29" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>Closet Indexer</t>
         </is>
       </c>
     </row>
@@ -1738,10 +1721,10 @@
       <c r="B32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C32" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>Closet Indexer</t>
         </is>
@@ -1754,14 +1737,14 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.05566283756079451</v>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>0.6755292397488672</v>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
-        <is>
-          <t>High Conviction Active</t>
+        <v>0.05645299427673103</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>0.364425723493131</v>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>Moderate Active</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1755,12 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.0568110828478045</v>
-      </c>
-      <c r="C34" s="30" t="n">
-        <v>0.4482051204348193</v>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
+        <v>0.05369797654498694</v>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>0.2945578217774981</v>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
         <is>
           <t>Moderate Active</t>
         </is>
@@ -1790,12 +1773,12 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.06544241006043219</v>
+        <v>0.07404845446758664</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>0.6355342602606397</v>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
+        <v>0.5717326055122662</v>
+      </c>
+      <c r="D35" s="30" t="inlineStr">
         <is>
           <t>High Conviction Active</t>
         </is>
@@ -1843,7 +1826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1926,23 +1909,23 @@
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
-        <v>0.9625042408608269</v>
-      </c>
-      <c r="C3" s="35" t="n">
-        <v>0.02345556695950097</v>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>0.9221660405720516</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>0.3996132467526616</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>-0.005854488358147634</v>
+      <c r="B3" s="33" t="n">
+        <v>0.9625042408608263</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>0.02345556695950237</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>0.9221660405720529</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>0.3996132467527052</v>
+      </c>
+      <c r="F3" s="33" t="n">
+        <v>-0.005854488358147615</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0</v>
+        <v>0.02681788977738234</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>0.9906918940400172</v>
@@ -1959,26 +1942,26 @@
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
-        <v>0.9713542877937703</v>
-      </c>
-      <c r="C4" s="36" t="n">
-        <v>-0.02791969853016975</v>
-      </c>
-      <c r="D4" s="36" t="n">
-        <v>1.307588071319306</v>
-      </c>
-      <c r="E4" s="36" t="n">
-        <v>2.069722843884614</v>
-      </c>
-      <c r="F4" s="36" t="n">
-        <v>0.03673514360340332</v>
+      <c r="B4" s="34" t="n">
+        <v>0.971354889535758</v>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>-0.0279185738583745</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>1.307574570963585</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>2.069750684644512</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>0.03673471269025674</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0</v>
+        <v>0.02838076840528056</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>0.9123635173053706</v>
+        <v>0.9123631766041419</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
@@ -1992,26 +1975,26 @@
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
-        <v>1.184029795675607</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>-0.1590176041375175</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0.676937059242492</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>-2.052830116472316</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>-0.01476517062835937</v>
+      <c r="B5" s="33" t="n">
+        <v>1.184029620083211</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>-0.1590181004859705</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>0.6769277744832372</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>-2.052810693745579</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>-0.01476509282000907</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0</v>
+        <v>0.02543144571233723</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.8712833012703342</v>
+        <v>0.8712835998068817</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
@@ -2025,26 +2008,26 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
-        <v>0.7532197633494774</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>0.2392008134777396</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>5.685573550590397</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>6.29629067295865</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>-0.09556594450963743</v>
+      <c r="B6" s="34" t="n">
+        <v>0.7532195145960868</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>0.239200635449679</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>5.685577809098848</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>6.296292096835225</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>-0.0955658312106086</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>0.0206718781744882</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.6355398384728477</v>
+        <v>0.6355403296685542</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
@@ -2058,26 +2041,26 @@
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
-        <v>0.02522250650681003</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>1.139230258689664</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>-0.1658015292723478</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>-2.135877837199861</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>-0.007930514856369857</v>
+      <c r="B7" s="33" t="n">
+        <v>0.02522245718052332</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>1.139232287873908</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>-0.1657940661604688</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>-2.13589950876659</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>-0.007930157885479423</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0</v>
+        <v>0.01148282418385831</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.9812439847251684</v>
+        <v>0.9812438336595104</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
@@ -2091,26 +2074,26 @@
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
-        <v>0.0194482843814953</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>0.4459887403586637</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>-0.1250616872544132</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>6.421673019699722</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>-0.005981872260688031</v>
+      <c r="B8" s="34" t="n">
+        <v>0.01944981703587667</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>0.4459870996647048</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>-0.1250823047768445</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>6.421690474074236</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>-0.005982858425101597</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0</v>
+        <v>0.008734871552751659</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.8015086616077469</v>
+        <v>0.8015107862181039</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
@@ -2124,26 +2107,26 @@
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
-        <v>0.2750954294387477</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0.5137951400731287</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>0.2429914492158691</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>-0.1457078507988893</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>0.01162261473964993</v>
+      <c r="B9" s="33" t="n">
+        <v>0.2750935238828958</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0.5137949658837728</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>0.2430069382283973</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>-0.1456786200674224</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>0.011623355600392</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>0.01057001448042171</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.6374629953920316</v>
+        <v>0.6374633033903678</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
@@ -2157,26 +2140,26 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
-        <v>1.035110339377469</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>0.3934971993740877</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>9.352421615745463</v>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>-8.299634434854106</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>-0.136211101334049</v>
+      <c r="B10" s="34" t="n">
+        <v>1.035110447452133</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>0.3934959490536423</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>9.352440086495633</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>-8.299662990213015</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>-0.1362108916081567</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0</v>
+        <v>0.0240698586185005</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.6337080092805776</v>
+        <v>0.6337084793755835</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2190,26 +2173,26 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
-        <v>0.01657438583919279</v>
-      </c>
-      <c r="C11" s="35" t="n">
-        <v>-0.3464828245407032</v>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>4.883589691416405</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>16.0388589163062</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>0.06933460659340032</v>
+      <c r="B11" s="33" t="n">
+        <v>0.1086076548864854</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>-0.322256513988238</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>4.246990685914242</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>15.42135885368741</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>0.0372673088981893</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>0.004127872859151399</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.4370483747153048</v>
+        <v>0.4445765852026022</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
@@ -2217,444 +2200,228 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B12" s="36" t="n">
-        <v>0.2139108894699562</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.2787451901424915</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>3.43229865495527</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>3.647889816547432</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>0.1641715585741692</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.8431315161474411</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>BAA-Treasury</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="n">
-        <v>0.2662615280266115</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0.03413008712923776</v>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>0.2697224940806349</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>2.055745923262592</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>0.01290119732786036</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>0.7443129475785015</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>BAA-Treasury</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Equity Premium Beta: Full-Sample OLS vs Stress (Q10 Quantile Regression)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="36" t="n">
-        <v>0.3475645787692835</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>-0.01789473558713058</v>
-      </c>
-      <c r="D14" s="36" t="n">
-        <v>1.510698166693959</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>4.474796912527248</v>
-      </c>
-      <c r="F14" s="36" t="n">
-        <v>0.07225876810085358</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.4472956521780461</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>BAA-Treasury</t>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>OLS Beta</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Stress Beta (Q10)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Uplift</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n">
-        <v>-0.0422572163933037</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0.2525396594451277</v>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>0.008416326420867809</v>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>13.43606605605533</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>0.0004025644516642721</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>0.08716459731266091</v>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>BAA-Treasury</t>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="n">
+        <v>0.1086076548864854</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>0.815131539955253</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>0.7065238850687676</v>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Significant stress uplift</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n">
+        <v>0.01944981703587667</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>0.1007609043221211</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>0.08131108728624448</v>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Moderate stress uplift</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Equity Premium Beta: Full-Sample OLS vs Stress (Q10 Quantile Regression)</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="n">
+        <v>0.02522245718052332</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>0.07165142618821491</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>0.04642896900769159</v>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>OLS Beta</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Stress Beta (Q10)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Uplift</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="n">
+        <v>0.9625042408608263</v>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>0.9793425414193179</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>0.01683830055849156</v>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="n">
-        <v>0.01657438583919279</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0.612814361486727</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>0.5962399756475342</v>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>1.035110447452133</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>1.031109852175071</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>-0.004000595277062535</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>Significant stress uplift</t>
+          <t>Stable across regimes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B20" s="36" t="n">
-        <v>-0.0422572163933037</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>0.1943926134830137</v>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>0.2366498298763174</v>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>0.7532195145960868</v>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>0.7449314332372436</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>-0.00828808135884318</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Significant stress uplift</t>
+          <t>Stable across regimes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B21" s="35" t="n">
-        <v>0.2139108894699562</v>
-      </c>
-      <c r="C21" s="35" t="n">
-        <v>0.2968736681282671</v>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>0.08296277865831087</v>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="n">
+        <v>0.2750935238828958</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0.2323422009434037</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>-0.04275132293949202</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>Moderate stress uplift</t>
+          <t>Stable across regimes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n">
-        <v>0.0194482843814953</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>0.1007620091545305</v>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>0.08131372477303518</v>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
+        <v>0.971354889535758</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>0.8150671969591841</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>-0.1562876925765739</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Moderate stress uplift</t>
+          <t>Stable across regimes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n">
-        <v>0.02522250650681003</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.07165021511635317</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>0.04642770860954314</v>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>1.184029620083211</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>0.9628307198768065</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>-0.2211989002064045</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B24" s="36" t="n">
-        <v>0.9625042408608269</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>0.9793425414193206</v>
-      </c>
-      <c r="D24" s="36" t="n">
-        <v>0.01683830055849378</v>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="n">
-        <v>1.035110339377469</v>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>1.031110052707938</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>-0.004000286669531006</v>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>0.7532197633494774</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>0.7449298939758666</v>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>-0.008289869373610759</v>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B27" s="35" t="n">
-        <v>0.2750954294387477</v>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0.2323437215866302</v>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>-0.04275170785211746</v>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>0.3475645787692835</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>0.2923064843573329</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>-0.05525809441195068</v>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n">
-        <v>0.2662615280266115</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0.1884016479536835</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>-0.07785988007292804</v>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>0.9713542877937703</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>0.8150774240568861</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>-0.1562768637368842</v>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n">
-        <v>1.184029795675607</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>0.9628322446122715</v>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>-0.2211975510633357</v>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Stable across regimes</t>
         </is>
@@ -2663,7 +2430,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2733,16 +2500,16 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>-0.2929242982373964</v>
+        <v/>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.04460231281462567</v>
+        <v>-0.04948767209921656</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-0.1293955141254147</v>
+        <v>-0.1548212961496473</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0.5302180765976217</v>
+        <v>0.2143160465292979</v>
       </c>
     </row>
     <row r="4">
@@ -2752,16 +2519,16 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>-0.2495980726306681</v>
+        <v/>
       </c>
       <c r="C4" s="12" t="n">
-        <v>-0.003713565811961916</v>
+        <v>-0.003713680052704005</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>-0.2018217141761193</v>
+        <v>-0.2018217653802958</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.6016792378990492</v>
+        <v>0.2151526914615902</v>
       </c>
     </row>
     <row r="5">
@@ -2771,16 +2538,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>-0.1830486748285078</v>
+        <v/>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.03683695337861703</v>
+        <v>0.0581581967231346</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.1786484994678725</v>
+        <v>-0.250885602361373</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.5145573060842727</v>
+        <v>0.1374424892823327</v>
       </c>
     </row>
     <row r="6">
@@ -2790,16 +2557,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-0.1665091655061418</v>
+        <v/>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.01971956610018144</v>
+        <v>0.0378862523994854</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-0.1449286097236309</v>
+        <v>-0.1806387327290133</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3378735970052109</v>
+        <v>0.1274251187978204</v>
       </c>
     </row>
     <row r="7">
@@ -2809,16 +2576,16 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>-0.1050506428004342</v>
+        <v/>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.02485925553436985</v>
+        <v>0.05676145018542478</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>-0.1166178609836621</v>
+        <v>-0.1583714697754696</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.3183738177155639</v>
+        <v>0.09376517010863307</v>
       </c>
     </row>
   </sheetData>
@@ -2835,7 +2602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2910,19 +2677,19 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C4" s="35" t="n">
-        <v>0.07604848222125912</v>
-      </c>
-      <c r="D4" s="35" t="n">
-        <v>0.005849883247789164</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>0.07664168083031668</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>0.008515742314479631</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.1129636311829188</v>
+        <v>0.1437031813131897</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9718498340506939</v>
       </c>
     </row>
     <row r="5">
@@ -2932,19 +2699,19 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C5" s="36" t="n">
-        <v>0.08671094150982253</v>
-      </c>
-      <c r="D5" s="36" t="n">
-        <v>0.006670072423832504</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <v>0.08782259806744334</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>0.009758066451938149</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.1288018186574803</v>
+        <v>0.1646674054738244</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.9005691996051071</v>
       </c>
     </row>
     <row r="6">
@@ -2954,19 +2721,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>0.09160479264684693</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0.007046522511295919</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0.09343994377207028</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>0.01038221597467448</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1360712233682609</v>
+        <v>0.17519993085095</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8647854557196933</v>
       </c>
     </row>
     <row r="7">
@@ -2976,19 +2743,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C7" s="36" t="n">
-        <v>0.08975643374929826</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>0.006904341057638329</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <v>0.09133108763780659</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>0.01014789862642295</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.1333256415144526</v>
+        <v>0.1712458247804364</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6547261440685357</v>
       </c>
     </row>
     <row r="8">
@@ -2998,19 +2765,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>-0.01890725699586819</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>-0.001454404384297553</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>-0.01422440861340878</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>-0.001580489845934309</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.02808514178820586</v>
+        <v>-0.0266707716728077</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9800393733856876</v>
       </c>
     </row>
     <row r="9">
@@ -3020,19 +2787,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C9" s="36" t="n">
-        <v>0.009951105476017614</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>0.0007654696520013551</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>0.01048969378157021</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>0.001165521531285578</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.0147815311498871</v>
+        <v>0.01966817991309695</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.8261569337194916</v>
       </c>
     </row>
     <row r="10">
@@ -3042,19 +2809,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C10" s="35" t="n">
-        <v>0.01592770997060341</v>
-      </c>
-      <c r="D10" s="35" t="n">
-        <v>0.001225208459277186</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0.01878514918907328</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>0.00208723879878592</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0236592750066058</v>
+        <v>0.03522216202289886</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.6542475904087065</v>
       </c>
     </row>
     <row r="11">
@@ -3064,19 +2831,19 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>0.08804865704708366</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>0.006772973619006437</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>0.09287907293206586</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>0.01031989699245176</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1307888827009042</v>
+        <v>0.1741482978081821</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.6432518675233434</v>
       </c>
     </row>
     <row r="12">
@@ -3086,773 +2853,751 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>0.075133417224411</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0.005779493632647001</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>0.07616840530007137</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>0.008463156144452373</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1116043790086071</v>
+        <v>0.1428157895102292</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.4797912934834942</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>0.03992411329824733</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>0.003071085638326719</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.05930391610981455</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.4913807456936256</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <v>0.0273652664115515</v>
-      </c>
-      <c r="D14" s="35" t="n">
-        <v>0.002105020493196269</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0.04064880418182311</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0.7487919560463553</v>
-      </c>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>60/40 — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>0.05235587803403795</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>0.004027375233387536</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>0.07777025817934882</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>0.4284467817562575</v>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Private Real Estate</t>
+          <t>US Large Cap Equity</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0.03929254921739969</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0.003022503785953823</v>
+        <v>0.12</v>
+      </c>
+      <c r="C16" s="33" t="n">
+        <v>0.07480404287209469</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>0.008976485144651363</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05836578072810264</v>
+        <v>0.1582967093658338</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.9718498340506939</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>0.08443784634742667</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>0.0101325415616912</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0.1786832998530584</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0.9005691996051071</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>60/40 — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="6" t="n"/>
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>0.091633228354804</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>0.01099598740257648</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>0.1939098203814409</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.8647854557196933</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>0.08827070665032773</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>0.01059248479803933</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0.18679421405118</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0.6547261440685357</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>US Large Cap Equity</t>
+          <t>Long Duration Treasury</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C20" s="35" t="n">
-        <v>0.07489545797820696</v>
-      </c>
-      <c r="D20" s="35" t="n">
-        <v>0.008987454957384835</v>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>-0.001968814218307936</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>-0.0002625085624410581</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1592867957876898</v>
+        <v>-0.004629233040009552</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9800393733856876</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>US Mid Cap Equity</t>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>0.08397471326890485</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>0.01007696559226858</v>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>0.01159941221845756</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>0.001546588295794342</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.1785964511717921</v>
+        <v>0.02727346327909126</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8261569337194916</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>US Small Cap Equity</t>
+          <t>Investment Grade Credit</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C22" s="35" t="n">
-        <v>0.09111479827874773</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>0.01093377579344973</v>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>0.02377789275031428</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>0.003170385700041904</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.193781901579219</v>
+        <v>0.05590847816822411</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.6542475904087065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Emerging Market Equity</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C23" s="36" t="n">
-        <v>0.08745089141391921</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>0.0104941069696703</v>
+      <c r="C23" s="34" t="n">
+        <v>0.09628952361557561</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>0.01155474283386907</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.1859895467379832</v>
+        <v>0.203763247941181</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6432518675233434</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C24" s="35" t="n">
-        <v>-0.002026303910268667</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>-0.000270173854702489</v>
+        <v>0</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>0.04900614811888308</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-0.004788355304724739</v>
+        <v>0</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.9800395309996239</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C25" s="36" t="n">
-        <v>0.01128184223015831</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>0.001504245630687774</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>0.02666010207850974</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.4913807456936256</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>0.02366079429953975</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0.003154772573271966</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0.05591278254167711</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>0.6542475111182804</v>
-      </c>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MVO — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>0.0961829439959918</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>0.01154195327951901</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>0.2045607754078538</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>0.6432514443485702</v>
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>US Large Cap Equity</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="35" t="n">
-        <v>0.04363145447238432</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>0</v>
+        <v>0.1113000326304729</v>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>0.05525967850759534</v>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>0.006150404021044805</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0</v>
+        <v>0.1232608271314797</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.9718498340506939</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>High Yield Credit</t>
+          <t>US Mid Cap Equity</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>0.03736801761619855</v>
-      </c>
-      <c r="D29" s="36" t="n">
-        <v>0</v>
+        <v>1.182884879237745e-07</v>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>0.05849008269077163</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>6.918703440027913e-09</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>0</v>
+        <v>1.386583882582699e-07</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.9005691996051071</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>US Small Cap Equity</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="35" t="n">
-        <v>0.02593079077558953</v>
-      </c>
-      <c r="D30" s="35" t="n">
-        <v>0</v>
+        <v>3.383969452262664e-08</v>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>0.0626857816860128</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>2.121267703166737e-09</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0</v>
+        <v>4.251252613079699e-08</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8647854557196933</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>Private Equity</t>
+          <t>Emerging Market Equity</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>0.03961123437025107</v>
-      </c>
-      <c r="D31" s="36" t="n">
-        <v>0</v>
+        <v>0.1941851828535534</v>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>0.07269128437007231</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>0.01411557034726214</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0</v>
+        <v>0.2828914768009913</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.6547261440685357</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>Private Real Estate</t>
+          <t>Long Duration Treasury</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>0.01678542567237088</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>0</v>
+        <v>0.3499996938711326</v>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>0.03028038966751817</v>
+      </c>
+      <c r="D32" s="33" t="n">
+        <v>0.01059812711392997</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0</v>
+        <v>0.2123980651738803</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.9800393733856876</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n">
+        <v>0.1013184647973846</v>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>0.01675403652588427</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>0.001697493259961901</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>0.03401962254139395</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0.8261569337194916</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>MVO — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="6" t="n"/>
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>0.04962229361749572</v>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>0.0312707736028073</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>0.001551727509364738</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.03109831738411177</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0.6542475904087065</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="n">
+        <v>0.17363643054771</v>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>0.08842281076561428</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>0.01535342124033689</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>0.3076993633111713</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0.6432518675233434</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>US Large Cap Equity</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>1.540461288441797e-08</v>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>0.05604810820385785</v>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>8.633994097844016e-10</v>
+        <v>0.01993774955406831</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>0.02160335653579116</v>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>0.0004307223121378489</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1.958958153830204e-08</v>
+        <v>0.008632146486057308</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.9718498340506938</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>1.286140172707754e-08</v>
-      </c>
-      <c r="C37" s="36" t="n">
-        <v>0.05994390698587128</v>
-      </c>
-      <c r="D37" s="36" t="n">
-        <v>7.709626688358602e-10</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>1.749229370902436e-08</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.4913807456936256</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n">
-        <v>1.034391777355504e-08</v>
-      </c>
-      <c r="C38" s="35" t="n">
-        <v>0.06375923942128729</v>
-      </c>
-      <c r="D38" s="35" t="n">
-        <v>6.595203298782051e-10</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>1.496378979636218e-08</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>0.8647852106386994</v>
-      </c>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Risk Parity — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="6" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>0.07113737017120696</v>
-      </c>
-      <c r="C39" s="36" t="n">
-        <v>0.0671713405534603</v>
-      </c>
-      <c r="D39" s="36" t="n">
-        <v>0.004778392517847712</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>0.1084164626354847</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>0.6547256214279519</v>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
+          <t>US Large Cap Equity</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.2963200956729828</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0.02027839680564917</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0.00600889648154467</v>
+        <v>0.07066834344722557</v>
+      </c>
+      <c r="C40" s="33" t="n">
+        <v>0.06189973281410109</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>0.004374351577798394</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1363352421214061</v>
+        <v>0.1111060815861452</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9718498340506939</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>TIPS</t>
+          <t>US Mid Cap Equity</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>9.201562116762712e-09</v>
-      </c>
-      <c r="C41" s="36" t="n">
-        <v>0.01515708195138125</v>
-      </c>
-      <c r="D41" s="36" t="n">
-        <v>1.394688310844975e-10</v>
+        <v>0.06358658755192337</v>
+      </c>
+      <c r="C41" s="34" t="n">
+        <v>0.06879635141332556</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>0.004374525222396313</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.164394146694722e-09</v>
+        <v>0.1111104920617369</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.9005691996051071</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
+          <t>US Small Cap Equity</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8.935097992254681e-09</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>0.02639673412319088</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>2.358574060662035e-10</v>
+        <v>0.06106325534172019</v>
+      </c>
+      <c r="C42" s="33" t="n">
+        <v>0.0716716355372151</v>
+      </c>
+      <c r="D42" s="33" t="n">
+        <v>0.004376503381567673</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5.351344737078344e-09</v>
+        <v>0.1111607361974389</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8647854557196933</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Emerging Market Equity</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.1364634563400894</v>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>0.08498129605168149</v>
-      </c>
-      <c r="D43" s="36" t="n">
-        <v>0.01159684138347285</v>
+        <v>0.05775356931503555</v>
+      </c>
+      <c r="C43" s="34" t="n">
+        <v>0.07569763672300714</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>0.004371808709466574</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.2631195565966681</v>
+        <v>0.1110414941538565</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.6547261440685357</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Long Duration Treasury</t>
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>2.096350137433955e-08</v>
-      </c>
-      <c r="C44" s="35" t="n">
-        <v>0.02052878880749672</v>
-      </c>
-      <c r="D44" s="35" t="n">
-        <v>4.303552923794839e-10</v>
+        <v>0.219456840240033</v>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>0.01993219484577339</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>0.0043742564999021</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>9.764287530162752e-09</v>
+        <v>0.111103666660798</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.9800393733856876</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>High Yield Credit</t>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.1960790013757596</v>
-      </c>
-      <c r="C45" s="36" t="n">
-        <v>0.03660795132295001</v>
-      </c>
-      <c r="D45" s="36" t="n">
-        <v>0.007178050537816456</v>
+        <v>0.2451136482795938</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <v>0.01784709350445088</v>
+      </c>
+      <c r="D45" s="34" t="n">
+        <v>0.004374566200062996</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.1628620597872786</v>
+        <v>0.1111115328715339</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8261569337194916</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
+          <t>Investment Grade Credit</t>
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>1.618598277387212e-09</v>
-      </c>
-      <c r="C46" s="35" t="n">
-        <v>0.02013819062703088</v>
-      </c>
-      <c r="D46" s="35" t="n">
-        <v>3.259564065860747e-11</v>
+        <v>0.1447863145280247</v>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>0.03021220785439191</v>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>0.004374314228992046</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>7.395591811146036e-10</v>
+        <v>0.1111051329473695</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.6542475904087065</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>Private Equity</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.2822620050016704</v>
-      </c>
-      <c r="C47" s="36" t="n">
-        <v>0.04946939446322386</v>
-      </c>
-      <c r="D47" s="36" t="n">
-        <v>0.0139633304674081</v>
+        <v>0.05237042256659726</v>
+      </c>
+      <c r="C47" s="34" t="n">
+        <v>0.0835333836812642</v>
+      </c>
+      <c r="D47" s="34" t="n">
+        <v>0.004374678601805506</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.3168125871267995</v>
+        <v>0.1111143878128781</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.6432518675233434</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>Private Real Estate</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.01773799210959868</v>
-      </c>
-      <c r="C48" s="35" t="n">
-        <v>0.03094508737001761</v>
-      </c>
-      <c r="D48" s="35" t="n">
-        <v>0.0005489037156002144</v>
+        <v>0.0852010187298466</v>
+      </c>
+      <c r="C48" s="33" t="n">
+        <v>0.05136020669527075</v>
+      </c>
+      <c r="D48" s="33" t="n">
+        <v>0.004375941932612556</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.01245402066711213</v>
+        <v>0.1111464757082432</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.4913807456936256</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Risk Parity — Marginal and Total Risk Contribution</t>
+          <t>Enhanced HRP — Marginal and Total Risk Contribution</t>
         </is>
       </c>
       <c r="B50" s="5" t="n"/>
@@ -3900,19 +3645,19 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.04239826333525394</v>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>0.06287655228620767</v>
-      </c>
-      <c r="D52" s="35" t="n">
-        <v>0.002665856621443495</v>
+        <v>0.0131031441029488</v>
+      </c>
+      <c r="C52" s="33" t="n">
+        <v>0.03894766068625865</v>
+      </c>
+      <c r="D52" s="33" t="n">
+        <v>0.0005103368104448009</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.0769235281081268</v>
+        <v>0.01734019266614253</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9718498340506939</v>
       </c>
     </row>
     <row r="53">
@@ -3922,19 +3667,19 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.03838122897303223</v>
-      </c>
-      <c r="C53" s="36" t="n">
-        <v>0.06945530211249798</v>
-      </c>
-      <c r="D53" s="36" t="n">
-        <v>0.002665779853770914</v>
+        <v>0.01889748360197973</v>
+      </c>
+      <c r="C53" s="34" t="n">
+        <v>0.04139329986147902</v>
+      </c>
+      <c r="D53" s="34" t="n">
+        <v>0.0007822292053641297</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.07692131297015872</v>
+        <v>0.02657853568954868</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.9005691996051071</v>
       </c>
     </row>
     <row r="54">
@@ -3944,19 +3689,19 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.0370534553973652</v>
-      </c>
-      <c r="C54" s="35" t="n">
-        <v>0.07194606436802295</v>
-      </c>
-      <c r="D54" s="35" t="n">
-        <v>0.002665850287076504</v>
+        <v>0.008125992735504559</v>
+      </c>
+      <c r="C54" s="33" t="n">
+        <v>0.03948168045054935</v>
+      </c>
+      <c r="D54" s="33" t="n">
+        <v>0.0003208278485266763</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.07692334532940817</v>
+        <v>0.01090106884758666</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8647854557196933</v>
       </c>
     </row>
     <row r="55">
@@ -3966,19 +3711,19 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.03526861812873507</v>
-      </c>
-      <c r="C55" s="36" t="n">
-        <v>0.07558698122430507</v>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>0.002665848376303882</v>
+        <v>0.02978057137314431</v>
+      </c>
+      <c r="C55" s="34" t="n">
+        <v>0.05471704480868797</v>
+      </c>
+      <c r="D55" s="34" t="n">
+        <v>0.001629504858252668</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.07692329019389553</v>
+        <v>0.0553672155608159</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6547261440685357</v>
       </c>
     </row>
     <row r="56">
@@ -3988,19 +3733,19 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.1901058368847075</v>
-      </c>
-      <c r="C56" s="35" t="n">
-        <v>0.01402297004707323</v>
-      </c>
-      <c r="D56" s="35" t="n">
-        <v>0.002665848456408041</v>
+        <v>0.06443536846822434</v>
+      </c>
+      <c r="C56" s="33" t="n">
+        <v>0.04035307816359169</v>
+      </c>
+      <c r="D56" s="33" t="n">
+        <v>0.002600165460298088</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.07692329250530809</v>
+        <v>0.08834826162377085</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9800393733856876</v>
       </c>
     </row>
     <row r="57">
@@ -4010,19 +3755,19 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.1561033628971746</v>
-      </c>
-      <c r="C57" s="36" t="n">
-        <v>0.01707722545808812</v>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>0.002665812322960799</v>
+        <v>0.6177098330959241</v>
+      </c>
+      <c r="C57" s="34" t="n">
+        <v>0.02355606716845942</v>
+      </c>
+      <c r="D57" s="34" t="n">
+        <v>0.01455081431902545</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.07692224987149869</v>
+        <v>0.4944066713926716</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.8261569337194916</v>
       </c>
     </row>
     <row r="58">
@@ -4032,19 +3777,19 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.09891989158807808</v>
-      </c>
-      <c r="C58" s="35" t="n">
-        <v>0.02695041436455389</v>
-      </c>
-      <c r="D58" s="35" t="n">
-        <v>0.002665932067195453</v>
+        <v>0.1996560638318086</v>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>0.03480302416962155</v>
+      </c>
+      <c r="D58" s="33" t="n">
+        <v>0.006948634815149939</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.07692570510195859</v>
+        <v>0.2361002851359047</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.6542475904087065</v>
       </c>
     </row>
     <row r="59">
@@ -4054,19 +3799,19 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.03310675547604956</v>
-      </c>
-      <c r="C59" s="36" t="n">
-        <v>0.08052175975620805</v>
-      </c>
-      <c r="D59" s="36" t="n">
-        <v>0.002665814210749987</v>
+        <v>0.02725816753926526</v>
+      </c>
+      <c r="C59" s="34" t="n">
+        <v>0.05923205736966428</v>
+      </c>
+      <c r="D59" s="34" t="n">
+        <v>0.001614557343477681</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.07692230434382233</v>
+        <v>0.05485932982580027</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.6432518675233434</v>
       </c>
     </row>
     <row r="60">
@@ -4076,447 +3821,29 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.05454871770448565</v>
-      </c>
-      <c r="C60" s="35" t="n">
-        <v>0.04887037300574652</v>
-      </c>
-      <c r="D60" s="35" t="n">
-        <v>0.002665816181203382</v>
+        <v>0.02103337525120018</v>
+      </c>
+      <c r="C60" s="33" t="n">
+        <v>0.02252567322576673</v>
+      </c>
+      <c r="D60" s="33" t="n">
+        <v>0.0004737909377434645</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.07692236120142895</v>
+        <v>0.01609843925775884</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.4797912934834942</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n">
-        <v>0.07131481415928038</v>
-      </c>
-      <c r="C61" s="36" t="n">
-        <v>0.03738288332119384</v>
-      </c>
-      <c r="D61" s="36" t="n">
-        <v>0.002665953376789001</v>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>0.07692631999216128</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>0.6813173339403511</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="n">
-        <v>0.1147079339099366</v>
-      </c>
-      <c r="C62" s="35" t="n">
-        <v>0.0232394915358965</v>
-      </c>
-      <c r="D62" s="35" t="n">
-        <v>0.002665754059200145</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.07692056866554249</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>0.7487919560463553</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="n">
-        <v>0.06079007889326719</v>
-      </c>
-      <c r="C63" s="36" t="n">
-        <v>0.04385430184744837</v>
-      </c>
-      <c r="D63" s="36" t="n">
-        <v>0.002665906469115539</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>0.07692496646710331</v>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>0.4284467817562575</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="n">
-        <v>0.06730104265263419</v>
-      </c>
-      <c r="C64" s="35" t="n">
-        <v>0.0396094981648834</v>
-      </c>
-      <c r="D64" s="35" t="n">
-        <v>0.002665760525444253</v>
-      </c>
-      <c r="E64" s="9" t="n">
-        <v>0.07692075524958694</v>
-      </c>
-      <c r="F64" s="9" t="n">
-        <v>0.1297114447333514</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>Enhanced HRP — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="n"/>
-      <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="6" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="n">
-        <v>0.01418954230934598</v>
-      </c>
-      <c r="C68" s="35" t="n">
-        <v>0.0621455954800322</v>
-      </c>
-      <c r="D68" s="35" t="n">
-        <v>0.0008818175564034171</v>
-      </c>
-      <c r="E68" s="9" t="n">
-        <v>0.03108986518121491</v>
-      </c>
-      <c r="F68" s="9" t="n">
-        <v>0.9718498340506938</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n">
-        <v>0.01071962159834464</v>
-      </c>
-      <c r="C69" s="36" t="n">
-        <v>0.06881032714615799</v>
-      </c>
-      <c r="D69" s="36" t="n">
-        <v>0.0007376206690651157</v>
-      </c>
-      <c r="E69" s="12" t="n">
-        <v>0.0260059770749458</v>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>0.9005695345361184</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="n">
-        <v>0.01785691413064642</v>
-      </c>
-      <c r="C70" s="35" t="n">
-        <v>0.0699804705840664</v>
-      </c>
-      <c r="D70" s="35" t="n">
-        <v>0.001249635254041901</v>
-      </c>
-      <c r="E70" s="9" t="n">
-        <v>0.04405785674342171</v>
-      </c>
-      <c r="F70" s="9" t="n">
-        <v>0.8647852106386994</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B71" s="12" t="n">
-        <v>0.01018151128031412</v>
-      </c>
-      <c r="C71" s="36" t="n">
-        <v>0.07713721713992762</v>
-      </c>
-      <c r="D71" s="36" t="n">
-        <v>0.0007853734464422128</v>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>0.02768957636359879</v>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>0.6547256214279519</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="n">
-        <v>0.0596596557957153</v>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>0.01185652218885514</v>
-      </c>
-      <c r="D72" s="35" t="n">
-        <v>0.0007073560327213587</v>
-      </c>
-      <c r="E72" s="9" t="n">
-        <v>0.02493894970987092</v>
-      </c>
-      <c r="F72" s="9" t="n">
-        <v>0.9800395309996239</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="n">
-        <v>0.3316397889964033</v>
-      </c>
-      <c r="C73" s="36" t="n">
-        <v>0.01854942338164661</v>
-      </c>
-      <c r="D73" s="36" t="n">
-        <v>0.00615172685629423</v>
-      </c>
-      <c r="E73" s="12" t="n">
-        <v>0.2168888079002477</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>0.8261546883028913</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="n">
-        <v>0.1092060125556164</v>
-      </c>
-      <c r="C74" s="35" t="n">
-        <v>0.02838237345122105</v>
-      </c>
-      <c r="D74" s="35" t="n">
-        <v>0.003099525831472238</v>
-      </c>
-      <c r="E74" s="9" t="n">
-        <v>0.109278659203832</v>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>0.6542475111182804</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="n">
-        <v>0.009319148736044227</v>
-      </c>
-      <c r="C75" s="36" t="n">
-        <v>0.07416805794013157</v>
-      </c>
-      <c r="D75" s="36" t="n">
-        <v>0.0006911831634076319</v>
-      </c>
-      <c r="E75" s="12" t="n">
-        <v>0.02436874975988586</v>
-      </c>
-      <c r="F75" s="12" t="n">
-        <v>0.6432514443485702</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="18" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="n">
-        <v>0.01805983719241161</v>
-      </c>
-      <c r="C76" s="35" t="n">
-        <v>0.04543999203099216</v>
-      </c>
-      <c r="D76" s="35" t="n">
-        <v>0.0008206388581041992</v>
-      </c>
-      <c r="E76" s="9" t="n">
-        <v>0.02893291392948143</v>
-      </c>
-      <c r="F76" s="9" t="n">
-        <v>0.4797912934834942</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B77" s="12" t="n">
-        <v>0.1483922296615784</v>
-      </c>
-      <c r="C77" s="36" t="n">
-        <v>0.04167679313253376</v>
-      </c>
-      <c r="D77" s="36" t="n">
-        <v>0.006184512258081044</v>
-      </c>
-      <c r="E77" s="12" t="n">
-        <v>0.2180447088165566</v>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>0.6813173339403511</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="n">
-        <v>0.2280024325953268</v>
-      </c>
-      <c r="C78" s="35" t="n">
-        <v>0.02412051657055184</v>
-      </c>
-      <c r="D78" s="35" t="n">
-        <v>0.005499536453541706</v>
-      </c>
-      <c r="E78" s="9" t="n">
-        <v>0.1938948092586715</v>
-      </c>
-      <c r="F78" s="9" t="n">
-        <v>0.7487919560463553</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="21" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="n">
-        <v>0.02821942763967997</v>
-      </c>
-      <c r="C79" s="36" t="n">
-        <v>0.04155512604382863</v>
-      </c>
-      <c r="D79" s="36" t="n">
-        <v>0.001172661872451602</v>
-      </c>
-      <c r="E79" s="12" t="n">
-        <v>0.04134403908487444</v>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>0.4284467817562575</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="18" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="n">
-        <v>0.01455387750857305</v>
-      </c>
-      <c r="C80" s="35" t="n">
-        <v>0.02624160233260154</v>
-      </c>
-      <c r="D80" s="35" t="n">
-        <v>0.0003819170659773675</v>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>0.01346508697339823</v>
-      </c>
-      <c r="F80" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.4913807456936256</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4529,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4542,10 +3869,6 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4562,1095 +3885,779 @@
       <c r="G1" s="5" t="n"/>
       <c r="H1" s="5" t="n"/>
       <c r="I1" s="5" t="n"/>
-      <c r="J1" s="5" t="n"/>
-      <c r="K1" s="5" t="n"/>
-      <c r="L1" s="5" t="n"/>
-      <c r="M1" s="5" t="n"/>
-      <c r="N1" s="6" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="D2" s="37" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="E2" s="37" t="inlineStr">
+      <c r="E2" s="35" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="F2" s="37" t="inlineStr">
+      <c r="F2" s="35" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="G2" s="37" t="inlineStr">
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="H2" s="37" t="inlineStr">
+      <c r="H2" s="35" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
+      <c r="I2" s="35" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="J2" s="37" t="inlineStr">
+      <c r="J2" s="35" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="K2" s="37" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="L2" s="37" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="M2" s="37" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="N2" s="37" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="39" t="n">
+      <c r="B3" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="40" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="D3" s="40" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="E3" s="40" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="F3" s="41" t="n">
-        <v>-0.345</v>
-      </c>
-      <c r="G3" s="42" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="H3" s="42" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="I3" s="40" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="J3" s="43" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="K3" s="40" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="L3" s="40" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="M3" s="43" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="N3" s="42" t="n">
-        <v>0.19</v>
+      <c r="C3" s="38" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="D3" s="38" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E3" s="38" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F3" s="39" t="n">
+        <v>-0.344</v>
+      </c>
+      <c r="G3" s="40" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="H3" s="40" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="I3" s="38" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="J3" s="41" t="n">
+        <v>0.512</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="40" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="C4" s="39" t="n">
+      <c r="B4" s="38" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="C4" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="40" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="E4" s="40" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F4" s="41" t="n">
-        <v>-0.401</v>
-      </c>
-      <c r="G4" s="42" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="H4" s="42" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="I4" s="40" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="J4" s="43" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="K4" s="40" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="L4" s="40" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="M4" s="43" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="N4" s="42" t="n">
-        <v>0.198</v>
+      <c r="D4" s="38" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="E4" s="38" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F4" s="39" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G4" s="40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H4" s="40" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="I4" s="38" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="J4" s="41" t="n">
+        <v>0.553</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="C5" s="40" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="D5" s="39" t="n">
+      <c r="B5" s="38" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="C5" s="38" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="D5" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="40" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="F5" s="41" t="n">
+      <c r="E5" s="38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="39" t="n">
         <v>-0.382</v>
       </c>
-      <c r="G5" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H5" s="42" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="I5" s="40" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="L5" s="40" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="M5" s="43" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="N5" s="42" t="n">
-        <v>0.163</v>
+      <c r="G5" s="40" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="I5" s="38" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="J5" s="41" t="n">
+        <v>0.468</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="40" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="E6" s="39" t="n">
+      <c r="B6" s="38" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="C6" s="38" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E6" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="41" t="n">
-        <v>-0.312</v>
-      </c>
-      <c r="G6" s="42" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H6" s="42" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="I6" s="43" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="J6" s="43" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K6" s="43" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="M6" s="43" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="N6" s="42" t="n">
-        <v>0.178</v>
+      <c r="F6" s="39" t="n">
+        <v>-0.308</v>
+      </c>
+      <c r="G6" s="40" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="I6" s="41" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="J6" s="41" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
-        <v>-0.345</v>
-      </c>
-      <c r="C7" s="41" t="n">
-        <v>-0.401</v>
-      </c>
-      <c r="D7" s="41" t="n">
+      <c r="B7" s="39" t="n">
+        <v>-0.344</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D7" s="39" t="n">
         <v>-0.382</v>
       </c>
-      <c r="E7" s="41" t="n">
-        <v>-0.312</v>
-      </c>
-      <c r="F7" s="39" t="n">
+      <c r="E7" s="39" t="n">
+        <v>-0.308</v>
+      </c>
+      <c r="F7" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="43" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="I7" s="42" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="J7" s="41" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="K7" s="42" t="n">
-        <v>-0.177</v>
-      </c>
-      <c r="L7" s="41" t="n">
-        <v>-0.337</v>
-      </c>
-      <c r="M7" s="41" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="N7" s="42" t="n">
-        <v>-0.139</v>
+      <c r="G7" s="41" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H7" s="41" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="I7" s="40" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="J7" s="39" t="n">
+        <v>-0.536</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="38" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="C8" s="42" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="G8" s="39" t="n">
+      <c r="B8" s="40" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="C8" s="40" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="40" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="F8" s="41" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="G8" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="43" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>0.172</v>
+      <c r="H8" s="41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J8" s="40" t="n">
+        <v>0.115</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="C9" s="42" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="E9" s="42" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="H9" s="39" t="n">
+      <c r="B9" s="40" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="F9" s="41" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="G9" s="41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H9" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>-0.075</v>
+      <c r="I9" s="40" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>-0.131</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I10" s="39" t="n">
+      <c r="B10" s="38" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="C10" s="38" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E10" s="41" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="F10" s="40" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="I10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="42" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K10" s="43" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="L10" s="43" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="M10" s="43" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="N10" s="42" t="n">
-        <v>0.152</v>
+      <c r="J10" s="40" t="n">
+        <v>0.293</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B11" s="43" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="J11" s="39" t="n">
+      <c r="B11" s="41" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="C11" s="41" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="D11" s="41" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="E11" s="41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>-0.536</v>
+      </c>
+      <c r="G11" s="40" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>-0.131</v>
+      </c>
+      <c r="I11" s="40" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="J11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="42" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="N11" s="42" t="n">
-        <v>0.205</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B12" s="40" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="D12" s="43" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>-0.177</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I12" s="43" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="40" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="M12" s="43" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>0.176</v>
-      </c>
-    </row>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
     <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="E13" s="40" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="F13" s="41" t="n">
-        <v>-0.337</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="K13" s="40" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="L13" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>0.198</v>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Notable Correlation Pairs</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="C14" s="43" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="D14" s="43" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="F14" s="41" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="I14" s="43" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="K14" s="43" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="L14" s="43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="M14" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="43" t="n">
-        <v>0.441</v>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Asset A</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Asset B</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Implication</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C15" s="42" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>-0.139</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>-0.075</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="M15" s="43" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="N15" s="39" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1"/>
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>0.96360466770692</v>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>0.9585938725922083</v>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Notable Correlation Pairs</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>0.9351150389158752</v>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Asset A</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Asset B</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Correlation</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Implication</t>
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>0.8153011671069538</v>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>0.7921833148274291</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>0.756686346400972</v>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0.7550181047695816</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>0.7503301762560417</v>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
-        <v>0.9566682674249671</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>0.7467845731139183</v>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.6253590242908137</v>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0.6118581657309232</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>0.5930083533390097</v>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>Moderate Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Moderate diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>0.9564794466324271</v>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="C21" s="35" t="n">
-        <v>0.9327840363384619</v>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>0.8818708712318351</v>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.8772590564733882</v>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>0.8442031212496387</v>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>0.8378878973040726</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>0.8114105175622477</v>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0.7802907386399155</v>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>0.5532735406938195</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Moderate Positive</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>Low diversification benefit</t>
+          <t>Moderate diversification benefit</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>0.7527255327493332</v>
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>-0.5361296218117397</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Low diversification benefit</t>
+          <t>Hedging relationship</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0.7403645624314058</v>
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>0.528597871691144</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
-          <t>Strong Positive</t>
+          <t>Moderate Positive</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>0.7359354048313766</v>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>0.7346778006636191</v>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>0.7315398350882377</v>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
-        <v>0.7186127346808743</v>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E33" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
+          <t>Moderate diversification benefit</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5723,20 +4730,20 @@
           <t>Equal Weight</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
-        <v>0.4636952933150726</v>
-      </c>
-      <c r="C3" s="35" t="n">
-        <v>0.213020599450317</v>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>2.15396460797892</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>3.246662089897637</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>0.007778258572596125</v>
+      <c r="B3" s="33" t="n">
+        <v>0.5927324628348662</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>0.2495525907280696</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>2.460423059424298</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>1.997183727022387</v>
+      </c>
+      <c r="F3" s="33" t="n">
+        <v>-0.02007599367985166</v>
       </c>
     </row>
     <row r="4">
@@ -5745,20 +4752,20 @@
           <t>60/40</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
-        <v>0.6313817072904651</v>
-      </c>
-      <c r="C4" s="36" t="n">
-        <v>0.3361745051400977</v>
-      </c>
-      <c r="D4" s="36" t="n">
-        <v>2.146979458188246</v>
-      </c>
-      <c r="E4" s="36" t="n">
-        <v>0.3615911096991364</v>
-      </c>
-      <c r="F4" s="36" t="n">
-        <v>-0.02618469033086921</v>
+      <c r="B4" s="34" t="n">
+        <v>0.6313816852499345</v>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>0.3361744377105355</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>2.146979762765747</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>0.3615968606782248</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>-0.0261846790514917</v>
       </c>
     </row>
     <row r="5">
@@ -5767,20 +4774,20 @@
           <t>MVO</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
-        <v>0.3416089365452504</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>0.4623755448547925</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>2.731154020882983</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>0.8990702173391955</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0.02485752388917111</v>
+      <c r="B5" s="33" t="n">
+        <v>0.4597385026027135</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0.5803733430961843</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>2.856649546801769</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>0.02930984789698554</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>-0.04492216535560389</v>
       </c>
     </row>
     <row r="6">
@@ -5789,20 +4796,20 @@
           <t>Risk Parity</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
-        <v>0.2828260983022897</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>0.3733154718682769</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>1.232021384734952</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>3.096735624995443</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>0.0128324700331053</v>
+      <c r="B6" s="34" t="n">
+        <v>0.359180629674831</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>0.4308581354864889</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>1.337789206419006</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>2.361603006797575</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>-0.009980878555596838</v>
       </c>
     </row>
     <row r="7">
@@ -5811,20 +4818,20 @@
           <t>Enhanced HRP</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
-        <v>0.2024684798488106</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>0.3213380633688086</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>0.8611775407281035</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>3.585820188471193</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0.02721739711619306</v>
+      <c r="B7" s="33" t="n">
+        <v>0.1620839697497295</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0.4610386885106495</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>0.5164427744334301</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>4.113333203526983</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>-0.007163486376460381</v>
       </c>
     </row>
   </sheetData>

--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,6 +88,11 @@
     <font>
       <name val="Arial"/>
       <color rgb="00B7770D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001E7B45"/>
       <sz val="10"/>
     </font>
     <font>
@@ -318,16 +323,16 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -339,25 +344,25 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1019,25 +1024,25 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.07378527590086548</v>
+        <v>0.07378527980854011</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.1102367794102579</v>
+        <v>0.1102367739317823</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.4865415659165658</v>
+        <v>0.4865416255444058</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.6069203385934979</v>
+        <v>0.6069202987975629</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.1958991860781159</v>
+        <v>-0.1958990938318969</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.376649221357373</v>
+        <v>0.3766494186637537</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02666080197108656</v>
+        <v>0.02666080497247821</v>
       </c>
     </row>
     <row r="9">
@@ -1047,22 +1052,22 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.07998380339703903</v>
+        <v>0.07998380778198988</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.1069805129364676</v>
+        <v>0.1069805109235594</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.5592916048885708</v>
+        <v>0.5592916564003224</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>0.7881504656053266</v>
+        <v>0.7881504192348465</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>-0.241238590731507</v>
+        <v>-0.2412384953320925</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.3315547614272841</v>
+        <v>0.3315549107197132</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -1075,25 +1080,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.06222171082584271</v>
+        <v>0.07663819523679472</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.0973601500872822</v>
+        <v>0.08321356109257802</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.432119405764338</v>
+        <v>0.6788279923382992</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.5783968614119489</v>
+        <v>0.9323885697872637</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-0.27765624040269</v>
+        <v>-0.2151224545325302</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.2240962088069816</v>
+        <v>0.3562538155458137</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05645299427673103</v>
+        <v>0.06996092679099582</v>
       </c>
     </row>
     <row r="11">
@@ -1103,25 +1108,25 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05336149921976885</v>
+        <v>0.05975307784699102</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.07659729222579761</v>
+        <v>0.0638817408097252</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.4335792771481806</v>
+        <v>0.6199357863454225</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.5934387331649268</v>
+        <v>0.8940035467859482</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-0.2057596347263281</v>
+        <v>-0.1476443968503109</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.2593390063641134</v>
+        <v>0.4047094175038122</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.05369797654498694</v>
+        <v>0.04860572903543283</v>
       </c>
     </row>
     <row r="12">
@@ -1131,25 +1136,25 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.03786650154700966</v>
+        <v>0.04841833252063688</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.06181265212606881</v>
+        <v>0.05539011011202866</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.2866080052005819</v>
+        <v>0.5103407781364672</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.3782437630813464</v>
+        <v>0.6499482531048663</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-0.1798794517404291</v>
+        <v>-0.1602422571166676</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.2105104345195139</v>
+        <v>0.3021570801101792</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.07404845446758664</v>
+        <v>0.067186603360334</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1529,25 +1534,25 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.07378527590086548</v>
+        <v>0.07378527980854011</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>0.1102367794102579</v>
+        <v>0.1102367739317823</v>
       </c>
       <c r="D3" s="24" t="n">
-        <v>0.4865415659165658</v>
+        <v>0.4865416255444058</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.6069203385934979</v>
+        <v>0.6069202987975629</v>
       </c>
       <c r="F3" s="25" t="n">
-        <v>-0.1958991860781159</v>
+        <v>-0.1958990938318969</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.376649221357373</v>
+        <v>0.3766494186637537</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.02666080197108656</v>
+        <v>0.02666080497247821</v>
       </c>
     </row>
     <row r="4">
@@ -1557,22 +1562,22 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.07998380339703903</v>
+        <v>0.07998380778198988</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>0.1069805129364676</v>
+        <v>0.1069805109235594</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>0.5592916048885708</v>
+        <v>0.5592916564003224</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>0.7881504656053266</v>
+        <v>0.7881504192348465</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>-0.241238590731507</v>
+        <v>-0.2412384953320925</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.3315547614272841</v>
+        <v>0.3315549107197132</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -1585,25 +1590,25 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.06222171082584271</v>
+        <v>0.07663819523679472</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.0973601500872822</v>
+        <v>0.08321356109257802</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.432119405764338</v>
+        <v>0.6788279923382992</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.5783968614119489</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>-0.27765624040269</v>
+        <v>0.9323885697872637</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-0.2151224545325302</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.2240962088069816</v>
+        <v>0.3562538155458137</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.05645299427673103</v>
+        <v>0.06996092679099582</v>
       </c>
     </row>
     <row r="6">
@@ -1613,25 +1618,25 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.05336149921976885</v>
+        <v>0.05975307784699102</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.07659729222579761</v>
+        <v>0.0638817408097252</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.4335792771481806</v>
+        <v>0.6199357863454225</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.5934387331649268</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>-0.2057596347263281</v>
+        <v>0.8940035467859482</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-0.1476443968503109</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.2593390063641134</v>
+        <v>0.4047094175038122</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.05369797654498694</v>
+        <v>0.04860572903543283</v>
       </c>
     </row>
     <row r="7">
@@ -1641,25 +1646,25 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.03786650154700966</v>
+        <v>0.04841833252063688</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.06181265212606881</v>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>0.2866080052005819</v>
+        <v>0.05539011011202866</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>0.5103407781364672</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.3782437630813464</v>
+        <v>0.6499482531048663</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-0.1798794517404291</v>
+        <v>-0.1602422571166676</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.2105104345195139</v>
+        <v>0.3021570801101792</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.07404845446758664</v>
+        <v>0.067186603360334</v>
       </c>
     </row>
     <row r="29">
@@ -1701,7 +1706,7 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.02666080197108656</v>
+        <v>0.02666080497247821</v>
       </c>
       <c r="C31" s="29" t="n">
         <v>0.1111111111111111</v>
@@ -1737,10 +1742,10 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.05645299427673103</v>
+        <v>0.06996092679099582</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>0.364425723493131</v>
+        <v>0.3644257856776272</v>
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.05369797654498694</v>
+        <v>0.04860572903543283</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>0.2945578217774981</v>
+        <v>0.2945580612696407</v>
       </c>
       <c r="D34" s="32" t="inlineStr">
         <is>
@@ -1773,10 +1778,10 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.07404845446758664</v>
+        <v>0.067186603360334</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>0.5717326055122662</v>
+        <v>0.571732280411839</v>
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
@@ -1943,25 +1948,25 @@
         </is>
       </c>
       <c r="B4" s="34" t="n">
-        <v>0.971354889535758</v>
+        <v>0.9713543546890465</v>
       </c>
       <c r="C4" s="34" t="n">
-        <v>-0.0279185738583745</v>
+        <v>-0.02791868690570089</v>
       </c>
       <c r="D4" s="34" t="n">
-        <v>1.307574570963585</v>
+        <v>1.307584296732336</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>2.069750684644512</v>
+        <v>2.069745671519761</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>0.03673471269025674</v>
+        <v>0.03673461445983179</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.02838076840528056</v>
+        <v>0.02838075985627555</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>0.9123631766041419</v>
+        <v>0.9123633301070473</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
@@ -1976,25 +1981,25 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>1.184029620083211</v>
+        <v>1.184030233295581</v>
       </c>
       <c r="C5" s="33" t="n">
-        <v>-0.1590181004859705</v>
+        <v>-0.1590173667035335</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>0.6769277744832372</v>
+        <v>0.6769344744648144</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>-2.052810693745579</v>
+        <v>-2.052829348795206</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>-0.01476509282000907</v>
+        <v>-0.01476554280325399</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.02543144571233723</v>
+        <v>0.02543145418845582</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.8712835998068817</v>
+        <v>0.8712834190739561</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
@@ -2009,25 +2014,25 @@
         </is>
       </c>
       <c r="B6" s="34" t="n">
-        <v>0.7532195145960868</v>
+        <v>0.7532192116329343</v>
       </c>
       <c r="C6" s="34" t="n">
-        <v>0.239200635449679</v>
+        <v>0.2392006264404306</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>5.685577809098848</v>
+        <v>5.685559710072019</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>6.296292096835225</v>
+        <v>6.296323430647663</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>-0.0955658312106086</v>
+        <v>-0.09556557578946366</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.0206718781744882</v>
+        <v>0.02067188264244709</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.6355403296685542</v>
+        <v>0.6355401248164949</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
@@ -2042,25 +2047,25 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>0.02522245718052332</v>
+        <v>0.02522360442670393</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1.139232287873908</v>
+        <v>1.13922957972593</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>-0.1657940661604688</v>
+        <v>-0.1658095440767343</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>-2.13589950876659</v>
+        <v>-2.135898143828797</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-0.007930157885479423</v>
+        <v>-0.007930898215471631</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.01148282418385831</v>
+        <v>0.01148281541820169</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.9812438336595104</v>
+        <v>0.981243967023252</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
@@ -2075,25 +2080,25 @@
         </is>
       </c>
       <c r="B8" s="34" t="n">
-        <v>0.01944981703587667</v>
+        <v>0.01944867126558009</v>
       </c>
       <c r="C8" s="34" t="n">
-        <v>0.4459870996647048</v>
+        <v>0.4459868868234478</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>-0.1250823047768445</v>
+        <v>-0.1250762247422195</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>6.421690474074236</v>
+        <v>6.421664708875722</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>-0.005982858425101597</v>
+        <v>-0.005982567608695194</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.008734871552751659</v>
+        <v>0.008734870137983752</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.8015107862181039</v>
+        <v>0.8015088821539471</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
@@ -2108,25 +2113,25 @@
         </is>
       </c>
       <c r="B9" s="33" t="n">
-        <v>0.2750935238828958</v>
+        <v>0.2750960153447685</v>
       </c>
       <c r="C9" s="33" t="n">
-        <v>0.5137949658837728</v>
+        <v>0.5137940982593163</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.2430069382283973</v>
+        <v>0.2429920809566087</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>-0.1456786200674224</v>
+        <v>-0.145757769728357</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.011623355600392</v>
+        <v>0.01162264495667739</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.01057001448042171</v>
+        <v>0.01057001868840936</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.6374633033903678</v>
+        <v>0.6374618458308732</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
@@ -2141,25 +2146,25 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>1.035110447452133</v>
+        <v>1.035110678337744</v>
       </c>
       <c r="C10" s="34" t="n">
-        <v>0.3934959490536423</v>
+        <v>0.3934964445308032</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>9.352440086495633</v>
+        <v>9.352425086801601</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>-8.299662990213015</v>
+        <v>-8.299633141497763</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>-0.1362108916081567</v>
+        <v>-0.1362115190006306</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.0240698586185005</v>
+        <v>0.02406984915621184</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.6337084793755835</v>
+        <v>0.6337083217606877</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2174,25 +2179,25 @@
         </is>
       </c>
       <c r="B11" s="33" t="n">
-        <v>0.1086076548864854</v>
+        <v>0.1086074255047768</v>
       </c>
       <c r="C11" s="33" t="n">
-        <v>-0.322256513988238</v>
+        <v>-0.3222563603329497</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>4.246990685914242</v>
+        <v>4.246994947560707</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>15.42135885368741</v>
+        <v>15.42136218884538</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.0372673088981893</v>
+        <v>0.03726719926776158</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.004127872859151399</v>
+        <v>0.004127876963690224</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.4445765852026022</v>
+        <v>0.4445765743655131</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
@@ -2245,13 +2250,13 @@
         </is>
       </c>
       <c r="B15" s="33" t="n">
-        <v>0.1086076548864854</v>
+        <v>0.1086074255047768</v>
       </c>
       <c r="C15" s="33" t="n">
-        <v>0.815131539955253</v>
+        <v>0.8151360605982694</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>0.7065238850687676</v>
+        <v>0.7065286350934925</v>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
@@ -2266,13 +2271,13 @@
         </is>
       </c>
       <c r="B16" s="34" t="n">
-        <v>0.01944981703587667</v>
+        <v>0.01944867126558009</v>
       </c>
       <c r="C16" s="34" t="n">
-        <v>0.1007609043221211</v>
+        <v>0.1007618020644612</v>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.08131108728624448</v>
+        <v>0.08131313079888108</v>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
@@ -2287,13 +2292,13 @@
         </is>
       </c>
       <c r="B17" s="33" t="n">
-        <v>0.02522245718052332</v>
+        <v>0.02522360442670393</v>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.07165142618821491</v>
+        <v>0.07165818859001716</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>0.04642896900769159</v>
+        <v>0.04643458416331323</v>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
@@ -2329,13 +2334,13 @@
         </is>
       </c>
       <c r="B19" s="33" t="n">
-        <v>1.035110447452133</v>
+        <v>1.035110678337744</v>
       </c>
       <c r="C19" s="33" t="n">
-        <v>1.031109852175071</v>
+        <v>1.031110217491761</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>-0.004000595277062535</v>
+        <v>-0.004000460845982268</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
@@ -2350,13 +2355,13 @@
         </is>
       </c>
       <c r="B20" s="34" t="n">
-        <v>0.7532195145960868</v>
+        <v>0.7532192116329343</v>
       </c>
       <c r="C20" s="34" t="n">
-        <v>0.7449314332372436</v>
+        <v>0.7449323836182584</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>-0.00828808135884318</v>
+        <v>-0.00828682801467584</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
@@ -2371,13 +2376,13 @@
         </is>
       </c>
       <c r="B21" s="33" t="n">
-        <v>0.2750935238828958</v>
+        <v>0.2750960153447685</v>
       </c>
       <c r="C21" s="33" t="n">
-        <v>0.2323422009434037</v>
+        <v>0.2323438705888303</v>
       </c>
       <c r="D21" s="33" t="n">
-        <v>-0.04275132293949202</v>
+        <v>-0.04275214475593819</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
@@ -2392,13 +2397,13 @@
         </is>
       </c>
       <c r="B22" s="34" t="n">
-        <v>0.971354889535758</v>
+        <v>0.9713543546890465</v>
       </c>
       <c r="C22" s="34" t="n">
-        <v>0.8150671969591841</v>
+        <v>0.8150714885287655</v>
       </c>
       <c r="D22" s="34" t="n">
-        <v>-0.1562876925765739</v>
+        <v>-0.156282866160281</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
@@ -2413,13 +2418,13 @@
         </is>
       </c>
       <c r="B23" s="33" t="n">
-        <v>1.184029620083211</v>
+        <v>1.184030233295581</v>
       </c>
       <c r="C23" s="33" t="n">
-        <v>0.9628307198768065</v>
+        <v>0.9628342395707845</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>-0.2211989002064045</v>
+        <v>-0.2211959937247967</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
@@ -2500,16 +2505,16 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v/>
+        <v>-0.3134746014276183</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.04948767209921656</v>
+        <v>-0.04948761433926584</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-0.1548212961496473</v>
+        <v>-0.1548212823410495</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0.2143160465292979</v>
+        <v>0.5954501587549845</v>
       </c>
     </row>
     <row r="4">
@@ -2519,16 +2524,16 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v/>
+        <v>-0.2495977639371679</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>-0.003713680052704005</v>
+        <v>-0.003713611804167738</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>-0.2018217653802958</v>
+        <v>-0.2018217565810658</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.2151526914615902</v>
+        <v>0.6016793798524094</v>
       </c>
     </row>
     <row r="5">
@@ -2538,16 +2543,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v/>
+        <v>-0.1954153004416594</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.0581581967231346</v>
+        <v>0.0468524310147842</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.250885602361373</v>
+        <v>-0.2346489343424729</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.1374424892823327</v>
+        <v>0.4831002441572396</v>
       </c>
     </row>
     <row r="6">
@@ -2557,16 +2562,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v/>
+        <v>-0.1730524664274122</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.0378862523994854</v>
+        <v>0.02429344316360349</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-0.1806387327290133</v>
+        <v>-0.1674660311134522</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.1274251187978204</v>
+        <v>0.3559225224980567</v>
       </c>
     </row>
     <row r="7">
@@ -2576,16 +2581,16 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v/>
+        <v>-0.06759692357441749</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05676145018542478</v>
+        <v>0.05076908147634351</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>-0.1583714697754696</v>
+        <v>-0.1475039470866329</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.09376517010863307</v>
+        <v>0.2180544335778652</v>
       </c>
     </row>
   </sheetData>
@@ -2680,13 +2685,13 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C4" s="33" t="n">
-        <v>0.07664168083031668</v>
+        <v>0.07664168351224593</v>
       </c>
       <c r="D4" s="33" t="n">
-        <v>0.008515742314479631</v>
+        <v>0.008515742612471769</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.1437031813131897</v>
+        <v>0.1437032210168355</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.9718498340506939</v>
@@ -2702,16 +2707,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C5" s="34" t="n">
-        <v>0.08782259806744334</v>
+        <v>0.08782255892101108</v>
       </c>
       <c r="D5" s="34" t="n">
-        <v>0.009758066451938149</v>
+        <v>0.009758062102334564</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.1646674054738244</v>
+        <v>0.1646673718078441</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.9005691996051071</v>
+        <v>0.9005692931844215</v>
       </c>
     </row>
     <row r="6">
@@ -2724,16 +2729,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C6" s="33" t="n">
-        <v>0.09343994377207028</v>
+        <v>0.09343996140347188</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.01038221597467448</v>
+        <v>0.0103822179337191</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.17519993085095</v>
+        <v>0.1752000061849139</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.8647854557196933</v>
+        <v>0.8647853697421607</v>
       </c>
     </row>
     <row r="7">
@@ -2746,16 +2751,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C7" s="34" t="n">
-        <v>0.09133108763780659</v>
+        <v>0.09133107047002956</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>0.01014789862642295</v>
+        <v>0.01014789671889217</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.1712458247804364</v>
+        <v>0.1712458339118004</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.6547261440685357</v>
+        <v>0.654725765269208</v>
       </c>
     </row>
     <row r="8">
@@ -2768,16 +2773,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>-0.01422440861340878</v>
+        <v>-0.01422437146584231</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>-0.001580489845934309</v>
+        <v>-0.001580485718426923</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.0266707716728077</v>
+        <v>-0.0266707084566442</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.9800393733856876</v>
+        <v>0.9800394596124378</v>
       </c>
     </row>
     <row r="9">
@@ -2790,16 +2795,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C9" s="34" t="n">
-        <v>0.01048969378157021</v>
+        <v>0.01048960388641192</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>0.001165521531285578</v>
+        <v>0.001165511542934658</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.01966817991309695</v>
+        <v>0.01966801610545594</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.8261569337194916</v>
+        <v>0.8261549596926778</v>
       </c>
     </row>
     <row r="10">
@@ -2812,16 +2817,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C10" s="33" t="n">
-        <v>0.01878514918907328</v>
+        <v>0.01878512858404903</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>0.00208723879878592</v>
+        <v>0.002087236509338781</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.03522216202289886</v>
+        <v>0.03522213188743362</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.6542475904087065</v>
+        <v>0.654246587683997</v>
       </c>
     </row>
     <row r="11">
@@ -2834,16 +2839,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C11" s="34" t="n">
-        <v>0.09287907293206586</v>
+        <v>0.09287908065450565</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>0.01031989699245176</v>
+        <v>0.01031989785050063</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1741482978081821</v>
+        <v>0.1741483543090792</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.6432518675233434</v>
+        <v>0.6432517319898794</v>
       </c>
     </row>
     <row r="12">
@@ -2856,16 +2861,16 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="C12" s="33" t="n">
-        <v>0.07616840530007137</v>
+        <v>0.07616837823989694</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>0.008463156144452373</v>
+        <v>0.008463153137766327</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1428157895102292</v>
+        <v>0.1428157732332814</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.4913807456936256</v>
+        <v>0.4913808005382763</v>
       </c>
     </row>
     <row r="14">
@@ -2922,13 +2927,13 @@
         <v>0.12</v>
       </c>
       <c r="C16" s="33" t="n">
-        <v>0.07480404287209469</v>
+        <v>0.07480404058153603</v>
       </c>
       <c r="D16" s="33" t="n">
-        <v>0.008976485144651363</v>
+        <v>0.008976484869784323</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.1582967093658338</v>
+        <v>0.158296737888037</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9718498340506939</v>
@@ -2944,16 +2949,16 @@
         <v>0.12</v>
       </c>
       <c r="C17" s="34" t="n">
-        <v>0.08443784634742667</v>
+        <v>0.08443779803315991</v>
       </c>
       <c r="D17" s="34" t="n">
-        <v>0.0101325415616912</v>
+        <v>0.01013253576397919</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.1786832998530584</v>
+        <v>0.178683235279637</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0.9005691996051071</v>
+        <v>0.9005692931844215</v>
       </c>
     </row>
     <row r="18">
@@ -2966,16 +2971,16 @@
         <v>0.12</v>
       </c>
       <c r="C18" s="33" t="n">
-        <v>0.091633228354804</v>
+        <v>0.09163325284247642</v>
       </c>
       <c r="D18" s="33" t="n">
-        <v>0.01099598740257648</v>
+        <v>0.01099599034109717</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1939098203814409</v>
+        <v>0.1939099130777978</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.8647854557196933</v>
+        <v>0.8647853697421607</v>
       </c>
     </row>
     <row r="19">
@@ -2988,16 +2993,16 @@
         <v>0.12</v>
       </c>
       <c r="C19" s="34" t="n">
-        <v>0.08827070665032773</v>
+        <v>0.08827067970023333</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>0.01059248479803933</v>
+        <v>0.010592481564028</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.18679421405118</v>
+        <v>0.1867941963974024</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.6547261440685357</v>
+        <v>0.654725765269208</v>
       </c>
     </row>
     <row r="20">
@@ -3010,16 +3015,16 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C20" s="33" t="n">
-        <v>-0.001968814218307936</v>
+        <v>-0.001968768015688312</v>
       </c>
       <c r="D20" s="33" t="n">
-        <v>-0.0002625085624410581</v>
+        <v>-0.0002625024020917749</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>-0.004629233040009552</v>
+        <v>-0.004629125380556697</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9800393733856876</v>
+        <v>0.9800394596124378</v>
       </c>
     </row>
     <row r="21">
@@ -3032,16 +3037,16 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C21" s="34" t="n">
-        <v>0.01159941221845756</v>
+        <v>0.01159932567640918</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>0.001546588295794342</v>
+        <v>0.001546576756854557</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.02727346327909126</v>
+        <v>0.02727326554380059</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.8261569337194916</v>
+        <v>0.8261549596926778</v>
       </c>
     </row>
     <row r="22">
@@ -3054,16 +3059,16 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>0.02377789275031428</v>
+        <v>0.02377789461211848</v>
       </c>
       <c r="D22" s="33" t="n">
-        <v>0.003170385700041904</v>
+        <v>0.003170385948282464</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.05590847816822411</v>
+        <v>0.05590849433150584</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.6542475904087065</v>
+        <v>0.654246587683997</v>
       </c>
     </row>
     <row r="23">
@@ -3076,16 +3081,16 @@
         <v>0.12</v>
       </c>
       <c r="C23" s="34" t="n">
-        <v>0.09628952361557561</v>
+        <v>0.09628951981970114</v>
       </c>
       <c r="D23" s="34" t="n">
-        <v>0.01155474283386907</v>
+        <v>0.01155474237836414</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.203763247941181</v>
+        <v>0.2037632828623759</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.6432518675233434</v>
+        <v>0.6432517319898794</v>
       </c>
     </row>
     <row r="24">
@@ -3098,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>0.04900614811888308</v>
+        <v>0.04900610376782925</v>
       </c>
       <c r="D24" s="33" t="n">
         <v>0</v>
@@ -3107,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.4913807456936256</v>
+        <v>0.4913808005382763</v>
       </c>
     </row>
     <row r="26">
@@ -3161,16 +3166,16 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.1113000326304729</v>
+        <v>0.1112995622680132</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>0.05525967850759534</v>
+        <v>0.05525968237192978</v>
       </c>
       <c r="D28" s="33" t="n">
-        <v>0.006150404021044805</v>
+        <v>0.006150378459065228</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.1232608271314797</v>
+        <v>0.123260483719362</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.9718498340506939</v>
@@ -3183,19 +3188,19 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>1.182884879237745e-07</v>
+        <v>1.182944781530638e-07</v>
       </c>
       <c r="C29" s="34" t="n">
-        <v>0.05849008269077163</v>
+        <v>0.05849004051353848</v>
       </c>
       <c r="D29" s="34" t="n">
-        <v>6.918703440027913e-09</v>
+        <v>6.919048819700591e-09</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.386583882582699e-07</v>
+        <v>1.386655000290496e-07</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.9005691996051071</v>
+        <v>0.9005692931844215</v>
       </c>
     </row>
     <row r="30">
@@ -3205,19 +3210,19 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>3.383969452262664e-08</v>
+        <v>3.383947803280196e-08</v>
       </c>
       <c r="C30" s="33" t="n">
-        <v>0.0626857816860128</v>
+        <v>0.06268585950187984</v>
       </c>
       <c r="D30" s="33" t="n">
-        <v>2.121267703166737e-09</v>
+        <v>2.121256765581173e-09</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>4.251252613079699e-08</v>
+        <v>4.251236517536906e-08</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.8647854557196933</v>
+        <v>0.8647853697421607</v>
       </c>
     </row>
     <row r="31">
@@ -3227,19 +3232,19 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>0.1941851828535534</v>
+        <v>0.1941851401027252</v>
       </c>
       <c r="C31" s="34" t="n">
-        <v>0.07269128437007231</v>
+        <v>0.07269131211729911</v>
       </c>
       <c r="D31" s="34" t="n">
-        <v>0.01411557034726214</v>
+        <v>0.01411557262774865</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.2828914768009913</v>
+        <v>0.2828919100917447</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.6547261440685357</v>
+        <v>0.654725765269208</v>
       </c>
     </row>
     <row r="32">
@@ -3249,19 +3254,19 @@
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.3499996938711326</v>
+        <v>0.3499996939032552</v>
       </c>
       <c r="C32" s="33" t="n">
-        <v>0.03028038966751817</v>
+        <v>0.03028031615699537</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>0.01059812711392997</v>
+        <v>0.01059810138624217</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.2123980651738803</v>
+        <v>0.2123978405669681</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.9800393733856876</v>
+        <v>0.9800394596124378</v>
       </c>
     </row>
     <row r="33">
@@ -3271,19 +3276,19 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>0.1013184647973846</v>
+        <v>0.101322928358229</v>
       </c>
       <c r="C33" s="34" t="n">
-        <v>0.01675403652588427</v>
+        <v>0.01675398763389107</v>
       </c>
       <c r="D33" s="34" t="n">
-        <v>0.001697493259961901</v>
+        <v>0.001697563088743399</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.03401962254139395</v>
+        <v>0.03402106859850826</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0.8261569337194916</v>
+        <v>0.8261549596926778</v>
       </c>
     </row>
     <row r="34">
@@ -3293,19 +3298,19 @@
         </is>
       </c>
       <c r="B34" s="9" t="n">
-        <v>0.04962229361749572</v>
+        <v>0.04961823822884117</v>
       </c>
       <c r="C34" s="33" t="n">
-        <v>0.0312707736028073</v>
+        <v>0.03127074460076728</v>
       </c>
       <c r="D34" s="33" t="n">
-        <v>0.001551727509364738</v>
+        <v>0.001551599255194119</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.03109831738411177</v>
+        <v>0.03109578963420348</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.6542475904087065</v>
+        <v>0.654246587683997</v>
       </c>
     </row>
     <row r="35">
@@ -3315,19 +3320,19 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>0.17363643054771</v>
+        <v>0.1736368658373325</v>
       </c>
       <c r="C35" s="34" t="n">
-        <v>0.08842281076561428</v>
+        <v>0.08842286006646781</v>
       </c>
       <c r="D35" s="34" t="n">
-        <v>0.01535342124033689</v>
+        <v>0.0153534682903145</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.3076993633111713</v>
+        <v>0.3077007278218259</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0.6432518675233434</v>
+        <v>0.6432517319898794</v>
       </c>
     </row>
     <row r="36">
@@ -3337,19 +3342,19 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01993774955406831</v>
+        <v>0.01993741916764761</v>
       </c>
       <c r="C36" s="33" t="n">
-        <v>0.02160335653579116</v>
+        <v>0.02160331428831735</v>
       </c>
       <c r="D36" s="33" t="n">
-        <v>0.0004307223121378489</v>
+        <v>0.0004307143323766138</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.008632146486057308</v>
+        <v>0.008631998389522265</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.4913807456936256</v>
+        <v>0.4913808005382763</v>
       </c>
     </row>
     <row r="38">
@@ -3403,16 +3408,16 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.07066834344722557</v>
+        <v>0.07066828745635954</v>
       </c>
       <c r="C40" s="33" t="n">
-        <v>0.06189973281410109</v>
+        <v>0.06189971578576542</v>
       </c>
       <c r="D40" s="33" t="n">
-        <v>0.004374351577798394</v>
+        <v>0.004374346908615427</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1111060815861452</v>
+        <v>0.1111060767534358</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.9718498340506939</v>
@@ -3425,19 +3430,19 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>0.06358658755192337</v>
+        <v>0.06358657635061872</v>
       </c>
       <c r="C41" s="34" t="n">
-        <v>0.06879635141332556</v>
+        <v>0.06879628490735507</v>
       </c>
       <c r="D41" s="34" t="n">
-        <v>0.004374525222396313</v>
+        <v>0.004374520222900451</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.1111104920617369</v>
+        <v>0.1111104788437722</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.9005691996051071</v>
+        <v>0.9005692931844215</v>
       </c>
     </row>
     <row r="42">
@@ -3447,19 +3452,19 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.06106325534172019</v>
+        <v>0.06106318561939598</v>
       </c>
       <c r="C42" s="33" t="n">
-        <v>0.0716716355372151</v>
+        <v>0.07167165933255069</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>0.004376503381567673</v>
+        <v>0.004376499837473657</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1111607361974389</v>
+        <v>0.1111607599973496</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.8647854557196933</v>
+        <v>0.8647853697421607</v>
       </c>
     </row>
     <row r="43">
@@ -3469,19 +3474,19 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.05775356931503555</v>
+        <v>0.0577535240921918</v>
       </c>
       <c r="C43" s="34" t="n">
-        <v>0.07569763672300714</v>
+        <v>0.07569760669607641</v>
       </c>
       <c r="D43" s="34" t="n">
-        <v>0.004371808709466574</v>
+        <v>0.004371803552043108</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.1110414941538565</v>
+        <v>0.1110414768539677</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.6547261440685357</v>
+        <v>0.654725765269208</v>
       </c>
     </row>
     <row r="44">
@@ -3491,19 +3496,19 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.219456840240033</v>
+        <v>0.2194568708623782</v>
       </c>
       <c r="C44" s="33" t="n">
-        <v>0.01993219484577339</v>
+        <v>0.01993217108192795</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>0.0043742564999021</v>
+        <v>0.004374251895133492</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.111103666660798</v>
+        <v>0.1111036634617063</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.9800393733856876</v>
+        <v>0.9800394596124378</v>
       </c>
     </row>
     <row r="45">
@@ -3513,19 +3518,19 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.2451136482795938</v>
+        <v>0.2451141804419785</v>
       </c>
       <c r="C45" s="34" t="n">
-        <v>0.01784709350445088</v>
+        <v>0.01784703629190622</v>
       </c>
       <c r="D45" s="34" t="n">
-        <v>0.004374566200062996</v>
+        <v>0.00437456167400884</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.1111115328715339</v>
+        <v>0.1111115316798015</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.8261569337194916</v>
+        <v>0.8261549596926778</v>
       </c>
     </row>
     <row r="46">
@@ -3535,19 +3540,19 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.1447863145280247</v>
+        <v>0.1447859601512068</v>
       </c>
       <c r="C46" s="33" t="n">
-        <v>0.03021220785439191</v>
+        <v>0.03021225020406927</v>
       </c>
       <c r="D46" s="33" t="n">
-        <v>0.004374314228992046</v>
+        <v>0.004374309654124662</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>0.1111051329473695</v>
+        <v>0.1111051305092543</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.6542475904087065</v>
+        <v>0.654246587683997</v>
       </c>
     </row>
     <row r="47">
@@ -3557,19 +3562,19 @@
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.05237042256659726</v>
+        <v>0.05237036521179319</v>
       </c>
       <c r="C47" s="34" t="n">
-        <v>0.0835333836812642</v>
+        <v>0.08353339284924265</v>
       </c>
       <c r="D47" s="34" t="n">
-        <v>0.004374678601805506</v>
+        <v>0.004374674290895031</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.1111143878128781</v>
+        <v>0.1111143920886036</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.6432518675233434</v>
+        <v>0.6432517319898794</v>
       </c>
     </row>
     <row r="48">
@@ -3579,19 +3584,19 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.0852010187298466</v>
+        <v>0.08520104981407732</v>
       </c>
       <c r="C48" s="33" t="n">
-        <v>0.05136020669527075</v>
+        <v>0.05136014188675325</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>0.004375941932612556</v>
+        <v>0.004375938007351343</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.1111464757082432</v>
+        <v>0.111146489812109</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.4913807456936256</v>
+        <v>0.4913808005382763</v>
       </c>
     </row>
     <row r="50">
@@ -3645,16 +3650,16 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.0131031441029488</v>
+        <v>0.01310313745444653</v>
       </c>
       <c r="C52" s="33" t="n">
-        <v>0.03894766068625865</v>
+        <v>0.03894746836907385</v>
       </c>
       <c r="D52" s="33" t="n">
-        <v>0.0005103368104448009</v>
+        <v>0.0005103340315426829</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.01734019266614253</v>
+        <v>0.01734011091038029</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>0.9718498340506939</v>
@@ -3667,19 +3672,19 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.01889748360197973</v>
+        <v>0.01889748527636672</v>
       </c>
       <c r="C53" s="34" t="n">
-        <v>0.04139329986147902</v>
+        <v>0.04139305967161434</v>
       </c>
       <c r="D53" s="34" t="n">
-        <v>0.0007822292053641297</v>
+        <v>0.0007822247356881008</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.02657853568954868</v>
+        <v>0.02657840323262889</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.9005691996051071</v>
+        <v>0.9005692931844215</v>
       </c>
     </row>
     <row r="54">
@@ -3689,19 +3694,19 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.008125992735504559</v>
+        <v>0.008125988522225262</v>
       </c>
       <c r="C54" s="33" t="n">
-        <v>0.03948168045054935</v>
+        <v>0.03948149543843042</v>
       </c>
       <c r="D54" s="33" t="n">
-        <v>0.0003208278485266763</v>
+        <v>0.0003208261787729745</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.01090106884758666</v>
+        <v>0.01090102007514579</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.8647854557196933</v>
+        <v>0.8647853697421607</v>
       </c>
     </row>
     <row r="55">
@@ -3711,19 +3716,19 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.02978057137314431</v>
+        <v>0.02978060544931362</v>
       </c>
       <c r="C55" s="34" t="n">
-        <v>0.05471704480868797</v>
+        <v>0.05471677519182176</v>
       </c>
       <c r="D55" s="34" t="n">
-        <v>0.001629504858252668</v>
+        <v>0.001629498693446435</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.0553672155608159</v>
+        <v>0.05536704653473169</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.6547261440685357</v>
+        <v>0.654725765269208</v>
       </c>
     </row>
     <row r="56">
@@ -3733,19 +3738,19 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.06443536846822434</v>
+        <v>0.06443562047933843</v>
       </c>
       <c r="C56" s="33" t="n">
-        <v>0.04035307816359169</v>
+        <v>0.04035314262922677</v>
       </c>
       <c r="D56" s="33" t="n">
-        <v>0.002600165460298088</v>
+        <v>0.002600179783605468</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.08834826162377085</v>
+        <v>0.0883488128321626</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.9800393733856876</v>
+        <v>0.9800394596124378</v>
       </c>
     </row>
     <row r="57">
@@ -3755,19 +3760,19 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.6177098330959241</v>
+        <v>0.6177106857573594</v>
       </c>
       <c r="C57" s="34" t="n">
-        <v>0.02355606716845942</v>
+        <v>0.02355604513159771</v>
       </c>
       <c r="D57" s="34" t="n">
-        <v>0.01455081431902545</v>
+        <v>0.01455082079197053</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.4944066713926716</v>
+        <v>0.4944072524560491</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.8261569337194916</v>
+        <v>0.8261549596926778</v>
       </c>
     </row>
     <row r="58">
@@ -3777,19 +3782,19 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.1996560638318086</v>
+        <v>0.1996548712353037</v>
       </c>
       <c r="C58" s="33" t="n">
-        <v>0.03480302416962155</v>
+        <v>0.03480311487371655</v>
       </c>
       <c r="D58" s="33" t="n">
-        <v>0.006948634815149939</v>
+        <v>0.006948611418699359</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.2361002851359047</v>
+        <v>0.2360996626251926</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.6542475904087065</v>
+        <v>0.654246587683997</v>
       </c>
     </row>
     <row r="59">
@@ -3799,19 +3804,19 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.02725816753926526</v>
+        <v>0.02725821573980387</v>
       </c>
       <c r="C59" s="34" t="n">
-        <v>0.05923205736966428</v>
+        <v>0.05923194708907975</v>
       </c>
       <c r="D59" s="34" t="n">
-        <v>0.001614557343477681</v>
+        <v>0.001614557192442783</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.05485932982580027</v>
+        <v>0.0548593647644455</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.6432518675233434</v>
+        <v>0.6432517319898794</v>
       </c>
     </row>
     <row r="60">
@@ -3821,19 +3826,19 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.02103337525120018</v>
+        <v>0.02103339008584262</v>
       </c>
       <c r="C60" s="33" t="n">
-        <v>0.02252567322576673</v>
+        <v>0.02252548320671542</v>
       </c>
       <c r="D60" s="33" t="n">
-        <v>0.0004737909377434645</v>
+        <v>0.0004737872751589424</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.01609843925775884</v>
+        <v>0.0160983265692635</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.4913807456936256</v>
+        <v>0.4913808005382763</v>
       </c>
     </row>
   </sheetData>
@@ -4291,7 +4296,7 @@
         </is>
       </c>
       <c r="C15" s="33" t="n">
-        <v>0.96360466770692</v>
+        <v>0.963604579887064</v>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>0.9585938725922083</v>
+        <v>0.9585938857673019</v>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
@@ -4341,7 +4346,7 @@
         </is>
       </c>
       <c r="C17" s="33" t="n">
-        <v>0.9351150389158752</v>
+        <v>0.9351150145885929</v>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
@@ -4366,7 +4371,7 @@
         </is>
       </c>
       <c r="C18" s="34" t="n">
-        <v>0.8153011671069538</v>
+        <v>0.8153008916507385</v>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
@@ -4391,7 +4396,7 @@
         </is>
       </c>
       <c r="C19" s="33" t="n">
-        <v>0.7921833148274291</v>
+        <v>0.7921827030700286</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
@@ -4416,7 +4421,7 @@
         </is>
       </c>
       <c r="C20" s="34" t="n">
-        <v>0.756686346400972</v>
+        <v>0.7566863410399924</v>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
@@ -4441,7 +4446,7 @@
         </is>
       </c>
       <c r="C21" s="33" t="n">
-        <v>0.7550181047695816</v>
+        <v>0.7550185248134618</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
@@ -4466,7 +4471,7 @@
         </is>
       </c>
       <c r="C22" s="34" t="n">
-        <v>0.7503301762560417</v>
+        <v>0.7503296960631181</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
@@ -4491,7 +4496,7 @@
         </is>
       </c>
       <c r="C23" s="33" t="n">
-        <v>0.7467845731139183</v>
+        <v>0.746784625795175</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
@@ -4516,7 +4521,7 @@
         </is>
       </c>
       <c r="C24" s="34" t="n">
-        <v>0.6253590242908137</v>
+        <v>0.6253586382631419</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
@@ -4541,7 +4546,7 @@
         </is>
       </c>
       <c r="C25" s="33" t="n">
-        <v>0.6118581657309232</v>
+        <v>0.6118588409428388</v>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
@@ -4566,7 +4571,7 @@
         </is>
       </c>
       <c r="C26" s="34" t="n">
-        <v>0.5930083533390097</v>
+        <v>0.5930074609613168</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
@@ -4591,7 +4596,7 @@
         </is>
       </c>
       <c r="C27" s="33" t="n">
-        <v>0.5532735406938195</v>
+        <v>0.5532735481847542</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
@@ -4616,7 +4621,7 @@
         </is>
       </c>
       <c r="C28" s="34" t="n">
-        <v>-0.5361296218117397</v>
+        <v>-0.5361309580009153</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
@@ -4641,7 +4646,7 @@
         </is>
       </c>
       <c r="C29" s="33" t="n">
-        <v>0.528597871691144</v>
+        <v>0.5286001691139169</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
@@ -4731,19 +4736,19 @@
         </is>
       </c>
       <c r="B3" s="33" t="n">
-        <v>0.5927324628348662</v>
+        <v>0.5927327150397735</v>
       </c>
       <c r="C3" s="33" t="n">
-        <v>0.2495525907280696</v>
+        <v>0.2495523098663607</v>
       </c>
       <c r="D3" s="33" t="n">
-        <v>2.460423059424298</v>
+        <v>2.460418985371243</v>
       </c>
       <c r="E3" s="33" t="n">
-        <v>1.997183727022387</v>
+        <v>1.997176760310123</v>
       </c>
       <c r="F3" s="33" t="n">
-        <v>-0.02007599367985166</v>
+        <v>-0.02007623701015466</v>
       </c>
     </row>
     <row r="4">
@@ -4753,19 +4758,19 @@
         </is>
       </c>
       <c r="B4" s="34" t="n">
-        <v>0.6313816852499345</v>
+        <v>0.6313820183962096</v>
       </c>
       <c r="C4" s="34" t="n">
-        <v>0.3361744377105355</v>
+        <v>0.3361740654264061</v>
       </c>
       <c r="D4" s="34" t="n">
-        <v>2.146979762765747</v>
+        <v>2.146974527988826</v>
       </c>
       <c r="E4" s="34" t="n">
-        <v>0.3615968606782248</v>
+        <v>0.3615875557444018</v>
       </c>
       <c r="F4" s="34" t="n">
-        <v>-0.0261846790514917</v>
+        <v>-0.02618494416133161</v>
       </c>
     </row>
     <row r="5">
@@ -4775,19 +4780,19 @@
         </is>
       </c>
       <c r="B5" s="33" t="n">
-        <v>0.4597385026027135</v>
+        <v>0.4597377893280422</v>
       </c>
       <c r="C5" s="33" t="n">
-        <v>0.5803733430961843</v>
+        <v>0.580372581560643</v>
       </c>
       <c r="D5" s="33" t="n">
-        <v>2.856649546801769</v>
+        <v>2.856638421555682</v>
       </c>
       <c r="E5" s="33" t="n">
-        <v>0.02930984789698554</v>
+        <v>0.02933521107835607</v>
       </c>
       <c r="F5" s="33" t="n">
-        <v>-0.04492216535560389</v>
+        <v>-0.04492263039729934</v>
       </c>
     </row>
     <row r="6">
@@ -4797,19 +4802,19 @@
         </is>
       </c>
       <c r="B6" s="34" t="n">
-        <v>0.359180629674831</v>
+        <v>0.3591806160720604</v>
       </c>
       <c r="C6" s="34" t="n">
-        <v>0.4308581354864889</v>
+        <v>0.4308574963426787</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>1.337789206419006</v>
+        <v>1.337783775943102</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>2.361603006797575</v>
+        <v>2.361591902067863</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>-0.009980878555596838</v>
+        <v>-0.009981127111012841</v>
       </c>
     </row>
     <row r="7">
@@ -4819,19 +4824,19 @@
         </is>
       </c>
       <c r="B7" s="33" t="n">
-        <v>0.1620839697497295</v>
+        <v>0.162083582947631</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.4610386885106495</v>
+        <v>0.4610383070351105</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.5164427744334301</v>
+        <v>0.5164422089887049</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>4.113333203526983</v>
+        <v>4.113308307736573</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-0.007163486376460381</v>
+        <v>-0.007163543705210864</v>
       </c>
     </row>
   </sheetData>

--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +66,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="00D0D8E4"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B7770D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -244,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -284,13 +290,13 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -299,7 +305,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -308,31 +314,28 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -344,25 +347,25 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,7 +585,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8667750" cy="2952750"/>
@@ -612,7 +615,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9334500" cy="5715000"/>
@@ -956,7 +959,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Key Finding: A conventional 60/40 portfolio allocates 79.8% of total risk to Equity Premium. Enhanced HRP reduces this to 19.7% — a 60.1 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
+          <t>Key Finding: A conventional 60/40 portfolio allocates 83.0% of total risk to Equity Premium. Enhanced HRP reduces this to 48.1% — a 34.9 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
         </is>
       </c>
     </row>
@@ -1024,25 +1027,25 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.07378527980854011</v>
+        <v>0.07835404404409219</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.1102367739317823</v>
+        <v>0.09403533400378947</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.4865416255444058</v>
+        <v>0.618953971246033</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.6069202987975629</v>
+        <v>0.6816204339888274</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.1958990938318969</v>
+        <v>-0.1623091118121611</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.3766494186637537</v>
+        <v>0.4827458124148362</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.02666080497247821</v>
+        <v>0.03282896624428367</v>
       </c>
     </row>
     <row r="9">
@@ -1052,22 +1055,22 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.07998380778198988</v>
+        <v>0.07998379168931891</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.1069805109235594</v>
+        <v>0.1069804860098002</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.5592916564003224</v>
+        <v>0.5592916362226861</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>0.7881504192348465</v>
+        <v>0.7881497280472217</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>-0.2412384953320925</v>
+        <v>-0.2412385133194655</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.3315549107197132</v>
+        <v>0.3315548192895659</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -1080,25 +1083,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07663819523679472</v>
+        <v>0.07663817491065328</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.08321356109257802</v>
+        <v>0.08321361436209221</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.6788279923382992</v>
+        <v>0.6788273135193434</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.9323885697872637</v>
+        <v>0.9323890555502273</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-0.2151224545325302</v>
+        <v>-0.2151225241414461</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.3562538155458137</v>
+        <v>0.3562536057835702</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.06996092679099582</v>
+        <v>0.06996093532900778</v>
       </c>
     </row>
     <row r="11">
@@ -1108,25 +1111,25 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05975307784699102</v>
+        <v>0.0597530918297895</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.0638817408097252</v>
+        <v>0.06388180252257482</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.6199357863454225</v>
+        <v>0.6199354063435357</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>0.8940035467859482</v>
+        <v>0.8940029709429784</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-0.1476443968503109</v>
+        <v>-0.1476445163072504</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.4047094175038122</v>
+        <v>0.4047091847654026</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.04860572903543283</v>
+        <v>0.0486056279182925</v>
       </c>
     </row>
     <row r="12">
@@ -1136,25 +1139,25 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.04841833252063688</v>
+        <v>0.04841836263754429</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.05539011011202866</v>
+        <v>0.05539016078525481</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.5103407781364672</v>
+        <v>0.5103408549785217</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.6499482531048663</v>
+        <v>0.6499460046055323</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-0.1602422571166676</v>
+        <v>-0.1602423622198145</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.3021570801101792</v>
+        <v>0.3021570698709857</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.067186603360334</v>
+        <v>0.06718644706236643</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1214,22 +1217,22 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>0.73</v>
+        <v>0.6779999999999999</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>-0.043</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.064</v>
+        <v>0.13</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>-0.011</v>
+        <v>0.005</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.136</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="17">
@@ -1239,22 +1242,22 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>0.7979999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-0</v>
+        <v>-0.005</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.098</v>
+        <v>0.102</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>-0.015</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.109</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="18">
@@ -1264,22 +1267,22 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.478</v>
+        <v>0.425</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.303</v>
+        <v>0.194</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.083</v>
+        <v>0.114</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>-0.016</v>
+        <v>0.017</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.152</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="19">
@@ -1289,19 +1292,19 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.513</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.194</v>
+        <v>0.136</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.062</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.062</v>
+        <v>0.115</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>-0.006</v>
+        <v>0.01</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0.155</v>
@@ -1314,22 +1317,22 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.197</v>
+        <v>0.481</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.556</v>
+        <v>0.078</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.078</v>
+        <v>0.209</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>-0.002</v>
+        <v>0.017</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.16</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1"/>
@@ -1367,7 +1370,7 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
@@ -1382,7 +1385,7 @@
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
@@ -1413,7 +1416,7 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -1430,7 +1433,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -1534,25 +1537,25 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.07378527980854011</v>
+        <v>0.07835404404409219</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>0.1102367739317823</v>
+        <v>0.09403533400378947</v>
       </c>
       <c r="D3" s="24" t="n">
-        <v>0.4865416255444058</v>
+        <v>0.618953971246033</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.6069202987975629</v>
+        <v>0.6816204339888274</v>
       </c>
       <c r="F3" s="25" t="n">
-        <v>-0.1958990938318969</v>
+        <v>-0.1623091118121611</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.3766494186637537</v>
+        <v>0.4827458124148362</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.02666080497247821</v>
+        <v>0.03282896624428367</v>
       </c>
     </row>
     <row r="4">
@@ -1562,22 +1565,22 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.07998380778198988</v>
+        <v>0.07998379168931891</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>0.1069805109235594</v>
+        <v>0.1069804860098002</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>0.5592916564003224</v>
+        <v>0.5592916362226861</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>0.7881504192348465</v>
+        <v>0.7881497280472217</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>-0.2412384953320925</v>
+        <v>-0.2412385133194655</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.3315549107197132</v>
+        <v>0.3315548192895659</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -1590,25 +1593,25 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.07663819523679472</v>
+        <v>0.07663817491065328</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.08321356109257802</v>
+        <v>0.08321361436209221</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0.6788279923382992</v>
+        <v>0.6788273135193434</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.9323885697872637</v>
+        <v>0.9323890555502273</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>-0.2151224545325302</v>
+        <v>-0.2151225241414461</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3562538155458137</v>
+        <v>0.3562536057835702</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.06996092679099582</v>
+        <v>0.06996093532900778</v>
       </c>
     </row>
     <row r="6">
@@ -1618,25 +1621,25 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.05975307784699102</v>
+        <v>0.0597530918297895</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.0638817408097252</v>
+        <v>0.06388180252257482</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.6199357863454225</v>
+        <v>0.6199354063435357</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.8940035467859482</v>
+        <v>0.8940029709429784</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-0.1476443968503109</v>
+        <v>-0.1476445163072504</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.4047094175038122</v>
+        <v>0.4047091847654026</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.04860572903543283</v>
+        <v>0.0486056279182925</v>
       </c>
     </row>
     <row r="7">
@@ -1646,25 +1649,25 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.04841833252063688</v>
+        <v>0.04841836263754429</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05539011011202866</v>
+        <v>0.05539016078525481</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>0.5103407781364672</v>
+        <v>0.5103408549785217</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6499482531048663</v>
+        <v>0.6499460046055323</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-0.1602422571166676</v>
+        <v>-0.1602423622198145</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.3021570801101792</v>
+        <v>0.3021570698709857</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.067186603360334</v>
+        <v>0.06718644706236643</v>
       </c>
     </row>
     <row r="29">
@@ -1706,14 +1709,14 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.02666080497247821</v>
-      </c>
-      <c r="C31" s="29" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>Closet Indexer</t>
+        <v>0.03282896624428367</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>Moderate Active</t>
         </is>
       </c>
     </row>
@@ -1726,10 +1729,10 @@
       <c r="B32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="31" t="n">
+      <c r="C32" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>Closet Indexer</t>
         </is>
@@ -1742,14 +1745,14 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.06996092679099582</v>
-      </c>
-      <c r="C33" s="25" t="n">
-        <v>0.3644257856776272</v>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
-        <is>
-          <t>Moderate Active</t>
+        <v>0.06996093532900778</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>0.6821214431873773</v>
+      </c>
+      <c r="D33" s="29" t="inlineStr">
+        <is>
+          <t>High Conviction Active</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1763,12 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.04860572903543283</v>
+        <v>0.0486056279182925</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>0.2945580612696407</v>
-      </c>
-      <c r="D34" s="32" t="inlineStr">
+        <v>0.4482591879641857</v>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
         <is>
           <t>Moderate Active</t>
         </is>
@@ -1778,12 +1781,12 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.067186603360334</v>
+        <v>0.06718644706236643</v>
       </c>
       <c r="C35" s="16" t="n">
-        <v>0.571732280411839</v>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
+        <v>0.6585740701086883</v>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>High Conviction Active</t>
         </is>
@@ -1831,7 +1834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1914,26 +1917,26 @@
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="33" t="n">
-        <v>0.9625042408608263</v>
-      </c>
-      <c r="C3" s="33" t="n">
-        <v>0.02345556695950237</v>
-      </c>
-      <c r="D3" s="33" t="n">
-        <v>0.9221660405720529</v>
-      </c>
-      <c r="E3" s="33" t="n">
-        <v>0.3996132467527052</v>
-      </c>
-      <c r="F3" s="33" t="n">
-        <v>-0.005854488358147615</v>
+      <c r="B3" s="32" t="n">
+        <v>0.9629526363766361</v>
+      </c>
+      <c r="C3" s="32" t="n">
+        <v>0.02096934262164385</v>
+      </c>
+      <c r="D3" s="32" t="n">
+        <v>0.9114943179007943</v>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>0.3859510686858356</v>
+      </c>
+      <c r="F3" s="32" t="n">
+        <v>-0.005656224624349935</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.02681788977738234</v>
+        <v>0.02752235717871665</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.9906918940400172</v>
+        <v>0.9907423981554528</v>
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
@@ -1947,26 +1950,26 @@
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n">
-        <v>0.9713543546890465</v>
-      </c>
-      <c r="C4" s="34" t="n">
-        <v>-0.02791868690570089</v>
-      </c>
-      <c r="D4" s="34" t="n">
-        <v>1.307584296732336</v>
-      </c>
-      <c r="E4" s="34" t="n">
-        <v>2.069745671519761</v>
-      </c>
-      <c r="F4" s="34" t="n">
-        <v>0.03673461445983179</v>
+      <c r="B4" s="33" t="n">
+        <v>0.9705140714768685</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>-0.03947116173787261</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>1.288237417082033</v>
+      </c>
+      <c r="E4" s="33" t="n">
+        <v>1.958782358955348</v>
+      </c>
+      <c r="F4" s="33" t="n">
+        <v>0.03975655799465005</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.02838075985627555</v>
+        <v>0.02892951795413736</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>0.9123633301070473</v>
+        <v>0.9135202069719286</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
@@ -1980,26 +1983,26 @@
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
-        <v>1.184030233295581</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>-0.1590173667035335</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <v>0.6769344744648144</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>-2.052829348795206</v>
-      </c>
-      <c r="F5" s="33" t="n">
-        <v>-0.01476554280325399</v>
+      <c r="B5" s="32" t="n">
+        <v>1.186001067502022</v>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>-0.1754629168915425</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>0.6241674995537919</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>-2.247144403319392</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>-0.01209665385841775</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.02543145418845582</v>
+        <v>0.02592302184300589</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.8712834190739561</v>
+        <v>0.8734657447657567</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
@@ -2013,26 +2016,26 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
-        <v>0.7532192116329343</v>
-      </c>
-      <c r="C6" s="34" t="n">
-        <v>0.2392006264404306</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>5.685559710072019</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>6.296323430647663</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>-0.09556557578946366</v>
+      <c r="B6" s="33" t="n">
+        <v>0.7557855114145501</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0.1961768540104644</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>5.5454977732988</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>6.081937462925834</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>-0.08918291442247075</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.02067188264244709</v>
+        <v>0.02071158096226833</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.6355401248164949</v>
+        <v>0.6487319244544395</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
@@ -2046,26 +2049,26 @@
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n">
-        <v>0.02522360442670393</v>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>1.13922957972593</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>-0.1658095440767343</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>-2.135898143828797</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>-0.007930898215471631</v>
+      <c r="B7" s="32" t="n">
+        <v>0.02455123451311804</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>1.14318909029292</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>-0.1601061651482604</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>-2.105740712675675</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>-0.007682354266568784</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.01148281541820169</v>
+        <v>0.01105276411945654</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.981243967023252</v>
+        <v>0.9810940701723285</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
@@ -2079,26 +2082,26 @@
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n">
-        <v>0.01944867126558009</v>
-      </c>
-      <c r="C8" s="34" t="n">
-        <v>0.4459868868234478</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <v>-0.1250762247422195</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>6.421664708875722</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>-0.005982567608695194</v>
+      <c r="B8" s="33" t="n">
+        <v>0.0203365469187179</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0.4346594304116924</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>-0.1327129059855329</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>6.32895329765253</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>-0.006367946909368674</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.008734870137983752</v>
+        <v>0.0083565656750765</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.8015088821539471</v>
+        <v>0.8047652620682976</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
@@ -2112,26 +2115,26 @@
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n">
-        <v>0.2750960153447685</v>
-      </c>
-      <c r="C9" s="33" t="n">
-        <v>0.5137940982593163</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>0.2429920809566087</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>-0.145757769728357</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>0.01162264495667739</v>
+      <c r="B9" s="32" t="n">
+        <v>0.2770940760397295</v>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>0.503532751026925</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>0.2237121564332759</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>-0.1940108398155372</v>
+      </c>
+      <c r="F9" s="32" t="n">
+        <v>0.01073435265823161</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0.01057001868840936</v>
+        <v>0.01040464201533431</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.6374618458308732</v>
+        <v>0.6318366651642626</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
@@ -2145,26 +2148,26 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
-        <v>1.035110678337744</v>
-      </c>
-      <c r="C10" s="34" t="n">
-        <v>0.3934964445308032</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>9.352425086801601</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>-8.299633141497763</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>-0.1362115190006306</v>
+      <c r="B10" s="33" t="n">
+        <v>1.03511004432214</v>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0.3934962751305634</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>9.352409858806912</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>-8.299614656967426</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>-0.1362110668348173</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.02406984915621184</v>
+        <v>0.02474498124226852</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.6337083217606877</v>
+        <v>0.6337079398705867</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2178,26 +2181,26 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
-        <v>0.1086074255047768</v>
-      </c>
-      <c r="C11" s="33" t="n">
-        <v>-0.3222563603329497</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>4.246994947560707</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>15.42136218884538</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>0.03726719926776158</v>
+      <c r="B11" s="32" t="n">
+        <v>0.1230130675190794</v>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>-0.4212962539101503</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>3.87429582949361</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>14.62687553512604</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>0.04906950804478834</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.004127876963690224</v>
+        <v>0.001843154193156353</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.4445765743655131</v>
+        <v>0.4794580272579038</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
@@ -2205,228 +2208,444 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>0.2160674891090411</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>0.2677502129193075</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>3.408097655344705</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>3.636984973993301</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>0.1635303271374692</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.01739609780384551</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>0.8534682187892575</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>BAA-Treasury</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Equity Premium Beta: Full-Sample OLS vs Stress (Q10 Quantile Regression)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="n">
+        <v>0.2658699470620771</v>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>0.0201207674327414</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>0.2723363862123945</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>1.936340928338347</v>
+      </c>
+      <c r="F13" s="32" t="n">
+        <v>0.01306748304553633</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0.01840929059429198</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>0.7600392787599053</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>BAA-Treasury</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>OLS Beta</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Stress Beta (Q10)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Uplift</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="n">
+        <v>0.3468464741335978</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>-0.01861008752628902</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>1.506809712736098</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>4.581761659067179</v>
+      </c>
+      <c r="F14" s="33" t="n">
+        <v>0.07230106357757159</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.03299965737498766</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.4506213041501984</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>BAA-Treasury</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B15" s="33" t="n">
-        <v>0.1086074255047768</v>
-      </c>
-      <c r="C15" s="33" t="n">
-        <v>0.8151360605982694</v>
-      </c>
-      <c r="D15" s="33" t="n">
-        <v>0.7065286350934925</v>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>Significant stress uplift</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="n">
-        <v>0.01944867126558009</v>
-      </c>
-      <c r="C16" s="34" t="n">
-        <v>0.1007618020644612</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <v>0.08131313079888108</v>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>Moderate stress uplift</t>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="n">
+        <v>-0.03322629045934519</v>
+      </c>
+      <c r="C15" s="32" t="n">
+        <v>0.2707523857212094</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>-0.07481989405137703</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>13.74713522768516</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <v>-0.003590073697397051</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0.01615320883867902</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.09062085827372512</v>
+      </c>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>BAA-Treasury</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B17" s="33" t="n">
-        <v>0.02522360442670393</v>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>0.07165818859001716</v>
-      </c>
-      <c r="D17" s="33" t="n">
-        <v>0.04643458416331323</v>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
-        </is>
-      </c>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Equity Premium Beta: Full-Sample OLS vs Stress (Q10 Quantile Regression)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B18" s="34" t="n">
-        <v>0.9625042408608263</v>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>0.9793425414193179</v>
-      </c>
-      <c r="D18" s="34" t="n">
-        <v>0.01683830055849156</v>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>Stable across regimes</t>
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>OLS Beta</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Stress Beta (Q10)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Uplift</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B19" s="33" t="n">
-        <v>1.035110678337744</v>
-      </c>
-      <c r="C19" s="33" t="n">
-        <v>1.031110217491761</v>
-      </c>
-      <c r="D19" s="33" t="n">
-        <v>-0.004000460845982268</v>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n">
+        <v>0.1230130675190794</v>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>0.815129387850801</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>0.6921163203317217</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Significant stress uplift</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B20" s="34" t="n">
-        <v>0.7532192116329343</v>
-      </c>
-      <c r="C20" s="34" t="n">
-        <v>0.7449323836182584</v>
-      </c>
-      <c r="D20" s="34" t="n">
-        <v>-0.00828682801467584</v>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>-0.03322629045934519</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>0.1943926134830162</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0.2276189039423614</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Significant stress uplift</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B21" s="33" t="n">
-        <v>0.2750960153447685</v>
-      </c>
-      <c r="C21" s="33" t="n">
-        <v>0.2323438705888303</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>-0.04275214475593819</v>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="n">
+        <v>0.2160674891090411</v>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>0.2968736681282325</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>0.08080617901919132</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Moderate stress uplift</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B22" s="34" t="n">
-        <v>0.9713543546890465</v>
-      </c>
-      <c r="C22" s="34" t="n">
-        <v>0.8150714885287655</v>
-      </c>
-      <c r="D22" s="34" t="n">
-        <v>-0.156282866160281</v>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="n">
+        <v>0.0203365469187179</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>0.1007627943916267</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>0.08042624747290882</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Moderate stress uplift</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n">
+        <v>0.02455123451311804</v>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>0.07165088607331449</v>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>0.04709965156019645</v>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="n">
+        <v>0.9629526363766361</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>0.9793425414193179</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0.01638990504268178</v>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="n">
+        <v>1.03511004432214</v>
+      </c>
+      <c r="C25" s="32" t="n">
+        <v>1.03110936734226</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>-0.004000676979879936</v>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n">
+        <v>0.7557855114145501</v>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>0.744932359424098</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>-0.01085315199045211</v>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="n">
+        <v>0.2770940760397295</v>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>0.2323409958968115</v>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>-0.04475308014291807</v>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="n">
+        <v>0.3468464741335978</v>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>0.2923064843573338</v>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>-0.05453998977626406</v>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="n">
+        <v>0.2658699470620771</v>
+      </c>
+      <c r="C29" s="32" t="n">
+        <v>0.1884016479536811</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>-0.07746829910839603</v>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="n">
+        <v>0.9705140714768685</v>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>0.8150650417144192</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>-0.1554490297624493</v>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Stable across regimes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B23" s="33" t="n">
-        <v>1.184030233295581</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>0.9628342395707845</v>
-      </c>
-      <c r="D23" s="33" t="n">
-        <v>-0.2211959937247967</v>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="B31" s="32" t="n">
+        <v>1.186001067502022</v>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>0.9628299367516577</v>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>-0.2231711307503639</v>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Stable across regimes</t>
         </is>
@@ -2435,7 +2654,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2505,16 +2724,16 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>-0.3134746014276183</v>
+        <v>-0.2929241262139354</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.04948761433926584</v>
+        <v>-0.04460242978117723</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-0.1548212823410495</v>
+        <v>-0.1293955031647438</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0.5954501587549845</v>
+        <v>0.530218022612267</v>
       </c>
     </row>
     <row r="4">
@@ -2524,16 +2743,16 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>-0.2495977639371679</v>
+        <v>-0.2495977673882506</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>-0.003713611804167738</v>
+        <v>-0.003713758830968694</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>-0.2018217565810658</v>
+        <v>-0.2018216973403624</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.6016793798524094</v>
+        <v>0.6016791677702653</v>
       </c>
     </row>
     <row r="5">
@@ -2543,16 +2762,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>-0.1954153004416594</v>
+        <v>-0.1785457458635089</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.0468524310147842</v>
+        <v>0.04017046766354437</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.2346489343424729</v>
+        <v>-0.1794996750807218</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.4831002441572396</v>
+        <v>0.5181637667297441</v>
       </c>
     </row>
     <row r="6">
@@ -2562,16 +2781,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-0.1730524664274122</v>
+        <v>-0.1647008470980749</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.02429344316360349</v>
+        <v>0.02068406442033477</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-0.1674660311134522</v>
+        <v>-0.1457960326582141</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3559225224980567</v>
+        <v>0.3364380680146859</v>
       </c>
     </row>
     <row r="7">
@@ -2581,16 +2800,16 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>-0.06759692357441749</v>
+        <v>-0.09982261554835092</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05076908147634351</v>
+        <v>0.02695021584511825</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>-0.1475039470866329</v>
+        <v>-0.1049593246463363</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.2180544335778652</v>
+        <v>0.2876108636119603</v>
       </c>
     </row>
   </sheetData>
@@ -2607,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2682,19 +2901,19 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C4" s="33" t="n">
-        <v>0.07664168351224593</v>
-      </c>
-      <c r="D4" s="33" t="n">
-        <v>0.008515742612471769</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C4" s="32" t="n">
+        <v>0.07614036951284688</v>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>0.005856951500988222</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.1437032210168355</v>
+        <v>0.111863774407989</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.9718498340506939</v>
+        <v>1.003712510749121</v>
       </c>
     </row>
     <row r="5">
@@ -2704,19 +2923,19 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C5" s="34" t="n">
-        <v>0.08782255892101108</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>0.009758062102334564</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0.08749455707154688</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>0.006730350543965146</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.1646673718078441</v>
+        <v>0.1285450997519395</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.9005692931844215</v>
+        <v>0.9304117589616353</v>
       </c>
     </row>
     <row r="6">
@@ -2726,19 +2945,19 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C6" s="33" t="n">
-        <v>0.09343996140347188</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>0.0103822179337191</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>0.0921470351040931</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>0.007088233469545625</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1752000061849139</v>
+        <v>0.1353804192598527</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.8647853697421607</v>
+        <v>0.8923913124143709</v>
       </c>
     </row>
     <row r="7">
@@ -2748,19 +2967,19 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C7" s="34" t="n">
-        <v>0.09133107047002956</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <v>0.01014789671889217</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0.09060579578068487</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>0.006969676598514222</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.1712458339118004</v>
+        <v>0.133116063976505</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.654725765269208</v>
+        <v>0.6790697564157375</v>
       </c>
     </row>
     <row r="8">
@@ -2770,19 +2989,19 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C8" s="33" t="n">
-        <v>-0.01422437146584231</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>-0.001580485718426923</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>-0.01944083732130199</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>-0.001495449024715538</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.0266707084566442</v>
+        <v>-0.02856205524515619</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.9800394596124378</v>
+        <v>0.9940789078272613</v>
       </c>
     </row>
     <row r="9">
@@ -2792,19 +3011,19 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <v>0.01048960388641192</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <v>0.001165511542934658</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0.01024022541031441</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>0.0007877096469472626</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.01966801610545594</v>
+        <v>0.01504471639046998</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.8261549596926778</v>
+        <v>0.8296598221855379</v>
       </c>
     </row>
     <row r="10">
@@ -2814,19 +3033,19 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C10" s="33" t="n">
-        <v>0.01878512858404903</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>0.002087236509338781</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>0.01585305039156765</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>0.001219465414735974</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.03522213188743362</v>
+        <v>0.02329095674248849</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.654246587683997</v>
+        <v>0.6607008361249701</v>
       </c>
     </row>
     <row r="11">
@@ -2836,19 +3055,19 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>0.09287908065450565</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>0.01031989785050063</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>0.08919684178056769</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>0.006861295521582132</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1741483543090792</v>
+        <v>0.1310460594121884</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.6432517319898794</v>
+        <v>0.6648087085490335</v>
       </c>
     </row>
     <row r="12">
@@ -2858,751 +3077,773 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="C12" s="33" t="n">
-        <v>0.07616837823989694</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>0.008463153137766327</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>0.0773795348727935</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>0.00595227191329181</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1428157732332814</v>
+        <v>0.1136843291960226</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.4913808005382763</v>
+        <v>0.5183917993112132</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>0.04026322451363631</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>0.003097171116433563</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0.05915385350437107</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0.709927675625481</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>60/40 — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C14" s="32" t="n">
+        <v>0.02743626335672028</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>0.002110481796670791</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0.0403087612310115</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.7752370981178501</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>0.05374213886446366</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>0.004134010681881821</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0.07895678122658484</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.4456283804373475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>US Large Cap Equity</t>
+          <t>Private Real Estate</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C16" s="33" t="n">
-        <v>0.07480404058153603</v>
-      </c>
-      <c r="D16" s="33" t="n">
-        <v>0.008976484869784323</v>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="C16" s="32" t="n">
+        <v>0.03959440617087167</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>0.003045723551605514</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.158296737888037</v>
+        <v>0.05817124014573317</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.9718498340506939</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C17" s="34" t="n">
-        <v>0.08443779803315991</v>
-      </c>
-      <c r="D17" s="34" t="n">
-        <v>0.01013253576397919</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>0.178683235279637</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0.9005692931844215</v>
+        <v>0.138613651134196</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>0.09163325284247642</v>
-      </c>
-      <c r="D18" s="33" t="n">
-        <v>0.01099599034109717</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.1939099130777978</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.8647853697421607</v>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>60/40 — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C19" s="34" t="n">
-        <v>0.08827067970023333</v>
-      </c>
-      <c r="D19" s="34" t="n">
-        <v>0.010592481564028</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>0.1867941963974024</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>0.654725765269208</v>
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
+          <t>US Large Cap Equity</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C20" s="33" t="n">
-        <v>-0.001968768015688312</v>
-      </c>
-      <c r="D20" s="33" t="n">
-        <v>-0.0002625024020917749</v>
+        <v>0.12</v>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>0.07505700143058429</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>0.009006840171670114</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>-0.004629125380556697</v>
+        <v>0.1591035145939096</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9800394596124378</v>
+        <v>1.003712510749121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>TIPS</t>
+          <t>US Mid Cap Equity</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C21" s="34" t="n">
-        <v>0.01159932567640918</v>
-      </c>
-      <c r="D21" s="34" t="n">
-        <v>0.001546576756854557</v>
+        <v>0.12</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0.08459731351858084</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>0.0101516776222297</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.02727326554380059</v>
+        <v>0.1793267736449233</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.8261549596926778</v>
+        <v>0.9304117589616353</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
+          <t>US Small Cap Equity</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="C22" s="33" t="n">
-        <v>0.02377789461211848</v>
-      </c>
-      <c r="D22" s="33" t="n">
-        <v>0.003170385948282464</v>
+        <v>0.12</v>
+      </c>
+      <c r="C22" s="32" t="n">
+        <v>0.09183093044086164</v>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>0.0110197116529034</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.05590849433150584</v>
+        <v>0.194660371492224</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.654246587683997</v>
+        <v>0.8923913124143709</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Emerging Market Equity</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C23" s="34" t="n">
-        <v>0.09628951981970114</v>
-      </c>
-      <c r="D23" s="34" t="n">
-        <v>0.01155474237836414</v>
+      <c r="C23" s="33" t="n">
+        <v>0.08817954670886334</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>0.0105815456050636</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.2037632828623759</v>
+        <v>0.1869202809767611</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.6432517319898794</v>
+        <v>0.6790697564157375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Long Duration Treasury</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="33" t="n">
-        <v>0.04900610376782925</v>
-      </c>
-      <c r="D24" s="33" t="n">
-        <v>0</v>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C24" s="32" t="n">
+        <v>-0.00267880379738063</v>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>-0.0003571738396507507</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>0</v>
+        <v>-0.006309383993309894</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.4913808005382763</v>
+        <v>0.9940789078272613</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0.01130270381660219</v>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>0.001507027175546959</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>0.02662124736844236</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0.8296598221855379</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>MVO — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="6" t="n"/>
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="C26" s="32" t="n">
+        <v>0.02353731539917574</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>0.003138308719890098</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.05543741619683269</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.6607008361249701</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>0.09635001136064988</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>0.01156200136327799</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>0.2042397797202166</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0.6648087085490335</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>US Large Cap Equity</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>0.1112995622680132</v>
-      </c>
-      <c r="C28" s="33" t="n">
-        <v>0.05525968237192978</v>
-      </c>
-      <c r="D28" s="33" t="n">
-        <v>0.006150378459065228</v>
+        <v>0</v>
+      </c>
+      <c r="C28" s="32" t="n">
+        <v>0.04875656230803836</v>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.123260483719362</v>
+        <v>0</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.9718498340506939</v>
+        <v>0.5183917993112132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>US Mid Cap Equity</t>
+          <t>High Yield Credit</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>1.182944781530638e-07</v>
-      </c>
-      <c r="C29" s="34" t="n">
-        <v>0.05849004051353848</v>
-      </c>
-      <c r="D29" s="34" t="n">
-        <v>6.919048819700591e-09</v>
+        <v>0</v>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>0.03825920480661442</v>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1.386655000290496e-07</v>
+        <v>0</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.9005692931844215</v>
+        <v>0.709927675625481</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>US Small Cap Equity</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>3.383947803280196e-08</v>
-      </c>
-      <c r="C30" s="33" t="n">
-        <v>0.06268585950187984</v>
-      </c>
-      <c r="D30" s="33" t="n">
-        <v>2.121256765581173e-09</v>
+        <v>0</v>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>0.02601743790308528</v>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>4.251236517536906e-08</v>
+        <v>0</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.8647853697421607</v>
+        <v>0.7752370981178501</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>Emerging Market Equity</t>
+          <t>Private Equity</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>0.1941851401027252</v>
-      </c>
-      <c r="C31" s="34" t="n">
-        <v>0.07269131211729911</v>
-      </c>
-      <c r="D31" s="34" t="n">
-        <v>0.01411557262774865</v>
+        <v>0</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>0.04049297255821635</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>0.2828919100917447</v>
+        <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.654725765269208</v>
+        <v>0.4456283804373475</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
+          <t>Private Real Estate</t>
         </is>
       </c>
       <c r="B32" s="9" t="n">
-        <v>0.3499996939032552</v>
-      </c>
-      <c r="C32" s="33" t="n">
-        <v>0.03028031615699537</v>
-      </c>
-      <c r="D32" s="33" t="n">
-        <v>0.01059810138624217</v>
+        <v>0</v>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>0.01743554760871287</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>0.2123978405669681</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.9800394596124378</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="21" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>0.101322928358229</v>
-      </c>
-      <c r="C33" s="34" t="n">
-        <v>0.01675398763389107</v>
-      </c>
-      <c r="D33" s="34" t="n">
-        <v>0.001697563088743399</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>0.03402106859850826</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0.8261549596926778</v>
+        <v>0.138613651134196</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n">
-        <v>0.04961823822884117</v>
-      </c>
-      <c r="C34" s="33" t="n">
-        <v>0.03127074460076728</v>
-      </c>
-      <c r="D34" s="33" t="n">
-        <v>0.001551599255194119</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0.03109578963420348</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>0.654246587683997</v>
-      </c>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MVO — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="6" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n">
-        <v>0.1736368658373325</v>
-      </c>
-      <c r="C35" s="34" t="n">
-        <v>0.08842286006646781</v>
-      </c>
-      <c r="D35" s="34" t="n">
-        <v>0.0153534682903145</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>0.3077007278218259</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>0.6432517319898794</v>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>US Large Cap Equity</t>
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>0.01993741916764761</v>
-      </c>
-      <c r="C36" s="33" t="n">
-        <v>0.02160331428831735</v>
-      </c>
-      <c r="D36" s="33" t="n">
-        <v>0.0004307143323766138</v>
+        <v>6.46058755871492e-09</v>
+      </c>
+      <c r="C36" s="32" t="n">
+        <v>0.05564498156206564</v>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>3.594992755848024e-10</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>0.008631998389522265</v>
+        <v>8.076545419689078e-09</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.4913808005382763</v>
+        <v>1.003712510749121</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n">
+        <v>4.969612396196836e-09</v>
+      </c>
+      <c r="C37" s="33" t="n">
+        <v>0.0599672636167075</v>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>2.980140566355931e-10</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>6.695212556987172e-09</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>0.9304117589616353</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Risk Parity — Marginal and Total Risk Contribution</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="6" t="n"/>
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>3.893641291535671e-09</v>
+      </c>
+      <c r="C38" s="32" t="n">
+        <v>0.06372406311519405</v>
+      </c>
+      <c r="D38" s="32" t="n">
+        <v>2.481186434097447e-10</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>5.574257388170261e-09</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>0.8923913124143709</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Asset Class</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Weight</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Marginal Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Total Risk Contrib.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>% of Portfolio Risk</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Factor Risk Share</t>
-        </is>
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>0.06454520065859198</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>0.06722787907250567</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>0.004339236944586436</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>0.09748571596628486</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>0.6790697564157375</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>US Large Cap Equity</t>
+          <t>Long Duration Treasury</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.07066828745635954</v>
-      </c>
-      <c r="C40" s="33" t="n">
-        <v>0.06189971578576542</v>
-      </c>
-      <c r="D40" s="33" t="n">
-        <v>0.004374346908615427</v>
+        <v>0.3046537019161151</v>
+      </c>
+      <c r="C40" s="32" t="n">
+        <v>0.02079541939899359</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>0.006335401502801592</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1111060767534358</v>
+        <v>0.1423317415761341</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.9718498340506939</v>
+        <v>0.9940789078272613</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>US Mid Cap Equity</t>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>0.06358657635061872</v>
-      </c>
-      <c r="C41" s="34" t="n">
-        <v>0.06879628490735507</v>
-      </c>
-      <c r="D41" s="34" t="n">
-        <v>0.004374520222900451</v>
+        <v>3.814616944158453e-09</v>
+      </c>
+      <c r="C41" s="33" t="n">
+        <v>0.01539025660518165</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>5.87079336210725e-11</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.1111104788437722</v>
+        <v>1.318938102490931e-09</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.9005692931844215</v>
+        <v>0.8296598221855379</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>US Small Cap Equity</t>
+          <t>Investment Grade Credit</t>
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>0.06106318561939598</v>
-      </c>
-      <c r="C42" s="33" t="n">
-        <v>0.07167165933255069</v>
-      </c>
-      <c r="D42" s="33" t="n">
-        <v>0.004376499837473657</v>
+        <v>3.682239094864438e-09</v>
+      </c>
+      <c r="C42" s="32" t="n">
+        <v>0.02611305126723754</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>9.615449826242141e-11</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1111607599973496</v>
+        <v>2.160216237600372e-09</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.8647853697421607</v>
+        <v>0.6607008361249701</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>Emerging Market Equity</t>
+          <t>REITs</t>
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.0577535240921918</v>
-      </c>
-      <c r="C43" s="34" t="n">
-        <v>0.07569760669607641</v>
-      </c>
-      <c r="D43" s="34" t="n">
-        <v>0.004371803552043108</v>
+        <v>0.1415186667252243</v>
+      </c>
+      <c r="C43" s="33" t="n">
+        <v>0.08486294339388882</v>
+      </c>
+      <c r="D43" s="33" t="n">
+        <v>0.01200969060348133</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.1110414768539677</v>
+        <v>0.2698108681238483</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.654725765269208</v>
+        <v>0.6648087085490335</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>0.2194568708623782</v>
-      </c>
-      <c r="C44" s="33" t="n">
-        <v>0.01993217108192795</v>
-      </c>
-      <c r="D44" s="33" t="n">
-        <v>0.004374251895133492</v>
+        <v>6.286874574318605e-09</v>
+      </c>
+      <c r="C44" s="32" t="n">
+        <v>0.02236473216874675</v>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>1.406042660331393e-10</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.1111036634617063</v>
+        <v>3.158829010076322e-09</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.9800394596124378</v>
+        <v>0.5183917993112132</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="inlineStr">
         <is>
-          <t>TIPS</t>
+          <t>High Yield Credit</t>
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.2451141804419785</v>
-      </c>
-      <c r="C45" s="34" t="n">
-        <v>0.01784703629190622</v>
-      </c>
-      <c r="D45" s="34" t="n">
-        <v>0.00437456167400884</v>
+        <v>0.1892824021588812</v>
+      </c>
+      <c r="C45" s="33" t="n">
+        <v>0.03696461888969434</v>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>0.006996751858328901</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.1111115316798015</v>
+        <v>0.1571897024887252</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.8261549596926778</v>
+        <v>0.709927675625481</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
+          <t>Hedge Funds</t>
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>0.1447859601512068</v>
-      </c>
-      <c r="C46" s="33" t="n">
-        <v>0.03021225020406927</v>
-      </c>
-      <c r="D46" s="33" t="n">
-        <v>0.004374309654124662</v>
+        <v>6.475838226232178e-10</v>
+      </c>
+      <c r="C46" s="32" t="n">
+        <v>0.01994941425249256</v>
+      </c>
+      <c r="D46" s="32" t="n">
+        <v>1.291891794072323e-11</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>0.1111051305092543</v>
+        <v>2.902376572296443e-10</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.654246587683997</v>
+        <v>0.7752370981178501</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>REITs</t>
+          <t>Private Equity</t>
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.05237036521179319</v>
-      </c>
-      <c r="C47" s="34" t="n">
-        <v>0.08353339284924265</v>
-      </c>
-      <c r="D47" s="34" t="n">
-        <v>0.004374674290895031</v>
+        <v>0.2957635488123281</v>
+      </c>
+      <c r="C47" s="33" t="n">
+        <v>0.04969379780009286</v>
+      </c>
+      <c r="D47" s="33" t="n">
+        <v>0.01469761399131773</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.1111143920886036</v>
+        <v>0.3301980143599309</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.6432517319898794</v>
+        <v>0.4456283804373475</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Private Real Estate</t>
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.08520104981407732</v>
-      </c>
-      <c r="C48" s="33" t="n">
-        <v>0.05136014188675325</v>
-      </c>
-      <c r="D48" s="33" t="n">
-        <v>0.004375938007351343</v>
+        <v>0.00423644997370353</v>
+      </c>
+      <c r="C48" s="32" t="n">
+        <v>0.03135154581482032</v>
+      </c>
+      <c r="D48" s="32" t="n">
+        <v>0.0001328192554427606</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.111146489812109</v>
+        <v>0.002983930210840431</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.4913808005382763</v>
+        <v>0.138613651134196</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Enhanced HRP — Marginal and Total Risk Contribution</t>
+          <t>Risk Parity — Marginal and Total Risk Contribution</t>
         </is>
       </c>
       <c r="B50" s="5" t="n"/>
@@ -3650,19 +3891,19 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.01310313745444653</v>
-      </c>
-      <c r="C52" s="33" t="n">
-        <v>0.03894746836907385</v>
-      </c>
-      <c r="D52" s="33" t="n">
-        <v>0.0005103340315426829</v>
+        <v>0.04246598453859012</v>
+      </c>
+      <c r="C52" s="32" t="n">
+        <v>0.06307197340025736</v>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>0.002678413447233696</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.01734011091038029</v>
+        <v>0.07692927828706723</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.9718498340506939</v>
+        <v>1.003712510749121</v>
       </c>
     </row>
     <row r="53">
@@ -3672,19 +3913,19 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.01889748527636672</v>
-      </c>
-      <c r="C53" s="34" t="n">
-        <v>0.04139305967161434</v>
-      </c>
-      <c r="D53" s="34" t="n">
-        <v>0.0007822247356881008</v>
+        <v>0.03810690195767557</v>
+      </c>
+      <c r="C53" s="33" t="n">
+        <v>0.07027347462441945</v>
+      </c>
+      <c r="D53" s="33" t="n">
+        <v>0.002677904407737954</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.02657840323262889</v>
+        <v>0.0769146576760979</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.9005692931844215</v>
+        <v>0.9304117589616353</v>
       </c>
     </row>
     <row r="54">
@@ -3694,19 +3935,19 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.008125988522225262</v>
-      </c>
-      <c r="C54" s="33" t="n">
-        <v>0.03948149543843042</v>
-      </c>
-      <c r="D54" s="33" t="n">
-        <v>0.0003208261787729745</v>
+        <v>0.03701544985961134</v>
+      </c>
+      <c r="C54" s="32" t="n">
+        <v>0.07235265192584776</v>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>0.00267816595957113</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.01090102007514579</v>
+        <v>0.07692216995684067</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.8647853697421607</v>
+        <v>0.8923913124143709</v>
       </c>
     </row>
     <row r="55">
@@ -3716,19 +3957,19 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.02978060544931362</v>
-      </c>
-      <c r="C55" s="34" t="n">
-        <v>0.05471677519182176</v>
-      </c>
-      <c r="D55" s="34" t="n">
-        <v>0.001629498693446435</v>
+        <v>0.0352592633428864</v>
+      </c>
+      <c r="C55" s="33" t="n">
+        <v>0.07596201414569798</v>
+      </c>
+      <c r="D55" s="33" t="n">
+        <v>0.002678364660819227</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.05536704653473169</v>
+        <v>0.07692787704572444</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.654725765269208</v>
+        <v>0.6790697564157375</v>
       </c>
     </row>
     <row r="56">
@@ -3738,19 +3979,19 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.06443562047933843</v>
-      </c>
-      <c r="C56" s="33" t="n">
-        <v>0.04035314262922677</v>
-      </c>
-      <c r="D56" s="33" t="n">
-        <v>0.002600179783605468</v>
+        <v>0.192288401899513</v>
+      </c>
+      <c r="C56" s="32" t="n">
+        <v>0.01392804025985757</v>
+      </c>
+      <c r="D56" s="32" t="n">
+        <v>0.002678200603160091</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.0883488128321626</v>
+        <v>0.07692316498854454</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.9800394596124378</v>
+        <v>0.9940789078272613</v>
       </c>
     </row>
     <row r="57">
@@ -3760,19 +4001,19 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.6177106857573594</v>
-      </c>
-      <c r="C57" s="34" t="n">
-        <v>0.02355604513159771</v>
-      </c>
-      <c r="D57" s="34" t="n">
-        <v>0.01455082079197053</v>
+        <v>0.155178654597196</v>
+      </c>
+      <c r="C57" s="33" t="n">
+        <v>0.01725804189560544</v>
+      </c>
+      <c r="D57" s="33" t="n">
+        <v>0.002678079722342093</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.4944072524560491</v>
+        <v>0.07691969305477833</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.8261549596926778</v>
+        <v>0.8296598221855379</v>
       </c>
     </row>
     <row r="58">
@@ -3782,19 +4023,19 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.1996548712353037</v>
-      </c>
-      <c r="C58" s="33" t="n">
-        <v>0.03480311487371655</v>
-      </c>
-      <c r="D58" s="33" t="n">
-        <v>0.006948611418699359</v>
+        <v>0.09947716750858411</v>
+      </c>
+      <c r="C58" s="32" t="n">
+        <v>0.02692517790572135</v>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>0.002678440432725871</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.2360996626251926</v>
+        <v>0.07693005336323755</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.654246587683997</v>
+        <v>0.6607008361249701</v>
       </c>
     </row>
     <row r="59">
@@ -3804,19 +4045,19 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.02725821573980387</v>
-      </c>
-      <c r="C59" s="34" t="n">
-        <v>0.05923194708907975</v>
-      </c>
-      <c r="D59" s="34" t="n">
-        <v>0.001614557192442783</v>
+        <v>0.03274937816180006</v>
+      </c>
+      <c r="C59" s="33" t="n">
+        <v>0.08177670389455144</v>
+      </c>
+      <c r="D59" s="33" t="n">
+        <v>0.002678136200668213</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.0548593647644455</v>
+        <v>0.07692131522288377</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.6432517319898794</v>
+        <v>0.6648087085490335</v>
       </c>
     </row>
     <row r="60">
@@ -3826,29 +4067,447 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.02103339008584262</v>
-      </c>
-      <c r="C60" s="33" t="n">
-        <v>0.02252548320671542</v>
-      </c>
-      <c r="D60" s="33" t="n">
-        <v>0.0004737872751589424</v>
+        <v>0.05348849401364011</v>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>0.0500680087725636</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>0.002678062387506149</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.0160983265692635</v>
+        <v>0.07691919516435003</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.4913808005382763</v>
+        <v>0.5183917993112132</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n">
+        <v>0.07177807601461969</v>
+      </c>
+      <c r="C61" s="33" t="n">
+        <v>0.03731545955679919</v>
+      </c>
+      <c r="D61" s="33" t="n">
+        <v>0.002678431892588399</v>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>0.07692980807376858</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>0.709927675625481</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="n">
+        <v>0.1157711205580592</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>0.02313126525201032</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>0.002677932498150931</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0.07691546448775699</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.7752370981178501</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="n">
+        <v>0.05909684148435081</v>
+      </c>
+      <c r="C63" s="33" t="n">
+        <v>0.04532124936123065</v>
+      </c>
+      <c r="D63" s="33" t="n">
+        <v>0.002678342689373383</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>0.07692724598278179</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0.4456283804373475</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n">
+        <v>0.06732426606347358</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>0.03977901633407638</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>0.00267809307941862</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0.07692007669616807</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>0.138613651134196</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced HRP — Marginal and Total Risk Contribution</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Marginal Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Total Risk Contrib.</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>% of Portfolio Risk</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Factor Risk Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="n">
+        <v>0.01042699644536602</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>0.06390377522929269</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>0.0006663244371613042</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0.02478621110720801</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>1.003712510749121</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n">
+        <v>0.007877217307104837</v>
+      </c>
+      <c r="C69" s="33" t="n">
+        <v>0.07180544771946636</v>
+      </c>
+      <c r="D69" s="33" t="n">
+        <v>0.0005656271155201919</v>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>0.02104043062411456</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>0.9304117589616353</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="n">
+        <v>0.01199876878492511</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>0.07291455747544447</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>0.0008748849162029907</v>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>0.03254432978610655</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>0.8923913124143709</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="n">
+        <v>0.007445323417489978</v>
+      </c>
+      <c r="C71" s="33" t="n">
+        <v>0.08137963297571774</v>
+      </c>
+      <c r="D71" s="33" t="n">
+        <v>0.0006058976871008508</v>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>0.02253843194740163</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0.6790697564157375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="n">
+        <v>0.06008769802326347</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.007542847709285006</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.000453232355390982</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.0168595240018467</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>0.9940789078272613</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="n">
+        <v>0.2775274350114209</v>
+      </c>
+      <c r="C73" s="33" t="n">
+        <v>0.01732507900038118</v>
+      </c>
+      <c r="D73" s="33" t="n">
+        <v>0.004808184736346022</v>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>0.1788568380070944</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>0.8296598221855379</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="n">
+        <v>0.1034099518290001</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.02676075945935788</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.002767328846599656</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0.1029402392730808</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>0.6607008361249701</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n">
+        <v>0.006846640750828856</v>
+      </c>
+      <c r="C75" s="33" t="n">
+        <v>0.07352885948428194</v>
+      </c>
+      <c r="D75" s="33" t="n">
+        <v>0.0005034256857070535</v>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>0.01872663619525227</v>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>0.6648087085490335</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="n">
+        <v>0.01171849185106932</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>0.05027835827915828</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>0.0005891865317794601</v>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>0.02191680350254683</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>0.5183917993112132</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n">
+        <v>0.0501118930893833</v>
+      </c>
+      <c r="C77" s="33" t="n">
+        <v>0.03935824411758022</v>
+      </c>
+      <c r="D77" s="33" t="n">
+        <v>0.001972316121406029</v>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>0.07336702817562298</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>0.709927675625481</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="n">
+        <v>0.3688608075794205</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>0.02562363105505561</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>0.009451553244084929</v>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>0.3515827739966169</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>0.7752370981178501</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>0.05046387852911244</v>
+      </c>
+      <c r="C79" s="33" t="n">
+        <v>0.04875208851106526</v>
+      </c>
+      <c r="D79" s="33" t="n">
+        <v>0.002460219472662935</v>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>0.09151625817488293</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>0.4456283804373475</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="n">
+        <v>0.03322489738161522</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.03505463583638689</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.001164686678413846</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.04332449520822549</v>
+      </c>
+      <c r="F80" s="9" t="n">
+        <v>0.138613651134196</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3861,7 +4520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3874,6 +4533,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3890,779 +4553,1095 @@
       <c r="G1" s="5" t="n"/>
       <c r="H1" s="5" t="n"/>
       <c r="I1" s="5" t="n"/>
-      <c r="J1" s="6" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="5" t="n"/>
+      <c r="M1" s="5" t="n"/>
+      <c r="N1" s="6" t="n"/>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="C2" s="35" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="D2" s="35" t="inlineStr">
+      <c r="D2" s="34" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="E2" s="35" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="F2" s="35" t="inlineStr">
+      <c r="F2" s="34" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="G2" s="35" t="inlineStr">
+      <c r="G2" s="34" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="H2" s="35" t="inlineStr">
+      <c r="H2" s="34" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="I2" s="35" t="inlineStr">
+      <c r="I2" s="34" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="J2" s="35" t="inlineStr">
+      <c r="J2" s="34" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
+      <c r="K2" s="34" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="L2" s="34" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="M2" s="34" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="N2" s="34" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="37" t="n">
+      <c r="B3" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="38" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="D3" s="38" t="n">
+      <c r="C3" s="37" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="D3" s="37" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="E3" s="38" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="F3" s="39" t="n">
-        <v>-0.344</v>
-      </c>
-      <c r="G3" s="40" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="H3" s="40" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="I3" s="38" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="J3" s="41" t="n">
-        <v>0.512</v>
+      <c r="E3" s="37" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="F3" s="38" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="G3" s="39" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H3" s="39" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="I3" s="37" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="J3" s="40" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="K3" s="37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L3" s="37" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="M3" s="40" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="N3" s="39" t="n">
+        <v>0.194</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="38" t="n">
-        <v>0.959</v>
-      </c>
-      <c r="C4" s="37" t="n">
+      <c r="B4" s="37" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="C4" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="38" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="F4" s="39" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G4" s="40" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H4" s="40" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="I4" s="38" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="J4" s="41" t="n">
-        <v>0.553</v>
+      <c r="D4" s="37" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="E4" s="37" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F4" s="38" t="n">
+        <v>-0.404</v>
+      </c>
+      <c r="G4" s="39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="H4" s="39" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I4" s="37" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="J4" s="40" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K4" s="37" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="L4" s="37" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="M4" s="40" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="N4" s="39" t="n">
+        <v>0.211</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="38" t="n">
+      <c r="B5" s="37" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="C5" s="38" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="D5" s="37" t="n">
+      <c r="C5" s="37" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="D5" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F5" s="39" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="G5" s="40" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="H5" s="40" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="I5" s="38" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="J5" s="41" t="n">
-        <v>0.468</v>
+      <c r="E5" s="37" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="F5" s="38" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="H5" s="39" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="I5" s="37" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="J5" s="40" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K5" s="40" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="L5" s="37" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="M5" s="40" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="N5" s="39" t="n">
+        <v>0.164</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="C6" s="38" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E6" s="37" t="n">
+      <c r="B6" s="37" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="C6" s="37" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="E6" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="39" t="n">
-        <v>-0.308</v>
-      </c>
-      <c r="G6" s="40" t="n">
+      <c r="F6" s="38" t="n">
+        <v>-0.327</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="H6" s="39" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J6" s="40" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="K6" s="40" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L6" s="37" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="M6" s="40" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="N6" s="39" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="n">
+        <v>-0.345</v>
+      </c>
+      <c r="C7" s="38" t="n">
+        <v>-0.404</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>-0.387</v>
+      </c>
+      <c r="E7" s="38" t="n">
+        <v>-0.327</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="40" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="I7" s="39" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="J7" s="38" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="K7" s="39" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="L7" s="38" t="n">
+        <v>-0.352</v>
+      </c>
+      <c r="M7" s="38" t="n">
+        <v>-0.363</v>
+      </c>
+      <c r="N7" s="39" t="n">
+        <v>-0.133</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="F8" s="40" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="I8" s="39" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="J8" s="39" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K8" s="39" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L8" s="39" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="M8" s="39" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="N8" s="39" t="n">
+        <v>0.213</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C9" s="39" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="F9" s="40" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="G9" s="40" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="39" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="J9" s="39" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="K9" s="39" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="L9" s="39" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="M9" s="39" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>-0.107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="G10" s="39" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="H10" s="39" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="I10" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="39" t="n">
         <v>0.287</v>
       </c>
-      <c r="H6" s="40" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="I6" s="41" t="n">
+      <c r="K10" s="40" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="N10" s="39" t="n">
+        <v>0.195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="C11" s="40" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="F11" s="38" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="I11" s="39" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="J11" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="M11" s="40" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="N11" s="39" t="n">
+        <v>0.205</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="D12" s="40" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="E12" s="40" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="G12" s="39" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H12" s="39" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="I12" s="40" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="37" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="N12" s="39" t="n">
+        <v>0.144</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="D13" s="37" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="F13" s="38" t="n">
+        <v>-0.352</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="H13" s="39" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J13" s="40" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="K13" s="37" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="N13" s="39" t="n">
+        <v>0.169</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="E14" s="40" t="n">
         <v>0.593</v>
       </c>
-      <c r="J6" s="41" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B7" s="39" t="n">
-        <v>-0.344</v>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="E7" s="39" t="n">
-        <v>-0.308</v>
-      </c>
-      <c r="F7" s="37" t="n">
+      <c r="F14" s="38" t="n">
+        <v>-0.363</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="M14" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="41" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="H7" s="41" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="J7" s="39" t="n">
-        <v>-0.536</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B8" s="40" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="C8" s="40" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="F8" s="41" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="G8" s="37" t="n">
+      <c r="N14" s="40" t="n">
+        <v>0.492</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>-0.133</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>-0.107</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="J15" s="39" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="L15" s="39" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="M15" s="40" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="N15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="41" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="I8" s="40" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J8" s="40" t="n">
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B9" s="40" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="C9" s="40" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="D9" s="40" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="F9" s="41" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="G9" s="41" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="H9" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="40" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="J9" s="40" t="n">
-        <v>-0.131</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+    </row>
+    <row r="16" ht="8" customHeight="1"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Notable Correlation Pairs</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Asset A</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Asset B</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Correlation</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Implication</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>0.9632992963845223</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>0.958294397091232</v>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>0.9345877915077815</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>0.893065257942776</v>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>0.8810201279768825</v>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>0.8655517514829589</v>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n">
+        <v>0.8514124303096332</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>0.8177061971060048</v>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>0.7948293211789398</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="C10" s="38" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="D10" s="38" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E10" s="41" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="F10" s="40" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="G10" s="40" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H10" s="40" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="I10" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="40" t="n">
-        <v>0.293</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B11" s="41" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="C11" s="41" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="E11" s="41" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="39" t="n">
-        <v>-0.536</v>
-      </c>
-      <c r="G11" s="40" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="H11" s="40" t="n">
-        <v>-0.131</v>
-      </c>
-      <c r="I11" s="40" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="J11" s="37" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Notable Correlation Pairs</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Asset A</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Asset B</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Correlation</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Implication</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="C28" s="33" t="n">
+        <v>0.7562736433623717</v>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n">
+        <v>0.753028382336137</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>0.7527410591942199</v>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="n">
-        <v>0.963604579887064</v>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>0.745140294201513</v>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>0.7402538872505268</v>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="C16" s="34" t="n">
-        <v>0.9585938857673019</v>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>0.7356620478388783</v>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>0.9351150145885929</v>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>0.8153008916507385</v>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="n">
-        <v>0.7921827030700286</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="n">
-        <v>0.7566863410399924</v>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C21" s="33" t="n">
-        <v>0.7550185248134618</v>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C22" s="34" t="n">
-        <v>0.7503296960631181</v>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>0.746784625795175</v>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="32" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B24" s="32" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="n">
-        <v>0.6253586382631419</v>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="C25" s="33" t="n">
-        <v>0.6118588409428388</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>0.5930074609613168</v>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>Moderate Positive</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>Moderate diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="n">
-        <v>0.5532735481847542</v>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Moderate Positive</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>Moderate diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n">
-        <v>-0.5361309580009153</v>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Hedging relationship</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="C29" s="33" t="n">
-        <v>0.5286001691139169</v>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Moderate Positive</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>Moderate diversification benefit</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4735,20 +5714,20 @@
           <t>Equal Weight</t>
         </is>
       </c>
-      <c r="B3" s="33" t="n">
-        <v>0.5927327150397735</v>
-      </c>
-      <c r="C3" s="33" t="n">
-        <v>0.2495523098663607</v>
-      </c>
-      <c r="D3" s="33" t="n">
-        <v>2.460418985371243</v>
-      </c>
-      <c r="E3" s="33" t="n">
-        <v>1.997176760310123</v>
-      </c>
-      <c r="F3" s="33" t="n">
-        <v>-0.02007623701015466</v>
+      <c r="B3" s="32" t="n">
+        <v>0.4731473750714025</v>
+      </c>
+      <c r="C3" s="32" t="n">
+        <v>0.1996774376539702</v>
+      </c>
+      <c r="D3" s="32" t="n">
+        <v>2.049186126282865</v>
+      </c>
+      <c r="E3" s="32" t="n">
+        <v>3.110631684588581</v>
+      </c>
+      <c r="F3" s="32" t="n">
+        <v>0.006744004449604376</v>
       </c>
     </row>
     <row r="4">
@@ -4757,20 +5736,20 @@
           <t>60/40</t>
         </is>
       </c>
-      <c r="B4" s="34" t="n">
-        <v>0.6313820183962096</v>
-      </c>
-      <c r="C4" s="34" t="n">
-        <v>0.3361740654264061</v>
-      </c>
-      <c r="D4" s="34" t="n">
-        <v>2.146974527988826</v>
-      </c>
-      <c r="E4" s="34" t="n">
-        <v>0.3615875557444018</v>
-      </c>
-      <c r="F4" s="34" t="n">
-        <v>-0.02618494416133161</v>
+      <c r="B4" s="33" t="n">
+        <v>0.632174514060608</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>0.3250025100735291</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>2.117402568703677</v>
+      </c>
+      <c r="E4" s="33" t="n">
+        <v>0.2828163189884664</v>
+      </c>
+      <c r="F4" s="33" t="n">
+        <v>-0.02484896267847612</v>
       </c>
     </row>
     <row r="5">
@@ -4779,20 +5758,20 @@
           <t>MVO</t>
         </is>
       </c>
-      <c r="B5" s="33" t="n">
-        <v>0.4597377893280422</v>
-      </c>
-      <c r="C5" s="33" t="n">
-        <v>0.580372581560643</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <v>2.856638421555682</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>0.02933521107835607</v>
-      </c>
-      <c r="F5" s="33" t="n">
-        <v>-0.04492263039729934</v>
+      <c r="B5" s="32" t="n">
+        <v>0.3460909189945736</v>
+      </c>
+      <c r="C5" s="32" t="n">
+        <v>0.4629493779918627</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>2.723134272356956</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>0.6782622813409744</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>0.02494902822637727</v>
       </c>
     </row>
     <row r="6">
@@ -4801,20 +5780,20 @@
           <t>Risk Parity</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
-        <v>0.3591806160720604</v>
-      </c>
-      <c r="C6" s="34" t="n">
-        <v>0.4308574963426787</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <v>1.337783775943102</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <v>2.361591902067863</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>-0.009981127111012841</v>
+      <c r="B6" s="33" t="n">
+        <v>0.2888946290602907</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0.3661991166779472</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>1.150987468462854</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>2.972281686197025</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>0.01173056227268853</v>
       </c>
     </row>
     <row r="7">
@@ -4823,20 +5802,20 @@
           <t>Enhanced HRP</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n">
-        <v>0.162083582947631</v>
-      </c>
-      <c r="C7" s="33" t="n">
-        <v>0.4610383070351105</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>0.5164422089887049</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>4.113308307736573</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>-0.007163543705210864</v>
+      <c r="B7" s="32" t="n">
+        <v>0.2071411228229106</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>0.2673077872105172</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>0.4993388383265021</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>3.346677045003516</v>
+      </c>
+      <c r="F7" s="32" t="n">
+        <v>0.01451283822328706</v>
       </c>
     </row>
   </sheetData>

--- a/analytics_report.xlsx
+++ b/analytics_report.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Backtest Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Portfolio Analytics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Factor Model" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stress Testing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Risk Decomposition" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Covariance" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Net Factor Exposure" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Analytics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Testing" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Decomposition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covariance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Net Factor Exposure" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,19 +71,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B7770D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00B03A2E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001E7B45"/>
+      <color rgb="00B7770D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -98,12 +92,13 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="001E7B45"/>
+      <color rgb="00B03A2E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00B03A2E"/>
+      <b val="1"/>
+      <color rgb="001E7B45"/>
       <sz val="10"/>
     </font>
     <font>
@@ -124,7 +119,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -165,12 +160,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="006B1A1A"/>
         <bgColor rgb="006B1A1A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A3A6B"/>
-        <bgColor rgb="001A3A6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -250,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,13 +279,13 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,7 +294,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -314,41 +303,35 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -356,25 +339,22 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -454,7 +434,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -469,13 +449,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -484,7 +464,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>2</col>
@@ -499,13 +479,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -524,13 +504,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -549,13 +529,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -574,13 +554,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -589,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -604,13 +584,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -619,7 +599,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -634,13 +614,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -960,7 +940,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>POET Covariance  |  JPMorgan 2026 LTCMA  |  Enhanced HRP  |  13 Asset Classes  |  2004 Q1 – 2024 Q4</t>
+          <t>POET Covariance  |  JPMorgan 2026 LTCMA  |  Enhanced HRP  |  13 Asset Classes  |  Full History: 2004 Q4 – 2024 Q4  |  OOS Backtest: 2009 Q4 – 2024 Q4</t>
         </is>
       </c>
     </row>
@@ -968,7 +948,7 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Key Finding: A conventional 60/40 portfolio allocates 80.6% of total risk to Equity Premium. Enhanced HRP reduces this to 42.0% — a 38.6 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
+          <t>Key Finding: A conventional 60/40 portfolio allocates 76.6% of total risk to Equity Premium. Enhanced HRP reduces this to 68.9% — a 7.7 pp reduction — while maintaining balanced systematic risk exposure across all five factors.</t>
         </is>
       </c>
     </row>
@@ -976,7 +956,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Portfolio Performance Metrics</t>
+          <t>Portfolio Performance Metrics (Walk-Forward Out-of-Sample, 2009 Q4 – 2024 Q4)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -1036,25 +1016,25 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>0.06499352425022981</v>
+        <v>0.07780564228482141</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.1035710907401094</v>
+        <v>0.09357355671388688</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.6275257292917563</v>
+        <v>0.5002015946442608</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>1.00809746126433</v>
+        <v>0.8168103859393345</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>-0.2929242982373964</v>
+        <v>-0.1727975788256963</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>0.221878228065453</v>
+        <v>0.4502704425234175</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0.03956381298337185</v>
+        <v>0.02886331827843378</v>
       </c>
     </row>
     <row r="9">
@@ -1064,22 +1044,22 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.06245310112278191</v>
+        <v>0.07769089574321396</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.1128462018830994</v>
+        <v>0.1069804901339125</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>0.5534355616813655</v>
+        <v>0.4364430905557523</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>1.04098829241875</v>
+        <v>0.7310947682269382</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>-0.2800420148978708</v>
+        <v>-0.2412384909745431</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>0.2230133258595432</v>
+        <v>0.3220501646704976</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
@@ -1092,25 +1072,25 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>0.07315951727129666</v>
+        <v>0.06995759674778912</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.08814883647169917</v>
+        <v>0.0796535820366803</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.8299544293450209</v>
+        <v>0.4890878194259892</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1.707951735971837</v>
+        <v>0.8479625219904645</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>-0.1999559307284849</v>
+        <v>-0.1875007639279591</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>0.3658782062865549</v>
+        <v>0.3731056625170231</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.05566283756079451</v>
+        <v>0.06792120949901236</v>
       </c>
     </row>
     <row r="11">
@@ -1120,25 +1100,25 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.05891136643505968</v>
+        <v>0.06079051168756591</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.06931186561532279</v>
+        <v>0.06373111055503076</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>0.8499463390873745</v>
+        <v>0.467440649129161</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>1.563746143545916</v>
+        <v>0.7882504931505657</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-0.1665091655061419</v>
+        <v>-0.1567953386437756</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.35380254447847</v>
+        <v>0.3877061155859759</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0.0568110828478045</v>
+        <v>0.05795006682429227</v>
       </c>
     </row>
     <row r="12">
@@ -1148,25 +1128,25 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.05191532254690638</v>
+        <v>0.06185350220722437</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.05672701063600805</v>
+        <v>0.06139100041103865</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.9151781834587384</v>
+        <v>0.5025736997385145</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>1.720196379330979</v>
+        <v>0.8806414039179555</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>-0.1388515020427566</v>
+        <v>-0.1519866962332772</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.3738909682872574</v>
+        <v>0.4069665552324944</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0.06544241006043219</v>
+        <v>0.05485359091027586</v>
       </c>
     </row>
     <row r="13" ht="8" customHeight="1"/>
@@ -1226,22 +1206,22 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>0.6509999999999999</v>
+        <v>0.802</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>-0.05599999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.131</v>
+        <v>0.038</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.133</v>
+        <v>-0.013</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.006</v>
+        <v>0.043</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.135</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="17">
@@ -1251,22 +1231,22 @@
         </is>
       </c>
       <c r="B17" s="15" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-0</v>
+        <v>0.159</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.099</v>
+        <v>0.026</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.005</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>-0.015</v>
+        <v>0.016</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.1</v>
+        <v>0.03700000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1276,22 +1256,22 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.414</v>
+        <v>0.5870000000000001</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.191</v>
+        <v>0.15</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.113</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.015</v>
+        <v>-0.012</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.016</v>
+        <v>0.118</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.25</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="19">
@@ -1301,22 +1281,22 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.487</v>
+        <v>0.6970000000000001</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.144</v>
+        <v>0.174</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>0.118</v>
+        <v>-0.017</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>0.011</v>
+        <v>0.052</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.166</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="20">
@@ -1326,22 +1306,22 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.42</v>
+        <v>0.6890000000000001</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>0.14</v>
+        <v>0.168</v>
       </c>
       <c r="D20" s="9" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G20" s="9" t="n">
         <v>0.065</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>0.154</v>
       </c>
     </row>
     <row r="21" ht="8" customHeight="1"/>
@@ -1379,7 +1359,7 @@
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
@@ -1425,7 +1405,7 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -1442,7 +1422,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -1486,7 +1466,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Backtest Summary Statistics — All Portfolios (2004 Q4 – 2024 Q4)</t>
+          <t>Backtest Summary Statistics — Walk-Forward OOS (2009 Q4 – 2024 Q4, 20Q burn-in)</t>
         </is>
       </c>
       <c r="B1" s="5" t="n"/>
@@ -1546,25 +1526,25 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>0.06499352425022981</v>
+        <v>0.07780564228482141</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>0.1035710907401094</v>
+        <v>0.09357355671388688</v>
       </c>
       <c r="D3" s="24" t="n">
-        <v>0.6275257292917563</v>
+        <v>0.5002015946442608</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1.00809746126433</v>
+        <v>0.8168103859393345</v>
       </c>
       <c r="F3" s="25" t="n">
-        <v>-0.2929242982373964</v>
+        <v>-0.1727975788256963</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>0.221878228065453</v>
+        <v>0.4502704425234175</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.03956381298337185</v>
+        <v>0.02886331827843378</v>
       </c>
     </row>
     <row r="4">
@@ -1574,22 +1554,22 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>0.06245310112278191</v>
+        <v>0.07769089574321396</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>0.1128462018830994</v>
+        <v>0.1069804901339125</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>0.5534355616813655</v>
+        <v>0.4364430905557523</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>1.04098829241875</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>-0.2800420148978708</v>
+        <v>0.7310947682269382</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>-0.2412384909745431</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>0.2230133258595432</v>
+        <v>0.3220501646704976</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -1602,25 +1582,25 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.07315951727129666</v>
+        <v>0.06995759674778912</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.08814883647169917</v>
-      </c>
-      <c r="D5" s="27" t="n">
-        <v>0.8299544293450209</v>
+        <v>0.0796535820366803</v>
+      </c>
+      <c r="D5" s="24" t="n">
+        <v>0.4890878194259892</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1.707951735971837</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-0.1999559307284849</v>
+        <v>0.8479625219904645</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-0.1875007639279591</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3658782062865549</v>
+        <v>0.3731056625170231</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.05566283756079451</v>
+        <v>0.06792120949901236</v>
       </c>
     </row>
     <row r="6">
@@ -1630,25 +1610,25 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.05891136643505968</v>
+        <v>0.06079051168756591</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.06931186561532279</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>0.8499463390873745</v>
+        <v>0.06373111055503076</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.467440649129161</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>1.563746143545916</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>-0.1665091655061419</v>
+        <v>0.7882504931505657</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>-0.1567953386437756</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>0.35380254447847</v>
+        <v>0.3877061155859759</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.0568110828478045</v>
+        <v>0.05795006682429227</v>
       </c>
     </row>
     <row r="7">
@@ -1658,25 +1638,25 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>0.05191532254690638</v>
+        <v>0.06185350220722437</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.05672701063600805</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0.9151781834587384</v>
+        <v>0.06139100041103865</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>0.5025736997385145</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1.720196379330979</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>-0.1388515020427566</v>
+        <v>0.8806414039179555</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-0.1519866962332772</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.3738909682872574</v>
+        <v>0.4069665552324944</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.06544241006043219</v>
+        <v>0.05485359091027586</v>
       </c>
     </row>
     <row r="29">
@@ -1718,12 +1698,12 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>0.03956381298337185</v>
-      </c>
-      <c r="C31" s="28" t="n">
-        <v>0.3846153846153845</v>
-      </c>
-      <c r="D31" s="32" t="inlineStr">
+        <v>0.02886331827843378</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
         <is>
           <t>Moderate Active</t>
         </is>
@@ -1738,10 +1718,10 @@
       <c r="B32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="33" t="n">
+      <c r="C32" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>Closet Indexer</t>
         </is>
@@ -1754,12 +1734,12 @@
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>0.05566283756079451</v>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>0.6755292397488672</v>
-      </c>
-      <c r="D33" s="32" t="inlineStr">
+        <v>0.06792120949901236</v>
+      </c>
+      <c r="C33" s="31" t="n">
+        <v>0.6783671888098582</v>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
         <is>
           <t>High Conviction Active</t>
         </is>
@@ -1772,14 +1752,14 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.0568110828478045</v>
-      </c>
-      <c r="C34" s="30" t="n">
-        <v>0.4482051204348193</v>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>Moderate Active</t>
+        <v>0.05795006682429227</v>
+      </c>
+      <c r="C34" s="32" t="n">
+        <v>0.5133705760103389</v>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>High Conviction Active</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1770,12 @@
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>0.06544241006043219</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>0.6355342602606397</v>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
+        <v>0.05485359091027586</v>
+      </c>
+      <c r="C35" s="31" t="n">
+        <v>0.5859973137144824</v>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
         <is>
           <t>High Conviction Active</t>
         </is>
@@ -1850,7 +1830,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1926,26 +1906,26 @@
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
-        <v>0.9625042408608269</v>
-      </c>
-      <c r="C3" s="35" t="n">
-        <v>0.02345556695950097</v>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>0.9221660405720516</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>0.3996132467526616</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>-0.005854488358147634</v>
+      <c r="B3" s="33" t="n">
+        <v>0.9723255785595877</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>0.02264960800350821</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>0.2587802532817873</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>0.3142008309516391</v>
+      </c>
+      <c r="F3" s="33" t="n">
+        <v>0.8475225251078355</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0</v>
+        <v>0.0003852377794763112</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.9906918940400172</v>
+        <v>0.9915018601479982</v>
       </c>
       <c r="I3" s="19" t="inlineStr">
         <is>
@@ -1959,26 +1939,26 @@
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
-        <v>0.9713542877937703</v>
-      </c>
-      <c r="C4" s="36" t="n">
-        <v>-0.02791969853016975</v>
-      </c>
-      <c r="D4" s="36" t="n">
-        <v>1.307588071319306</v>
-      </c>
-      <c r="E4" s="36" t="n">
-        <v>2.069722843884614</v>
-      </c>
-      <c r="F4" s="36" t="n">
-        <v>0.03673514360340332</v>
+      <c r="B4" s="34" t="n">
+        <v>1.00004972012272</v>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>-0.07886446856508984</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>2.601569085667045</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>-0.1176097107742471</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>-0.9135351917706455</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0</v>
+        <v>0.004307831966098818</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>0.9123635173053706</v>
+        <v>0.9106321335323445</v>
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
@@ -1992,26 +1972,26 @@
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
-        <v>1.184029795675607</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>-0.1590176041375175</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0.676937059242492</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>-2.052830116472316</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>-0.01476517062835937</v>
+      <c r="B5" s="33" t="n">
+        <v>1.143226873957848</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>-0.1526647161540682</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>1.676662359350227</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>-0.7046326721240791</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>-2.031662076974286</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0</v>
+        <v>0.001948473297198281</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0.8712833012703342</v>
+        <v>0.8740422818725411</v>
       </c>
       <c r="I5" s="19" t="inlineStr">
         <is>
@@ -2025,26 +2005,26 @@
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
-        <v>0.7532197633494774</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>0.2392008134777396</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>5.685573550590397</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>6.29629067295865</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>-0.09556594450963743</v>
+      <c r="B6" s="34" t="n">
+        <v>0.7912705246888909</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>0.05339031840944732</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>1.727516095928932</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>-0.0272548455565519</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>8.629112104074631</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>-0.0001298368730119708</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>0.6355398384728477</v>
+        <v>0.6340086675560316</v>
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
@@ -2058,30 +2038,30 @@
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
-        <v>0.02522250650681003</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>1.139230258689664</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>-0.1658015292723478</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>-2.135877837199861</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>-0.007930514856369857</v>
+      <c r="B7" s="33" t="n">
+        <v>0.009056818092886477</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>1.204434900122915</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>0.8569850933349491</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>0.3371334910006847</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>-3.406825328980056</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0</v>
+        <v>0.001112452487722063</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.9812439847251684</v>
+        <v>0.9805179986326127</v>
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2091,30 +2071,30 @@
           <t>TIPS</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
-        <v>0.0194482843814953</v>
-      </c>
-      <c r="C8" s="36" t="n">
-        <v>0.4459887403586637</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>-0.1250616872544132</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>6.421673019699722</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>-0.005981872260688031</v>
+      <c r="B8" s="34" t="n">
+        <v>0.1028386326892127</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <v>0.3330851605797071</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>-1.221676271914379</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>0.8344693763148957</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>3.477865983718272</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0</v>
+        <v>-0.001677595321261801</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>0.8015086616077469</v>
+        <v>0.5642953190730762</v>
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2124,30 +2104,30 @@
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
-        <v>0.2750954294387477</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0.5137951400731287</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>0.2429914492158691</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>-0.1457078507988893</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>0.01162261473964993</v>
+      <c r="B9" s="33" t="n">
+        <v>0.2457323668658692</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0.4727624525191363</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>3.963584390835535</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>-1.236517480942052</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>-4.571745357976438</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>0.008777812700855923</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0.6374629953920316</v>
+        <v>0.6948213047243539</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2157,26 +2137,26 @@
           <t>REITs</t>
         </is>
       </c>
-      <c r="B10" s="36" t="n">
-        <v>1.035110339377469</v>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>0.3934971993740877</v>
-      </c>
-      <c r="D10" s="36" t="n">
-        <v>9.352421615745463</v>
-      </c>
-      <c r="E10" s="36" t="n">
-        <v>-8.299634434854106</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>-0.136211101334049</v>
+      <c r="B10" s="34" t="n">
+        <v>0.9568803689662021</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>0.6018788032960937</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>-0.09723383997855481</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>1.947874498999674</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>8.837106086054378</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0</v>
+        <v>-0.01623110099058055</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>0.6337080092805776</v>
+        <v>0.6261476795036272</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2190,26 +2170,26 @@
           <t>Commodities</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
-        <v>0.01657438583919279</v>
-      </c>
-      <c r="C11" s="35" t="n">
-        <v>-0.3464828245407032</v>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>4.883589691416405</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>16.0388589163062</v>
-      </c>
-      <c r="F11" s="35" t="n">
-        <v>0.06933460659340032</v>
+      <c r="B11" s="33" t="n">
+        <v>0.4450906076761416</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>0.04352504595939582</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>2.272249910967012</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>6.656212441465041</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>1.110466072938367</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>-0.04550138558878881</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>0.4370483747153048</v>
+        <v>0.5010494738109886</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
@@ -2223,30 +2203,30 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="B12" s="36" t="n">
-        <v>0.2139108894699562</v>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>0.2787451901424915</v>
-      </c>
-      <c r="D12" s="36" t="n">
-        <v>3.43229865495527</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>3.647889816547432</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>0.1641715585741692</v>
+      <c r="B12" s="34" t="n">
+        <v>0.2395400846824166</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>0.151441047602926</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>4.316605502223371</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>-0.7978531571144418</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>6.903584241036213</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0</v>
+        <v>0.01482000171226959</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>0.8431315161474411</v>
+        <v>0.8597022309446328</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2256,30 +2236,30 @@
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0.2662615280266115</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0.03413008712923776</v>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>0.2697224940806349</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>2.055745923262592</v>
-      </c>
-      <c r="F13" s="35" t="n">
-        <v>0.01290119732786036</v>
+      <c r="B13" s="33" t="n">
+        <v>0.2808853927489229</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>-0.02525420771361412</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>1.129527049173438</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>-0.1956517891265285</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>0.11919079395306</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>0</v>
+        <v>0.0125048329035973</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.7443129475785015</v>
+        <v>0.7380364015058198</v>
       </c>
       <c r="I13" s="19" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2289,30 +2269,30 @@
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="B14" s="36" t="n">
-        <v>0.3475645787692835</v>
-      </c>
-      <c r="C14" s="36" t="n">
-        <v>-0.01789473558713058</v>
-      </c>
-      <c r="D14" s="36" t="n">
-        <v>1.510698166693959</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>4.474796912527248</v>
-      </c>
-      <c r="F14" s="36" t="n">
-        <v>0.07225876810085358</v>
+      <c r="B14" s="34" t="n">
+        <v>0.415919141762514</v>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>-0.08517026109323211</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>0.5051951073520926</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>0.9601631865501158</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>5.179134026938361</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0</v>
+        <v>0.01656015420254579</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>0.4472956521780461</v>
+        <v>0.4413048240918499</v>
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
@@ -2322,37 +2302,37 @@
           <t>Private Real Estate</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
-        <v>-0.0422572163933037</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <v>0.2525396594451277</v>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>0.008416326420867809</v>
-      </c>
-      <c r="E15" s="35" t="n">
-        <v>13.43606605605533</v>
-      </c>
-      <c r="F15" s="35" t="n">
-        <v>0.0004025644516642721</v>
+      <c r="B15" s="33" t="n">
+        <v>0.1741880464813794</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>0.1070450167865624</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>-2.748851861398335</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>3.26746621655988</v>
+      </c>
+      <c r="F15" s="33" t="n">
+        <v>6.765352359636767</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0</v>
+        <v>-0.009757327900751281</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0.08716459731266091</v>
+        <v>0.04151457469511732</v>
       </c>
       <c r="I15" s="19" t="inlineStr">
         <is>
-          <t>BAA-Treasury</t>
+          <t>AAA-BAA Spread</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Equity Premium Beta: Full-Sample OLS vs Stress (Q10 Quantile Regression)</t>
+          <t>Equity Premium Beta: OLS (Mean) vs Q10 Quantile Regression (Left-Tail Conditional)</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
@@ -2373,7 +2353,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Stress Beta (Q10)</t>
+          <t>Q10 Beta</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -2383,28 +2363,28 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Interpretation</t>
+          <t>Left-Tail Interpretation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B19" s="35" t="n">
-        <v>0.01657438583919279</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>0.612814361486727</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>0.5962399756475342</v>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="n">
+        <v>0.7912705246888909</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>1.000784512210129</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>0.209513987521238</v>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>Significant stress uplift</t>
+          <t>Co-crash: factor-driven downside</t>
         </is>
       </c>
     </row>
@@ -2414,18 +2394,18 @@
           <t>Private Real Estate</t>
         </is>
       </c>
-      <c r="B20" s="36" t="n">
-        <v>-0.0422572163933037</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>0.1943926134830137</v>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>0.2366498298763174</v>
+      <c r="B20" s="34" t="n">
+        <v>0.1741880464813794</v>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>0.3693038897983212</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>0.1951158433169419</v>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Significant stress uplift</t>
+          <t>Co-crash: factor-driven downside</t>
         </is>
       </c>
     </row>
@@ -2435,60 +2415,60 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
-        <v>0.2139108894699562</v>
-      </c>
-      <c r="C21" s="35" t="n">
-        <v>0.2968736681282671</v>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>0.08296277865831087</v>
+      <c r="B21" s="33" t="n">
+        <v>0.2395400846824166</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0.3346909738622495</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>0.09515088917983289</v>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>Moderate stress uplift</t>
+          <t>Moderate co-crash tendency</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B22" s="36" t="n">
-        <v>0.0194482843814953</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>0.1007620091545305</v>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>0.08131372477303518</v>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="n">
+        <v>0.009056818092886477</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>0.04718443049201591</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>0.03812761239912943</v>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Moderate stress uplift</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B23" s="35" t="n">
-        <v>0.02522250650681003</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.07165021511635317</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>0.04642770860954314</v>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="n">
+        <v>0.1028386326892127</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>0.1303836897659673</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>0.02754505707675468</v>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
@@ -2498,165 +2478,165 @@
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n">
-        <v>0.9625042408608269</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>0.9793425414193206</v>
-      </c>
-      <c r="D24" s="36" t="n">
-        <v>0.01683830055849378</v>
+      <c r="B24" s="34" t="n">
+        <v>0.9723255785595877</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.9691959722404784</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>-0.003129606319109302</v>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B25" s="35" t="n">
-        <v>1.035110339377469</v>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>1.031110052707938</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>-0.004000286669531006</v>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="n">
+        <v>0.2457323668658692</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0.238616110998717</v>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>-0.007116255867152116</v>
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>0.7532197633494774</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>0.7449298939758666</v>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>-0.008289869373610759</v>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n">
+        <v>1.143226873957848</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>1.109751750293088</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <v>-0.03347512366475947</v>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B27" s="35" t="n">
-        <v>0.2750954294387477</v>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0.2323437215866302</v>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>-0.04275170785211746</v>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="n">
+        <v>0.2808853927489229</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>0.2366039999832863</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>-0.04428139276563656</v>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Symmetric tail sensitivity</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>0.3475645787692835</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>0.2923064843573329</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>-0.05525809441195068</v>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="n">
+        <v>1.00004972012272</v>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>0.9000960312596521</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>-0.09995368886306755</v>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Idiosyncratic downside risk</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n">
-        <v>0.2662615280266115</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0.1884016479536835</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>-0.07785988007292804</v>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="n">
+        <v>0.415919141762514</v>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>0.3025104958205753</v>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>-0.1134086459419388</v>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Idiosyncratic downside risk</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>0.9713542877937703</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>0.8150774240568861</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>-0.1562768637368842</v>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n">
+        <v>0.4450906076761416</v>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>0.3019321348390776</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>-0.143158472837064</v>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Idiosyncratic downside risk</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n">
-        <v>1.184029795675607</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>0.9628322446122715</v>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>-0.2211975510633357</v>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>0.9568803689662021</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>0.7902512514282529</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>-0.1666291175379492</v>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>Stable across regimes</t>
+          <t>Strongly idiosyncratic downside</t>
         </is>
       </c>
     </row>
@@ -2733,16 +2713,16 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>-0.2929242982373964</v>
+        <v>-0.2814808907634485</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.04460231281462567</v>
+        <v>-0.03192743681062316</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>-0.1293955141254147</v>
+        <v>-0.1399937126074327</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>0.5302180765976217</v>
+        <v>0.5598501534146194</v>
       </c>
     </row>
     <row r="4">
@@ -2752,16 +2732,16 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>-0.2495980726306681</v>
+        <v>-0.2495977059310831</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>-0.003713565811961916</v>
+        <v>-0.003713469979544914</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>-0.2018217141761193</v>
+        <v>-0.2018217614714174</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>0.6016792378990492</v>
+        <v>0.6016792501106374</v>
       </c>
     </row>
     <row r="5">
@@ -2771,16 +2751,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>-0.1830486748285078</v>
+        <v>-0.2610967083727261</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.03683695337861703</v>
+        <v>-0.02037701805258418</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>-0.1786484994678725</v>
+        <v>-0.1494269766701456</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>0.5145573060842727</v>
+        <v>0.5636143277194465</v>
       </c>
     </row>
     <row r="6">
@@ -2790,16 +2770,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>-0.1665091655061418</v>
+        <v>-0.2181968588076418</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.01971956610018144</v>
+        <v>-0.007269881146988344</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>-0.1449286097236309</v>
+        <v>-0.1225298236572626</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>0.3378735970052109</v>
+        <v>0.3894965368994237</v>
       </c>
     </row>
     <row r="7">
@@ -2809,16 +2789,16 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>-0.1050506428004342</v>
+        <v>-0.1781466131979096</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.02485925553436985</v>
+        <v>0.0006797619798637466</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>-0.1166178609836621</v>
+        <v>-0.1142972758801939</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.3183738177155639</v>
+        <v>0.3482635591968987</v>
       </c>
     </row>
   </sheetData>
@@ -2912,17 +2892,17 @@
       <c r="B4" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C4" s="35" t="n">
-        <v>0.07604848222125912</v>
-      </c>
-      <c r="D4" s="35" t="n">
-        <v>0.005849883247789164</v>
+      <c r="C4" s="33" t="n">
+        <v>0.07484932932269879</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>0.005757640717130677</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.1129636311829188</v>
+        <v>0.1173311368561452</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9924714026227938</v>
       </c>
     </row>
     <row r="5">
@@ -2934,17 +2914,17 @@
       <c r="B5" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C5" s="36" t="n">
-        <v>0.08671094150982253</v>
-      </c>
-      <c r="D5" s="36" t="n">
-        <v>0.006670072423832504</v>
+      <c r="C5" s="34" t="n">
+        <v>0.07888802937568137</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>0.006068309951975492</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.1288018186574803</v>
+        <v>0.1236620588954656</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8777511079444464</v>
       </c>
     </row>
     <row r="6">
@@ -2956,17 +2936,17 @@
       <c r="B6" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C6" s="35" t="n">
-        <v>0.09160479264684693</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0.007046522511295919</v>
+      <c r="C6" s="33" t="n">
+        <v>0.0870849672938426</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>0.006698843637987894</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.1360712233682609</v>
+        <v>0.1365112861815335</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8435113695831095</v>
       </c>
     </row>
     <row r="7">
@@ -2978,17 +2958,17 @@
       <c r="B7" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C7" s="36" t="n">
-        <v>0.08975643374929826</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>0.006904341057638329</v>
+      <c r="C7" s="34" t="n">
+        <v>0.07553598088402713</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>0.005810460068002088</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.1333256415144526</v>
+        <v>0.1184075073332588</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6749512644444484</v>
       </c>
     </row>
     <row r="8">
@@ -3000,17 +2980,17 @@
       <c r="B8" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C8" s="35" t="n">
-        <v>-0.01890725699586819</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>-0.001454404384297553</v>
+      <c r="C8" s="33" t="n">
+        <v>0.02407203700308885</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>0.001851695154083758</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>-0.02808514178820586</v>
+        <v>0.03773446594075337</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9820450787184068</v>
       </c>
     </row>
     <row r="9">
@@ -3022,17 +3002,17 @@
       <c r="B9" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C9" s="36" t="n">
-        <v>0.009951105476017614</v>
-      </c>
-      <c r="D9" s="36" t="n">
-        <v>0.0007654696520013551</v>
+      <c r="C9" s="34" t="n">
+        <v>0.01546372355180135</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>0.001189517196292412</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.0147815311498871</v>
+        <v>0.02424038105324443</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.7943547652209734</v>
       </c>
     </row>
     <row r="10">
@@ -3044,17 +3024,17 @@
       <c r="B10" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C10" s="35" t="n">
-        <v>0.01592770997060341</v>
-      </c>
-      <c r="D10" s="35" t="n">
-        <v>0.001225208459277186</v>
+      <c r="C10" s="33" t="n">
+        <v>0.03201200679008828</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>0.002462462060776022</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0236592750066058</v>
+        <v>0.05018087915703813</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8721710870286241</v>
       </c>
     </row>
     <row r="11">
@@ -3066,17 +3046,17 @@
       <c r="B11" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C11" s="36" t="n">
-        <v>0.08804865704708366</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>0.006772973619006437</v>
+      <c r="C11" s="34" t="n">
+        <v>0.09619887919817495</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>0.007399913784474998</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>0.1307888827009042</v>
+        <v>0.1507979291564062</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.7282328929273317</v>
       </c>
     </row>
     <row r="12">
@@ -3088,17 +3068,17 @@
       <c r="B12" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C12" s="35" t="n">
-        <v>0.075133417224411</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0.005779493632647001</v>
+      <c r="C12" s="33" t="n">
+        <v>0.0405892154499536</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>0.003122247342304124</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.1116043790086071</v>
+        <v>0.06362620528381718</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.4471345099507237</v>
       </c>
     </row>
     <row r="13">
@@ -3110,17 +3090,17 @@
       <c r="B13" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C13" s="36" t="n">
-        <v>0.03992411329824733</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>0.003071085638326719</v>
+      <c r="C13" s="34" t="n">
+        <v>0.03524344872072763</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>0.002711034516979049</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>0.05930391610981455</v>
+        <v>0.05524637217931896</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8460701286144402</v>
       </c>
     </row>
     <row r="14">
@@ -3132,17 +3112,17 @@
       <c r="B14" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C14" s="35" t="n">
-        <v>0.0273652664115515</v>
-      </c>
-      <c r="D14" s="35" t="n">
-        <v>0.002105020493196269</v>
+      <c r="C14" s="33" t="n">
+        <v>0.02294880442705742</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>0.001765292648235186</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04064880418182311</v>
+        <v>0.0359737266490032</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8085079193866584</v>
       </c>
     </row>
     <row r="15">
@@ -3154,17 +3134,17 @@
       <c r="B15" s="12" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C15" s="36" t="n">
-        <v>0.05235587803403795</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>0.004027375233387536</v>
+      <c r="C15" s="34" t="n">
+        <v>0.03714004235298929</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>0.00285692633484533</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.07777025817934882</v>
+        <v>0.0582194046572453</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.4648302531487577</v>
       </c>
     </row>
     <row r="16">
@@ -3176,17 +3156,17 @@
       <c r="B16" s="9" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="C16" s="35" t="n">
-        <v>0.03929254921739969</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0.003022503785953823</v>
+      <c r="C16" s="33" t="n">
+        <v>0.01790589807231554</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>0.001377376774793503</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.05836578072810264</v>
+        <v>0.02806864665676994</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.2258308249171992</v>
       </c>
     </row>
     <row r="18">
@@ -3242,17 +3222,17 @@
       <c r="B20" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="C20" s="35" t="n">
-        <v>0.07489545797820696</v>
-      </c>
-      <c r="D20" s="35" t="n">
-        <v>0.008987454957384835</v>
+      <c r="C20" s="33" t="n">
+        <v>0.07279723043355497</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0.008735667652026597</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>0.1592867957876898</v>
+        <v>0.1440509619550968</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9924714026227938</v>
       </c>
     </row>
     <row r="21">
@@ -3264,17 +3244,17 @@
       <c r="B21" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C21" s="36" t="n">
-        <v>0.08397471326890485</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>0.01007696559226858</v>
+      <c r="C21" s="34" t="n">
+        <v>0.07616840730622126</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>0.009140208876746551</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>0.1785964511717921</v>
+        <v>0.1507218375988014</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8777511079444464</v>
       </c>
     </row>
     <row r="22">
@@ -3286,17 +3266,17 @@
       <c r="B22" s="9" t="n">
         <v>0.12</v>
       </c>
-      <c r="C22" s="35" t="n">
-        <v>0.09111479827874773</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>0.01093377579344973</v>
+      <c r="C22" s="33" t="n">
+        <v>0.08466327521407054</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>0.01015959302568846</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.193781901579219</v>
+        <v>0.1675314591533478</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8435113695831095</v>
       </c>
     </row>
     <row r="23">
@@ -3308,17 +3288,17 @@
       <c r="B23" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C23" s="36" t="n">
-        <v>0.08745089141391921</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>0.0104941069696703</v>
+      <c r="C23" s="34" t="n">
+        <v>0.07409809575001078</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>0.008891771490001293</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.1859895467379832</v>
+        <v>0.1466251107117658</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6749512644444484</v>
       </c>
     </row>
     <row r="24">
@@ -3330,17 +3310,17 @@
       <c r="B24" s="9" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="C24" s="35" t="n">
-        <v>-0.002026303910268667</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>-0.000270173854702489</v>
+      <c r="C24" s="33" t="n">
+        <v>0.03508715738877045</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>0.004678287651836061</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-0.004788355304724739</v>
+        <v>0.07714485754197552</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9820450787184068</v>
       </c>
     </row>
     <row r="25">
@@ -3352,17 +3332,17 @@
       <c r="B25" s="12" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="C25" s="36" t="n">
-        <v>0.01128184223015831</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>0.001504245630687774</v>
+      <c r="C25" s="34" t="n">
+        <v>0.01758742179585586</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <v>0.002344989572780782</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.02666010207850974</v>
+        <v>0.03866882500450632</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.7943547652209734</v>
       </c>
     </row>
     <row r="26">
@@ -3374,17 +3354,17 @@
       <c r="B26" s="9" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="C26" s="35" t="n">
-        <v>0.02366079429953975</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0.003154772573271966</v>
+      <c r="C26" s="33" t="n">
+        <v>0.03662751209257904</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>0.004883668279010539</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.05591278254167711</v>
+        <v>0.08053157943776115</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8721710870286241</v>
       </c>
     </row>
     <row r="27">
@@ -3396,17 +3376,17 @@
       <c r="B27" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="C27" s="36" t="n">
-        <v>0.0961829439959918</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>0.01154195327951901</v>
+      <c r="C27" s="34" t="n">
+        <v>0.09840592063116478</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <v>0.01180871047573977</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>0.2045607754078538</v>
+        <v>0.1947253685967452</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.7282328929273317</v>
       </c>
     </row>
     <row r="28">
@@ -3418,17 +3398,17 @@
       <c r="B28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="35" t="n">
-        <v>0.04363145447238432</v>
-      </c>
-      <c r="D28" s="35" t="n">
+      <c r="C28" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.4471345099507237</v>
       </c>
     </row>
     <row r="29">
@@ -3440,17 +3420,17 @@
       <c r="B29" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C29" s="36" t="n">
-        <v>0.03736801761619855</v>
-      </c>
-      <c r="D29" s="36" t="n">
+      <c r="C29" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="34" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8460701286144402</v>
       </c>
     </row>
     <row r="30">
@@ -3462,17 +3442,17 @@
       <c r="B30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C30" s="35" t="n">
-        <v>0.02593079077558953</v>
-      </c>
-      <c r="D30" s="35" t="n">
+      <c r="C30" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8085079193866584</v>
       </c>
     </row>
     <row r="31">
@@ -3484,17 +3464,17 @@
       <c r="B31" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C31" s="36" t="n">
-        <v>0.03961123437025107</v>
-      </c>
-      <c r="D31" s="36" t="n">
+      <c r="C31" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="34" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.4648302531487577</v>
       </c>
     </row>
     <row r="32">
@@ -3506,17 +3486,17 @@
       <c r="B32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C32" s="35" t="n">
-        <v>0.01678542567237088</v>
-      </c>
-      <c r="D32" s="35" t="n">
+      <c r="C32" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="33" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.2258308249171992</v>
       </c>
     </row>
     <row r="34">
@@ -3570,19 +3550,19 @@
         </is>
       </c>
       <c r="B36" s="9" t="n">
-        <v>1.540461288441797e-08</v>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>0.05604810820385785</v>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>8.633994097844016e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>1.958958153830204e-08</v>
+        <v>0</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9924714026227938</v>
       </c>
     </row>
     <row r="37">
@@ -3592,19 +3572,19 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>1.286140172707754e-08</v>
-      </c>
-      <c r="C37" s="36" t="n">
-        <v>0.05994390698587128</v>
-      </c>
-      <c r="D37" s="36" t="n">
-        <v>7.709626688358602e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C37" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="34" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>1.749229370902436e-08</v>
+        <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8777511079444464</v>
       </c>
     </row>
     <row r="38">
@@ -3614,19 +3594,19 @@
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>1.034391777355504e-08</v>
-      </c>
-      <c r="C38" s="35" t="n">
-        <v>0.06375923942128729</v>
-      </c>
-      <c r="D38" s="35" t="n">
-        <v>6.595203298782051e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C38" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>1.496378979636218e-08</v>
+        <v>0</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8435113695831095</v>
       </c>
     </row>
     <row r="39">
@@ -3636,19 +3616,19 @@
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>0.07113737017120696</v>
-      </c>
-      <c r="C39" s="36" t="n">
-        <v>0.0671713405534603</v>
-      </c>
-      <c r="D39" s="36" t="n">
-        <v>0.004778392517847712</v>
+        <v>0.1483670381692468</v>
+      </c>
+      <c r="C39" s="34" t="n">
+        <v>0.07664513155514592</v>
+      </c>
+      <c r="D39" s="34" t="n">
+        <v>0.01137161115892927</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>0.1084164626354847</v>
+        <v>0.2572423578510876</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6749512644444484</v>
       </c>
     </row>
     <row r="40">
@@ -3658,19 +3638,19 @@
         </is>
       </c>
       <c r="B40" s="9" t="n">
-        <v>0.2963200956729828</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0.02027839680564917</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0.00600889648154467</v>
+        <v>0.1244012044836054</v>
+      </c>
+      <c r="C40" s="33" t="n">
+        <v>0.02989157568849701</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>0.003718548019561883</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.1363352421214061</v>
+        <v>0.08411895614136169</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9820450787184068</v>
       </c>
     </row>
     <row r="41">
@@ -3680,19 +3660,19 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>9.201562116762712e-09</v>
-      </c>
-      <c r="C41" s="36" t="n">
-        <v>0.01515708195138125</v>
-      </c>
-      <c r="D41" s="36" t="n">
-        <v>1.394688310844975e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C41" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>0</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>3.164394146694722e-09</v>
+        <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.7943547652209734</v>
       </c>
     </row>
     <row r="42">
@@ -3702,19 +3682,19 @@
         </is>
       </c>
       <c r="B42" s="9" t="n">
-        <v>8.935097992254681e-09</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>0.02639673412319088</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>2.358574060662035e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C42" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5.351344737078344e-09</v>
+        <v>0</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8721710870286241</v>
       </c>
     </row>
     <row r="43">
@@ -3724,19 +3704,19 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.1364634563400894</v>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>0.08498129605168149</v>
-      </c>
-      <c r="D43" s="36" t="n">
-        <v>0.01159684138347285</v>
+        <v>0.07723160670653635</v>
+      </c>
+      <c r="C43" s="34" t="n">
+        <v>0.09440214392754148</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>0.007290829252065723</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.2631195565966681</v>
+        <v>0.1649291451562139</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.7282328929273317</v>
       </c>
     </row>
     <row r="44">
@@ -3746,19 +3726,19 @@
         </is>
       </c>
       <c r="B44" s="9" t="n">
-        <v>2.096350137433955e-08</v>
-      </c>
-      <c r="C44" s="35" t="n">
-        <v>0.02052878880749672</v>
-      </c>
-      <c r="D44" s="35" t="n">
-        <v>4.303552923794839e-10</v>
+        <v>0</v>
+      </c>
+      <c r="C44" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>9.764287530162752e-09</v>
+        <v>0</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.4471345099507237</v>
       </c>
     </row>
     <row r="45">
@@ -3768,19 +3748,19 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.1960790013757596</v>
-      </c>
-      <c r="C45" s="36" t="n">
-        <v>0.03660795132295001</v>
-      </c>
-      <c r="D45" s="36" t="n">
-        <v>0.007178050537816456</v>
+        <v>0.3500000787941104</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <v>0.03644794788558067</v>
+      </c>
+      <c r="D45" s="34" t="n">
+        <v>0.01275678463183686</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.1628620597872786</v>
+        <v>0.2885769933063047</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8460701286144402</v>
       </c>
     </row>
     <row r="46">
@@ -3790,19 +3770,19 @@
         </is>
       </c>
       <c r="B46" s="9" t="n">
-        <v>1.618598277387212e-09</v>
-      </c>
-      <c r="C46" s="35" t="n">
-        <v>0.02013819062703088</v>
-      </c>
-      <c r="D46" s="35" t="n">
-        <v>3.259564065860747e-11</v>
+        <v>0</v>
+      </c>
+      <c r="C46" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="9" t="n">
-        <v>7.395591811146036e-10</v>
+        <v>0</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8085079193866584</v>
       </c>
     </row>
     <row r="47">
@@ -3812,19 +3792,19 @@
         </is>
       </c>
       <c r="B47" s="12" t="n">
-        <v>0.2822620050016704</v>
-      </c>
-      <c r="C47" s="36" t="n">
-        <v>0.04946939446322386</v>
-      </c>
-      <c r="D47" s="36" t="n">
-        <v>0.0139633304674081</v>
+        <v>0.1678456114977098</v>
+      </c>
+      <c r="C47" s="34" t="n">
+        <v>0.03836283086706017</v>
+      </c>
+      <c r="D47" s="34" t="n">
+        <v>0.006439032805664931</v>
       </c>
       <c r="E47" s="12" t="n">
-        <v>0.3168125871267995</v>
+        <v>0.1456602725911104</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.4648302531487577</v>
       </c>
     </row>
     <row r="48">
@@ -3834,19 +3814,19 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>0.01773799210959868</v>
-      </c>
-      <c r="C48" s="35" t="n">
-        <v>0.03094508737001761</v>
-      </c>
-      <c r="D48" s="35" t="n">
-        <v>0.0005489037156002144</v>
+        <v>0.1321544603487914</v>
+      </c>
+      <c r="C48" s="33" t="n">
+        <v>0.01989354796515283</v>
+      </c>
+      <c r="D48" s="33" t="n">
+        <v>0.00262902109575757</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.01245402066711213</v>
+        <v>0.0594722749539218</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.2258308249171992</v>
       </c>
     </row>
     <row r="50">
@@ -3900,19 +3880,19 @@
         </is>
       </c>
       <c r="B52" s="9" t="n">
-        <v>0.04239826333525394</v>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>0.06287655228620767</v>
-      </c>
-      <c r="D52" s="35" t="n">
-        <v>0.002665856621443495</v>
+        <v>0.03987326844377296</v>
+      </c>
+      <c r="C52" s="33" t="n">
+        <v>0.070985159347736</v>
+      </c>
+      <c r="D52" s="33" t="n">
+        <v>0.002830410314196277</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.0769235281081268</v>
+        <v>0.07692306943290814</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9924714026227938</v>
       </c>
     </row>
     <row r="53">
@@ -3922,19 +3902,19 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>0.03838122897303223</v>
-      </c>
-      <c r="C53" s="36" t="n">
-        <v>0.06945530211249798</v>
-      </c>
-      <c r="D53" s="36" t="n">
-        <v>0.002665779853770914</v>
+        <v>0.03867879490077662</v>
+      </c>
+      <c r="C53" s="34" t="n">
+        <v>0.07317731494509823</v>
+      </c>
+      <c r="D53" s="34" t="n">
+        <v>0.00283041035615099</v>
       </c>
       <c r="E53" s="12" t="n">
-        <v>0.07692131297015872</v>
+        <v>0.07692307057312633</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8777511079444464</v>
       </c>
     </row>
     <row r="54">
@@ -3944,19 +3924,19 @@
         </is>
       </c>
       <c r="B54" s="9" t="n">
-        <v>0.0370534553973652</v>
-      </c>
-      <c r="C54" s="35" t="n">
-        <v>0.07194606436802295</v>
-      </c>
-      <c r="D54" s="35" t="n">
-        <v>0.002665850287076504</v>
+        <v>0.03536029051496707</v>
+      </c>
+      <c r="C54" s="33" t="n">
+        <v>0.08004487969000451</v>
+      </c>
+      <c r="D54" s="33" t="n">
+        <v>0.002830410200074147</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.07692334532940817</v>
+        <v>0.07692306633137035</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8435113695831095</v>
       </c>
     </row>
     <row r="55">
@@ -3966,19 +3946,19 @@
         </is>
       </c>
       <c r="B55" s="12" t="n">
-        <v>0.03526861812873507</v>
-      </c>
-      <c r="C55" s="36" t="n">
-        <v>0.07558698122430507</v>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>0.002665848376303882</v>
+        <v>0.04019586482616282</v>
+      </c>
+      <c r="C55" s="34" t="n">
+        <v>0.07041546015406547</v>
+      </c>
+      <c r="D55" s="34" t="n">
+        <v>0.00283041031802487</v>
       </c>
       <c r="E55" s="12" t="n">
-        <v>0.07692329019389553</v>
+        <v>0.07692306953695917</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6749512644444484</v>
       </c>
     </row>
     <row r="56">
@@ -3988,19 +3968,19 @@
         </is>
       </c>
       <c r="B56" s="9" t="n">
-        <v>0.1901058368847075</v>
-      </c>
-      <c r="C56" s="35" t="n">
-        <v>0.01402297004707323</v>
-      </c>
-      <c r="D56" s="35" t="n">
-        <v>0.002665848456408041</v>
+        <v>0.08567740317293628</v>
+      </c>
+      <c r="C56" s="33" t="n">
+        <v>0.03303567124195798</v>
+      </c>
+      <c r="D56" s="33" t="n">
+        <v>0.002830410524085811</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.07692329250530809</v>
+        <v>0.07692307513715077</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9820450787184068</v>
       </c>
     </row>
     <row r="57">
@@ -4010,19 +3990,19 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>0.1561033628971746</v>
-      </c>
-      <c r="C57" s="36" t="n">
-        <v>0.01707722545808812</v>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>0.002665812322960799</v>
+        <v>0.15694385966558</v>
+      </c>
+      <c r="C57" s="34" t="n">
+        <v>0.01803454567424043</v>
+      </c>
+      <c r="D57" s="34" t="n">
+        <v>0.002830411205430484</v>
       </c>
       <c r="E57" s="12" t="n">
-        <v>0.07692224987149869</v>
+        <v>0.07692309365429768</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.7943547652209734</v>
       </c>
     </row>
     <row r="58">
@@ -4032,19 +4012,19 @@
         </is>
       </c>
       <c r="B58" s="9" t="n">
-        <v>0.09891989158807808</v>
-      </c>
-      <c r="C58" s="35" t="n">
-        <v>0.02695041436455389</v>
-      </c>
-      <c r="D58" s="35" t="n">
-        <v>0.002665932067195453</v>
+        <v>0.08335081068950211</v>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>0.03395780587527319</v>
+      </c>
+      <c r="D58" s="33" t="n">
+        <v>0.002830410648940758</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.07692570510195859</v>
+        <v>0.07692307853037814</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8721710870286241</v>
       </c>
     </row>
     <row r="59">
@@ -4054,19 +4034,19 @@
         </is>
       </c>
       <c r="B59" s="12" t="n">
-        <v>0.03310675547604956</v>
-      </c>
-      <c r="C59" s="36" t="n">
-        <v>0.08052175975620805</v>
-      </c>
-      <c r="D59" s="36" t="n">
-        <v>0.002665814210749987</v>
+        <v>0.03015965810820996</v>
+      </c>
+      <c r="C59" s="34" t="n">
+        <v>0.0938475522530505</v>
+      </c>
+      <c r="D59" s="34" t="n">
+        <v>0.002830410090244373</v>
       </c>
       <c r="E59" s="12" t="n">
-        <v>0.07692230434382233</v>
+        <v>0.07692306334648746</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.7282328929273317</v>
       </c>
     </row>
     <row r="60">
@@ -4076,19 +4056,19 @@
         </is>
       </c>
       <c r="B60" s="9" t="n">
-        <v>0.05454871770448565</v>
-      </c>
-      <c r="C60" s="35" t="n">
-        <v>0.04887037300574652</v>
-      </c>
-      <c r="D60" s="35" t="n">
-        <v>0.002665816181203382</v>
+        <v>0.06984889487127563</v>
+      </c>
+      <c r="C60" s="33" t="n">
+        <v>0.04052190882519306</v>
+      </c>
+      <c r="D60" s="33" t="n">
+        <v>0.002830410549514326</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.07692236120142895</v>
+        <v>0.07692307582823059</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.4471345099507237</v>
       </c>
     </row>
     <row r="61">
@@ -4098,19 +4078,19 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>0.07131481415928038</v>
-      </c>
-      <c r="C61" s="36" t="n">
-        <v>0.03738288332119384</v>
-      </c>
-      <c r="D61" s="36" t="n">
-        <v>0.002665953376789001</v>
+        <v>0.08327108817039276</v>
+      </c>
+      <c r="C61" s="34" t="n">
+        <v>0.03399031844795079</v>
+      </c>
+      <c r="D61" s="34" t="n">
+        <v>0.002830410804419038</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>0.07692631999216128</v>
+        <v>0.07692308275586675</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8460701286144402</v>
       </c>
     </row>
     <row r="62">
@@ -4120,19 +4100,19 @@
         </is>
       </c>
       <c r="B62" s="9" t="n">
-        <v>0.1147079339099366</v>
-      </c>
-      <c r="C62" s="35" t="n">
-        <v>0.0232394915358965</v>
-      </c>
-      <c r="D62" s="35" t="n">
-        <v>0.002665754059200145</v>
+        <v>0.1308642414047931</v>
+      </c>
+      <c r="C62" s="33" t="n">
+        <v>0.02162860647289513</v>
+      </c>
+      <c r="D62" s="33" t="n">
+        <v>0.00283041117871822</v>
       </c>
       <c r="E62" s="9" t="n">
-        <v>0.07692056866554249</v>
+        <v>0.07692309292832895</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8085079193866584</v>
       </c>
     </row>
     <row r="63">
@@ -4142,19 +4122,19 @@
         </is>
       </c>
       <c r="B63" s="12" t="n">
-        <v>0.06079007889326719</v>
-      </c>
-      <c r="C63" s="36" t="n">
-        <v>0.04385430184744837</v>
-      </c>
-      <c r="D63" s="36" t="n">
-        <v>0.002665906469115539</v>
+        <v>0.07966052785799263</v>
+      </c>
+      <c r="C63" s="34" t="n">
+        <v>0.03553090485369297</v>
+      </c>
+      <c r="D63" s="34" t="n">
+        <v>0.002830410635917294</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>0.07692496646710331</v>
+        <v>0.07692307817643483</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.4648302531487577</v>
       </c>
     </row>
     <row r="64">
@@ -4164,19 +4144,19 @@
         </is>
       </c>
       <c r="B64" s="9" t="n">
-        <v>0.06730104265263419</v>
-      </c>
-      <c r="C64" s="35" t="n">
-        <v>0.0396094981648834</v>
-      </c>
-      <c r="D64" s="35" t="n">
-        <v>0.002665760525444253</v>
+        <v>0.126115297373638</v>
+      </c>
+      <c r="C64" s="33" t="n">
+        <v>0.02244304141227376</v>
+      </c>
+      <c r="D64" s="33" t="n">
+        <v>0.002830410841677777</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.07692075524958694</v>
+        <v>0.07692308376846077</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.2258308249171992</v>
       </c>
     </row>
     <row r="66">
@@ -4230,19 +4210,19 @@
         </is>
       </c>
       <c r="B68" s="9" t="n">
-        <v>0.01418954230934598</v>
-      </c>
-      <c r="C68" s="35" t="n">
-        <v>0.0621455954800322</v>
-      </c>
-      <c r="D68" s="35" t="n">
-        <v>0.0008818175564034171</v>
+        <v>0.02305936166468336</v>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>0.07144519308852298</v>
+      </c>
+      <c r="D68" s="33" t="n">
+        <v>0.001647480546631388</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.03108986518121491</v>
+        <v>0.0507455555165692</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.9718498340506938</v>
+        <v>0.9924714026227938</v>
       </c>
     </row>
     <row r="69">
@@ -4252,19 +4232,19 @@
         </is>
       </c>
       <c r="B69" s="12" t="n">
-        <v>0.01071962159834464</v>
-      </c>
-      <c r="C69" s="36" t="n">
-        <v>0.06881032714615799</v>
-      </c>
-      <c r="D69" s="36" t="n">
-        <v>0.0007376206690651157</v>
+        <v>0.03310363022050327</v>
+      </c>
+      <c r="C69" s="34" t="n">
+        <v>0.07381516215937943</v>
+      </c>
+      <c r="D69" s="34" t="n">
+        <v>0.002443549832790583</v>
       </c>
       <c r="E69" s="12" t="n">
-        <v>0.0260059770749458</v>
+        <v>0.07526601388460698</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0.9005695345361184</v>
+        <v>0.8777511079444464</v>
       </c>
     </row>
     <row r="70">
@@ -4274,19 +4254,19 @@
         </is>
       </c>
       <c r="B70" s="9" t="n">
-        <v>0.01785691413064642</v>
-      </c>
-      <c r="C70" s="35" t="n">
-        <v>0.0699804705840664</v>
-      </c>
-      <c r="D70" s="35" t="n">
-        <v>0.001249635254041901</v>
+        <v>0.02603121636143095</v>
+      </c>
+      <c r="C70" s="33" t="n">
+        <v>0.08072405643970303</v>
+      </c>
+      <c r="D70" s="33" t="n">
+        <v>0.002101345378754273</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>0.04405785674342171</v>
+        <v>0.06472546142963334</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.8647852106386994</v>
+        <v>0.8435113695831095</v>
       </c>
     </row>
     <row r="71">
@@ -4296,19 +4276,19 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>0.01018151128031412</v>
-      </c>
-      <c r="C71" s="36" t="n">
-        <v>0.07713721713992762</v>
-      </c>
-      <c r="D71" s="36" t="n">
-        <v>0.0007853734464422128</v>
+        <v>0.02060263848181127</v>
+      </c>
+      <c r="C71" s="34" t="n">
+        <v>0.06981930593850848</v>
+      </c>
+      <c r="D71" s="34" t="n">
+        <v>0.001438461919302069</v>
       </c>
       <c r="E71" s="12" t="n">
-        <v>0.02768957636359879</v>
+        <v>0.04430738155522882</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0.6547256214279519</v>
+        <v>0.6749512644444484</v>
       </c>
     </row>
     <row r="72">
@@ -4318,19 +4298,19 @@
         </is>
       </c>
       <c r="B72" s="9" t="n">
-        <v>0.0596596557957153</v>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>0.01185652218885514</v>
-      </c>
-      <c r="D72" s="35" t="n">
-        <v>0.0007073560327213587</v>
+        <v>0.03749863439002018</v>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>0.03281688828087267</v>
+      </c>
+      <c r="D72" s="33" t="n">
+        <v>0.001230588495462583</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.02493894970987092</v>
+        <v>0.0379044820542697</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.9800395309996239</v>
+        <v>0.9820450787184068</v>
       </c>
     </row>
     <row r="73">
@@ -4340,19 +4320,19 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>0.3316397889964033</v>
-      </c>
-      <c r="C73" s="36" t="n">
-        <v>0.01854942338164661</v>
-      </c>
-      <c r="D73" s="36" t="n">
-        <v>0.00615172685629423</v>
+        <v>0.2</v>
+      </c>
+      <c r="C73" s="34" t="n">
+        <v>0.01812949183673748</v>
+      </c>
+      <c r="D73" s="34" t="n">
+        <v>0.003625898367347496</v>
       </c>
       <c r="E73" s="12" t="n">
-        <v>0.2168888079002477</v>
+        <v>0.1116846127706285</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0.8261546883028913</v>
+        <v>0.7943547652209734</v>
       </c>
     </row>
     <row r="74">
@@ -4362,19 +4342,19 @@
         </is>
       </c>
       <c r="B74" s="9" t="n">
-        <v>0.1092060125556164</v>
-      </c>
-      <c r="C74" s="35" t="n">
-        <v>0.02838237345122105</v>
-      </c>
-      <c r="D74" s="35" t="n">
-        <v>0.003099525831472238</v>
+        <v>0.1262250412976768</v>
+      </c>
+      <c r="C74" s="33" t="n">
+        <v>0.03506918531633658</v>
+      </c>
+      <c r="D74" s="33" t="n">
+        <v>0.004426609364830465</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.109278659203832</v>
+        <v>0.1363480447356257</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>0.6542475111182804</v>
+        <v>0.8721710870286241</v>
       </c>
     </row>
     <row r="75">
@@ -4384,19 +4364,19 @@
         </is>
       </c>
       <c r="B75" s="12" t="n">
-        <v>0.009319148736044227</v>
-      </c>
-      <c r="C75" s="36" t="n">
-        <v>0.07416805794013157</v>
-      </c>
-      <c r="D75" s="36" t="n">
-        <v>0.0006911831634076319</v>
+        <v>0.0141488305360585</v>
+      </c>
+      <c r="C75" s="34" t="n">
+        <v>0.09259006000329839</v>
+      </c>
+      <c r="D75" s="34" t="n">
+        <v>0.001310041068310157</v>
       </c>
       <c r="E75" s="12" t="n">
-        <v>0.02436874975988586</v>
+        <v>0.0403517734378401</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0.6432514443485702</v>
+        <v>0.7282328929273317</v>
       </c>
     </row>
     <row r="76">
@@ -4406,19 +4386,19 @@
         </is>
       </c>
       <c r="B76" s="9" t="n">
-        <v>0.01805983719241161</v>
-      </c>
-      <c r="C76" s="35" t="n">
-        <v>0.04543999203099216</v>
-      </c>
-      <c r="D76" s="35" t="n">
-        <v>0.0008206388581041992</v>
+        <v>0.02428255468825181</v>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>0.03369311406837477</v>
+      </c>
+      <c r="D76" s="33" t="n">
+        <v>0.0008181548849828169</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.02893291392948143</v>
+        <v>0.0252007371024437</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.4797912934834942</v>
+        <v>0.4471345099507237</v>
       </c>
     </row>
     <row r="77">
@@ -4428,19 +4408,19 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>0.1483922296615784</v>
-      </c>
-      <c r="C77" s="36" t="n">
-        <v>0.04167679313253376</v>
-      </c>
-      <c r="D77" s="36" t="n">
-        <v>0.006184512258081044</v>
+        <v>0.1046790724432472</v>
+      </c>
+      <c r="C77" s="34" t="n">
+        <v>0.03490870147963174</v>
+      </c>
+      <c r="D77" s="34" t="n">
+        <v>0.003654210491086062</v>
       </c>
       <c r="E77" s="12" t="n">
-        <v>0.2180447088165566</v>
+        <v>0.1125566803952843</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0.6813173339403511</v>
+        <v>0.8460701286144402</v>
       </c>
     </row>
     <row r="78">
@@ -4450,19 +4430,19 @@
         </is>
       </c>
       <c r="B78" s="9" t="n">
-        <v>0.2280024325953268</v>
-      </c>
-      <c r="C78" s="35" t="n">
-        <v>0.02412051657055184</v>
-      </c>
-      <c r="D78" s="35" t="n">
-        <v>0.005499536453541706</v>
+        <v>0.1887103957446237</v>
+      </c>
+      <c r="C78" s="33" t="n">
+        <v>0.022223074126806</v>
+      </c>
+      <c r="D78" s="33" t="n">
+        <v>0.004193725113131669</v>
       </c>
       <c r="E78" s="9" t="n">
-        <v>0.1938948092586715</v>
+        <v>0.1291747638445827</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.7487919560463553</v>
+        <v>0.8085079193866584</v>
       </c>
     </row>
     <row r="79">
@@ -4472,19 +4452,19 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>0.02821942763967997</v>
-      </c>
-      <c r="C79" s="36" t="n">
-        <v>0.04155512604382863</v>
-      </c>
-      <c r="D79" s="36" t="n">
-        <v>0.001172661872451602</v>
+        <v>0.08055454278307357</v>
+      </c>
+      <c r="C79" s="34" t="n">
+        <v>0.03608620200236767</v>
+      </c>
+      <c r="D79" s="34" t="n">
+        <v>0.002906907503078362</v>
       </c>
       <c r="E79" s="12" t="n">
-        <v>0.04134403908487444</v>
+        <v>0.08953831739052368</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0.4284467817562575</v>
+        <v>0.4648302531487577</v>
       </c>
     </row>
     <row r="80">
@@ -4494,19 +4474,19 @@
         </is>
       </c>
       <c r="B80" s="9" t="n">
-        <v>0.01455387750857305</v>
-      </c>
-      <c r="C80" s="35" t="n">
-        <v>0.02624160233260154</v>
-      </c>
-      <c r="D80" s="35" t="n">
-        <v>0.0003819170659773675</v>
+        <v>0.1211040813886194</v>
+      </c>
+      <c r="C80" s="33" t="n">
+        <v>0.02203510463110096</v>
+      </c>
+      <c r="D80" s="33" t="n">
+        <v>0.002668541104651594</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.01346508697339823</v>
+        <v>0.08219617588276319</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1297114447333514</v>
+        <v>0.2258308249171992</v>
       </c>
     </row>
   </sheetData>
@@ -4569,667 +4549,667 @@
       <c r="N1" s="6" t="n"/>
     </row>
     <row r="2" ht="56" customHeight="1">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="D2" s="37" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="E2" s="37" t="inlineStr">
+      <c r="E2" s="35" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="F2" s="37" t="inlineStr">
+      <c r="F2" s="35" t="inlineStr">
         <is>
           <t>Long Duration Treasury</t>
         </is>
       </c>
-      <c r="G2" s="37" t="inlineStr">
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="H2" s="37" t="inlineStr">
+      <c r="H2" s="35" t="inlineStr">
         <is>
           <t>Investment Grade Credit</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
+      <c r="I2" s="35" t="inlineStr">
         <is>
           <t>REITs</t>
         </is>
       </c>
-      <c r="J2" s="37" t="inlineStr">
+      <c r="J2" s="35" t="inlineStr">
         <is>
           <t>Commodities</t>
         </is>
       </c>
-      <c r="K2" s="37" t="inlineStr">
+      <c r="K2" s="35" t="inlineStr">
         <is>
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="L2" s="35" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="M2" s="35" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
-      <c r="N2" s="37" t="inlineStr">
+      <c r="N2" s="35" t="inlineStr">
         <is>
           <t>Private Real Estate</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="38" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B3" s="39" t="n">
+      <c r="B3" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="40" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="D3" s="40" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="E3" s="40" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="F3" s="41" t="n">
-        <v>-0.345</v>
-      </c>
-      <c r="G3" s="42" t="n">
+      <c r="C3" s="38" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="D3" s="38" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="E3" s="38" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F3" s="39" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="G3" s="40" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="H3" s="40" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="I3" s="38" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="J3" s="40" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="K3" s="38" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L3" s="38" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="M3" s="40" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="N3" s="39" t="n">
+        <v>0.249</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="36" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="C4" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="38" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="E4" s="38" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="F4" s="39" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="G4" s="39" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H4" s="40" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="I4" s="38" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J4" s="39" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="K4" s="38" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L4" s="38" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="M4" s="40" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="N4" s="39" t="n">
+        <v>0.219</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="C5" s="38" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="D5" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="38" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="F5" s="39" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="G5" s="39" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="I5" s="40" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="J5" s="39" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="K5" s="38" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L5" s="38" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="M5" s="40" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="N5" s="39" t="n">
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C6" s="38" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="39" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="G6" s="39" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I6" s="40" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="J6" s="39" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="K6" s="38" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="L6" s="38" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="M6" s="40" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="N6" s="39" t="n">
+        <v>0.206</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="38" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I7" s="39" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="J7" s="39" t="n">
+        <v>-0.158</v>
+      </c>
+      <c r="K7" s="39" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="L7" s="39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M7" s="39" t="n">
+        <v>-0.123</v>
+      </c>
+      <c r="N7" s="39" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="C8" s="39" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="I8" s="40" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="J8" s="39" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="K8" s="40" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="L8" s="39" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="M8" s="39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="N8" s="39" t="n">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="F9" s="38" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G9" s="38" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="40" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="J9" s="39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K9" s="40" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="M9" s="39" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="N9" s="39" t="n">
+        <v>0.067</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="C10" s="38" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="D10" s="40" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="F10" s="39" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="G10" s="40" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="I10" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="39" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K10" s="38" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="N10" s="39" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="36" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="B11" s="40" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="E11" s="39" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="F11" s="39" t="n">
+        <v>-0.158</v>
+      </c>
+      <c r="G11" s="39" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="H11" s="39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I11" s="39" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="J11" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="L11" s="39" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="M11" s="39" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="N11" s="39" t="n">
+        <v>0.289</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="C12" s="38" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E12" s="38" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="G12" s="40" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="I12" s="38" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="J12" s="39" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="K12" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="38" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="M12" s="40" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="N12" s="39" t="n">
+        <v>0.181</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="C13" s="38" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="D13" s="38" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="E13" s="38" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="F13" s="39" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G13" s="39" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="I13" s="40" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J13" s="39" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="K13" s="38" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="L13" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="40" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="N13" s="39" t="n">
+        <v>0.197</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>Private Equity</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="C14" s="40" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="E14" s="40" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="F14" s="39" t="n">
+        <v>-0.123</v>
+      </c>
+      <c r="G14" s="39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="H14" s="39" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="I14" s="40" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="J14" s="39" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="K14" s="40" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="M14" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="39" t="n">
         <v>0.204</v>
       </c>
-      <c r="H3" s="42" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="I3" s="40" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="J3" s="43" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="K3" s="40" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="L3" s="40" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="M3" s="43" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="N3" s="42" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="38" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="C4" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="40" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="E4" s="40" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F4" s="41" t="n">
-        <v>-0.401</v>
-      </c>
-      <c r="G4" s="42" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="H4" s="42" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="I4" s="40" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="J4" s="43" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="K4" s="40" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="L4" s="40" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="M4" s="43" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="N4" s="42" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>Private Real Estate</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="D15" s="39" t="n">
         <v>0.198</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="38" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="C5" s="40" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="D5" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="40" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="F5" s="41" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="G5" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H5" s="42" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="I5" s="40" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J5" s="43" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="K5" s="43" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="L5" s="40" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="M5" s="43" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="N5" s="42" t="n">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="n">
-        <v>0.8110000000000001</v>
-      </c>
-      <c r="C6" s="40" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="E6" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="41" t="n">
-        <v>-0.312</v>
-      </c>
-      <c r="G6" s="42" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="H6" s="42" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="I6" s="43" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="J6" s="43" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="K6" s="43" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="M6" s="43" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="N6" s="42" t="n">
-        <v>0.178</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="38" t="inlineStr">
-        <is>
-          <t>Long Duration Treasury</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="n">
-        <v>-0.345</v>
-      </c>
-      <c r="C7" s="41" t="n">
-        <v>-0.401</v>
-      </c>
-      <c r="D7" s="41" t="n">
-        <v>-0.382</v>
-      </c>
-      <c r="E7" s="41" t="n">
-        <v>-0.312</v>
-      </c>
-      <c r="F7" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="43" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H7" s="43" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="I7" s="42" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="J7" s="41" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="K7" s="42" t="n">
-        <v>-0.177</v>
-      </c>
-      <c r="L7" s="41" t="n">
-        <v>-0.337</v>
-      </c>
-      <c r="M7" s="41" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="N7" s="42" t="n">
-        <v>-0.139</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="B8" s="42" t="n">
+      <c r="E15" s="39" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="J15" s="39" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="L15" s="39" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="M15" s="39" t="n">
         <v>0.204</v>
       </c>
-      <c r="C8" s="42" t="n">
-        <v>0.171</v>
-      </c>
-      <c r="D8" s="42" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="F8" s="43" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="G8" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="43" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>0.172</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="38" t="inlineStr">
-        <is>
-          <t>Investment Grade Credit</t>
-        </is>
-      </c>
-      <c r="B9" s="42" t="n">
-        <v>0.302</v>
-      </c>
-      <c r="C9" s="42" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="D9" s="42" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="E9" s="42" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="F9" s="43" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="G9" s="43" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="H9" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>-0.075</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="B10" s="40" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="C10" s="40" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E10" s="43" t="n">
-        <v>0.587</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>-0.048</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I10" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="K10" s="43" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="L10" s="43" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="M10" s="43" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="N10" s="42" t="n">
-        <v>0.152</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="B11" s="43" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="C11" s="43" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="D11" s="43" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="E11" s="43" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>-0.543</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="J11" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="L11" s="43" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="N11" s="42" t="n">
-        <v>0.205</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="B12" s="40" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="C12" s="40" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="D12" s="43" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="E12" s="43" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>-0.177</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I12" s="43" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="K12" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="40" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="M12" s="43" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>0.176</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="E13" s="40" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="F13" s="41" t="n">
-        <v>-0.337</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="I13" s="43" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="J13" s="43" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="K13" s="40" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="L13" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>0.198</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>Private Equity</t>
-        </is>
-      </c>
-      <c r="B14" s="43" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="C14" s="43" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="D14" s="43" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E14" s="43" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="F14" s="41" t="n">
-        <v>-0.361</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="I14" s="43" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="K14" s="43" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="L14" s="43" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="M14" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" s="43" t="n">
-        <v>0.441</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="inlineStr">
-        <is>
-          <t>Private Real Estate</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C15" s="42" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="D15" s="42" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="E15" s="42" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <v>-0.139</v>
-      </c>
-      <c r="G15" s="42" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="H15" s="42" t="n">
-        <v>-0.075</v>
-      </c>
-      <c r="I15" s="42" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="J15" s="42" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="K15" s="42" t="n">
-        <v>0.176</v>
-      </c>
-      <c r="L15" s="42" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="M15" s="43" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="N15" s="39" t="n">
+      <c r="N15" s="37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5273,18 +5253,18 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
-        <v>0.9566682674249671</v>
+      <c r="C19" s="33" t="n">
+        <v>0.927118498301069</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
@@ -5298,343 +5278,343 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>0.9063779840192618</v>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>0.884865673909043</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n">
-        <v>0.9564794466324271</v>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="C22" s="34" t="n">
+        <v>0.8680914692441687</v>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>US Large Cap Equity</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>0.8464834060960965</v>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.8410554319008319</v>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="C21" s="35" t="n">
-        <v>0.9327840363384619</v>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>Hedge Funds</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0.8235774617795111</v>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Emerging Market Equity</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>0.8097215569509887</v>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>Long Duration Treasury</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>0.7953668160834089</v>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>US Mid Cap Equity</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>0.7938193069823031</v>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>US Large Cap Equity</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>REITs</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>0.7877299075557362</v>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Strong Positive</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>Low diversification benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n">
-        <v>0.8818708712318351</v>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="C30" s="34" t="n">
+        <v>0.7718335025966312</v>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0.8772590564733882</v>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>US Small Cap Equity</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>0.7700223237053355</v>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>US Mid Cap Equity</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>0.8442031212496387</v>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="C32" s="34" t="n">
+        <v>0.7608795672544655</v>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>Strong Positive</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>Low diversification benefit</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>Hedge Funds</t>
-        </is>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>0.8378878973040726</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n">
-        <v>0.8114105175622477</v>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0.7802907386399155</v>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>0.7527255327493332</v>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0.7403645624314058</v>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>US Small Cap Equity</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>Emerging Market Equity</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>0.7359354048313766</v>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>REITs</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>0.7346778006636191</v>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E31" s="19" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>US Large Cap Equity</t>
-        </is>
-      </c>
-      <c r="B32" s="34" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>0.7315398350882377</v>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>Strong Positive</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>Low diversification benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>US Mid Cap Equity</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
-        <v>0.7186127346808743</v>
+      <c r="C33" s="33" t="n">
+        <v>0.7413309423450163</v>
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
@@ -5723,20 +5703,20 @@
           <t>Equal Weight</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
-        <v>0.4636952933150726</v>
-      </c>
-      <c r="C3" s="35" t="n">
-        <v>0.213020599450317</v>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>2.15396460797892</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>3.246662089897637</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>0.007778258572596125</v>
+      <c r="B3" s="33" t="n">
+        <v>0.521308012099584</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>0.2037122076733606</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>1.172377913447933</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>0.8644615681695409</v>
+      </c>
+      <c r="F3" s="33" t="n">
+        <v>2.380428172135113</v>
       </c>
     </row>
     <row r="4">
@@ -5745,20 +5725,20 @@
           <t>60/40</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
-        <v>0.6313817072904651</v>
-      </c>
-      <c r="C4" s="36" t="n">
-        <v>0.3361745051400977</v>
-      </c>
-      <c r="D4" s="36" t="n">
-        <v>2.146979458188246</v>
-      </c>
-      <c r="E4" s="36" t="n">
-        <v>0.3615911096991364</v>
-      </c>
-      <c r="F4" s="36" t="n">
-        <v>-0.02618469033086921</v>
+      <c r="B4" s="34" t="n">
+        <v>0.6313340769751589</v>
+      </c>
+      <c r="C4" s="34" t="n">
+        <v>0.3216044138283547</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>1.219927702810746</v>
+      </c>
+      <c r="E4" s="34" t="n">
+        <v>0.1608540903627093</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <v>1.244131253147267</v>
       </c>
     </row>
     <row r="5">
@@ -5767,20 +5747,20 @@
           <t>MVO</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
-        <v>0.3416089365452504</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>0.4623755448547925</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>2.731154020882983</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>0.8990702173391955</v>
-      </c>
-      <c r="F5" s="35" t="n">
-        <v>0.02485752388917111</v>
+      <c r="B5" s="33" t="n">
+        <v>0.3690955300173461</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0.257093983193398</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>1.587740911988815</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>0.5020543127469839</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>5.718587968445404</v>
       </c>
     </row>
     <row r="6">
@@ -5789,20 +5769,20 @@
           <t>Risk Parity</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
-        <v>0.2828260983022897</v>
-      </c>
-      <c r="C6" s="36" t="n">
-        <v>0.3733154718682769</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>1.232021384734952</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>3.096735624995443</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>0.0128324700331053</v>
+      <c r="B6" s="34" t="n">
+        <v>0.358832007703879</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <v>0.2266879210660498</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>0.8083444659594701</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>0.9589514646366359</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>2.346699283228613</v>
       </c>
     </row>
     <row r="7">
@@ -5811,20 +5791,20 @@
           <t>Enhanced HRP</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
-        <v>0.2024684798488106</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>0.3213380633688086</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>0.8611775407281035</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>3.585820188471193</v>
-      </c>
-      <c r="F7" s="35" t="n">
-        <v>0.02721739711619306</v>
+      <c r="B7" s="33" t="n">
+        <v>0.3105398153460164</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0.193256168989747</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>0.8860403838992889</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>0.5497033805786093</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>2.238618554636641</v>
       </c>
     </row>
   </sheetData>
